--- a/data/condominio.xlsx
+++ b/data/condominio.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\pedrohamacher\OneDrive\Documentos antigo\Projetos_jl\Streamlit\Dashboard Pelada\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="26" documentId="14_{AFBA81A4-2B23-449D-B209-30A32CB7CB1E}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{B3428EA7-6856-4212-B670-CF3EDE330DD7}"/>
+  <xr:revisionPtr revIDLastSave="27" documentId="14_{AFBA81A4-2B23-449D-B209-30A32CB7CB1E}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{C7BBF518-F9C7-45B2-B982-14E2EBDE0B1C}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="19180" windowHeight="7870" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="19180" windowHeight="7870" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="notas" sheetId="1" r:id="rId1"/>
@@ -2986,7 +2986,7 @@
         <v>46190</v>
       </c>
       <c r="DA1" s="1">
-        <v>46569</v>
+        <v>46204</v>
       </c>
       <c r="DB1" s="1">
         <v>46211</v>

--- a/data/condominio.xlsx
+++ b/data/condominio.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\pedrohamacher\OneDrive\Documentos antigo\Projetos_jl\Streamlit\Dashboard Pelada\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="27" documentId="14_{AFBA81A4-2B23-449D-B209-30A32CB7CB1E}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{C7BBF518-F9C7-45B2-B982-14E2EBDE0B1C}"/>
+  <xr:revisionPtr revIDLastSave="28" documentId="14_{AFBA81A4-2B23-449D-B209-30A32CB7CB1E}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{EED607B5-2F2C-4CDC-8922-B2AB6296AA49}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="19180" windowHeight="7870" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="19180" windowHeight="7870" firstSheet="1" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="notas" sheetId="1" r:id="rId1"/>
@@ -21,9 +21,9 @@
     <sheet name="artilharia total" sheetId="3" r:id="rId6"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">artilharia!$A$1:$CN$103</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">artilharia!$A$1:$CN$104</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'artilharia total'!$A$1:$AI$51</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">notas!$A$1:$DQ$83</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">notas!$A$1:$DR$83</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
 </workbook>
@@ -54,7 +54,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9382" uniqueCount="173">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9420" uniqueCount="174">
   <si>
     <t>Jogador</t>
   </si>
@@ -573,6 +573,9 @@
   </si>
   <si>
     <t>Tauã</t>
+  </si>
+  <si>
+    <t>Felipe Menezes</t>
   </si>
 </sst>
 </file>
@@ -2646,7 +2649,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:DQ103"/>
+  <dimension ref="A1:DR104"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="2" max="2" width="9.453125" hidden="1" customWidth="1"/>
@@ -2669,10 +2672,10 @@
     <col min="49" max="58" width="9.54296875" hidden="1" customWidth="1"/>
     <col min="59" max="65" width="10.453125" hidden="1" customWidth="1"/>
     <col min="66" max="80" width="11" hidden="1" customWidth="1"/>
-    <col min="81" max="115" width="11" customWidth="1"/>
+    <col min="81" max="116" width="11" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:121" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:122" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -3015,27 +3018,30 @@
       <c r="DJ1" s="1">
         <v>46274</v>
       </c>
-      <c r="DK1" s="1"/>
-      <c r="DL1" t="s">
+      <c r="DK1" s="1">
+        <v>46281</v>
+      </c>
+      <c r="DL1" s="1"/>
+      <c r="DM1" t="s">
         <v>56</v>
       </c>
-      <c r="DM1" t="s">
+      <c r="DN1" t="s">
         <v>57</v>
       </c>
-      <c r="DN1" t="s">
+      <c r="DO1" t="s">
         <v>58</v>
       </c>
-      <c r="DO1" t="s">
+      <c r="DP1" t="s">
         <v>61</v>
       </c>
-      <c r="DP1" t="s">
+      <c r="DQ1" t="s">
         <v>150</v>
       </c>
-      <c r="DQ1" t="s">
+      <c r="DR1" t="s">
         <v>135</v>
       </c>
     </row>
-    <row r="2" spans="1:121" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:122" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>1</v>
       </c>
@@ -3372,31 +3378,34 @@
       <c r="DJ2">
         <v>5.5</v>
       </c>
-      <c r="DL2">
-        <f>COUNT(B2:DJ2)</f>
-        <v>106</v>
-      </c>
-      <c r="DM2" s="18">
-        <f>AVERAGE(B2:DJ2)</f>
+      <c r="DK2">
         <v>6</v>
       </c>
-      <c r="DN2">
-        <f>IF(DL2&gt;1,_xlfn.STDEV.S(B2:DI2),"")</f>
+      <c r="DM2">
+        <f>COUNT(B2:DK2)</f>
+        <v>107</v>
+      </c>
+      <c r="DN2" s="18">
+        <f>AVERAGE(B2:DK2)</f>
+        <v>6</v>
+      </c>
+      <c r="DO2">
+        <f>IF(DM2&gt;1,_xlfn.STDEV.S(B2:DI2),"")</f>
         <v>1.1104729547135237</v>
       </c>
-      <c r="DO2">
-        <v>1</v>
-      </c>
       <c r="DP2">
-        <f t="shared" ref="DP2:DP33" si="0">COUNT(DF2:DH2)</f>
+        <v>1</v>
+      </c>
+      <c r="DQ2">
+        <f t="shared" ref="DQ2:DQ33" si="0">COUNT(DF2:DH2)</f>
         <v>3</v>
       </c>
-      <c r="DQ2">
-        <f t="shared" ref="DQ2:DQ33" si="1">IF(DO2=0,DP2,0)</f>
+      <c r="DR2">
+        <f t="shared" ref="DR2:DR33" si="1">IF(DP2=0,DQ2,0)</f>
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:121" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:122" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>10</v>
       </c>
@@ -3709,31 +3718,31 @@
       <c r="DE3">
         <v>5.5</v>
       </c>
-      <c r="DL3">
-        <f t="shared" ref="DL3:DL66" si="2">COUNT(B3:DI3)</f>
+      <c r="DM3">
+        <f t="shared" ref="DM3:DM66" si="2">COUNT(B3:DI3)</f>
         <v>94</v>
       </c>
-      <c r="DM3" s="18">
-        <f t="shared" ref="DM3:DM66" si="3">AVERAGE(B3:DI3)</f>
+      <c r="DN3" s="18">
+        <f t="shared" ref="DN3:DN66" si="3">AVERAGE(B3:DI3)</f>
         <v>5.6382978723404253</v>
       </c>
-      <c r="DN3">
-        <f t="shared" ref="DN3:DN66" si="4">IF(DL3&gt;1,_xlfn.STDEV.S(B3:DI3),"")</f>
+      <c r="DO3">
+        <f t="shared" ref="DO3:DO66" si="4">IF(DM3&gt;1,_xlfn.STDEV.S(B3:DI3),"")</f>
         <v>0.94869535577019815</v>
       </c>
-      <c r="DO3">
-        <v>1</v>
-      </c>
       <c r="DP3">
+        <v>1</v>
+      </c>
+      <c r="DQ3">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="DQ3">
+      <c r="DR3">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:121" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:122" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>81</v>
       </c>
@@ -4040,31 +4049,34 @@
       <c r="DJ4">
         <v>6</v>
       </c>
-      <c r="DL4">
+      <c r="DK4">
+        <v>6</v>
+      </c>
+      <c r="DM4">
         <f t="shared" si="2"/>
         <v>83</v>
       </c>
-      <c r="DM4" s="18">
+      <c r="DN4" s="18">
         <f t="shared" si="3"/>
         <v>6.524096385542169</v>
       </c>
-      <c r="DN4">
+      <c r="DO4">
         <f t="shared" si="4"/>
         <v>0.91699274692529897</v>
       </c>
-      <c r="DO4">
+      <c r="DP4">
         <v>0</v>
       </c>
-      <c r="DP4">
+      <c r="DQ4">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="DQ4">
+      <c r="DR4">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:121" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:122" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>9</v>
       </c>
@@ -4380,31 +4392,34 @@
       <c r="DJ5">
         <v>6</v>
       </c>
-      <c r="DL5">
-        <f>COUNT(B5:DJ5)</f>
-        <v>86</v>
-      </c>
-      <c r="DM5" s="18">
-        <f>AVERAGE(B5:DJ5)</f>
-        <v>6.5697674418604652</v>
-      </c>
-      <c r="DN5">
+      <c r="DK5">
+        <v>6.5</v>
+      </c>
+      <c r="DM5">
+        <f>COUNT(B5:DK5)</f>
+        <v>87</v>
+      </c>
+      <c r="DN5" s="18">
+        <f>AVERAGE(B5:DK5)</f>
+        <v>6.568965517241379</v>
+      </c>
+      <c r="DO5">
         <f t="shared" si="4"/>
         <v>0.95277127855729371</v>
       </c>
-      <c r="DO5">
-        <v>1</v>
-      </c>
       <c r="DP5">
+        <v>1</v>
+      </c>
+      <c r="DQ5">
         <f t="shared" si="0"/>
         <v>2</v>
       </c>
-      <c r="DQ5">
+      <c r="DR5">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:121" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:122" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>4</v>
       </c>
@@ -4669,31 +4684,31 @@
       <c r="DD6">
         <v>5.5</v>
       </c>
-      <c r="DL6">
+      <c r="DM6">
         <f t="shared" si="2"/>
         <v>73</v>
       </c>
-      <c r="DM6" s="18">
+      <c r="DN6" s="18">
         <f t="shared" si="3"/>
         <v>5.7054794520547949</v>
       </c>
-      <c r="DN6">
+      <c r="DO6">
         <f t="shared" si="4"/>
         <v>0.93851099723606146</v>
       </c>
-      <c r="DO6">
+      <c r="DP6">
         <v>0</v>
       </c>
-      <c r="DP6">
+      <c r="DQ6">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="DQ6">
+      <c r="DR6">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:121" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:122" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>5</v>
       </c>
@@ -4997,31 +5012,34 @@
       <c r="DJ7">
         <v>7.5</v>
       </c>
-      <c r="DL7">
-        <f>COUNT(B7:DJ7)</f>
-        <v>83</v>
-      </c>
-      <c r="DM7" s="18">
-        <f>AVERAGE(B7:DJ7)</f>
-        <v>7.2108433734939759</v>
-      </c>
-      <c r="DN7">
+      <c r="DK7">
+        <v>6</v>
+      </c>
+      <c r="DM7">
+        <f>COUNT(B7:DK7)</f>
+        <v>84</v>
+      </c>
+      <c r="DN7" s="18">
+        <f>AVERAGE(B7:DK7)</f>
+        <v>7.1964285714285712</v>
+      </c>
+      <c r="DO7">
         <f t="shared" si="4"/>
         <v>1.105405404410513</v>
       </c>
-      <c r="DO7">
-        <v>1</v>
-      </c>
       <c r="DP7">
+        <v>1</v>
+      </c>
+      <c r="DQ7">
         <f t="shared" si="0"/>
         <v>3</v>
       </c>
-      <c r="DQ7">
+      <c r="DR7">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:121" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:122" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>19</v>
       </c>
@@ -5289,31 +5307,31 @@
       <c r="DD8">
         <v>5.5</v>
       </c>
-      <c r="DL8">
+      <c r="DM8">
         <f t="shared" si="2"/>
         <v>72</v>
       </c>
-      <c r="DM8" s="18">
+      <c r="DN8" s="18">
         <f t="shared" si="3"/>
         <v>5.9375</v>
       </c>
-      <c r="DN8">
+      <c r="DO8">
         <f t="shared" si="4"/>
         <v>0.93423728023165931</v>
       </c>
-      <c r="DO8">
+      <c r="DP8">
         <v>0</v>
       </c>
-      <c r="DP8">
+      <c r="DQ8">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="DQ8">
+      <c r="DR8">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:121" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:122" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>11</v>
       </c>
@@ -5608,31 +5626,31 @@
       <c r="DF9">
         <v>5.5</v>
       </c>
-      <c r="DL9">
+      <c r="DM9">
         <f t="shared" si="2"/>
         <v>75</v>
       </c>
-      <c r="DM9" s="18">
+      <c r="DN9" s="18">
         <f t="shared" si="3"/>
         <v>5.753333333333333</v>
       </c>
-      <c r="DN9">
+      <c r="DO9">
         <f t="shared" si="4"/>
         <v>1.2664414214142996</v>
       </c>
-      <c r="DO9">
-        <v>1</v>
-      </c>
       <c r="DP9">
+        <v>1</v>
+      </c>
+      <c r="DQ9">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="DQ9">
+      <c r="DR9">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:121" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:122" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
         <v>6</v>
       </c>
@@ -5882,31 +5900,31 @@
       <c r="CE10">
         <v>5</v>
       </c>
-      <c r="DL10">
+      <c r="DM10">
         <f t="shared" si="2"/>
         <v>68</v>
       </c>
-      <c r="DM10" s="18">
+      <c r="DN10" s="18">
         <f t="shared" si="3"/>
         <v>6.4191176470588234</v>
       </c>
-      <c r="DN10">
+      <c r="DO10">
         <f t="shared" si="4"/>
         <v>1.1769245721961776</v>
       </c>
-      <c r="DO10">
+      <c r="DP10">
         <v>0</v>
       </c>
-      <c r="DP10">
+      <c r="DQ10">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="DQ10">
+      <c r="DR10">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:121" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:122" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
         <v>15</v>
       </c>
@@ -6213,31 +6231,31 @@
       <c r="DJ11">
         <v>7</v>
       </c>
-      <c r="DL11">
+      <c r="DM11">
         <f t="shared" si="2"/>
         <v>74</v>
       </c>
-      <c r="DM11" s="18">
+      <c r="DN11" s="18">
         <f t="shared" si="3"/>
         <v>6.6351351351351351</v>
       </c>
-      <c r="DN11">
+      <c r="DO11">
         <f t="shared" si="4"/>
         <v>0.92268702784386913</v>
       </c>
-      <c r="DO11">
+      <c r="DP11">
         <v>0</v>
       </c>
-      <c r="DP11">
+      <c r="DQ11">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="DQ11">
+      <c r="DR11">
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
     </row>
-    <row r="12" spans="1:121" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:122" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
         <v>2</v>
       </c>
@@ -6544,31 +6562,31 @@
       <c r="DH12">
         <v>5.5</v>
       </c>
-      <c r="DL12">
+      <c r="DM12">
         <f t="shared" si="2"/>
         <v>70</v>
       </c>
-      <c r="DM12" s="18">
+      <c r="DN12" s="18">
         <f t="shared" si="3"/>
         <v>5.5357142857142856</v>
       </c>
-      <c r="DN12">
+      <c r="DO12">
         <f t="shared" si="4"/>
         <v>0.92986452407127196</v>
       </c>
-      <c r="DO12">
-        <v>1</v>
-      </c>
       <c r="DP12">
+        <v>1</v>
+      </c>
+      <c r="DQ12">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="DQ12">
+      <c r="DR12">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:121" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:122" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
         <v>18</v>
       </c>
@@ -6890,31 +6908,34 @@
       <c r="DJ13">
         <v>6</v>
       </c>
-      <c r="DL13">
+      <c r="DK13">
+        <v>6</v>
+      </c>
+      <c r="DM13">
         <f t="shared" si="2"/>
         <v>71</v>
       </c>
-      <c r="DM13" s="18">
+      <c r="DN13" s="18">
         <f t="shared" si="3"/>
         <v>6.225352112676056</v>
       </c>
-      <c r="DN13">
+      <c r="DO13">
         <f t="shared" si="4"/>
         <v>1.064990718921216</v>
       </c>
-      <c r="DO13">
-        <v>1</v>
-      </c>
       <c r="DP13">
+        <v>1</v>
+      </c>
+      <c r="DQ13">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="DQ13">
+      <c r="DR13">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:121" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:122" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
         <v>118</v>
       </c>
@@ -7188,31 +7209,31 @@
       <c r="DF14">
         <v>6</v>
       </c>
-      <c r="DL14">
+      <c r="DM14">
         <f t="shared" si="2"/>
         <v>65</v>
       </c>
-      <c r="DM14" s="18">
+      <c r="DN14" s="18">
         <f t="shared" si="3"/>
         <v>6.2461538461538462</v>
       </c>
-      <c r="DN14">
+      <c r="DO14">
         <f t="shared" si="4"/>
         <v>1.0387909021846209</v>
       </c>
-      <c r="DO14">
+      <c r="DP14">
         <v>0</v>
       </c>
-      <c r="DP14">
+      <c r="DQ14">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="DQ14">
+      <c r="DR14">
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
     </row>
-    <row r="15" spans="1:121" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:122" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
         <v>55</v>
       </c>
@@ -7546,31 +7567,34 @@
       <c r="DJ15">
         <v>6.5</v>
       </c>
-      <c r="DL15">
-        <f>COUNT(B15:DJ15)</f>
-        <v>67</v>
-      </c>
-      <c r="DM15" s="18">
-        <f>AVERAGE(B15:DJ15)</f>
-        <v>6.044776119402985</v>
-      </c>
-      <c r="DN15">
+      <c r="DK15">
+        <v>6</v>
+      </c>
+      <c r="DM15">
+        <f>COUNT(B15:DK15)</f>
+        <v>68</v>
+      </c>
+      <c r="DN15" s="18">
+        <f>AVERAGE(B15:DK15)</f>
+        <v>6.0441176470588234</v>
+      </c>
+      <c r="DO15">
         <f t="shared" si="4"/>
         <v>0.80532175156462971</v>
       </c>
-      <c r="DO15">
-        <v>1</v>
-      </c>
       <c r="DP15">
+        <v>1</v>
+      </c>
+      <c r="DQ15">
         <f t="shared" si="0"/>
         <v>2</v>
       </c>
-      <c r="DQ15">
+      <c r="DR15">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:121" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:122" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
         <v>13</v>
       </c>
@@ -7817,31 +7841,31 @@
       <c r="CW16">
         <v>6</v>
       </c>
-      <c r="DL16">
+      <c r="DM16">
         <f t="shared" si="2"/>
         <v>53</v>
       </c>
-      <c r="DM16" s="18">
+      <c r="DN16" s="18">
         <f t="shared" si="3"/>
         <v>5.6981132075471699</v>
       </c>
-      <c r="DN16">
+      <c r="DO16">
         <f t="shared" si="4"/>
         <v>0.83975513052632311</v>
       </c>
-      <c r="DO16">
+      <c r="DP16">
         <v>0</v>
       </c>
-      <c r="DP16">
+      <c r="DQ16">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="DQ16">
+      <c r="DR16">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:121" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:122" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
         <v>14</v>
       </c>
@@ -8136,31 +8160,31 @@
       <c r="DH17">
         <v>5.5</v>
       </c>
-      <c r="DL17">
+      <c r="DM17">
         <f t="shared" si="2"/>
         <v>52</v>
       </c>
-      <c r="DM17" s="18">
+      <c r="DN17" s="18">
         <f t="shared" si="3"/>
         <v>5.7115384615384617</v>
       </c>
-      <c r="DN17">
+      <c r="DO17">
         <f t="shared" si="4"/>
         <v>0.87080171448079058</v>
       </c>
-      <c r="DO17">
-        <v>1</v>
-      </c>
       <c r="DP17">
+        <v>1</v>
+      </c>
+      <c r="DQ17">
         <f t="shared" si="0"/>
         <v>2</v>
       </c>
-      <c r="DQ17">
+      <c r="DR17">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:121" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:122" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
         <v>24</v>
       </c>
@@ -8410,31 +8434,31 @@
       <c r="CF18">
         <v>5.5</v>
       </c>
-      <c r="DL18">
+      <c r="DM18">
         <f t="shared" si="2"/>
         <v>47</v>
       </c>
-      <c r="DM18" s="18">
+      <c r="DN18" s="18">
         <f t="shared" si="3"/>
         <v>4.4255319148936172</v>
       </c>
-      <c r="DN18">
+      <c r="DO18">
         <f t="shared" si="4"/>
         <v>1.3391217246854428</v>
       </c>
-      <c r="DO18">
+      <c r="DP18">
         <v>0</v>
       </c>
-      <c r="DP18">
+      <c r="DQ18">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="DQ18">
+      <c r="DR18">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:121" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:122" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
         <v>83</v>
       </c>
@@ -8732,31 +8756,34 @@
       <c r="DJ19">
         <v>5</v>
       </c>
-      <c r="DL19">
-        <f>COUNT(B19:DJ19)</f>
-        <v>53</v>
-      </c>
-      <c r="DM19" s="18">
-        <f>AVERAGE(B19:DJ19)</f>
-        <v>5.7735849056603774</v>
-      </c>
-      <c r="DN19">
+      <c r="DK19">
+        <v>5.5</v>
+      </c>
+      <c r="DM19">
+        <f>COUNT(B19:DK19)</f>
+        <v>54</v>
+      </c>
+      <c r="DN19" s="18">
+        <f>AVERAGE(B19:DK19)</f>
+        <v>5.7685185185185182</v>
+      </c>
+      <c r="DO19">
         <f t="shared" si="4"/>
         <v>0.80040525180633026</v>
       </c>
-      <c r="DO19">
-        <v>1</v>
-      </c>
       <c r="DP19">
+        <v>1</v>
+      </c>
+      <c r="DQ19">
         <f t="shared" si="0"/>
         <v>2</v>
       </c>
-      <c r="DQ19">
+      <c r="DR19">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:121" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:122" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
         <v>43</v>
       </c>
@@ -9051,31 +9078,34 @@
       <c r="DI20">
         <v>5.5</v>
       </c>
-      <c r="DL20">
+      <c r="DK20">
+        <v>5.5</v>
+      </c>
+      <c r="DM20">
         <f t="shared" si="2"/>
         <v>53</v>
       </c>
-      <c r="DM20" s="18">
+      <c r="DN20" s="18">
         <f t="shared" si="3"/>
         <v>5.1132075471698117</v>
       </c>
-      <c r="DN20">
+      <c r="DO20">
         <f t="shared" si="4"/>
         <v>0.98372090629426312</v>
       </c>
-      <c r="DO20">
-        <v>1</v>
-      </c>
       <c r="DP20">
+        <v>1</v>
+      </c>
+      <c r="DQ20">
         <f t="shared" si="0"/>
         <v>2</v>
       </c>
-      <c r="DQ20">
+      <c r="DR20">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:121" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:122" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
         <v>45</v>
       </c>
@@ -9361,31 +9391,31 @@
       <c r="CZ21">
         <v>5.5</v>
       </c>
-      <c r="DL21">
+      <c r="DM21">
         <f t="shared" si="2"/>
         <v>45</v>
       </c>
-      <c r="DM21" s="18">
+      <c r="DN21" s="18">
         <f t="shared" si="3"/>
         <v>5.2555555555555555</v>
       </c>
-      <c r="DN21">
+      <c r="DO21">
         <f t="shared" si="4"/>
         <v>1.1659088447830879</v>
       </c>
-      <c r="DO21">
+      <c r="DP21">
         <v>0</v>
       </c>
-      <c r="DP21">
+      <c r="DQ21">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="DQ21">
+      <c r="DR21">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:121" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:122" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
         <v>54</v>
       </c>
@@ -9629,31 +9659,31 @@
       <c r="CK22">
         <v>5.5</v>
       </c>
-      <c r="DL22">
+      <c r="DM22">
         <f t="shared" si="2"/>
         <v>39</v>
       </c>
-      <c r="DM22" s="18">
+      <c r="DN22" s="18">
         <f t="shared" si="3"/>
         <v>6.1410256410256414</v>
       </c>
-      <c r="DN22">
+      <c r="DO22">
         <f t="shared" si="4"/>
         <v>1.0879042984027267</v>
       </c>
-      <c r="DO22">
+      <c r="DP22">
         <v>0</v>
       </c>
-      <c r="DP22">
+      <c r="DQ22">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="DQ22">
+      <c r="DR22">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:121" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:122" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
         <v>47</v>
       </c>
@@ -9942,31 +9972,31 @@
       <c r="DH23">
         <v>6</v>
       </c>
-      <c r="DL23">
+      <c r="DM23">
         <f t="shared" si="2"/>
         <v>36</v>
       </c>
-      <c r="DM23" s="18">
+      <c r="DN23" s="18">
         <f t="shared" si="3"/>
         <v>6.2777777777777777</v>
       </c>
-      <c r="DN23">
+      <c r="DO23">
         <f t="shared" si="4"/>
         <v>0.9520237425343997</v>
       </c>
-      <c r="DO23">
+      <c r="DP23">
         <v>0</v>
       </c>
-      <c r="DP23">
+      <c r="DQ23">
         <f t="shared" si="0"/>
         <v>2</v>
       </c>
-      <c r="DQ23">
+      <c r="DR23">
         <f t="shared" si="1"/>
         <v>2</v>
       </c>
     </row>
-    <row r="24" spans="1:121" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:122" x14ac:dyDescent="0.35">
       <c r="A24" t="s">
         <v>65</v>
       </c>
@@ -10231,31 +10261,31 @@
       <c r="DD24">
         <v>6</v>
       </c>
-      <c r="DL24">
+      <c r="DM24">
         <f t="shared" si="2"/>
         <v>31</v>
       </c>
-      <c r="DM24" s="18">
+      <c r="DN24" s="18">
         <f t="shared" si="3"/>
         <v>5.4838709677419351</v>
       </c>
-      <c r="DN24">
+      <c r="DO24">
         <f t="shared" si="4"/>
         <v>0.67680463660426593</v>
       </c>
-      <c r="DO24">
+      <c r="DP24">
         <v>0</v>
       </c>
-      <c r="DP24">
+      <c r="DQ24">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="DQ24">
+      <c r="DR24">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:121" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:122" x14ac:dyDescent="0.35">
       <c r="A25" t="s">
         <v>21</v>
       </c>
@@ -10541,31 +10571,31 @@
       <c r="DJ25">
         <v>6</v>
       </c>
-      <c r="DL25">
+      <c r="DM25">
         <f>COUNT(B25:DJ25)</f>
         <v>31</v>
       </c>
-      <c r="DM25" s="18">
+      <c r="DN25" s="18">
         <f>AVERAGE(B25:DJ25)</f>
         <v>6.467741935483871</v>
       </c>
-      <c r="DN25">
+      <c r="DO25">
         <f t="shared" si="4"/>
         <v>0.63630578928001602</v>
       </c>
-      <c r="DO25">
-        <v>1</v>
-      </c>
       <c r="DP25">
+        <v>1</v>
+      </c>
+      <c r="DQ25">
         <f t="shared" si="0"/>
         <v>3</v>
       </c>
-      <c r="DQ25">
+      <c r="DR25">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="1:121" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:122" x14ac:dyDescent="0.35">
       <c r="A26" t="s">
         <v>80</v>
       </c>
@@ -10863,31 +10893,34 @@
       <c r="DJ26">
         <v>5.5</v>
       </c>
-      <c r="DL26">
-        <f>COUNT(B26:DJ26)</f>
-        <v>23</v>
-      </c>
-      <c r="DM26" s="18">
-        <f>AVERAGE(B26:DJ26)</f>
-        <v>6.1086956521739131</v>
-      </c>
-      <c r="DN26">
+      <c r="DK26">
+        <v>6</v>
+      </c>
+      <c r="DM26">
+        <f>COUNT(B26:DK26)</f>
+        <v>24</v>
+      </c>
+      <c r="DN26" s="18">
+        <f>AVERAGE(B26:DK26)</f>
+        <v>6.104166666666667</v>
+      </c>
+      <c r="DO26">
         <f t="shared" si="4"/>
         <v>0.65795169495977013</v>
       </c>
-      <c r="DO26">
+      <c r="DP26">
         <v>0</v>
       </c>
-      <c r="DP26">
+      <c r="DQ26">
         <f t="shared" si="0"/>
         <v>2</v>
       </c>
-      <c r="DQ26">
+      <c r="DR26">
         <f t="shared" si="1"/>
         <v>2</v>
       </c>
     </row>
-    <row r="27" spans="1:121" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:122" x14ac:dyDescent="0.35">
       <c r="A27" t="s">
         <v>3</v>
       </c>
@@ -11128,31 +11161,31 @@
       <c r="CB27" t="s">
         <v>25</v>
       </c>
-      <c r="DL27">
+      <c r="DM27">
         <f t="shared" si="2"/>
         <v>19</v>
       </c>
-      <c r="DM27" s="18">
+      <c r="DN27" s="18">
         <f t="shared" si="3"/>
         <v>5.7894736842105265</v>
       </c>
-      <c r="DN27">
+      <c r="DO27">
         <f t="shared" si="4"/>
         <v>1.3674366679797902</v>
       </c>
-      <c r="DO27">
+      <c r="DP27">
         <v>0</v>
       </c>
-      <c r="DP27">
+      <c r="DQ27">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="DQ27">
+      <c r="DR27">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="1:121" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:122" x14ac:dyDescent="0.35">
       <c r="A28" t="s">
         <v>62</v>
       </c>
@@ -11414,31 +11447,31 @@
       <c r="DG28">
         <v>5.5</v>
       </c>
-      <c r="DL28">
+      <c r="DM28">
         <f t="shared" si="2"/>
         <v>19</v>
       </c>
-      <c r="DM28" s="18">
+      <c r="DN28" s="18">
         <f t="shared" si="3"/>
         <v>5.0263157894736841</v>
       </c>
-      <c r="DN28">
+      <c r="DO28">
         <f t="shared" si="4"/>
         <v>0.84119102419206049</v>
       </c>
-      <c r="DO28">
+      <c r="DP28">
         <v>0</v>
       </c>
-      <c r="DP28">
+      <c r="DQ28">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="DQ28">
+      <c r="DR28">
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
     </row>
-    <row r="29" spans="1:121" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:122" x14ac:dyDescent="0.35">
       <c r="A29" t="s">
         <v>100</v>
       </c>
@@ -11679,31 +11712,31 @@
       <c r="CB29" t="s">
         <v>25</v>
       </c>
-      <c r="DL29">
+      <c r="DM29">
         <f t="shared" si="2"/>
         <v>18</v>
       </c>
-      <c r="DM29" s="18">
+      <c r="DN29" s="18">
         <f t="shared" si="3"/>
         <v>5.9444444444444446</v>
       </c>
-      <c r="DN29">
+      <c r="DO29">
         <f t="shared" si="4"/>
         <v>0.72535769855270305</v>
       </c>
-      <c r="DO29">
+      <c r="DP29">
         <v>0</v>
       </c>
-      <c r="DP29">
+      <c r="DQ29">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="DQ29">
+      <c r="DR29">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
-    <row r="30" spans="1:121" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:122" x14ac:dyDescent="0.35">
       <c r="A30" t="s">
         <v>8</v>
       </c>
@@ -11947,31 +11980,31 @@
       <c r="DD30">
         <v>5.5</v>
       </c>
-      <c r="DL30">
+      <c r="DM30">
         <f t="shared" si="2"/>
         <v>18</v>
       </c>
-      <c r="DM30" s="18">
+      <c r="DN30" s="18">
         <f t="shared" si="3"/>
         <v>5.333333333333333</v>
       </c>
-      <c r="DN30">
+      <c r="DO30">
         <f t="shared" si="4"/>
         <v>1.3060943124220303</v>
       </c>
-      <c r="DO30">
+      <c r="DP30">
         <v>0</v>
       </c>
-      <c r="DP30">
+      <c r="DQ30">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="DQ30">
+      <c r="DR30">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
-    <row r="31" spans="1:121" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:122" x14ac:dyDescent="0.35">
       <c r="A31" t="s">
         <v>170</v>
       </c>
@@ -12248,31 +12281,34 @@
       <c r="DI31">
         <v>6</v>
       </c>
-      <c r="DL31">
+      <c r="DK31">
+        <v>6</v>
+      </c>
+      <c r="DM31">
         <f t="shared" si="2"/>
         <v>20</v>
       </c>
-      <c r="DM31" s="18">
+      <c r="DN31" s="18">
         <f t="shared" si="3"/>
         <v>5.125</v>
       </c>
-      <c r="DN31">
+      <c r="DO31">
         <f t="shared" si="4"/>
         <v>1.3943023156290106</v>
       </c>
-      <c r="DO31">
-        <v>1</v>
-      </c>
       <c r="DP31">
+        <v>1</v>
+      </c>
+      <c r="DQ31">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="DQ31">
+      <c r="DR31">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
-    <row r="32" spans="1:121" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:122" x14ac:dyDescent="0.35">
       <c r="A32" t="s">
         <v>67</v>
       </c>
@@ -12519,31 +12555,31 @@
       <c r="DA32">
         <v>5.5</v>
       </c>
-      <c r="DL32">
+      <c r="DM32">
         <f t="shared" si="2"/>
         <v>18</v>
       </c>
-      <c r="DM32" s="18">
+      <c r="DN32" s="18">
         <f t="shared" si="3"/>
         <v>4.583333333333333</v>
       </c>
-      <c r="DN32">
+      <c r="DO32">
         <f t="shared" si="4"/>
         <v>1.4677914581799016</v>
       </c>
-      <c r="DO32">
+      <c r="DP32">
         <v>0</v>
       </c>
-      <c r="DP32">
+      <c r="DQ32">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="DQ32">
+      <c r="DR32">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
-    <row r="33" spans="1:121" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:122" x14ac:dyDescent="0.35">
       <c r="A33" t="s">
         <v>7</v>
       </c>
@@ -12784,31 +12820,31 @@
       <c r="CB33">
         <v>5.5</v>
       </c>
-      <c r="DL33">
+      <c r="DM33">
         <f t="shared" si="2"/>
         <v>15</v>
       </c>
-      <c r="DM33" s="18">
+      <c r="DN33" s="18">
         <f t="shared" si="3"/>
         <v>3.8666666666666667</v>
       </c>
-      <c r="DN33">
+      <c r="DO33">
         <f t="shared" si="4"/>
         <v>2.3563490726929555</v>
       </c>
-      <c r="DO33">
+      <c r="DP33">
         <v>0</v>
       </c>
-      <c r="DP33">
+      <c r="DQ33">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="DQ33">
+      <c r="DR33">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
-    <row r="34" spans="1:121" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:122" x14ac:dyDescent="0.35">
       <c r="A34" t="s">
         <v>12</v>
       </c>
@@ -13058,31 +13094,31 @@
       <c r="DB34">
         <v>6.5</v>
       </c>
-      <c r="DL34">
+      <c r="DM34">
         <f t="shared" si="2"/>
         <v>16</v>
       </c>
-      <c r="DM34" s="18">
+      <c r="DN34" s="18">
         <f t="shared" si="3"/>
         <v>7.125</v>
       </c>
-      <c r="DN34">
+      <c r="DO34">
         <f t="shared" si="4"/>
         <v>1.4433756729740645</v>
       </c>
-      <c r="DO34">
+      <c r="DP34">
         <v>0</v>
       </c>
-      <c r="DP34">
-        <f t="shared" ref="DP34:DP65" si="5">COUNT(DF34:DH34)</f>
+      <c r="DQ34">
+        <f t="shared" ref="DQ34:DQ65" si="5">COUNT(DF34:DH34)</f>
         <v>0</v>
       </c>
-      <c r="DQ34">
-        <f t="shared" ref="DQ34:DQ65" si="6">IF(DO34=0,DP34,0)</f>
+      <c r="DR34">
+        <f t="shared" ref="DR34:DR65" si="6">IF(DP34=0,DQ34,0)</f>
         <v>0</v>
       </c>
     </row>
-    <row r="35" spans="1:121" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:122" x14ac:dyDescent="0.35">
       <c r="A35" t="s">
         <v>127</v>
       </c>
@@ -13365,31 +13401,31 @@
       <c r="DE35">
         <v>6.5</v>
       </c>
-      <c r="DL35">
+      <c r="DM35">
         <f t="shared" si="2"/>
         <v>21</v>
       </c>
-      <c r="DM35" s="18">
+      <c r="DN35" s="18">
         <f t="shared" si="3"/>
         <v>6.0952380952380949</v>
       </c>
-      <c r="DN35">
+      <c r="DO35">
         <f t="shared" si="4"/>
         <v>0.5616726720040689</v>
       </c>
-      <c r="DO35">
-        <v>1</v>
-      </c>
       <c r="DP35">
+        <v>1</v>
+      </c>
+      <c r="DQ35">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="DQ35">
+      <c r="DR35">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
     </row>
-    <row r="36" spans="1:121" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:122" x14ac:dyDescent="0.35">
       <c r="A36" t="s">
         <v>129</v>
       </c>
@@ -13657,31 +13693,31 @@
       <c r="CQ36">
         <v>5.5</v>
       </c>
-      <c r="DL36">
+      <c r="DM36">
         <f t="shared" si="2"/>
         <v>12</v>
       </c>
-      <c r="DM36" s="18">
+      <c r="DN36" s="18">
         <f t="shared" si="3"/>
         <v>5.25</v>
       </c>
-      <c r="DN36">
+      <c r="DO36">
         <f t="shared" si="4"/>
         <v>0.3988620176087328</v>
       </c>
-      <c r="DO36">
+      <c r="DP36">
         <v>0</v>
       </c>
-      <c r="DP36">
+      <c r="DQ36">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="DQ36">
+      <c r="DR36">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
     </row>
-    <row r="37" spans="1:121" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:122" x14ac:dyDescent="0.35">
       <c r="A37" t="s">
         <v>16</v>
       </c>
@@ -13922,31 +13958,31 @@
       <c r="CB37" t="s">
         <v>25</v>
       </c>
-      <c r="DL37">
+      <c r="DM37">
         <f t="shared" si="2"/>
         <v>11</v>
       </c>
-      <c r="DM37" s="18">
+      <c r="DN37" s="18">
         <f t="shared" si="3"/>
         <v>4.6818181818181817</v>
       </c>
-      <c r="DN37">
+      <c r="DO37">
         <f t="shared" si="4"/>
         <v>0.81463879335344846</v>
       </c>
-      <c r="DO37">
+      <c r="DP37">
         <v>0</v>
       </c>
-      <c r="DP37">
+      <c r="DQ37">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="DQ37">
+      <c r="DR37">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
     </row>
-    <row r="38" spans="1:121" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:122" x14ac:dyDescent="0.35">
       <c r="A38" t="s">
         <v>44</v>
       </c>
@@ -14190,31 +14226,31 @@
       <c r="CC38">
         <v>6</v>
       </c>
-      <c r="DL38">
+      <c r="DM38">
         <f t="shared" si="2"/>
         <v>10</v>
       </c>
-      <c r="DM38" s="18">
+      <c r="DN38" s="18">
         <f t="shared" si="3"/>
         <v>8.4499999999999993</v>
       </c>
-      <c r="DN38">
+      <c r="DO38">
         <f t="shared" si="4"/>
         <v>1.1890705987824657</v>
       </c>
-      <c r="DO38">
+      <c r="DP38">
         <v>0</v>
       </c>
-      <c r="DP38">
+      <c r="DQ38">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="DQ38">
+      <c r="DR38">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
     </row>
-    <row r="39" spans="1:121" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:122" x14ac:dyDescent="0.35">
       <c r="A39" t="s">
         <v>95</v>
       </c>
@@ -14458,31 +14494,31 @@
       <c r="CL39">
         <v>6</v>
       </c>
-      <c r="DL39">
+      <c r="DM39">
         <f t="shared" si="2"/>
         <v>8</v>
       </c>
-      <c r="DM39" s="18">
+      <c r="DN39" s="18">
         <f t="shared" si="3"/>
         <v>5.75</v>
       </c>
-      <c r="DN39">
+      <c r="DO39">
         <f t="shared" si="4"/>
         <v>0.53452248382484879</v>
       </c>
-      <c r="DO39">
+      <c r="DP39">
         <v>0</v>
       </c>
-      <c r="DP39">
+      <c r="DQ39">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="DQ39">
+      <c r="DR39">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
     </row>
-    <row r="40" spans="1:121" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:122" x14ac:dyDescent="0.35">
       <c r="A40" t="s">
         <v>151</v>
       </c>
@@ -14540,31 +14576,34 @@
       <c r="DI40">
         <v>7</v>
       </c>
-      <c r="DL40">
+      <c r="DK40">
+        <v>6</v>
+      </c>
+      <c r="DM40">
         <f t="shared" si="2"/>
         <v>18</v>
       </c>
-      <c r="DM40" s="18">
+      <c r="DN40" s="18">
         <f t="shared" si="3"/>
         <v>6.8611111111111107</v>
       </c>
-      <c r="DN40">
+      <c r="DO40">
         <f t="shared" si="4"/>
         <v>1.0262088360384556</v>
       </c>
-      <c r="DO40">
-        <v>1</v>
-      </c>
       <c r="DP40">
+        <v>1</v>
+      </c>
+      <c r="DQ40">
         <f t="shared" si="5"/>
         <v>3</v>
       </c>
-      <c r="DQ40">
+      <c r="DR40">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
     </row>
-    <row r="41" spans="1:121" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:122" x14ac:dyDescent="0.35">
       <c r="A41" t="s">
         <v>99</v>
       </c>
@@ -14823,31 +14862,31 @@
       <c r="CO41">
         <v>4.5</v>
       </c>
-      <c r="DL41">
+      <c r="DM41">
         <f t="shared" si="2"/>
         <v>7</v>
       </c>
-      <c r="DM41" s="18">
+      <c r="DN41" s="18">
         <f t="shared" si="3"/>
         <v>4.5</v>
       </c>
-      <c r="DN41">
+      <c r="DO41">
         <f t="shared" si="4"/>
         <v>1.2583057392117916</v>
       </c>
-      <c r="DO41">
+      <c r="DP41">
         <v>0</v>
       </c>
-      <c r="DP41">
+      <c r="DQ41">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="DQ41">
+      <c r="DR41">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
     </row>
-    <row r="42" spans="1:121" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:122" x14ac:dyDescent="0.35">
       <c r="A42" t="s">
         <v>143</v>
       </c>
@@ -14872,31 +14911,31 @@
       <c r="CY42">
         <v>4.5</v>
       </c>
-      <c r="DL42">
+      <c r="DM42">
         <f t="shared" si="2"/>
         <v>7</v>
       </c>
-      <c r="DM42" s="18">
+      <c r="DN42" s="18">
         <f t="shared" si="3"/>
         <v>5.6428571428571432</v>
       </c>
-      <c r="DN42">
+      <c r="DO42">
         <f t="shared" si="4"/>
         <v>1.248808956375558</v>
       </c>
-      <c r="DO42">
+      <c r="DP42">
         <v>0</v>
       </c>
-      <c r="DP42">
+      <c r="DQ42">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="DQ42">
+      <c r="DR42">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
     </row>
-    <row r="43" spans="1:121" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:122" x14ac:dyDescent="0.35">
       <c r="A43" t="s">
         <v>148</v>
       </c>
@@ -14936,31 +14975,31 @@
       <c r="DI43">
         <v>6</v>
       </c>
-      <c r="DL43">
+      <c r="DM43">
         <f t="shared" si="2"/>
         <v>12</v>
       </c>
-      <c r="DM43" s="18">
+      <c r="DN43" s="18">
         <f t="shared" si="3"/>
         <v>6.041666666666667</v>
       </c>
-      <c r="DN43">
+      <c r="DO43">
         <f t="shared" si="4"/>
         <v>0.39648073054937955</v>
       </c>
-      <c r="DO43">
+      <c r="DP43">
         <v>0</v>
       </c>
-      <c r="DP43">
+      <c r="DQ43">
         <f t="shared" si="5"/>
         <v>1</v>
       </c>
-      <c r="DQ43">
+      <c r="DR43">
         <f t="shared" si="6"/>
         <v>1</v>
       </c>
     </row>
-    <row r="44" spans="1:121" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:122" x14ac:dyDescent="0.35">
       <c r="A44" t="s">
         <v>97</v>
       </c>
@@ -15213,31 +15252,34 @@
       <c r="DJ44">
         <v>6</v>
       </c>
-      <c r="DL44">
+      <c r="DK44">
+        <v>6</v>
+      </c>
+      <c r="DM44">
         <f t="shared" si="2"/>
         <v>5</v>
       </c>
-      <c r="DM44" s="18">
+      <c r="DN44" s="18">
         <f t="shared" si="3"/>
         <v>5.6</v>
       </c>
-      <c r="DN44">
+      <c r="DO44">
         <f t="shared" si="4"/>
         <v>1.0839741694339387</v>
       </c>
-      <c r="DO44">
+      <c r="DP44">
         <v>0</v>
       </c>
-      <c r="DP44">
+      <c r="DQ44">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="DQ44">
+      <c r="DR44">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
     </row>
-    <row r="45" spans="1:121" x14ac:dyDescent="0.35">
+    <row r="45" spans="1:122" x14ac:dyDescent="0.35">
       <c r="A45" t="s">
         <v>141</v>
       </c>
@@ -15493,31 +15535,31 @@
       <c r="CU45">
         <v>6</v>
       </c>
-      <c r="DL45">
+      <c r="DM45">
         <f t="shared" si="2"/>
         <v>5</v>
       </c>
-      <c r="DM45" s="18">
+      <c r="DN45" s="18">
         <f t="shared" si="3"/>
         <v>6.5</v>
       </c>
-      <c r="DN45">
+      <c r="DO45">
         <f t="shared" si="4"/>
         <v>0.5</v>
       </c>
-      <c r="DO45">
+      <c r="DP45">
         <v>0</v>
       </c>
-      <c r="DP45">
+      <c r="DQ45">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="DQ45">
+      <c r="DR45">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
     </row>
-    <row r="46" spans="1:121" x14ac:dyDescent="0.35">
+    <row r="46" spans="1:122" x14ac:dyDescent="0.35">
       <c r="A46" t="s">
         <v>23</v>
       </c>
@@ -15761,31 +15803,31 @@
       <c r="CH46">
         <v>6.5</v>
       </c>
-      <c r="DL46">
+      <c r="DM46">
         <f t="shared" si="2"/>
         <v>5</v>
       </c>
-      <c r="DM46" s="18">
+      <c r="DN46" s="18">
         <f t="shared" si="3"/>
         <v>7.8</v>
       </c>
-      <c r="DN46">
+      <c r="DO46">
         <f t="shared" si="4"/>
         <v>1.1510864433221351</v>
       </c>
-      <c r="DO46">
+      <c r="DP46">
         <v>0</v>
       </c>
-      <c r="DP46">
+      <c r="DQ46">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="DQ46">
+      <c r="DR46">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
     </row>
-    <row r="47" spans="1:121" x14ac:dyDescent="0.35">
+    <row r="47" spans="1:122" x14ac:dyDescent="0.35">
       <c r="A47" t="s">
         <v>59</v>
       </c>
@@ -16032,31 +16074,31 @@
       <c r="DJ47">
         <v>5.5</v>
       </c>
-      <c r="DL47">
+      <c r="DM47">
         <f t="shared" si="2"/>
         <v>5</v>
       </c>
-      <c r="DM47" s="18">
+      <c r="DN47" s="18">
         <f t="shared" si="3"/>
         <v>3.8</v>
       </c>
-      <c r="DN47">
+      <c r="DO47">
         <f t="shared" si="4"/>
         <v>1.0368220676663857</v>
       </c>
-      <c r="DO47">
+      <c r="DP47">
         <v>0</v>
       </c>
-      <c r="DP47">
+      <c r="DQ47">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="DQ47">
+      <c r="DR47">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
     </row>
-    <row r="48" spans="1:121" x14ac:dyDescent="0.35">
+    <row r="48" spans="1:122" x14ac:dyDescent="0.35">
       <c r="A48" t="s">
         <v>115</v>
       </c>
@@ -16306,31 +16348,31 @@
       <c r="CN48">
         <v>6</v>
       </c>
-      <c r="DL48">
+      <c r="DM48">
         <f t="shared" si="2"/>
         <v>5</v>
       </c>
-      <c r="DM48" s="18">
+      <c r="DN48" s="18">
         <f t="shared" si="3"/>
         <v>6.2</v>
       </c>
-      <c r="DN48">
+      <c r="DO48">
         <f t="shared" si="4"/>
         <v>0.44721359549995793</v>
       </c>
-      <c r="DO48">
+      <c r="DP48">
         <v>0</v>
       </c>
-      <c r="DP48">
+      <c r="DQ48">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="DQ48">
+      <c r="DR48">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
     </row>
-    <row r="49" spans="1:121" x14ac:dyDescent="0.35">
+    <row r="49" spans="1:122" x14ac:dyDescent="0.35">
       <c r="A49" t="s">
         <v>53</v>
       </c>
@@ -16574,31 +16616,34 @@
       <c r="CY49">
         <v>5.5</v>
       </c>
-      <c r="DL49">
+      <c r="DK49">
+        <v>5.5</v>
+      </c>
+      <c r="DM49">
         <f t="shared" si="2"/>
         <v>5</v>
       </c>
-      <c r="DM49" s="18">
+      <c r="DN49" s="18">
         <f t="shared" si="3"/>
         <v>6.5</v>
       </c>
-      <c r="DN49">
+      <c r="DO49">
         <f t="shared" si="4"/>
         <v>1.0606601717798212</v>
       </c>
-      <c r="DO49">
+      <c r="DP49">
         <v>0</v>
       </c>
-      <c r="DP49">
+      <c r="DQ49">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="DQ49">
+      <c r="DR49">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
     </row>
-    <row r="50" spans="1:121" x14ac:dyDescent="0.35">
+    <row r="50" spans="1:122" x14ac:dyDescent="0.35">
       <c r="A50" t="s">
         <v>51</v>
       </c>
@@ -16845,31 +16890,31 @@
       <c r="CV50">
         <v>5.5</v>
       </c>
-      <c r="DL50">
+      <c r="DM50">
         <f t="shared" si="2"/>
         <v>4</v>
       </c>
-      <c r="DM50" s="18">
+      <c r="DN50" s="18">
         <f t="shared" si="3"/>
         <v>5.625</v>
       </c>
-      <c r="DN50">
+      <c r="DO50">
         <f t="shared" si="4"/>
         <v>0.25</v>
       </c>
-      <c r="DO50">
+      <c r="DP50">
         <v>0</v>
       </c>
-      <c r="DP50">
+      <c r="DQ50">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="DQ50">
+      <c r="DR50">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
     </row>
-    <row r="51" spans="1:121" x14ac:dyDescent="0.35">
+    <row r="51" spans="1:122" x14ac:dyDescent="0.35">
       <c r="A51" t="s">
         <v>60</v>
       </c>
@@ -17110,31 +17155,31 @@
       <c r="CB51" t="s">
         <v>25</v>
       </c>
-      <c r="DL51">
+      <c r="DM51">
         <f t="shared" si="2"/>
         <v>4</v>
       </c>
-      <c r="DM51" s="18">
+      <c r="DN51" s="18">
         <f t="shared" si="3"/>
         <v>5.625</v>
       </c>
-      <c r="DN51">
+      <c r="DO51">
         <f t="shared" si="4"/>
         <v>0.9464847243000456</v>
       </c>
-      <c r="DO51">
+      <c r="DP51">
         <v>0</v>
       </c>
-      <c r="DP51">
+      <c r="DQ51">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="DQ51">
+      <c r="DR51">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
     </row>
-    <row r="52" spans="1:121" x14ac:dyDescent="0.35">
+    <row r="52" spans="1:122" x14ac:dyDescent="0.35">
       <c r="A52" t="s">
         <v>20</v>
       </c>
@@ -17375,31 +17420,31 @@
       <c r="CB52" t="s">
         <v>25</v>
       </c>
-      <c r="DL52">
+      <c r="DM52">
         <f t="shared" si="2"/>
         <v>4</v>
       </c>
-      <c r="DM52" s="18">
+      <c r="DN52" s="18">
         <f t="shared" si="3"/>
         <v>1.375</v>
       </c>
-      <c r="DN52">
+      <c r="DO52">
         <f t="shared" si="4"/>
         <v>1.8874586088176875</v>
       </c>
-      <c r="DO52">
+      <c r="DP52">
         <v>0</v>
       </c>
-      <c r="DP52">
+      <c r="DQ52">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="DQ52">
+      <c r="DR52">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
     </row>
-    <row r="53" spans="1:121" x14ac:dyDescent="0.35">
+    <row r="53" spans="1:122" x14ac:dyDescent="0.35">
       <c r="A53" t="s">
         <v>98</v>
       </c>
@@ -17640,31 +17685,31 @@
       <c r="CB53" t="s">
         <v>25</v>
       </c>
-      <c r="DL53">
+      <c r="DM53">
         <f t="shared" si="2"/>
         <v>4</v>
       </c>
-      <c r="DM53" s="18">
+      <c r="DN53" s="18">
         <f t="shared" si="3"/>
         <v>4.625</v>
       </c>
-      <c r="DN53">
+      <c r="DO53">
         <f t="shared" si="4"/>
         <v>1.4361406616345072</v>
       </c>
-      <c r="DO53">
+      <c r="DP53">
         <v>0</v>
       </c>
-      <c r="DP53">
+      <c r="DQ53">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="DQ53">
+      <c r="DR53">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
     </row>
-    <row r="54" spans="1:121" x14ac:dyDescent="0.35">
+    <row r="54" spans="1:122" x14ac:dyDescent="0.35">
       <c r="A54" t="s">
         <v>112</v>
       </c>
@@ -17905,31 +17950,31 @@
       <c r="CB54" t="s">
         <v>25</v>
       </c>
-      <c r="DL54">
+      <c r="DM54">
         <f t="shared" si="2"/>
         <v>4</v>
       </c>
-      <c r="DM54" s="18">
+      <c r="DN54" s="18">
         <f t="shared" si="3"/>
         <v>6.25</v>
       </c>
-      <c r="DN54">
+      <c r="DO54">
         <f t="shared" si="4"/>
         <v>0.8660254037844386</v>
       </c>
-      <c r="DO54">
+      <c r="DP54">
         <v>0</v>
       </c>
-      <c r="DP54">
+      <c r="DQ54">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="DQ54">
+      <c r="DR54">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
     </row>
-    <row r="55" spans="1:121" x14ac:dyDescent="0.35">
+    <row r="55" spans="1:122" x14ac:dyDescent="0.35">
       <c r="A55" t="s">
         <v>42</v>
       </c>
@@ -18170,31 +18215,31 @@
       <c r="CB55" t="s">
         <v>25</v>
       </c>
-      <c r="DL55">
+      <c r="DM55">
         <f t="shared" si="2"/>
         <v>4</v>
       </c>
-      <c r="DM55" s="18">
+      <c r="DN55" s="18">
         <f t="shared" si="3"/>
         <v>2.875</v>
       </c>
-      <c r="DN55">
+      <c r="DO55">
         <f t="shared" si="4"/>
         <v>2.7801378862687129</v>
       </c>
-      <c r="DO55">
+      <c r="DP55">
         <v>0</v>
       </c>
-      <c r="DP55">
+      <c r="DQ55">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="DQ55">
+      <c r="DR55">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
     </row>
-    <row r="56" spans="1:121" x14ac:dyDescent="0.35">
+    <row r="56" spans="1:122" x14ac:dyDescent="0.35">
       <c r="A56" t="s">
         <v>17</v>
       </c>
@@ -18435,31 +18480,31 @@
       <c r="CB56" t="s">
         <v>25</v>
       </c>
-      <c r="DL56">
+      <c r="DM56">
         <f t="shared" si="2"/>
         <v>3</v>
       </c>
-      <c r="DM56" s="18">
+      <c r="DN56" s="18">
         <f t="shared" si="3"/>
         <v>4.666666666666667</v>
       </c>
-      <c r="DN56">
+      <c r="DO56">
         <f t="shared" si="4"/>
         <v>1.4433756729740652</v>
       </c>
-      <c r="DO56">
+      <c r="DP56">
         <v>0</v>
       </c>
-      <c r="DP56">
+      <c r="DQ56">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="DQ56">
+      <c r="DR56">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
     </row>
-    <row r="57" spans="1:121" x14ac:dyDescent="0.35">
+    <row r="57" spans="1:122" x14ac:dyDescent="0.35">
       <c r="A57" t="s">
         <v>84</v>
       </c>
@@ -18706,31 +18751,31 @@
       <c r="DJ57">
         <v>7</v>
       </c>
-      <c r="DL57">
+      <c r="DM57">
         <f t="shared" si="2"/>
         <v>4</v>
       </c>
-      <c r="DM57" s="18">
+      <c r="DN57" s="18">
         <f t="shared" si="3"/>
         <v>7.875</v>
       </c>
-      <c r="DN57">
+      <c r="DO57">
         <f t="shared" si="4"/>
         <v>1.75</v>
       </c>
-      <c r="DO57">
+      <c r="DP57">
         <v>0</v>
       </c>
-      <c r="DP57">
+      <c r="DQ57">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="DQ57">
+      <c r="DR57">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
     </row>
-    <row r="58" spans="1:121" x14ac:dyDescent="0.35">
+    <row r="58" spans="1:122" x14ac:dyDescent="0.35">
       <c r="A58" t="s">
         <v>48</v>
       </c>
@@ -18971,31 +19016,31 @@
       <c r="CB58" t="s">
         <v>25</v>
       </c>
-      <c r="DL58">
+      <c r="DM58">
         <f t="shared" si="2"/>
         <v>3</v>
       </c>
-      <c r="DM58" s="18">
+      <c r="DN58" s="18">
         <f t="shared" si="3"/>
         <v>4</v>
       </c>
-      <c r="DN58">
+      <c r="DO58">
         <f t="shared" si="4"/>
         <v>1.7320508075688772</v>
       </c>
-      <c r="DO58">
+      <c r="DP58">
         <v>0</v>
       </c>
-      <c r="DP58">
+      <c r="DQ58">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="DQ58">
+      <c r="DR58">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
     </row>
-    <row r="59" spans="1:121" x14ac:dyDescent="0.35">
+    <row r="59" spans="1:122" x14ac:dyDescent="0.35">
       <c r="A59" t="s">
         <v>119</v>
       </c>
@@ -19239,31 +19284,31 @@
       <c r="CG59">
         <v>6</v>
       </c>
-      <c r="DL59">
+      <c r="DM59">
         <f t="shared" si="2"/>
         <v>3</v>
       </c>
-      <c r="DM59" s="18">
+      <c r="DN59" s="18">
         <f t="shared" si="3"/>
         <v>8.5</v>
       </c>
-      <c r="DN59">
+      <c r="DO59">
         <f t="shared" si="4"/>
         <v>2.179449471770337</v>
       </c>
-      <c r="DO59">
+      <c r="DP59">
         <v>0</v>
       </c>
-      <c r="DP59">
+      <c r="DQ59">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="DQ59">
+      <c r="DR59">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
     </row>
-    <row r="60" spans="1:121" x14ac:dyDescent="0.35">
+    <row r="60" spans="1:122" x14ac:dyDescent="0.35">
       <c r="A60" t="s">
         <v>52</v>
       </c>
@@ -19507,31 +19552,31 @@
       <c r="CS60">
         <v>5.5</v>
       </c>
-      <c r="DL60">
+      <c r="DM60">
         <f t="shared" si="2"/>
         <v>3</v>
       </c>
-      <c r="DM60" s="18">
+      <c r="DN60" s="18">
         <f t="shared" si="3"/>
         <v>5.333333333333333</v>
       </c>
-      <c r="DN60">
+      <c r="DO60">
         <f t="shared" si="4"/>
         <v>0.28867513459481287</v>
       </c>
-      <c r="DO60">
+      <c r="DP60">
         <v>0</v>
       </c>
-      <c r="DP60">
+      <c r="DQ60">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="DQ60">
+      <c r="DR60">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
     </row>
-    <row r="61" spans="1:121" x14ac:dyDescent="0.35">
+    <row r="61" spans="1:122" x14ac:dyDescent="0.35">
       <c r="A61" t="s">
         <v>138</v>
       </c>
@@ -19781,31 +19826,31 @@
       <c r="CJ61">
         <v>7</v>
       </c>
-      <c r="DL61">
+      <c r="DM61">
         <f t="shared" si="2"/>
         <v>3</v>
       </c>
-      <c r="DM61" s="18">
+      <c r="DN61" s="18">
         <f t="shared" si="3"/>
         <v>6.666666666666667</v>
       </c>
-      <c r="DN61">
+      <c r="DO61">
         <f t="shared" si="4"/>
         <v>0.57735026918962584</v>
       </c>
-      <c r="DO61">
+      <c r="DP61">
         <v>0</v>
       </c>
-      <c r="DP61">
+      <c r="DQ61">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="DQ61">
+      <c r="DR61">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
     </row>
-    <row r="62" spans="1:121" x14ac:dyDescent="0.35">
+    <row r="62" spans="1:122" x14ac:dyDescent="0.35">
       <c r="A62" t="s">
         <v>130</v>
       </c>
@@ -20049,31 +20094,31 @@
       <c r="DF62">
         <v>5</v>
       </c>
-      <c r="DL62">
+      <c r="DM62">
         <f t="shared" si="2"/>
         <v>3</v>
       </c>
-      <c r="DM62" s="18">
+      <c r="DN62" s="18">
         <f t="shared" si="3"/>
         <v>5.333333333333333</v>
       </c>
-      <c r="DN62">
+      <c r="DO62">
         <f t="shared" si="4"/>
         <v>0.28867513459481287</v>
       </c>
-      <c r="DO62">
+      <c r="DP62">
         <v>0</v>
       </c>
-      <c r="DP62">
+      <c r="DQ62">
         <f t="shared" si="5"/>
         <v>1</v>
       </c>
-      <c r="DQ62">
+      <c r="DR62">
         <f t="shared" si="6"/>
         <v>1</v>
       </c>
     </row>
-    <row r="63" spans="1:121" x14ac:dyDescent="0.35">
+    <row r="63" spans="1:122" x14ac:dyDescent="0.35">
       <c r="A63" t="s">
         <v>113</v>
       </c>
@@ -20317,31 +20362,31 @@
       <c r="CD63">
         <v>5.5</v>
       </c>
-      <c r="DL63">
+      <c r="DM63">
         <f t="shared" si="2"/>
         <v>2</v>
       </c>
-      <c r="DM63" s="18">
+      <c r="DN63" s="18">
         <f t="shared" si="3"/>
         <v>5.25</v>
       </c>
-      <c r="DN63">
+      <c r="DO63">
         <f t="shared" si="4"/>
         <v>0.35355339059327379</v>
       </c>
-      <c r="DO63">
+      <c r="DP63">
         <v>0</v>
       </c>
-      <c r="DP63">
+      <c r="DQ63">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="DQ63">
+      <c r="DR63">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
     </row>
-    <row r="64" spans="1:121" x14ac:dyDescent="0.35">
+    <row r="64" spans="1:122" x14ac:dyDescent="0.35">
       <c r="A64" t="s">
         <v>94</v>
       </c>
@@ -20582,31 +20627,31 @@
       <c r="CB64" t="s">
         <v>25</v>
       </c>
-      <c r="DL64">
+      <c r="DM64">
         <f t="shared" si="2"/>
         <v>2</v>
       </c>
-      <c r="DM64" s="18">
+      <c r="DN64" s="18">
         <f t="shared" si="3"/>
         <v>6.75</v>
       </c>
-      <c r="DN64">
+      <c r="DO64">
         <f t="shared" si="4"/>
         <v>2.4748737341529163</v>
       </c>
-      <c r="DO64">
+      <c r="DP64">
         <v>0</v>
       </c>
-      <c r="DP64">
+      <c r="DQ64">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="DQ64">
+      <c r="DR64">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
     </row>
-    <row r="65" spans="1:121" x14ac:dyDescent="0.35">
+    <row r="65" spans="1:122" x14ac:dyDescent="0.35">
       <c r="A65" t="s">
         <v>120</v>
       </c>
@@ -20847,31 +20892,31 @@
       <c r="CB65" t="s">
         <v>25</v>
       </c>
-      <c r="DL65">
+      <c r="DM65">
         <f t="shared" si="2"/>
         <v>2</v>
       </c>
-      <c r="DM65" s="18">
+      <c r="DN65" s="18">
         <f t="shared" si="3"/>
         <v>5.75</v>
       </c>
-      <c r="DN65">
+      <c r="DO65">
         <f t="shared" si="4"/>
         <v>1.0606601717798212</v>
       </c>
-      <c r="DO65">
+      <c r="DP65">
         <v>0</v>
       </c>
-      <c r="DP65">
+      <c r="DQ65">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="DQ65">
+      <c r="DR65">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
     </row>
-    <row r="66" spans="1:121" x14ac:dyDescent="0.35">
+    <row r="66" spans="1:122" x14ac:dyDescent="0.35">
       <c r="A66" t="s">
         <v>139</v>
       </c>
@@ -21115,31 +21160,31 @@
       <c r="CH66">
         <v>5</v>
       </c>
-      <c r="DL66">
+      <c r="DM66">
         <f t="shared" si="2"/>
         <v>2</v>
       </c>
-      <c r="DM66" s="18">
+      <c r="DN66" s="18">
         <f t="shared" si="3"/>
         <v>4.25</v>
       </c>
-      <c r="DN66">
+      <c r="DO66">
         <f t="shared" si="4"/>
         <v>1.0606601717798212</v>
       </c>
-      <c r="DO66">
+      <c r="DP66">
         <v>0</v>
       </c>
-      <c r="DP66">
-        <f t="shared" ref="DP66:DP89" si="7">COUNT(DF66:DH66)</f>
+      <c r="DQ66">
+        <f t="shared" ref="DQ66:DQ89" si="7">COUNT(DF66:DH66)</f>
         <v>0</v>
       </c>
-      <c r="DQ66">
-        <f t="shared" ref="DQ66:DQ89" si="8">IF(DO66=0,DP66,0)</f>
+      <c r="DR66">
+        <f t="shared" ref="DR66:DR89" si="8">IF(DP66=0,DQ66,0)</f>
         <v>0</v>
       </c>
     </row>
-    <row r="67" spans="1:121" x14ac:dyDescent="0.35">
+    <row r="67" spans="1:122" x14ac:dyDescent="0.35">
       <c r="A67" t="s">
         <v>146</v>
       </c>
@@ -21149,62 +21194,62 @@
       <c r="DA67">
         <v>7</v>
       </c>
-      <c r="DL67">
-        <f t="shared" ref="DL67:DL102" si="9">COUNT(B67:DI67)</f>
-        <v>2</v>
-      </c>
-      <c r="DM67" s="18">
-        <f t="shared" ref="DM67:DM102" si="10">AVERAGE(B67:DI67)</f>
+      <c r="DM67">
+        <f t="shared" ref="DM67:DM102" si="9">COUNT(B67:DI67)</f>
+        <v>2</v>
+      </c>
+      <c r="DN67" s="18">
+        <f t="shared" ref="DN67:DN102" si="10">AVERAGE(B67:DI67)</f>
         <v>7.25</v>
       </c>
-      <c r="DN67">
-        <f t="shared" ref="DN67:DN102" si="11">IF(DL67&gt;1,_xlfn.STDEV.S(B67:DI67),"")</f>
+      <c r="DO67">
+        <f t="shared" ref="DO67:DO102" si="11">IF(DM67&gt;1,_xlfn.STDEV.S(B67:DI67),"")</f>
         <v>0.35355339059327379</v>
       </c>
-      <c r="DO67">
+      <c r="DP67">
         <v>0</v>
       </c>
-      <c r="DP67">
+      <c r="DQ67">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="DQ67">
+      <c r="DR67">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
     </row>
-    <row r="68" spans="1:121" x14ac:dyDescent="0.35">
+    <row r="68" spans="1:122" x14ac:dyDescent="0.35">
       <c r="A68" t="s">
         <v>147</v>
       </c>
       <c r="CV68">
         <v>6</v>
       </c>
-      <c r="DL68">
+      <c r="DM68">
         <f t="shared" si="9"/>
         <v>1</v>
       </c>
-      <c r="DM68" s="18">
+      <c r="DN68" s="18">
         <f t="shared" si="10"/>
         <v>6</v>
       </c>
-      <c r="DN68" t="str">
+      <c r="DO68" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
-      <c r="DO68">
+      <c r="DP68">
         <v>0</v>
       </c>
-      <c r="DP68">
+      <c r="DQ68">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="DQ68">
+      <c r="DR68">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
     </row>
-    <row r="69" spans="1:121" x14ac:dyDescent="0.35">
+    <row r="69" spans="1:122" x14ac:dyDescent="0.35">
       <c r="A69" t="s">
         <v>85</v>
       </c>
@@ -21445,31 +21490,31 @@
       <c r="CB69" t="s">
         <v>25</v>
       </c>
-      <c r="DL69">
+      <c r="DM69">
         <f t="shared" si="9"/>
         <v>1</v>
       </c>
-      <c r="DM69" s="18">
+      <c r="DN69" s="18">
         <f t="shared" si="10"/>
         <v>10</v>
       </c>
-      <c r="DN69" t="str">
+      <c r="DO69" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
-      <c r="DO69">
+      <c r="DP69">
         <v>0</v>
       </c>
-      <c r="DP69">
+      <c r="DQ69">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="DQ69">
+      <c r="DR69">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
     </row>
-    <row r="70" spans="1:121" x14ac:dyDescent="0.35">
+    <row r="70" spans="1:122" x14ac:dyDescent="0.35">
       <c r="A70" t="s">
         <v>76</v>
       </c>
@@ -21710,31 +21755,31 @@
       <c r="CB70" t="s">
         <v>25</v>
       </c>
-      <c r="DL70">
+      <c r="DM70">
         <f t="shared" si="9"/>
         <v>1</v>
       </c>
-      <c r="DM70" s="18">
+      <c r="DN70" s="18">
         <f t="shared" si="10"/>
         <v>7</v>
       </c>
-      <c r="DN70" t="str">
+      <c r="DO70" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
-      <c r="DO70">
+      <c r="DP70">
         <v>0</v>
       </c>
-      <c r="DP70">
+      <c r="DQ70">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="DQ70">
+      <c r="DR70">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
     </row>
-    <row r="71" spans="1:121" x14ac:dyDescent="0.35">
+    <row r="71" spans="1:122" x14ac:dyDescent="0.35">
       <c r="A71" t="s">
         <v>107</v>
       </c>
@@ -21975,31 +22020,31 @@
       <c r="CB71" t="s">
         <v>25</v>
       </c>
-      <c r="DL71">
+      <c r="DM71">
         <f t="shared" si="9"/>
         <v>1</v>
       </c>
-      <c r="DM71" s="18">
+      <c r="DN71" s="18">
         <f t="shared" si="10"/>
         <v>7</v>
       </c>
-      <c r="DN71" t="str">
+      <c r="DO71" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
-      <c r="DO71">
+      <c r="DP71">
         <v>0</v>
       </c>
-      <c r="DP71">
+      <c r="DQ71">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="DQ71">
+      <c r="DR71">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
     </row>
-    <row r="72" spans="1:121" x14ac:dyDescent="0.35">
+    <row r="72" spans="1:122" x14ac:dyDescent="0.35">
       <c r="A72" t="s">
         <v>79</v>
       </c>
@@ -22240,31 +22285,31 @@
       <c r="CB72" t="s">
         <v>25</v>
       </c>
-      <c r="DL72">
+      <c r="DM72">
         <f t="shared" si="9"/>
         <v>1</v>
       </c>
-      <c r="DM72" s="18">
+      <c r="DN72" s="18">
         <f t="shared" si="10"/>
         <v>7</v>
       </c>
-      <c r="DN72" t="str">
+      <c r="DO72" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
-      <c r="DO72">
+      <c r="DP72">
         <v>0</v>
       </c>
-      <c r="DP72">
+      <c r="DQ72">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="DQ72">
+      <c r="DR72">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
     </row>
-    <row r="73" spans="1:121" x14ac:dyDescent="0.35">
+    <row r="73" spans="1:122" x14ac:dyDescent="0.35">
       <c r="A73" t="s">
         <v>46</v>
       </c>
@@ -22505,31 +22550,31 @@
       <c r="CB73" t="s">
         <v>25</v>
       </c>
-      <c r="DL73">
+      <c r="DM73">
         <f t="shared" si="9"/>
         <v>1</v>
       </c>
-      <c r="DM73" s="18">
+      <c r="DN73" s="18">
         <f t="shared" si="10"/>
         <v>3.5</v>
       </c>
-      <c r="DN73" t="str">
+      <c r="DO73" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
-      <c r="DO73">
+      <c r="DP73">
         <v>0</v>
       </c>
-      <c r="DP73">
+      <c r="DQ73">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="DQ73">
+      <c r="DR73">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
     </row>
-    <row r="74" spans="1:121" x14ac:dyDescent="0.35">
+    <row r="74" spans="1:122" x14ac:dyDescent="0.35">
       <c r="A74" t="s">
         <v>82</v>
       </c>
@@ -22770,31 +22815,31 @@
       <c r="CB74" t="s">
         <v>25</v>
       </c>
-      <c r="DL74">
+      <c r="DM74">
         <f t="shared" si="9"/>
         <v>1</v>
       </c>
-      <c r="DM74" s="18">
+      <c r="DN74" s="18">
         <f t="shared" si="10"/>
         <v>3</v>
       </c>
-      <c r="DN74" t="str">
+      <c r="DO74" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
-      <c r="DO74">
+      <c r="DP74">
         <v>0</v>
       </c>
-      <c r="DP74">
+      <c r="DQ74">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="DQ74">
+      <c r="DR74">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
     </row>
-    <row r="75" spans="1:121" x14ac:dyDescent="0.35">
+    <row r="75" spans="1:122" x14ac:dyDescent="0.35">
       <c r="A75" t="s">
         <v>101</v>
       </c>
@@ -23035,31 +23080,31 @@
       <c r="CB75" t="s">
         <v>25</v>
       </c>
-      <c r="DL75">
+      <c r="DM75">
         <f t="shared" si="9"/>
         <v>1</v>
       </c>
-      <c r="DM75" s="18">
+      <c r="DN75" s="18">
         <f t="shared" si="10"/>
         <v>6.5</v>
       </c>
-      <c r="DN75" t="str">
+      <c r="DO75" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
-      <c r="DO75">
+      <c r="DP75">
         <v>0</v>
       </c>
-      <c r="DP75">
+      <c r="DQ75">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="DQ75">
+      <c r="DR75">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
     </row>
-    <row r="76" spans="1:121" x14ac:dyDescent="0.35">
+    <row r="76" spans="1:122" x14ac:dyDescent="0.35">
       <c r="A76" t="s">
         <v>104</v>
       </c>
@@ -23300,31 +23345,31 @@
       <c r="CB76" t="s">
         <v>25</v>
       </c>
-      <c r="DL76">
+      <c r="DM76">
         <f t="shared" si="9"/>
         <v>1</v>
       </c>
-      <c r="DM76" s="18">
+      <c r="DN76" s="18">
         <f t="shared" si="10"/>
         <v>4</v>
       </c>
-      <c r="DN76" t="str">
+      <c r="DO76" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
-      <c r="DO76">
+      <c r="DP76">
         <v>0</v>
       </c>
-      <c r="DP76">
+      <c r="DQ76">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="DQ76">
+      <c r="DR76">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
     </row>
-    <row r="77" spans="1:121" x14ac:dyDescent="0.35">
+    <row r="77" spans="1:122" x14ac:dyDescent="0.35">
       <c r="A77" t="s">
         <v>105</v>
       </c>
@@ -23565,31 +23610,31 @@
       <c r="CB77" t="s">
         <v>25</v>
       </c>
-      <c r="DL77">
+      <c r="DM77">
         <f t="shared" si="9"/>
         <v>1</v>
       </c>
-      <c r="DM77" s="18">
+      <c r="DN77" s="18">
         <f t="shared" si="10"/>
         <v>6.5</v>
       </c>
-      <c r="DN77" t="str">
+      <c r="DO77" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
-      <c r="DO77">
+      <c r="DP77">
         <v>0</v>
       </c>
-      <c r="DP77">
+      <c r="DQ77">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="DQ77">
+      <c r="DR77">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
     </row>
-    <row r="78" spans="1:121" x14ac:dyDescent="0.35">
+    <row r="78" spans="1:122" x14ac:dyDescent="0.35">
       <c r="A78" t="s">
         <v>106</v>
       </c>
@@ -23830,31 +23875,31 @@
       <c r="CB78" t="s">
         <v>25</v>
       </c>
-      <c r="DL78">
+      <c r="DM78">
         <f t="shared" si="9"/>
         <v>1</v>
       </c>
-      <c r="DM78" s="18">
+      <c r="DN78" s="18">
         <f t="shared" si="10"/>
         <v>5</v>
       </c>
-      <c r="DN78" t="str">
+      <c r="DO78" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
-      <c r="DO78">
+      <c r="DP78">
         <v>0</v>
       </c>
-      <c r="DP78">
+      <c r="DQ78">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="DQ78">
+      <c r="DR78">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
     </row>
-    <row r="79" spans="1:121" x14ac:dyDescent="0.35">
+    <row r="79" spans="1:122" x14ac:dyDescent="0.35">
       <c r="A79" t="s">
         <v>108</v>
       </c>
@@ -24101,31 +24146,34 @@
       <c r="DJ79">
         <v>6.5</v>
       </c>
-      <c r="DL79">
+      <c r="DK79">
+        <v>6.5</v>
+      </c>
+      <c r="DM79">
         <f t="shared" si="9"/>
         <v>2</v>
       </c>
-      <c r="DM79" s="18">
+      <c r="DN79" s="18">
         <f t="shared" si="10"/>
         <v>5.75</v>
       </c>
-      <c r="DN79">
+      <c r="DO79">
         <f t="shared" si="11"/>
         <v>0.35355339059327379</v>
       </c>
-      <c r="DO79">
+      <c r="DP79">
         <v>0</v>
       </c>
-      <c r="DP79">
+      <c r="DQ79">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="DQ79">
+      <c r="DR79">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
     </row>
-    <row r="80" spans="1:121" x14ac:dyDescent="0.35">
+    <row r="80" spans="1:122" x14ac:dyDescent="0.35">
       <c r="A80" t="s">
         <v>116</v>
       </c>
@@ -24366,31 +24414,31 @@
       <c r="CB80" t="s">
         <v>25</v>
       </c>
-      <c r="DL80">
+      <c r="DM80">
         <f t="shared" si="9"/>
         <v>1</v>
       </c>
-      <c r="DM80" s="18">
+      <c r="DN80" s="18">
         <f t="shared" si="10"/>
         <v>2</v>
       </c>
-      <c r="DN80" t="str">
+      <c r="DO80" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
-      <c r="DO80">
+      <c r="DP80">
         <v>0</v>
       </c>
-      <c r="DP80">
+      <c r="DQ80">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="DQ80">
+      <c r="DR80">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
     </row>
-    <row r="81" spans="1:121" x14ac:dyDescent="0.35">
+    <row r="81" spans="1:122" x14ac:dyDescent="0.35">
       <c r="A81" t="s">
         <v>117</v>
       </c>
@@ -24631,31 +24679,31 @@
       <c r="CB81" t="s">
         <v>25</v>
       </c>
-      <c r="DL81">
+      <c r="DM81">
         <f t="shared" si="9"/>
         <v>1</v>
       </c>
-      <c r="DM81" s="18">
+      <c r="DN81" s="18">
         <f t="shared" si="10"/>
         <v>2.5</v>
       </c>
-      <c r="DN81" t="str">
+      <c r="DO81" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
-      <c r="DO81">
+      <c r="DP81">
         <v>0</v>
       </c>
-      <c r="DP81">
+      <c r="DQ81">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="DQ81">
+      <c r="DR81">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
     </row>
-    <row r="82" spans="1:121" x14ac:dyDescent="0.35">
+    <row r="82" spans="1:122" x14ac:dyDescent="0.35">
       <c r="A82" t="s">
         <v>125</v>
       </c>
@@ -24896,31 +24944,31 @@
       <c r="CB82" t="s">
         <v>25</v>
       </c>
-      <c r="DL82">
+      <c r="DM82">
         <f t="shared" si="9"/>
         <v>1</v>
       </c>
-      <c r="DM82" s="18">
+      <c r="DN82" s="18">
         <f t="shared" si="10"/>
         <v>7</v>
       </c>
-      <c r="DN82" t="str">
+      <c r="DO82" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
-      <c r="DO82">
+      <c r="DP82">
         <v>0</v>
       </c>
-      <c r="DP82">
+      <c r="DQ82">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="DQ82">
+      <c r="DR82">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
     </row>
-    <row r="83" spans="1:121" x14ac:dyDescent="0.35">
+    <row r="83" spans="1:122" x14ac:dyDescent="0.35">
       <c r="A83" t="s">
         <v>126</v>
       </c>
@@ -25161,31 +25209,31 @@
       <c r="CB83" t="s">
         <v>25</v>
       </c>
-      <c r="DL83">
+      <c r="DM83">
         <f t="shared" si="9"/>
         <v>1</v>
       </c>
-      <c r="DM83" s="18">
+      <c r="DN83" s="18">
         <f t="shared" si="10"/>
         <v>5.5</v>
       </c>
-      <c r="DN83" t="str">
+      <c r="DO83" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
-      <c r="DO83">
+      <c r="DP83">
         <v>0</v>
       </c>
-      <c r="DP83">
+      <c r="DQ83">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="DQ83">
+      <c r="DR83">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
     </row>
-    <row r="84" spans="1:121" x14ac:dyDescent="0.35">
+    <row r="84" spans="1:122" x14ac:dyDescent="0.35">
       <c r="A84" t="s">
         <v>128</v>
       </c>
@@ -25426,31 +25474,31 @@
       <c r="CB84" t="s">
         <v>25</v>
       </c>
-      <c r="DL84">
+      <c r="DM84">
         <f t="shared" si="9"/>
         <v>1</v>
       </c>
-      <c r="DM84" s="18">
+      <c r="DN84" s="18">
         <f t="shared" si="10"/>
         <v>5</v>
       </c>
-      <c r="DN84" t="str">
+      <c r="DO84" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
-      <c r="DO84">
+      <c r="DP84">
         <v>0</v>
       </c>
-      <c r="DP84">
+      <c r="DQ84">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="DQ84">
+      <c r="DR84">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
     </row>
-    <row r="85" spans="1:121" x14ac:dyDescent="0.35">
+    <row r="85" spans="1:122" x14ac:dyDescent="0.35">
       <c r="A85" t="s">
         <v>132</v>
       </c>
@@ -25691,31 +25739,31 @@
       <c r="CB85" t="s">
         <v>25</v>
       </c>
-      <c r="DL85">
+      <c r="DM85">
         <f t="shared" si="9"/>
         <v>1</v>
       </c>
-      <c r="DM85" s="18">
+      <c r="DN85" s="18">
         <f t="shared" si="10"/>
         <v>5.5</v>
       </c>
-      <c r="DN85" t="str">
+      <c r="DO85" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
-      <c r="DO85">
+      <c r="DP85">
         <v>0</v>
       </c>
-      <c r="DP85">
+      <c r="DQ85">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="DQ85">
+      <c r="DR85">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
     </row>
-    <row r="86" spans="1:121" x14ac:dyDescent="0.35">
+    <row r="86" spans="1:122" x14ac:dyDescent="0.35">
       <c r="A86" t="s">
         <v>133</v>
       </c>
@@ -25956,31 +26004,31 @@
       <c r="CB86" t="s">
         <v>25</v>
       </c>
-      <c r="DL86">
+      <c r="DM86">
         <f t="shared" si="9"/>
         <v>1</v>
       </c>
-      <c r="DM86" s="18">
+      <c r="DN86" s="18">
         <f t="shared" si="10"/>
         <v>5.5</v>
       </c>
-      <c r="DN86" t="str">
+      <c r="DO86" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
-      <c r="DO86">
+      <c r="DP86">
         <v>0</v>
       </c>
-      <c r="DP86">
+      <c r="DQ86">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="DQ86">
+      <c r="DR86">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
     </row>
-    <row r="87" spans="1:121" x14ac:dyDescent="0.35">
+    <row r="87" spans="1:122" x14ac:dyDescent="0.35">
       <c r="A87" t="s">
         <v>140</v>
       </c>
@@ -26224,31 +26272,31 @@
       <c r="CH87">
         <v>7.5</v>
       </c>
-      <c r="DL87">
+      <c r="DM87">
         <f t="shared" si="9"/>
         <v>1</v>
       </c>
-      <c r="DM87" s="18">
+      <c r="DN87" s="18">
         <f t="shared" si="10"/>
         <v>7.5</v>
       </c>
-      <c r="DN87" t="str">
+      <c r="DO87" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
-      <c r="DO87">
+      <c r="DP87">
         <v>0</v>
       </c>
-      <c r="DP87">
+      <c r="DQ87">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="DQ87">
+      <c r="DR87">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
     </row>
-    <row r="88" spans="1:121" x14ac:dyDescent="0.35">
+    <row r="88" spans="1:122" x14ac:dyDescent="0.35">
       <c r="A88" t="s">
         <v>142</v>
       </c>
@@ -26492,93 +26540,93 @@
       <c r="CI88">
         <v>7</v>
       </c>
-      <c r="DL88">
+      <c r="DM88">
         <f t="shared" si="9"/>
         <v>1</v>
       </c>
-      <c r="DM88" s="18">
+      <c r="DN88" s="18">
         <f t="shared" si="10"/>
         <v>7</v>
       </c>
-      <c r="DN88" t="str">
+      <c r="DO88" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
-      <c r="DO88">
+      <c r="DP88">
         <v>0</v>
       </c>
-      <c r="DP88">
+      <c r="DQ88">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="DQ88">
+      <c r="DR88">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
     </row>
-    <row r="89" spans="1:121" x14ac:dyDescent="0.35">
+    <row r="89" spans="1:122" x14ac:dyDescent="0.35">
       <c r="A89" t="s">
         <v>144</v>
       </c>
       <c r="CP89">
         <v>6.5</v>
       </c>
-      <c r="DL89">
+      <c r="DM89">
         <f t="shared" si="9"/>
         <v>1</v>
       </c>
-      <c r="DM89" s="18">
+      <c r="DN89" s="18">
         <f t="shared" si="10"/>
         <v>6.5</v>
       </c>
-      <c r="DN89" t="str">
+      <c r="DO89" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
-      <c r="DO89">
+      <c r="DP89">
         <v>0</v>
       </c>
-      <c r="DP89">
+      <c r="DQ89">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="DQ89">
+      <c r="DR89">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
     </row>
-    <row r="90" spans="1:121" x14ac:dyDescent="0.35">
+    <row r="90" spans="1:122" x14ac:dyDescent="0.35">
       <c r="A90" t="s">
         <v>145</v>
       </c>
       <c r="CQ90">
         <v>6.5</v>
       </c>
-      <c r="DL90">
+      <c r="DM90">
         <f t="shared" si="9"/>
         <v>1</v>
       </c>
-      <c r="DM90" s="18">
+      <c r="DN90" s="18">
         <f t="shared" si="10"/>
         <v>6.5</v>
       </c>
-      <c r="DN90" t="str">
+      <c r="DO90" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
-      <c r="DO90">
-        <v>1</v>
-      </c>
       <c r="DP90">
-        <f t="shared" ref="DP90:DP102" si="12">COUNT(DF90:DH90)</f>
+        <v>1</v>
+      </c>
+      <c r="DQ90">
+        <f t="shared" ref="DQ90:DQ102" si="12">COUNT(DF90:DH90)</f>
         <v>0</v>
       </c>
-      <c r="DQ90">
-        <f t="shared" ref="DQ90:DQ102" si="13">IF(DO90=0,DP90,0)</f>
+      <c r="DR90">
+        <f t="shared" ref="DR90:DR102" si="13">IF(DP90=0,DQ90,0)</f>
         <v>0</v>
       </c>
     </row>
-    <row r="91" spans="1:121" x14ac:dyDescent="0.35">
+    <row r="91" spans="1:122" x14ac:dyDescent="0.35">
       <c r="A91" t="s">
         <v>152</v>
       </c>
@@ -26591,31 +26639,31 @@
       <c r="DI91">
         <v>6</v>
       </c>
-      <c r="DL91">
+      <c r="DM91">
         <f t="shared" si="9"/>
         <v>3</v>
       </c>
-      <c r="DM91" s="18">
+      <c r="DN91" s="18">
         <f t="shared" si="10"/>
         <v>6</v>
       </c>
-      <c r="DN91">
+      <c r="DO91">
         <f t="shared" si="11"/>
         <v>0</v>
       </c>
-      <c r="DO91">
-        <v>1</v>
-      </c>
       <c r="DP91">
+        <v>1</v>
+      </c>
+      <c r="DQ91">
         <f t="shared" si="12"/>
         <v>1</v>
       </c>
-      <c r="DQ91">
+      <c r="DR91">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
     </row>
-    <row r="92" spans="1:121" x14ac:dyDescent="0.35">
+    <row r="92" spans="1:122" x14ac:dyDescent="0.35">
       <c r="A92" t="s">
         <v>165</v>
       </c>
@@ -26625,186 +26673,189 @@
       <c r="DH92">
         <v>6</v>
       </c>
-      <c r="DL92">
+      <c r="DM92">
         <f t="shared" si="9"/>
         <v>2</v>
       </c>
-      <c r="DM92" s="18">
+      <c r="DN92" s="18">
         <f t="shared" si="10"/>
         <v>6</v>
       </c>
-      <c r="DN92">
+      <c r="DO92">
         <f t="shared" si="11"/>
         <v>0</v>
       </c>
-      <c r="DO92">
-        <v>1</v>
-      </c>
       <c r="DP92">
+        <v>1</v>
+      </c>
+      <c r="DQ92">
         <f t="shared" si="12"/>
         <v>1</v>
       </c>
-      <c r="DQ92">
+      <c r="DR92">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
     </row>
-    <row r="93" spans="1:121" x14ac:dyDescent="0.35">
+    <row r="93" spans="1:122" x14ac:dyDescent="0.35">
       <c r="A93" t="s">
         <v>159</v>
       </c>
       <c r="DF93">
         <v>5.5</v>
       </c>
-      <c r="DL93">
+      <c r="DM93">
         <f t="shared" si="9"/>
         <v>1</v>
       </c>
-      <c r="DM93" s="18">
+      <c r="DN93" s="18">
         <f t="shared" si="10"/>
         <v>5.5</v>
       </c>
-      <c r="DN93" t="str">
+      <c r="DO93" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
-      <c r="DO93">
-        <v>1</v>
-      </c>
       <c r="DP93">
+        <v>1</v>
+      </c>
+      <c r="DQ93">
         <f t="shared" si="12"/>
         <v>1</v>
       </c>
-      <c r="DQ93">
+      <c r="DR93">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
     </row>
-    <row r="94" spans="1:121" x14ac:dyDescent="0.35">
+    <row r="94" spans="1:122" x14ac:dyDescent="0.35">
       <c r="A94" t="s">
         <v>169</v>
       </c>
       <c r="DF94">
         <v>6</v>
       </c>
-      <c r="DL94">
+      <c r="DM94">
         <f t="shared" si="9"/>
         <v>1</v>
       </c>
-      <c r="DM94" s="18">
+      <c r="DN94" s="18">
         <f t="shared" si="10"/>
         <v>6</v>
       </c>
-      <c r="DN94" t="str">
+      <c r="DO94" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
-      <c r="DO94">
-        <v>1</v>
-      </c>
       <c r="DP94">
+        <v>1</v>
+      </c>
+      <c r="DQ94">
         <f t="shared" si="12"/>
         <v>1</v>
       </c>
-      <c r="DQ94">
+      <c r="DR94">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
     </row>
-    <row r="95" spans="1:121" x14ac:dyDescent="0.35">
+    <row r="95" spans="1:122" x14ac:dyDescent="0.35">
       <c r="A95" t="s">
         <v>160</v>
       </c>
       <c r="DG95">
         <v>6</v>
       </c>
-      <c r="DL95">
+      <c r="DK95">
+        <v>6</v>
+      </c>
+      <c r="DM95">
         <f t="shared" si="9"/>
         <v>1</v>
       </c>
-      <c r="DM95" s="18">
+      <c r="DN95" s="18">
         <f t="shared" si="10"/>
         <v>6</v>
       </c>
-      <c r="DN95" t="str">
+      <c r="DO95" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
-      <c r="DO95">
-        <v>1</v>
-      </c>
       <c r="DP95">
+        <v>1</v>
+      </c>
+      <c r="DQ95">
         <f t="shared" si="12"/>
         <v>1</v>
       </c>
-      <c r="DQ95">
+      <c r="DR95">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
     </row>
-    <row r="96" spans="1:121" x14ac:dyDescent="0.35">
+    <row r="96" spans="1:122" x14ac:dyDescent="0.35">
       <c r="A96" t="s">
         <v>161</v>
       </c>
       <c r="DG96">
         <v>5.5</v>
       </c>
-      <c r="DL96">
+      <c r="DM96">
         <f t="shared" si="9"/>
         <v>1</v>
       </c>
-      <c r="DM96" s="18">
+      <c r="DN96" s="18">
         <f t="shared" si="10"/>
         <v>5.5</v>
       </c>
-      <c r="DN96" t="str">
+      <c r="DO96" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
-      <c r="DO96">
-        <v>1</v>
-      </c>
       <c r="DP96">
+        <v>1</v>
+      </c>
+      <c r="DQ96">
         <f t="shared" si="12"/>
         <v>1</v>
       </c>
-      <c r="DQ96">
+      <c r="DR96">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
     </row>
-    <row r="97" spans="1:121" x14ac:dyDescent="0.35">
+    <row r="97" spans="1:122" x14ac:dyDescent="0.35">
       <c r="A97" t="s">
         <v>162</v>
       </c>
       <c r="DG97">
         <v>6</v>
       </c>
-      <c r="DL97">
+      <c r="DM97">
         <f t="shared" si="9"/>
         <v>1</v>
       </c>
-      <c r="DM97" s="18">
+      <c r="DN97" s="18">
         <f t="shared" si="10"/>
         <v>6</v>
       </c>
-      <c r="DN97" t="str">
+      <c r="DO97" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
-      <c r="DO97">
-        <v>1</v>
-      </c>
       <c r="DP97">
+        <v>1</v>
+      </c>
+      <c r="DQ97">
         <f t="shared" si="12"/>
         <v>1</v>
       </c>
-      <c r="DQ97">
+      <c r="DR97">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
     </row>
-    <row r="98" spans="1:121" x14ac:dyDescent="0.35">
+    <row r="98" spans="1:122" x14ac:dyDescent="0.35">
       <c r="A98" t="s">
         <v>171</v>
       </c>
@@ -26814,93 +26865,93 @@
       <c r="DI98">
         <v>6</v>
       </c>
-      <c r="DL98">
+      <c r="DM98">
         <f t="shared" si="9"/>
         <v>2</v>
       </c>
-      <c r="DM98" s="18">
+      <c r="DN98" s="18">
         <f t="shared" si="10"/>
         <v>5.75</v>
       </c>
-      <c r="DN98">
+      <c r="DO98">
         <f t="shared" si="11"/>
         <v>0.35355339059327379</v>
       </c>
-      <c r="DO98">
-        <v>1</v>
-      </c>
       <c r="DP98">
+        <v>1</v>
+      </c>
+      <c r="DQ98">
         <f t="shared" si="12"/>
         <v>1</v>
       </c>
-      <c r="DQ98">
+      <c r="DR98">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
     </row>
-    <row r="99" spans="1:121" x14ac:dyDescent="0.35">
+    <row r="99" spans="1:122" x14ac:dyDescent="0.35">
       <c r="A99" t="s">
         <v>153</v>
       </c>
       <c r="DB99">
         <v>5.5</v>
       </c>
-      <c r="DL99">
+      <c r="DM99">
         <f t="shared" si="9"/>
         <v>1</v>
       </c>
-      <c r="DM99" s="18">
+      <c r="DN99" s="18">
         <f t="shared" si="10"/>
         <v>5.5</v>
       </c>
-      <c r="DN99" t="str">
+      <c r="DO99" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
-      <c r="DO99">
-        <v>1</v>
-      </c>
       <c r="DP99">
+        <v>1</v>
+      </c>
+      <c r="DQ99">
         <f t="shared" si="12"/>
         <v>0</v>
       </c>
-      <c r="DQ99">
+      <c r="DR99">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
     </row>
-    <row r="100" spans="1:121" x14ac:dyDescent="0.35">
+    <row r="100" spans="1:122" x14ac:dyDescent="0.35">
       <c r="A100" t="s">
         <v>154</v>
       </c>
       <c r="DB100">
         <v>5.5</v>
       </c>
-      <c r="DL100">
+      <c r="DM100">
         <f t="shared" si="9"/>
         <v>1</v>
       </c>
-      <c r="DM100" s="18">
+      <c r="DN100" s="18">
         <f t="shared" si="10"/>
         <v>5.5</v>
       </c>
-      <c r="DN100" t="str">
+      <c r="DO100" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
-      <c r="DO100">
-        <v>1</v>
-      </c>
       <c r="DP100">
+        <v>1</v>
+      </c>
+      <c r="DQ100">
         <f t="shared" si="12"/>
         <v>0</v>
       </c>
-      <c r="DQ100">
+      <c r="DR100">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
     </row>
-    <row r="101" spans="1:121" x14ac:dyDescent="0.35">
+    <row r="101" spans="1:122" x14ac:dyDescent="0.35">
       <c r="A101" t="s">
         <v>149</v>
       </c>
@@ -26928,76 +26979,136 @@
       <c r="DI101">
         <v>5.5</v>
       </c>
-      <c r="DL101">
+      <c r="DK101">
+        <v>6</v>
+      </c>
+      <c r="DM101">
         <f t="shared" si="9"/>
         <v>8</v>
       </c>
-      <c r="DM101" s="18">
+      <c r="DN101" s="18">
         <f t="shared" si="10"/>
         <v>6.4375</v>
       </c>
-      <c r="DN101">
+      <c r="DO101">
         <f t="shared" si="11"/>
         <v>0.77632375426014844</v>
       </c>
-      <c r="DO101">
-        <v>1</v>
-      </c>
       <c r="DP101">
+        <v>1</v>
+      </c>
+      <c r="DQ101">
         <f t="shared" si="12"/>
         <v>2</v>
       </c>
-      <c r="DQ101">
+      <c r="DR101">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
     </row>
-    <row r="102" spans="1:121" x14ac:dyDescent="0.35">
+    <row r="102" spans="1:122" x14ac:dyDescent="0.35">
       <c r="A102" t="s">
         <v>155</v>
       </c>
       <c r="DC102">
         <v>6</v>
       </c>
-      <c r="DL102">
+      <c r="DM102">
         <f t="shared" si="9"/>
         <v>1</v>
       </c>
-      <c r="DM102" s="18">
+      <c r="DN102" s="18">
         <f t="shared" si="10"/>
         <v>6</v>
       </c>
-      <c r="DN102" t="str">
+      <c r="DO102" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
-      <c r="DO102">
-        <v>1</v>
-      </c>
       <c r="DP102">
+        <v>1</v>
+      </c>
+      <c r="DQ102">
         <f t="shared" si="12"/>
         <v>0</v>
       </c>
-      <c r="DQ102">
+      <c r="DR102">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
     </row>
-    <row r="103" spans="1:121" x14ac:dyDescent="0.35">
+    <row r="103" spans="1:122" x14ac:dyDescent="0.35">
       <c r="A103" t="s">
         <v>172</v>
       </c>
       <c r="DJ103">
         <v>6</v>
       </c>
+      <c r="DK103">
+        <v>6</v>
+      </c>
+      <c r="DM103">
+        <f t="shared" ref="DM103:DM104" si="14">COUNT(B103:DI103)</f>
+        <v>0</v>
+      </c>
+      <c r="DN103" s="18" t="e">
+        <f t="shared" ref="DN103:DN104" si="15">AVERAGE(B103:DI103)</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="DO103" t="str">
+        <f t="shared" ref="DO103:DO104" si="16">IF(DM103&gt;1,_xlfn.STDEV.S(B103:DI103),"")</f>
+        <v/>
+      </c>
+      <c r="DP103">
+        <v>1</v>
+      </c>
+      <c r="DQ103">
+        <f t="shared" ref="DQ103:DQ104" si="17">COUNT(DF103:DH103)</f>
+        <v>0</v>
+      </c>
+      <c r="DR103">
+        <f t="shared" ref="DR103:DR104" si="18">IF(DP103=0,DQ103,0)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="104" spans="1:122" x14ac:dyDescent="0.35">
+      <c r="A104" t="s">
+        <v>173</v>
+      </c>
+      <c r="DK104">
+        <v>6.5</v>
+      </c>
+      <c r="DM104">
+        <f t="shared" si="14"/>
+        <v>0</v>
+      </c>
+      <c r="DN104" s="18" t="e">
+        <f t="shared" si="15"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="DO104" t="str">
+        <f t="shared" si="16"/>
+        <v/>
+      </c>
+      <c r="DP104">
+        <v>1</v>
+      </c>
+      <c r="DQ104">
+        <f t="shared" si="17"/>
+        <v>0</v>
+      </c>
+      <c r="DR104">
+        <f t="shared" si="18"/>
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:DQ83" xr:uid="{B9A4D56B-02EF-476F-9B0E-F093A198C591}">
-    <sortState ref="A2:DQ102">
-      <sortCondition descending="1" ref="DL1:DL83"/>
+  <autoFilter ref="A1:DR83" xr:uid="{B9A4D56B-02EF-476F-9B0E-F093A198C591}">
+    <sortState ref="A2:DR102">
+      <sortCondition descending="1" ref="DM1:DM83"/>
     </sortState>
   </autoFilter>
-  <conditionalFormatting sqref="DL2:DL102">
+  <conditionalFormatting sqref="DM2:DM104">
     <cfRule type="colorScale" priority="98">
       <colorScale>
         <cfvo type="min"/>
@@ -27009,7 +27120,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="DN2:DN102">
+  <conditionalFormatting sqref="DO2:DO104">
     <cfRule type="colorScale" priority="96">
       <colorScale>
         <cfvo type="min"/>
@@ -27021,7 +27132,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="DL2:DL102">
+  <conditionalFormatting sqref="DM2:DM104">
     <cfRule type="colorScale" priority="91">
       <colorScale>
         <cfvo type="min"/>
@@ -27033,7 +27144,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="DM2:DM102">
+  <conditionalFormatting sqref="DN2:DN104">
     <cfRule type="colorScale" priority="90">
       <colorScale>
         <cfvo type="min"/>
@@ -27045,7 +27156,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="DM2:DM102">
+  <conditionalFormatting sqref="DN2:DN104">
     <cfRule type="colorScale" priority="88">
       <colorScale>
         <cfvo type="min"/>
@@ -27057,7 +27168,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="DL2:DL102">
+  <conditionalFormatting sqref="DM2:DM104">
     <cfRule type="colorScale" priority="55">
       <colorScale>
         <cfvo type="min"/>
@@ -27069,7 +27180,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="DM2:DM102">
+  <conditionalFormatting sqref="DN2:DN104">
     <cfRule type="colorScale" priority="54">
       <colorScale>
         <cfvo type="min"/>
@@ -27081,7 +27192,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="DK2:DK79">
+  <conditionalFormatting sqref="DL2:DL79">
     <cfRule type="colorScale" priority="16">
       <colorScale>
         <cfvo type="min"/>
@@ -27093,7 +27204,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="DK2:DK67">
+  <conditionalFormatting sqref="DL2:DL67">
     <cfRule type="colorScale" priority="139">
       <colorScale>
         <cfvo type="min"/>
@@ -27105,7 +27216,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="DK2:DK67">
+  <conditionalFormatting sqref="DL2:DL67">
     <cfRule type="colorScale" priority="141">
       <colorScale>
         <cfvo type="min"/>
@@ -27117,7 +27228,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="DK2:DK67">
+  <conditionalFormatting sqref="DL2:DL67">
     <cfRule type="colorScale" priority="143">
       <colorScale>
         <cfvo type="min"/>
@@ -27129,7 +27240,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B2:DJ83">
+  <conditionalFormatting sqref="B2:DK83">
     <cfRule type="colorScale" priority="15">
       <colorScale>
         <cfvo type="min"/>
@@ -33248,7 +33359,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:X330"/>
+  <dimension ref="A1:X333"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="10.54296875" bestFit="1" customWidth="1"/>
@@ -49550,6 +49661,156 @@
       </c>
       <c r="P330" s="8"/>
     </row>
+    <row r="331" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="A331" s="1">
+        <v>46281</v>
+      </c>
+      <c r="B331" s="32">
+        <v>4</v>
+      </c>
+      <c r="C331" s="8" t="s">
+        <v>81</v>
+      </c>
+      <c r="D331" s="8" t="s">
+        <v>170</v>
+      </c>
+      <c r="E331" s="8" t="s">
+        <v>97</v>
+      </c>
+      <c r="F331" s="8" t="s">
+        <v>53</v>
+      </c>
+      <c r="G331" s="8" t="s">
+        <v>5</v>
+      </c>
+      <c r="H331" s="8" t="s">
+        <v>173</v>
+      </c>
+      <c r="I331" s="9">
+        <v>2</v>
+      </c>
+      <c r="J331" s="10">
+        <v>4</v>
+      </c>
+      <c r="K331" s="10" t="s">
+        <v>55</v>
+      </c>
+      <c r="L331" s="10" t="s">
+        <v>9</v>
+      </c>
+      <c r="M331" s="10" t="s">
+        <v>18</v>
+      </c>
+      <c r="N331" s="10" t="s">
+        <v>151</v>
+      </c>
+      <c r="O331" s="10" t="s">
+        <v>43</v>
+      </c>
+      <c r="P331" s="10" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="332" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="A332" s="1">
+        <v>46281</v>
+      </c>
+      <c r="B332" s="32">
+        <v>3</v>
+      </c>
+      <c r="C332" s="10" t="s">
+        <v>55</v>
+      </c>
+      <c r="D332" s="10" t="s">
+        <v>9</v>
+      </c>
+      <c r="E332" s="10" t="s">
+        <v>18</v>
+      </c>
+      <c r="F332" s="10" t="s">
+        <v>151</v>
+      </c>
+      <c r="G332" s="10" t="s">
+        <v>43</v>
+      </c>
+      <c r="H332" s="10" t="s">
+        <v>108</v>
+      </c>
+      <c r="I332" s="11">
+        <v>4</v>
+      </c>
+      <c r="J332" s="2">
+        <v>0</v>
+      </c>
+      <c r="K332" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="L332" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="M332" s="31" t="s">
+        <v>80</v>
+      </c>
+      <c r="N332" s="31" t="s">
+        <v>149</v>
+      </c>
+      <c r="O332" s="31" t="s">
+        <v>160</v>
+      </c>
+      <c r="P332" s="2" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="333" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="A333" s="1">
+        <v>46281</v>
+      </c>
+      <c r="B333" s="32">
+        <v>3</v>
+      </c>
+      <c r="C333" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="D333" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="E333" s="31" t="s">
+        <v>80</v>
+      </c>
+      <c r="F333" s="31" t="s">
+        <v>149</v>
+      </c>
+      <c r="G333" s="31" t="s">
+        <v>160</v>
+      </c>
+      <c r="H333" s="2" t="s">
+        <v>172</v>
+      </c>
+      <c r="I333" s="5">
+        <v>1</v>
+      </c>
+      <c r="J333" s="8">
+        <v>4</v>
+      </c>
+      <c r="K333" s="8" t="s">
+        <v>81</v>
+      </c>
+      <c r="L333" s="8" t="s">
+        <v>170</v>
+      </c>
+      <c r="M333" s="8" t="s">
+        <v>97</v>
+      </c>
+      <c r="N333" s="8" t="s">
+        <v>53</v>
+      </c>
+      <c r="O333" s="8" t="s">
+        <v>5</v>
+      </c>
+      <c r="P333" s="8" t="s">
+        <v>173</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -49557,7 +49818,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{77DDCCA6-42DC-4211-A42F-70F3625FA6AA}">
-  <dimension ref="A1:CQ103"/>
+  <dimension ref="A1:CR104"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="16.81640625" bestFit="1" customWidth="1"/>
@@ -49569,10 +49830,10 @@
     <col min="13" max="13" width="9.54296875" bestFit="1" customWidth="1"/>
     <col min="14" max="92" width="10.453125" bestFit="1" customWidth="1"/>
     <col min="93" max="93" width="10.453125" customWidth="1"/>
-    <col min="94" max="95" width="10.453125" bestFit="1" customWidth="1"/>
+    <col min="94" max="96" width="10.453125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:95" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:96" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -49858,8 +50119,11 @@
       <c r="CQ1" s="1">
         <v>46274</v>
       </c>
-    </row>
-    <row r="2" spans="1:95" x14ac:dyDescent="0.35">
+      <c r="CR1" s="1">
+        <v>46281</v>
+      </c>
+    </row>
+    <row r="2" spans="1:96" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>2</v>
       </c>
@@ -49936,7 +50200,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:95" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:96" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>23</v>
       </c>
@@ -49944,7 +50208,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="4" spans="1:95" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:96" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>100</v>
       </c>
@@ -49982,7 +50246,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="5" spans="1:95" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:96" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>149</v>
       </c>
@@ -50004,13 +50268,16 @@
       <c r="CM5">
         <v>4</v>
       </c>
-    </row>
-    <row r="6" spans="1:95" hidden="1" x14ac:dyDescent="0.35">
+      <c r="CR5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:96" hidden="1" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>116</v>
       </c>
     </row>
-    <row r="7" spans="1:95" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:96" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>76</v>
       </c>
@@ -50018,7 +50285,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="8" spans="1:95" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:96" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>115</v>
       </c>
@@ -50035,7 +50302,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="9" spans="1:95" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:96" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>151</v>
       </c>
@@ -50082,7 +50349,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="10" spans="1:95" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:96" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
         <v>7</v>
       </c>
@@ -50090,7 +50357,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="11" spans="1:95" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:96" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
         <v>107</v>
       </c>
@@ -50098,17 +50365,17 @@
         <v>1</v>
       </c>
     </row>
-    <row r="12" spans="1:95" hidden="1" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:96" hidden="1" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
         <v>101</v>
       </c>
     </row>
-    <row r="13" spans="1:95" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:96" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
         <v>47</v>
       </c>
     </row>
-    <row r="14" spans="1:95" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:96" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
         <v>145</v>
       </c>
@@ -50116,7 +50383,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="15" spans="1:95" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:96" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
         <v>148</v>
       </c>
@@ -50139,12 +50406,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="16" spans="1:95" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:96" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
         <v>133</v>
       </c>
     </row>
-    <row r="17" spans="1:95" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:96" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
         <v>113</v>
       </c>
@@ -50152,12 +50419,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="18" spans="1:95" hidden="1" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:96" hidden="1" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="19" spans="1:95" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:96" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
         <v>24</v>
       </c>
@@ -50207,7 +50474,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="20" spans="1:95" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:96" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
         <v>13</v>
       </c>
@@ -50248,7 +50515,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="21" spans="1:95" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:96" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
         <v>129</v>
       </c>
@@ -50262,7 +50529,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="22" spans="1:95" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:96" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
         <v>53</v>
       </c>
@@ -50278,8 +50545,11 @@
       <c r="CF22">
         <v>1</v>
       </c>
-    </row>
-    <row r="23" spans="1:95" x14ac:dyDescent="0.35">
+      <c r="CR22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="23" spans="1:96" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
         <v>65</v>
       </c>
@@ -50344,7 +50614,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="24" spans="1:95" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:96" x14ac:dyDescent="0.35">
       <c r="A24" t="s">
         <v>83</v>
       </c>
@@ -50469,7 +50739,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="25" spans="1:95" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:96" x14ac:dyDescent="0.35">
       <c r="A25" t="s">
         <v>142</v>
       </c>
@@ -50477,7 +50747,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="26" spans="1:95" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:96" x14ac:dyDescent="0.35">
       <c r="A26" t="s">
         <v>14</v>
       </c>
@@ -50554,12 +50824,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="27" spans="1:95" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:96" x14ac:dyDescent="0.35">
       <c r="A27" t="s">
         <v>161</v>
       </c>
     </row>
-    <row r="28" spans="1:95" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:96" x14ac:dyDescent="0.35">
       <c r="A28" t="s">
         <v>126</v>
       </c>
@@ -50567,7 +50837,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="29" spans="1:95" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:96" x14ac:dyDescent="0.35">
       <c r="A29" t="s">
         <v>6</v>
       </c>
@@ -50722,370 +50992,226 @@
         <v>2</v>
       </c>
     </row>
-    <row r="30" spans="1:95" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:96" x14ac:dyDescent="0.35">
       <c r="A30" t="s">
+        <v>173</v>
+      </c>
+      <c r="CR30">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="31" spans="1:96" x14ac:dyDescent="0.35">
+      <c r="A31" t="s">
         <v>97</v>
       </c>
-      <c r="T30">
+      <c r="T31">
         <v>4</v>
       </c>
-      <c r="AH30">
-        <v>1</v>
-      </c>
-      <c r="AK30">
-        <v>1</v>
-      </c>
-      <c r="BQ30">
-        <v>2</v>
-      </c>
-      <c r="BV30">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="31" spans="1:95" x14ac:dyDescent="0.35">
-      <c r="A31" t="s">
+      <c r="AH31">
+        <v>1</v>
+      </c>
+      <c r="AK31">
+        <v>1</v>
+      </c>
+      <c r="BQ31">
+        <v>2</v>
+      </c>
+      <c r="BV31">
+        <v>2</v>
+      </c>
+      <c r="CR31">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="32" spans="1:96" x14ac:dyDescent="0.35">
+      <c r="A32" t="s">
         <v>51</v>
       </c>
-      <c r="CC31">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="32" spans="1:95" x14ac:dyDescent="0.35">
-      <c r="A32" t="s">
-        <v>154</v>
+      <c r="CC32">
+        <v>1</v>
       </c>
     </row>
     <row r="33" spans="1:95" x14ac:dyDescent="0.35">
       <c r="A33" t="s">
-        <v>140</v>
-      </c>
-      <c r="BO33">
-        <v>3</v>
+        <v>154</v>
       </c>
     </row>
     <row r="34" spans="1:95" x14ac:dyDescent="0.35">
       <c r="A34" t="s">
-        <v>139</v>
+        <v>140</v>
+      </c>
+      <c r="BO34">
+        <v>3</v>
       </c>
     </row>
     <row r="35" spans="1:95" x14ac:dyDescent="0.35">
       <c r="A35" t="s">
-        <v>147</v>
-      </c>
-      <c r="CC35">
-        <v>1</v>
+        <v>139</v>
       </c>
     </row>
     <row r="36" spans="1:95" x14ac:dyDescent="0.35">
       <c r="A36" t="s">
-        <v>12</v>
-      </c>
-      <c r="N36">
-        <v>2</v>
-      </c>
-      <c r="U36">
-        <v>1</v>
-      </c>
-      <c r="AI36">
-        <v>1</v>
-      </c>
-      <c r="CH36">
-        <v>1</v>
-      </c>
-      <c r="CI36">
-        <v>2</v>
+        <v>147</v>
+      </c>
+      <c r="CC36">
+        <v>1</v>
       </c>
     </row>
     <row r="37" spans="1:95" x14ac:dyDescent="0.35">
       <c r="A37" t="s">
-        <v>4</v>
-      </c>
-      <c r="E37">
-        <v>1</v>
-      </c>
-      <c r="F37">
-        <v>3</v>
-      </c>
-      <c r="H37">
-        <v>1</v>
-      </c>
-      <c r="J37">
-        <v>1</v>
-      </c>
-      <c r="K37">
-        <v>3</v>
-      </c>
-      <c r="P37">
-        <v>3</v>
+        <v>12</v>
+      </c>
+      <c r="N37">
+        <v>2</v>
       </c>
       <c r="U37">
-        <v>3</v>
-      </c>
-      <c r="W37">
-        <v>1</v>
-      </c>
-      <c r="AD37">
-        <v>1</v>
-      </c>
-      <c r="AF37">
-        <v>1</v>
-      </c>
-      <c r="AH37">
         <v>1</v>
       </c>
       <c r="AI37">
         <v>1</v>
       </c>
-      <c r="AJ37">
-        <v>2</v>
-      </c>
-      <c r="AO37">
-        <v>2</v>
-      </c>
-      <c r="AP37">
-        <v>2</v>
-      </c>
-      <c r="AQ37">
-        <v>4</v>
-      </c>
-      <c r="AR37">
-        <v>2</v>
-      </c>
-      <c r="AT37">
-        <v>1</v>
-      </c>
-      <c r="AU37">
-        <v>2</v>
-      </c>
-      <c r="AV37">
-        <v>1</v>
-      </c>
-      <c r="AW37">
-        <v>1</v>
-      </c>
-      <c r="AX37">
-        <v>1</v>
-      </c>
-      <c r="AZ37">
-        <v>2</v>
-      </c>
-      <c r="BA37">
-        <v>2</v>
-      </c>
-      <c r="BB37">
-        <v>1</v>
-      </c>
-      <c r="BD37">
-        <v>2</v>
-      </c>
-      <c r="BE37">
-        <v>3</v>
-      </c>
-      <c r="BF37">
-        <v>1</v>
-      </c>
-      <c r="BG37">
-        <v>1</v>
-      </c>
-      <c r="BJ37">
-        <v>1</v>
-      </c>
-      <c r="BK37">
-        <v>1</v>
-      </c>
-      <c r="BL37">
-        <v>1</v>
-      </c>
-      <c r="BM37">
+      <c r="CH37">
+        <v>1</v>
+      </c>
+      <c r="CI37">
         <v>2</v>
       </c>
     </row>
     <row r="38" spans="1:95" x14ac:dyDescent="0.35">
       <c r="A38" t="s">
+        <v>4</v>
+      </c>
+      <c r="E38">
+        <v>1</v>
+      </c>
+      <c r="F38">
+        <v>3</v>
+      </c>
+      <c r="H38">
+        <v>1</v>
+      </c>
+      <c r="J38">
+        <v>1</v>
+      </c>
+      <c r="K38">
+        <v>3</v>
+      </c>
+      <c r="P38">
+        <v>3</v>
+      </c>
+      <c r="U38">
+        <v>3</v>
+      </c>
+      <c r="W38">
+        <v>1</v>
+      </c>
+      <c r="AD38">
+        <v>1</v>
+      </c>
+      <c r="AF38">
+        <v>1</v>
+      </c>
+      <c r="AH38">
+        <v>1</v>
+      </c>
+      <c r="AI38">
+        <v>1</v>
+      </c>
+      <c r="AJ38">
+        <v>2</v>
+      </c>
+      <c r="AO38">
+        <v>2</v>
+      </c>
+      <c r="AP38">
+        <v>2</v>
+      </c>
+      <c r="AQ38">
+        <v>4</v>
+      </c>
+      <c r="AR38">
+        <v>2</v>
+      </c>
+      <c r="AT38">
+        <v>1</v>
+      </c>
+      <c r="AU38">
+        <v>2</v>
+      </c>
+      <c r="AV38">
+        <v>1</v>
+      </c>
+      <c r="AW38">
+        <v>1</v>
+      </c>
+      <c r="AX38">
+        <v>1</v>
+      </c>
+      <c r="AZ38">
+        <v>2</v>
+      </c>
+      <c r="BA38">
+        <v>2</v>
+      </c>
+      <c r="BB38">
+        <v>1</v>
+      </c>
+      <c r="BD38">
+        <v>2</v>
+      </c>
+      <c r="BE38">
+        <v>3</v>
+      </c>
+      <c r="BF38">
+        <v>1</v>
+      </c>
+      <c r="BG38">
+        <v>1</v>
+      </c>
+      <c r="BJ38">
+        <v>1</v>
+      </c>
+      <c r="BK38">
+        <v>1</v>
+      </c>
+      <c r="BL38">
+        <v>1</v>
+      </c>
+      <c r="BM38">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="39" spans="1:95" x14ac:dyDescent="0.35">
+      <c r="A39" t="s">
         <v>112</v>
       </c>
-      <c r="AD38">
-        <v>2</v>
-      </c>
-      <c r="AM38">
-        <v>1</v>
-      </c>
-      <c r="AU38">
-        <v>1</v>
-      </c>
-      <c r="BF38">
+      <c r="AD39">
+        <v>2</v>
+      </c>
+      <c r="AM39">
+        <v>1</v>
+      </c>
+      <c r="AU39">
+        <v>1</v>
+      </c>
+      <c r="BF39">
         <v>3</v>
       </c>
     </row>
-    <row r="39" spans="1:95" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A39" t="s">
+    <row r="40" spans="1:95" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A40" t="s">
         <v>105</v>
       </c>
-      <c r="Z39">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="40" spans="1:95" x14ac:dyDescent="0.35">
-      <c r="A40" t="s">
-        <v>1</v>
-      </c>
-      <c r="B40">
-        <v>1</v>
-      </c>
-      <c r="C40">
-        <v>1</v>
-      </c>
-      <c r="D40">
-        <v>1</v>
-      </c>
-      <c r="E40">
-        <v>1</v>
-      </c>
-      <c r="F40">
-        <v>2</v>
-      </c>
-      <c r="I40">
-        <v>2</v>
-      </c>
-      <c r="J40">
-        <v>1</v>
-      </c>
-      <c r="K40">
-        <v>2</v>
-      </c>
-      <c r="L40">
-        <v>1</v>
-      </c>
-      <c r="M40">
-        <v>2</v>
-      </c>
-      <c r="N40">
-        <v>1</v>
-      </c>
-      <c r="O40">
-        <v>1</v>
-      </c>
-      <c r="P40">
-        <v>2</v>
-      </c>
-      <c r="R40">
-        <v>1</v>
-      </c>
-      <c r="T40">
-        <v>1</v>
-      </c>
-      <c r="U40">
-        <v>2</v>
-      </c>
-      <c r="Y40">
-        <v>2</v>
-      </c>
-      <c r="AB40">
-        <v>2</v>
-      </c>
-      <c r="AD40">
-        <v>1</v>
-      </c>
-      <c r="AH40">
-        <v>1</v>
-      </c>
-      <c r="AJ40">
-        <v>1</v>
-      </c>
-      <c r="AN40">
-        <v>2</v>
-      </c>
-      <c r="AO40">
-        <v>1</v>
-      </c>
-      <c r="AP40">
-        <v>2</v>
-      </c>
-      <c r="AQ40">
-        <v>1</v>
-      </c>
-      <c r="AS40">
-        <v>2</v>
-      </c>
-      <c r="AW40">
-        <v>1</v>
-      </c>
-      <c r="AX40">
-        <v>1</v>
-      </c>
-      <c r="AY40">
-        <v>2</v>
-      </c>
-      <c r="AZ40">
-        <v>2</v>
-      </c>
-      <c r="BA40">
-        <v>1</v>
-      </c>
-      <c r="BB40">
-        <v>2</v>
-      </c>
-      <c r="BC40">
-        <v>4</v>
-      </c>
-      <c r="BD40">
-        <v>1</v>
-      </c>
-      <c r="BE40">
-        <v>1</v>
-      </c>
-      <c r="BG40">
-        <v>2</v>
-      </c>
-      <c r="BH40">
-        <v>3</v>
-      </c>
-      <c r="BJ40">
-        <v>1</v>
-      </c>
-      <c r="BM40">
-        <v>3</v>
-      </c>
-      <c r="BN40">
-        <v>1</v>
-      </c>
-      <c r="BP40">
-        <v>1</v>
-      </c>
-      <c r="BR40">
-        <v>3</v>
-      </c>
-      <c r="BV40">
-        <v>1</v>
-      </c>
-      <c r="BW40">
-        <v>4</v>
-      </c>
-      <c r="BX40">
-        <v>2</v>
-      </c>
-      <c r="CB40">
-        <v>1</v>
-      </c>
-      <c r="CC40">
-        <v>1</v>
-      </c>
-      <c r="CJ40">
-        <v>2</v>
-      </c>
-      <c r="CK40">
-        <v>2</v>
-      </c>
-      <c r="CN40">
-        <v>1</v>
-      </c>
-      <c r="CQ40">
-        <v>2</v>
+      <c r="Z40">
+        <v>1</v>
       </c>
     </row>
     <row r="41" spans="1:95" x14ac:dyDescent="0.35">
       <c r="A41" t="s">
-        <v>9</v>
+        <v>1</v>
+      </c>
+      <c r="B41">
+        <v>1</v>
       </c>
       <c r="C41">
         <v>1</v>
@@ -51093,14 +51219,14 @@
       <c r="D41">
         <v>1</v>
       </c>
-      <c r="G41">
-        <v>2</v>
-      </c>
-      <c r="H41">
+      <c r="E41">
+        <v>1</v>
+      </c>
+      <c r="F41">
         <v>2</v>
       </c>
       <c r="I41">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J41">
         <v>1</v>
@@ -51109,567 +51235,705 @@
         <v>2</v>
       </c>
       <c r="L41">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="M41">
+        <v>2</v>
+      </c>
+      <c r="N41">
         <v>1</v>
       </c>
       <c r="O41">
+        <v>1</v>
+      </c>
+      <c r="P41">
+        <v>2</v>
+      </c>
+      <c r="R41">
+        <v>1</v>
+      </c>
+      <c r="T41">
+        <v>1</v>
+      </c>
+      <c r="U41">
+        <v>2</v>
+      </c>
+      <c r="Y41">
+        <v>2</v>
+      </c>
+      <c r="AB41">
+        <v>2</v>
+      </c>
+      <c r="AD41">
+        <v>1</v>
+      </c>
+      <c r="AH41">
+        <v>1</v>
+      </c>
+      <c r="AJ41">
+        <v>1</v>
+      </c>
+      <c r="AN41">
+        <v>2</v>
+      </c>
+      <c r="AO41">
+        <v>1</v>
+      </c>
+      <c r="AP41">
+        <v>2</v>
+      </c>
+      <c r="AQ41">
+        <v>1</v>
+      </c>
+      <c r="AS41">
+        <v>2</v>
+      </c>
+      <c r="AW41">
+        <v>1</v>
+      </c>
+      <c r="AX41">
+        <v>1</v>
+      </c>
+      <c r="AY41">
+        <v>2</v>
+      </c>
+      <c r="AZ41">
+        <v>2</v>
+      </c>
+      <c r="BA41">
+        <v>1</v>
+      </c>
+      <c r="BB41">
+        <v>2</v>
+      </c>
+      <c r="BC41">
         <v>4</v>
       </c>
-      <c r="P41">
-        <v>1</v>
-      </c>
-      <c r="Q41">
-        <v>2</v>
-      </c>
-      <c r="T41">
-        <v>6</v>
-      </c>
-      <c r="X41">
-        <v>2</v>
-      </c>
-      <c r="Y41">
-        <v>2</v>
-      </c>
-      <c r="Z41">
-        <v>1</v>
-      </c>
-      <c r="AA41">
-        <v>1</v>
-      </c>
-      <c r="AB41">
-        <v>1</v>
-      </c>
-      <c r="AC41">
-        <v>3</v>
-      </c>
-      <c r="AF41">
-        <v>4</v>
-      </c>
-      <c r="AI41">
-        <v>1</v>
-      </c>
-      <c r="AL41">
-        <v>1</v>
-      </c>
-      <c r="AN41">
-        <v>1</v>
-      </c>
-      <c r="AR41">
-        <v>2</v>
-      </c>
-      <c r="AS41">
-        <v>3</v>
-      </c>
-      <c r="AT41">
-        <v>1</v>
-      </c>
-      <c r="AW41">
-        <v>2</v>
-      </c>
-      <c r="AX41">
-        <v>5</v>
-      </c>
-      <c r="AY41">
-        <v>3</v>
-      </c>
-      <c r="AZ41">
-        <v>1</v>
-      </c>
-      <c r="BA41">
-        <v>3</v>
-      </c>
-      <c r="BB41">
-        <v>2</v>
-      </c>
       <c r="BD41">
-        <v>3</v>
-      </c>
-      <c r="BF41">
-        <v>3</v>
+        <v>1</v>
+      </c>
+      <c r="BE41">
+        <v>1</v>
       </c>
       <c r="BG41">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="BH41">
         <v>3</v>
       </c>
-      <c r="BI41">
-        <v>2</v>
-      </c>
       <c r="BJ41">
         <v>1</v>
       </c>
-      <c r="BL41">
-        <v>1</v>
-      </c>
       <c r="BM41">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="BN41">
         <v>1</v>
       </c>
       <c r="BP41">
         <v>1</v>
-      </c>
-      <c r="BQ41">
-        <v>2</v>
       </c>
       <c r="BR41">
         <v>3</v>
       </c>
-      <c r="BS41">
-        <v>2</v>
-      </c>
       <c r="BV41">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="BW41">
         <v>4</v>
       </c>
-      <c r="BY41">
-        <v>1</v>
-      </c>
-      <c r="BZ41">
-        <v>3</v>
+      <c r="BX41">
+        <v>2</v>
       </c>
       <c r="CB41">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="CC41">
-        <v>2</v>
-      </c>
-      <c r="CG41">
-        <v>2</v>
-      </c>
-      <c r="CL41">
-        <v>2</v>
-      </c>
-      <c r="CP41">
-        <v>1</v>
+        <v>1</v>
+      </c>
+      <c r="CJ41">
+        <v>2</v>
+      </c>
+      <c r="CK41">
+        <v>2</v>
+      </c>
+      <c r="CN41">
+        <v>1</v>
+      </c>
+      <c r="CQ41">
+        <v>2</v>
       </c>
     </row>
     <row r="42" spans="1:95" x14ac:dyDescent="0.35">
       <c r="A42" t="s">
-        <v>143</v>
+        <v>9</v>
+      </c>
+      <c r="C42">
+        <v>1</v>
+      </c>
+      <c r="D42">
+        <v>1</v>
+      </c>
+      <c r="G42">
+        <v>2</v>
+      </c>
+      <c r="H42">
+        <v>2</v>
+      </c>
+      <c r="I42">
+        <v>1</v>
+      </c>
+      <c r="J42">
+        <v>1</v>
+      </c>
+      <c r="K42">
+        <v>2</v>
+      </c>
+      <c r="L42">
+        <v>5</v>
+      </c>
+      <c r="M42">
+        <v>1</v>
+      </c>
+      <c r="O42">
+        <v>4</v>
+      </c>
+      <c r="P42">
+        <v>1</v>
+      </c>
+      <c r="Q42">
+        <v>2</v>
+      </c>
+      <c r="T42">
+        <v>6</v>
+      </c>
+      <c r="X42">
+        <v>2</v>
+      </c>
+      <c r="Y42">
+        <v>2</v>
+      </c>
+      <c r="Z42">
+        <v>1</v>
+      </c>
+      <c r="AA42">
+        <v>1</v>
+      </c>
+      <c r="AB42">
+        <v>1</v>
+      </c>
+      <c r="AC42">
+        <v>3</v>
+      </c>
+      <c r="AF42">
+        <v>4</v>
+      </c>
+      <c r="AI42">
+        <v>1</v>
+      </c>
+      <c r="AL42">
+        <v>1</v>
+      </c>
+      <c r="AN42">
+        <v>1</v>
+      </c>
+      <c r="AR42">
+        <v>2</v>
+      </c>
+      <c r="AS42">
+        <v>3</v>
+      </c>
+      <c r="AT42">
+        <v>1</v>
+      </c>
+      <c r="AW42">
+        <v>2</v>
+      </c>
+      <c r="AX42">
+        <v>5</v>
+      </c>
+      <c r="AY42">
+        <v>3</v>
+      </c>
+      <c r="AZ42">
+        <v>1</v>
+      </c>
+      <c r="BA42">
+        <v>3</v>
+      </c>
+      <c r="BB42">
+        <v>2</v>
+      </c>
+      <c r="BD42">
+        <v>3</v>
+      </c>
+      <c r="BF42">
+        <v>3</v>
+      </c>
+      <c r="BG42">
+        <v>4</v>
+      </c>
+      <c r="BH42">
+        <v>3</v>
+      </c>
+      <c r="BI42">
+        <v>2</v>
+      </c>
+      <c r="BJ42">
+        <v>1</v>
+      </c>
+      <c r="BL42">
+        <v>1</v>
+      </c>
+      <c r="BM42">
+        <v>2</v>
+      </c>
+      <c r="BN42">
+        <v>1</v>
+      </c>
+      <c r="BP42">
+        <v>1</v>
+      </c>
+      <c r="BQ42">
+        <v>2</v>
+      </c>
+      <c r="BR42">
+        <v>3</v>
+      </c>
+      <c r="BS42">
+        <v>2</v>
+      </c>
+      <c r="BV42">
+        <v>5</v>
       </c>
       <c r="BW42">
+        <v>4</v>
+      </c>
+      <c r="BY42">
         <v>1</v>
       </c>
       <c r="BZ42">
-        <v>2</v>
-      </c>
-      <c r="CA42">
-        <v>5</v>
+        <v>3</v>
+      </c>
+      <c r="CB42">
+        <v>4</v>
       </c>
       <c r="CC42">
-        <v>1</v>
-      </c>
-      <c r="CF42">
+        <v>2</v>
+      </c>
+      <c r="CG42">
+        <v>2</v>
+      </c>
+      <c r="CL42">
+        <v>2</v>
+      </c>
+      <c r="CP42">
         <v>1</v>
       </c>
     </row>
     <row r="43" spans="1:95" x14ac:dyDescent="0.35">
       <c r="A43" t="s">
-        <v>132</v>
-      </c>
-      <c r="BG43">
-        <v>2</v>
+        <v>143</v>
+      </c>
+      <c r="BW43">
+        <v>1</v>
+      </c>
+      <c r="BZ43">
+        <v>2</v>
+      </c>
+      <c r="CA43">
+        <v>5</v>
+      </c>
+      <c r="CC43">
+        <v>1</v>
+      </c>
+      <c r="CF43">
+        <v>1</v>
       </c>
     </row>
     <row r="44" spans="1:95" x14ac:dyDescent="0.35">
       <c r="A44" t="s">
-        <v>19</v>
-      </c>
-      <c r="B44">
-        <v>1</v>
-      </c>
-      <c r="D44">
-        <v>1</v>
-      </c>
-      <c r="F44">
-        <v>2</v>
-      </c>
-      <c r="G44">
-        <v>2</v>
-      </c>
-      <c r="H44">
-        <v>4</v>
-      </c>
-      <c r="J44">
-        <v>2</v>
-      </c>
-      <c r="K44">
-        <v>2</v>
-      </c>
-      <c r="L44">
-        <v>1</v>
-      </c>
-      <c r="M44">
-        <v>1</v>
-      </c>
-      <c r="P44">
-        <v>1</v>
-      </c>
-      <c r="Q44">
-        <v>1</v>
-      </c>
-      <c r="R44">
-        <v>3</v>
-      </c>
-      <c r="S44">
-        <v>2</v>
-      </c>
-      <c r="T44">
-        <v>2</v>
-      </c>
-      <c r="U44">
-        <v>2</v>
-      </c>
-      <c r="W44">
-        <v>3</v>
-      </c>
-      <c r="X44">
-        <v>3</v>
-      </c>
-      <c r="Y44">
-        <v>2</v>
-      </c>
-      <c r="AA44">
-        <v>2</v>
-      </c>
-      <c r="AB44">
-        <v>2</v>
-      </c>
-      <c r="AC44">
-        <v>2</v>
-      </c>
-      <c r="AE44">
-        <v>2</v>
-      </c>
-      <c r="AF44">
-        <v>1</v>
-      </c>
-      <c r="AG44">
-        <v>2</v>
-      </c>
-      <c r="AJ44">
-        <v>4</v>
-      </c>
-      <c r="AK44">
-        <v>2</v>
-      </c>
-      <c r="AM44">
-        <v>1</v>
-      </c>
-      <c r="AN44">
-        <v>1</v>
-      </c>
-      <c r="AO44">
-        <v>1</v>
-      </c>
-      <c r="AP44">
-        <v>1</v>
-      </c>
-      <c r="AU44">
-        <v>1</v>
-      </c>
-      <c r="AV44">
-        <v>1</v>
-      </c>
-      <c r="AW44">
-        <v>2</v>
-      </c>
-      <c r="BA44">
-        <v>1</v>
-      </c>
-      <c r="BH44">
-        <v>2</v>
-      </c>
-      <c r="BJ44">
-        <v>2</v>
-      </c>
-      <c r="BK44">
-        <v>3</v>
-      </c>
-      <c r="BP44">
-        <v>2</v>
-      </c>
-      <c r="CJ44">
-        <v>1</v>
+        <v>132</v>
+      </c>
+      <c r="BG44">
+        <v>2</v>
       </c>
     </row>
     <row r="45" spans="1:95" x14ac:dyDescent="0.35">
       <c r="A45" t="s">
+        <v>19</v>
+      </c>
+      <c r="B45">
+        <v>1</v>
+      </c>
+      <c r="D45">
+        <v>1</v>
+      </c>
+      <c r="F45">
+        <v>2</v>
+      </c>
+      <c r="G45">
+        <v>2</v>
+      </c>
+      <c r="H45">
+        <v>4</v>
+      </c>
+      <c r="J45">
+        <v>2</v>
+      </c>
+      <c r="K45">
+        <v>2</v>
+      </c>
+      <c r="L45">
+        <v>1</v>
+      </c>
+      <c r="M45">
+        <v>1</v>
+      </c>
+      <c r="P45">
+        <v>1</v>
+      </c>
+      <c r="Q45">
+        <v>1</v>
+      </c>
+      <c r="R45">
+        <v>3</v>
+      </c>
+      <c r="S45">
+        <v>2</v>
+      </c>
+      <c r="T45">
+        <v>2</v>
+      </c>
+      <c r="U45">
+        <v>2</v>
+      </c>
+      <c r="W45">
+        <v>3</v>
+      </c>
+      <c r="X45">
+        <v>3</v>
+      </c>
+      <c r="Y45">
+        <v>2</v>
+      </c>
+      <c r="AA45">
+        <v>2</v>
+      </c>
+      <c r="AB45">
+        <v>2</v>
+      </c>
+      <c r="AC45">
+        <v>2</v>
+      </c>
+      <c r="AE45">
+        <v>2</v>
+      </c>
+      <c r="AF45">
+        <v>1</v>
+      </c>
+      <c r="AG45">
+        <v>2</v>
+      </c>
+      <c r="AJ45">
+        <v>4</v>
+      </c>
+      <c r="AK45">
+        <v>2</v>
+      </c>
+      <c r="AM45">
+        <v>1</v>
+      </c>
+      <c r="AN45">
+        <v>1</v>
+      </c>
+      <c r="AO45">
+        <v>1</v>
+      </c>
+      <c r="AP45">
+        <v>1</v>
+      </c>
+      <c r="AU45">
+        <v>1</v>
+      </c>
+      <c r="AV45">
+        <v>1</v>
+      </c>
+      <c r="AW45">
+        <v>2</v>
+      </c>
+      <c r="BA45">
+        <v>1</v>
+      </c>
+      <c r="BH45">
+        <v>2</v>
+      </c>
+      <c r="BJ45">
+        <v>2</v>
+      </c>
+      <c r="BK45">
+        <v>3</v>
+      </c>
+      <c r="BP45">
+        <v>2</v>
+      </c>
+      <c r="CJ45">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="46" spans="1:95" x14ac:dyDescent="0.35">
+      <c r="A46" t="s">
         <v>144</v>
       </c>
     </row>
-    <row r="46" spans="1:95" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A46" t="s">
+    <row r="47" spans="1:95" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A47" t="s">
         <v>60</v>
       </c>
-      <c r="D46">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="47" spans="1:95" x14ac:dyDescent="0.35">
-      <c r="A47" t="s">
-        <v>79</v>
-      </c>
-      <c r="F47">
+      <c r="D47">
         <v>1</v>
       </c>
     </row>
     <row r="48" spans="1:95" x14ac:dyDescent="0.35">
       <c r="A48" t="s">
-        <v>160</v>
+        <v>79</v>
+      </c>
+      <c r="F48">
+        <v>1</v>
       </c>
     </row>
     <row r="49" spans="1:95" x14ac:dyDescent="0.35">
       <c r="A49" t="s">
-        <v>125</v>
-      </c>
-      <c r="AW49">
-        <v>2</v>
+        <v>160</v>
       </c>
     </row>
     <row r="50" spans="1:95" x14ac:dyDescent="0.35">
       <c r="A50" t="s">
-        <v>18</v>
-      </c>
-      <c r="B50">
-        <v>2</v>
-      </c>
-      <c r="C50">
-        <v>1</v>
-      </c>
-      <c r="D50">
-        <v>1</v>
-      </c>
-      <c r="F50">
-        <v>4</v>
-      </c>
-      <c r="G50">
-        <v>3</v>
-      </c>
-      <c r="H50">
-        <v>1</v>
-      </c>
-      <c r="I50">
-        <v>1</v>
-      </c>
-      <c r="M50">
-        <v>2</v>
-      </c>
-      <c r="N50">
-        <v>3</v>
-      </c>
-      <c r="T50">
-        <v>1</v>
-      </c>
-      <c r="X50">
-        <v>1</v>
-      </c>
-      <c r="AA50">
-        <v>2</v>
-      </c>
-      <c r="AB50">
-        <v>2</v>
-      </c>
-      <c r="AC50">
-        <v>1</v>
-      </c>
-      <c r="AD50">
-        <v>2</v>
-      </c>
-      <c r="AE50">
-        <v>1</v>
-      </c>
-      <c r="AG50">
-        <v>1</v>
-      </c>
-      <c r="AH50">
-        <v>2</v>
-      </c>
-      <c r="AJ50">
-        <v>1</v>
-      </c>
-      <c r="AM50">
-        <v>4</v>
-      </c>
-      <c r="AN50">
-        <v>1</v>
-      </c>
-      <c r="AP50">
-        <v>1</v>
-      </c>
-      <c r="AR50">
-        <v>1</v>
-      </c>
-      <c r="AS50">
-        <v>1</v>
-      </c>
-      <c r="AT50">
-        <v>1</v>
-      </c>
-      <c r="AV50">
-        <v>1</v>
-      </c>
-      <c r="AZ50">
-        <v>2</v>
-      </c>
-      <c r="BA50">
-        <v>1</v>
-      </c>
-      <c r="BC50">
-        <v>3</v>
-      </c>
-      <c r="BD50">
-        <v>1</v>
-      </c>
-      <c r="BI50">
-        <v>1</v>
-      </c>
-      <c r="BJ50">
-        <v>1</v>
-      </c>
-      <c r="BK50">
-        <v>3</v>
-      </c>
-      <c r="BL50">
-        <v>2</v>
-      </c>
-      <c r="BM50">
-        <v>5</v>
-      </c>
-      <c r="BO50">
-        <v>1</v>
-      </c>
-      <c r="BP50">
-        <v>3</v>
-      </c>
-      <c r="BQ50">
-        <v>3</v>
-      </c>
-      <c r="BS50">
-        <v>1</v>
-      </c>
-      <c r="BX50">
-        <v>3</v>
-      </c>
-      <c r="BY50">
-        <v>5</v>
-      </c>
-      <c r="BZ50">
-        <v>1</v>
-      </c>
-      <c r="CB50">
-        <v>3</v>
-      </c>
-      <c r="CC50">
-        <v>2</v>
-      </c>
-      <c r="CD50">
-        <v>4</v>
-      </c>
-      <c r="CF50">
-        <v>1</v>
-      </c>
-      <c r="CI50">
-        <v>2</v>
-      </c>
-      <c r="CJ50">
-        <v>2</v>
-      </c>
-      <c r="CK50">
-        <v>2</v>
-      </c>
-      <c r="CL50">
-        <v>1</v>
-      </c>
-      <c r="CM50">
-        <v>3</v>
-      </c>
-      <c r="CQ50">
-        <v>3</v>
+        <v>125</v>
+      </c>
+      <c r="AW50">
+        <v>2</v>
       </c>
     </row>
     <row r="51" spans="1:95" x14ac:dyDescent="0.35">
       <c r="A51" t="s">
-        <v>42</v>
-      </c>
-      <c r="AQ51">
-        <v>2</v>
+        <v>18</v>
+      </c>
+      <c r="B51">
+        <v>2</v>
+      </c>
+      <c r="C51">
+        <v>1</v>
+      </c>
+      <c r="D51">
+        <v>1</v>
+      </c>
+      <c r="F51">
+        <v>4</v>
+      </c>
+      <c r="G51">
+        <v>3</v>
+      </c>
+      <c r="H51">
+        <v>1</v>
+      </c>
+      <c r="I51">
+        <v>1</v>
+      </c>
+      <c r="M51">
+        <v>2</v>
+      </c>
+      <c r="N51">
+        <v>3</v>
+      </c>
+      <c r="T51">
+        <v>1</v>
+      </c>
+      <c r="X51">
+        <v>1</v>
+      </c>
+      <c r="AA51">
+        <v>2</v>
+      </c>
+      <c r="AB51">
+        <v>2</v>
+      </c>
+      <c r="AC51">
+        <v>1</v>
+      </c>
+      <c r="AD51">
+        <v>2</v>
+      </c>
+      <c r="AE51">
+        <v>1</v>
+      </c>
+      <c r="AG51">
+        <v>1</v>
+      </c>
+      <c r="AH51">
+        <v>2</v>
+      </c>
+      <c r="AJ51">
+        <v>1</v>
+      </c>
+      <c r="AM51">
+        <v>4</v>
+      </c>
+      <c r="AN51">
+        <v>1</v>
+      </c>
+      <c r="AP51">
+        <v>1</v>
+      </c>
+      <c r="AR51">
+        <v>1</v>
+      </c>
+      <c r="AS51">
+        <v>1</v>
+      </c>
+      <c r="AT51">
+        <v>1</v>
+      </c>
+      <c r="AV51">
+        <v>1</v>
+      </c>
+      <c r="AZ51">
+        <v>2</v>
+      </c>
+      <c r="BA51">
+        <v>1</v>
+      </c>
+      <c r="BC51">
+        <v>3</v>
+      </c>
+      <c r="BD51">
+        <v>1</v>
+      </c>
+      <c r="BI51">
+        <v>1</v>
+      </c>
+      <c r="BJ51">
+        <v>1</v>
+      </c>
+      <c r="BK51">
+        <v>3</v>
+      </c>
+      <c r="BL51">
+        <v>2</v>
+      </c>
+      <c r="BM51">
+        <v>5</v>
+      </c>
+      <c r="BO51">
+        <v>1</v>
+      </c>
+      <c r="BP51">
+        <v>3</v>
+      </c>
+      <c r="BQ51">
+        <v>3</v>
+      </c>
+      <c r="BS51">
+        <v>1</v>
+      </c>
+      <c r="BX51">
+        <v>3</v>
+      </c>
+      <c r="BY51">
+        <v>5</v>
+      </c>
+      <c r="BZ51">
+        <v>1</v>
+      </c>
+      <c r="CB51">
+        <v>3</v>
+      </c>
+      <c r="CC51">
+        <v>2</v>
+      </c>
+      <c r="CD51">
+        <v>4</v>
+      </c>
+      <c r="CF51">
+        <v>1</v>
+      </c>
+      <c r="CI51">
+        <v>2</v>
+      </c>
+      <c r="CJ51">
+        <v>2</v>
+      </c>
+      <c r="CK51">
+        <v>2</v>
+      </c>
+      <c r="CL51">
+        <v>1</v>
+      </c>
+      <c r="CM51">
+        <v>3</v>
+      </c>
+      <c r="CQ51">
+        <v>3</v>
       </c>
     </row>
     <row r="52" spans="1:95" x14ac:dyDescent="0.35">
       <c r="A52" t="s">
-        <v>67</v>
-      </c>
-      <c r="E52">
-        <v>1</v>
-      </c>
-      <c r="I52">
-        <v>1</v>
-      </c>
-      <c r="N52">
-        <v>1</v>
-      </c>
-      <c r="W52">
-        <v>2</v>
+        <v>42</v>
       </c>
       <c r="AQ52">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="53" spans="1:95" x14ac:dyDescent="0.35">
       <c r="A53" t="s">
-        <v>52</v>
+        <v>67</v>
+      </c>
+      <c r="E53">
+        <v>1</v>
+      </c>
+      <c r="I53">
+        <v>1</v>
       </c>
       <c r="N53">
         <v>1</v>
       </c>
-      <c r="BZ53">
-        <v>2</v>
+      <c r="W53">
+        <v>2</v>
+      </c>
+      <c r="AQ53">
+        <v>1</v>
       </c>
     </row>
     <row r="54" spans="1:95" x14ac:dyDescent="0.35">
       <c r="A54" t="s">
-        <v>119</v>
-      </c>
-      <c r="AM54">
-        <v>5</v>
-      </c>
-      <c r="BB54">
-        <v>9</v>
-      </c>
-      <c r="BN54">
+        <v>52</v>
+      </c>
+      <c r="N54">
+        <v>1</v>
+      </c>
+      <c r="BZ54">
         <v>2</v>
       </c>
     </row>
     <row r="55" spans="1:95" x14ac:dyDescent="0.35">
       <c r="A55" t="s">
-        <v>99</v>
-      </c>
-      <c r="U55">
-        <v>1</v>
-      </c>
-      <c r="BR55">
-        <v>1</v>
-      </c>
-      <c r="BS55">
-        <v>1</v>
-      </c>
-      <c r="BT55">
-        <v>1</v>
+        <v>119</v>
+      </c>
+      <c r="AM55">
+        <v>5</v>
+      </c>
+      <c r="BB55">
+        <v>9</v>
+      </c>
+      <c r="BN55">
+        <v>2</v>
       </c>
     </row>
     <row r="56" spans="1:95" x14ac:dyDescent="0.35">
       <c r="A56" t="s">
-        <v>170</v>
-      </c>
-      <c r="AN56">
+        <v>99</v>
+      </c>
+      <c r="U56">
         <v>1</v>
       </c>
       <c r="BR56">
@@ -51679,1754 +51943,1780 @@
         <v>1</v>
       </c>
       <c r="BT56">
-        <v>3</v>
-      </c>
-      <c r="CD56">
-        <v>1</v>
-      </c>
-      <c r="CJ56">
-        <v>1</v>
-      </c>
-      <c r="CN56">
         <v>1</v>
       </c>
     </row>
     <row r="57" spans="1:95" x14ac:dyDescent="0.35">
       <c r="A57" t="s">
-        <v>169</v>
+        <v>170</v>
+      </c>
+      <c r="AN57">
+        <v>1</v>
+      </c>
+      <c r="BR57">
+        <v>1</v>
+      </c>
+      <c r="BS57">
+        <v>1</v>
+      </c>
+      <c r="BT57">
+        <v>3</v>
+      </c>
+      <c r="CD57">
+        <v>1</v>
+      </c>
+      <c r="CJ57">
+        <v>1</v>
+      </c>
+      <c r="CN57">
+        <v>1</v>
       </c>
     </row>
     <row r="58" spans="1:95" x14ac:dyDescent="0.35">
       <c r="A58" t="s">
-        <v>98</v>
-      </c>
-      <c r="X58">
-        <v>1</v>
-      </c>
-      <c r="Y58">
-        <v>2</v>
-      </c>
-      <c r="AF58">
-        <v>2</v>
+        <v>169</v>
       </c>
     </row>
     <row r="59" spans="1:95" x14ac:dyDescent="0.35">
       <c r="A59" t="s">
-        <v>146</v>
-      </c>
-      <c r="CB59">
-        <v>5</v>
-      </c>
-      <c r="CH59">
-        <v>5</v>
+        <v>98</v>
+      </c>
+      <c r="X59">
+        <v>1</v>
+      </c>
+      <c r="Y59">
+        <v>2</v>
+      </c>
+      <c r="AF59">
+        <v>2</v>
       </c>
     </row>
     <row r="60" spans="1:95" x14ac:dyDescent="0.35">
       <c r="A60" t="s">
-        <v>10</v>
-      </c>
-      <c r="B60">
-        <v>2</v>
-      </c>
-      <c r="C60">
-        <v>3</v>
-      </c>
-      <c r="F60">
-        <v>2</v>
-      </c>
-      <c r="I60">
-        <v>2</v>
-      </c>
-      <c r="J60">
-        <v>2</v>
-      </c>
-      <c r="K60">
-        <v>1</v>
-      </c>
-      <c r="L60">
-        <v>1</v>
-      </c>
-      <c r="M60">
-        <v>1</v>
-      </c>
-      <c r="O60">
-        <v>2</v>
-      </c>
-      <c r="R60">
-        <v>3</v>
-      </c>
-      <c r="S60">
-        <v>1</v>
-      </c>
-      <c r="T60">
-        <v>1</v>
-      </c>
-      <c r="V60">
-        <v>1</v>
-      </c>
-      <c r="W60">
-        <v>3</v>
-      </c>
-      <c r="X60">
-        <v>1</v>
-      </c>
-      <c r="Y60">
-        <v>1</v>
-      </c>
-      <c r="Z60">
-        <v>1.5</v>
-      </c>
-      <c r="AC60">
-        <v>1</v>
-      </c>
-      <c r="AD60">
-        <v>2</v>
-      </c>
-      <c r="AE60">
-        <v>1</v>
-      </c>
-      <c r="AF60">
-        <v>2</v>
-      </c>
-      <c r="AH60">
-        <v>2</v>
-      </c>
-      <c r="AL60">
-        <v>3</v>
-      </c>
-      <c r="AP60">
-        <v>2</v>
-      </c>
-      <c r="AQ60">
-        <v>4</v>
-      </c>
-      <c r="AR60">
-        <v>3</v>
-      </c>
-      <c r="AS60">
-        <v>0.5</v>
-      </c>
-      <c r="AU60">
-        <v>2</v>
-      </c>
-      <c r="AV60">
-        <v>1</v>
-      </c>
-      <c r="BC60">
-        <v>1</v>
-      </c>
-      <c r="BD60">
-        <v>1</v>
-      </c>
-      <c r="BE60">
-        <v>7</v>
-      </c>
-      <c r="BH60">
-        <v>1</v>
-      </c>
-      <c r="BI60">
-        <v>1</v>
-      </c>
-      <c r="BJ60">
-        <v>3</v>
-      </c>
-      <c r="BK60">
-        <v>3</v>
-      </c>
-      <c r="BL60">
-        <v>1</v>
-      </c>
-      <c r="BM60">
-        <v>1</v>
-      </c>
-      <c r="BN60">
-        <v>4</v>
-      </c>
-      <c r="BP60">
-        <v>1</v>
-      </c>
-      <c r="BQ60">
-        <v>3</v>
-      </c>
-      <c r="BR60">
-        <v>1</v>
-      </c>
-      <c r="BT60">
-        <v>1</v>
-      </c>
-      <c r="BV60">
-        <v>1</v>
-      </c>
-      <c r="BW60">
-        <v>2</v>
-      </c>
-      <c r="BX60">
-        <v>2</v>
-      </c>
-      <c r="BZ60">
-        <v>2</v>
-      </c>
-      <c r="CC60">
-        <v>4</v>
-      </c>
-      <c r="CD60">
-        <v>1</v>
-      </c>
-      <c r="CJ60">
-        <v>1</v>
-      </c>
-      <c r="CK60">
-        <v>1</v>
-      </c>
-      <c r="CL60">
-        <v>1</v>
+        <v>146</v>
+      </c>
+      <c r="CB60">
+        <v>5</v>
+      </c>
+      <c r="CH60">
+        <v>5</v>
       </c>
     </row>
     <row r="61" spans="1:95" x14ac:dyDescent="0.35">
       <c r="A61" t="s">
-        <v>45</v>
+        <v>10</v>
       </c>
       <c r="B61">
+        <v>2</v>
+      </c>
+      <c r="C61">
+        <v>3</v>
+      </c>
+      <c r="F61">
+        <v>2</v>
+      </c>
+      <c r="I61">
+        <v>2</v>
+      </c>
+      <c r="J61">
+        <v>2</v>
+      </c>
+      <c r="K61">
+        <v>1</v>
+      </c>
+      <c r="L61">
+        <v>1</v>
+      </c>
+      <c r="M61">
         <v>1</v>
       </c>
       <c r="O61">
+        <v>2</v>
+      </c>
+      <c r="R61">
         <v>3</v>
       </c>
-      <c r="P61">
-        <v>1</v>
-      </c>
-      <c r="Q61">
-        <v>2</v>
-      </c>
-      <c r="AM61">
-        <v>1</v>
-      </c>
-      <c r="AN61">
-        <v>1</v>
+      <c r="S61">
+        <v>1</v>
+      </c>
+      <c r="T61">
+        <v>1</v>
+      </c>
+      <c r="V61">
+        <v>1</v>
+      </c>
+      <c r="W61">
+        <v>3</v>
+      </c>
+      <c r="X61">
+        <v>1</v>
+      </c>
+      <c r="Y61">
+        <v>1</v>
+      </c>
+      <c r="Z61">
+        <v>1.5</v>
+      </c>
+      <c r="AC61">
+        <v>1</v>
+      </c>
+      <c r="AD61">
+        <v>2</v>
+      </c>
+      <c r="AE61">
+        <v>1</v>
+      </c>
+      <c r="AF61">
+        <v>2</v>
+      </c>
+      <c r="AH61">
+        <v>2</v>
+      </c>
+      <c r="AL61">
+        <v>3</v>
       </c>
       <c r="AP61">
-        <v>1</v>
+        <v>2</v>
+      </c>
+      <c r="AQ61">
+        <v>4</v>
+      </c>
+      <c r="AR61">
+        <v>3</v>
       </c>
       <c r="AS61">
-        <v>1</v>
+        <v>0.5</v>
+      </c>
+      <c r="AU61">
+        <v>2</v>
       </c>
       <c r="AV61">
         <v>1</v>
       </c>
-      <c r="AX61">
-        <v>5</v>
-      </c>
-      <c r="AY61">
-        <v>1</v>
-      </c>
-      <c r="BA61">
-        <v>2</v>
-      </c>
-      <c r="BB61">
+      <c r="BC61">
+        <v>1</v>
+      </c>
+      <c r="BD61">
+        <v>1</v>
+      </c>
+      <c r="BE61">
+        <v>7</v>
+      </c>
+      <c r="BH61">
+        <v>1</v>
+      </c>
+      <c r="BI61">
+        <v>1</v>
+      </c>
+      <c r="BJ61">
+        <v>3</v>
+      </c>
+      <c r="BK61">
+        <v>3</v>
+      </c>
+      <c r="BL61">
+        <v>1</v>
+      </c>
+      <c r="BM61">
+        <v>1</v>
+      </c>
+      <c r="BN61">
         <v>4</v>
       </c>
-      <c r="BE61">
+      <c r="BP61">
+        <v>1</v>
+      </c>
+      <c r="BQ61">
         <v>3</v>
       </c>
-      <c r="BF61">
-        <v>2</v>
-      </c>
-      <c r="BH61">
-        <v>3</v>
-      </c>
-      <c r="BK61">
+      <c r="BR61">
         <v>1</v>
       </c>
       <c r="BT61">
-        <v>3</v>
+        <v>1</v>
+      </c>
+      <c r="BV61">
+        <v>1</v>
+      </c>
+      <c r="BW61">
+        <v>2</v>
+      </c>
+      <c r="BX61">
+        <v>2</v>
       </c>
       <c r="BZ61">
-        <v>1</v>
-      </c>
-      <c r="CB61">
         <v>2</v>
       </c>
       <c r="CC61">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="CD61">
         <v>1</v>
       </c>
-      <c r="CF61">
+      <c r="CJ61">
+        <v>1</v>
+      </c>
+      <c r="CK61">
+        <v>1</v>
+      </c>
+      <c r="CL61">
         <v>1</v>
       </c>
     </row>
     <row r="62" spans="1:95" x14ac:dyDescent="0.35">
       <c r="A62" t="s">
+        <v>45</v>
+      </c>
+      <c r="B62">
+        <v>1</v>
+      </c>
+      <c r="O62">
+        <v>3</v>
+      </c>
+      <c r="P62">
+        <v>1</v>
+      </c>
+      <c r="Q62">
+        <v>2</v>
+      </c>
+      <c r="AM62">
+        <v>1</v>
+      </c>
+      <c r="AN62">
+        <v>1</v>
+      </c>
+      <c r="AP62">
+        <v>1</v>
+      </c>
+      <c r="AS62">
+        <v>1</v>
+      </c>
+      <c r="AV62">
+        <v>1</v>
+      </c>
+      <c r="AX62">
+        <v>5</v>
+      </c>
+      <c r="AY62">
+        <v>1</v>
+      </c>
+      <c r="BA62">
+        <v>2</v>
+      </c>
+      <c r="BB62">
+        <v>4</v>
+      </c>
+      <c r="BE62">
+        <v>3</v>
+      </c>
+      <c r="BF62">
+        <v>2</v>
+      </c>
+      <c r="BH62">
+        <v>3</v>
+      </c>
+      <c r="BK62">
+        <v>1</v>
+      </c>
+      <c r="BT62">
+        <v>3</v>
+      </c>
+      <c r="BZ62">
+        <v>1</v>
+      </c>
+      <c r="CB62">
+        <v>2</v>
+      </c>
+      <c r="CC62">
+        <v>1</v>
+      </c>
+      <c r="CD62">
+        <v>1</v>
+      </c>
+      <c r="CF62">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="63" spans="1:95" x14ac:dyDescent="0.35">
+      <c r="A63" t="s">
         <v>152</v>
       </c>
-      <c r="CN62">
-        <v>1</v>
-      </c>
-      <c r="CO62">
-        <v>1</v>
-      </c>
-      <c r="CP62">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="63" spans="1:95" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A63" t="s">
+      <c r="CN63">
+        <v>1</v>
+      </c>
+      <c r="CO63">
+        <v>1</v>
+      </c>
+      <c r="CP63">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="64" spans="1:95" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A64" t="s">
         <v>104</v>
-      </c>
-    </row>
-    <row r="64" spans="1:95" x14ac:dyDescent="0.35">
-      <c r="A64" t="s">
-        <v>128</v>
       </c>
     </row>
     <row r="65" spans="1:95" x14ac:dyDescent="0.35">
       <c r="A65" t="s">
-        <v>3</v>
-      </c>
-      <c r="F65">
-        <v>3</v>
-      </c>
-      <c r="L65">
-        <v>1</v>
-      </c>
-      <c r="S65">
-        <v>3</v>
-      </c>
-      <c r="AH65">
-        <v>1</v>
+        <v>128</v>
       </c>
     </row>
     <row r="66" spans="1:95" x14ac:dyDescent="0.35">
       <c r="A66" t="s">
-        <v>55</v>
-      </c>
-      <c r="C66">
         <v>3</v>
       </c>
-      <c r="E66">
-        <v>2</v>
-      </c>
       <c r="F66">
-        <v>1</v>
-      </c>
-      <c r="G66">
-        <v>2</v>
-      </c>
-      <c r="I66">
-        <v>1</v>
-      </c>
-      <c r="J66">
-        <v>1</v>
-      </c>
-      <c r="K66">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L66">
         <v>1</v>
       </c>
-      <c r="M66">
-        <v>1</v>
-      </c>
-      <c r="P66">
-        <v>1</v>
-      </c>
-      <c r="R66">
-        <v>1</v>
-      </c>
       <c r="S66">
-        <v>4</v>
-      </c>
-      <c r="T66">
-        <v>1</v>
-      </c>
-      <c r="V66">
-        <v>1</v>
-      </c>
-      <c r="W66">
-        <v>2</v>
-      </c>
-      <c r="Z66">
-        <v>2</v>
-      </c>
-      <c r="AA66">
-        <v>1</v>
-      </c>
-      <c r="AB66">
-        <v>4</v>
-      </c>
-      <c r="AC66">
-        <v>1</v>
-      </c>
-      <c r="AD66">
-        <v>1</v>
-      </c>
-      <c r="AX66">
-        <v>1</v>
-      </c>
-      <c r="AY66">
-        <v>1</v>
-      </c>
-      <c r="AZ66">
-        <v>2</v>
-      </c>
-      <c r="BD66">
-        <v>1</v>
-      </c>
-      <c r="BF66">
-        <v>1</v>
-      </c>
-      <c r="BH66">
-        <v>1</v>
-      </c>
-      <c r="BI66">
-        <v>1</v>
-      </c>
-      <c r="BJ66">
-        <v>2</v>
-      </c>
-      <c r="BK66">
-        <v>1</v>
-      </c>
-      <c r="BL66">
-        <v>2</v>
-      </c>
-      <c r="BM66">
-        <v>2</v>
-      </c>
-      <c r="BN66">
-        <v>2</v>
-      </c>
-      <c r="BO66">
-        <v>1</v>
-      </c>
-      <c r="BP66">
-        <v>1</v>
-      </c>
-      <c r="BR66">
-        <v>1</v>
-      </c>
-      <c r="BS66">
-        <v>2</v>
-      </c>
-      <c r="BU66">
-        <v>2</v>
-      </c>
-      <c r="BV66">
-        <v>1</v>
-      </c>
-      <c r="BX66">
-        <v>1</v>
-      </c>
-      <c r="BY66">
-        <v>2</v>
-      </c>
-      <c r="BZ66">
-        <v>2</v>
-      </c>
-      <c r="CA66">
-        <v>2</v>
-      </c>
-      <c r="CB66">
-        <v>2</v>
-      </c>
-      <c r="CC66">
-        <v>4</v>
-      </c>
-      <c r="CD66">
-        <v>5</v>
-      </c>
-      <c r="CG66">
-        <v>1</v>
-      </c>
-      <c r="CH66">
-        <v>1</v>
-      </c>
-      <c r="CI66">
-        <v>2</v>
-      </c>
-      <c r="CJ66">
-        <v>5</v>
-      </c>
-      <c r="CN66">
-        <v>1</v>
-      </c>
-      <c r="CO66">
-        <v>1</v>
-      </c>
-      <c r="CQ66">
+        <v>3</v>
+      </c>
+      <c r="AH66">
         <v>1</v>
       </c>
     </row>
     <row r="67" spans="1:95" x14ac:dyDescent="0.35">
       <c r="A67" t="s">
-        <v>120</v>
-      </c>
-      <c r="AN67">
+        <v>55</v>
+      </c>
+      <c r="C67">
         <v>3</v>
+      </c>
+      <c r="E67">
+        <v>2</v>
+      </c>
+      <c r="F67">
+        <v>1</v>
+      </c>
+      <c r="G67">
+        <v>2</v>
+      </c>
+      <c r="I67">
+        <v>1</v>
+      </c>
+      <c r="J67">
+        <v>1</v>
+      </c>
+      <c r="K67">
+        <v>1</v>
+      </c>
+      <c r="L67">
+        <v>1</v>
+      </c>
+      <c r="M67">
+        <v>1</v>
+      </c>
+      <c r="P67">
+        <v>1</v>
+      </c>
+      <c r="R67">
+        <v>1</v>
+      </c>
+      <c r="S67">
+        <v>4</v>
+      </c>
+      <c r="T67">
+        <v>1</v>
+      </c>
+      <c r="V67">
+        <v>1</v>
+      </c>
+      <c r="W67">
+        <v>2</v>
+      </c>
+      <c r="Z67">
+        <v>2</v>
+      </c>
+      <c r="AA67">
+        <v>1</v>
+      </c>
+      <c r="AB67">
+        <v>4</v>
+      </c>
+      <c r="AC67">
+        <v>1</v>
+      </c>
+      <c r="AD67">
+        <v>1</v>
+      </c>
+      <c r="AX67">
+        <v>1</v>
+      </c>
+      <c r="AY67">
+        <v>1</v>
+      </c>
+      <c r="AZ67">
+        <v>2</v>
+      </c>
+      <c r="BD67">
+        <v>1</v>
+      </c>
+      <c r="BF67">
+        <v>1</v>
+      </c>
+      <c r="BH67">
+        <v>1</v>
+      </c>
+      <c r="BI67">
+        <v>1</v>
+      </c>
+      <c r="BJ67">
+        <v>2</v>
+      </c>
+      <c r="BK67">
+        <v>1</v>
+      </c>
+      <c r="BL67">
+        <v>2</v>
+      </c>
+      <c r="BM67">
+        <v>2</v>
+      </c>
+      <c r="BN67">
+        <v>2</v>
+      </c>
+      <c r="BO67">
+        <v>1</v>
+      </c>
+      <c r="BP67">
+        <v>1</v>
+      </c>
+      <c r="BR67">
+        <v>1</v>
+      </c>
+      <c r="BS67">
+        <v>2</v>
+      </c>
+      <c r="BU67">
+        <v>2</v>
+      </c>
+      <c r="BV67">
+        <v>1</v>
+      </c>
+      <c r="BX67">
+        <v>1</v>
+      </c>
+      <c r="BY67">
+        <v>2</v>
+      </c>
+      <c r="BZ67">
+        <v>2</v>
+      </c>
+      <c r="CA67">
+        <v>2</v>
+      </c>
+      <c r="CB67">
+        <v>2</v>
+      </c>
+      <c r="CC67">
+        <v>4</v>
+      </c>
+      <c r="CD67">
+        <v>5</v>
+      </c>
+      <c r="CG67">
+        <v>1</v>
+      </c>
+      <c r="CH67">
+        <v>1</v>
+      </c>
+      <c r="CI67">
+        <v>2</v>
+      </c>
+      <c r="CJ67">
+        <v>5</v>
+      </c>
+      <c r="CN67">
+        <v>1</v>
+      </c>
+      <c r="CO67">
+        <v>1</v>
+      </c>
+      <c r="CQ67">
+        <v>1</v>
       </c>
     </row>
     <row r="68" spans="1:95" x14ac:dyDescent="0.35">
       <c r="A68" t="s">
-        <v>138</v>
-      </c>
-      <c r="BN68">
+        <v>120</v>
+      </c>
+      <c r="AN68">
         <v>3</v>
-      </c>
-      <c r="BO68">
-        <v>2</v>
-      </c>
-      <c r="BQ68">
-        <v>2</v>
       </c>
     </row>
     <row r="69" spans="1:95" x14ac:dyDescent="0.35">
       <c r="A69" t="s">
-        <v>59</v>
-      </c>
-      <c r="B69">
-        <v>2</v>
-      </c>
-      <c r="BF69">
-        <v>1</v>
-      </c>
-      <c r="BT69">
+        <v>138</v>
+      </c>
+      <c r="BN69">
+        <v>3</v>
+      </c>
+      <c r="BO69">
+        <v>2</v>
+      </c>
+      <c r="BQ69">
         <v>2</v>
       </c>
     </row>
     <row r="70" spans="1:95" x14ac:dyDescent="0.35">
       <c r="A70" t="s">
-        <v>95</v>
-      </c>
-      <c r="Q70">
-        <v>1</v>
-      </c>
-      <c r="U70">
-        <v>1</v>
-      </c>
-      <c r="W70">
-        <v>1</v>
-      </c>
-      <c r="X70">
-        <v>3</v>
-      </c>
-      <c r="Y70">
-        <v>1</v>
-      </c>
-      <c r="Z70">
-        <v>1</v>
+        <v>59</v>
+      </c>
+      <c r="B70">
+        <v>2</v>
+      </c>
+      <c r="BF70">
+        <v>1</v>
+      </c>
+      <c r="BT70">
+        <v>2</v>
       </c>
     </row>
     <row r="71" spans="1:95" x14ac:dyDescent="0.35">
       <c r="A71" t="s">
-        <v>94</v>
+        <v>95</v>
+      </c>
+      <c r="Q71">
+        <v>1</v>
+      </c>
+      <c r="U71">
+        <v>1</v>
+      </c>
+      <c r="W71">
+        <v>1</v>
+      </c>
+      <c r="X71">
+        <v>3</v>
+      </c>
+      <c r="Y71">
+        <v>1</v>
+      </c>
+      <c r="Z71">
+        <v>1</v>
       </c>
     </row>
     <row r="72" spans="1:95" x14ac:dyDescent="0.35">
       <c r="A72" t="s">
-        <v>171</v>
+        <v>94</v>
       </c>
     </row>
     <row r="73" spans="1:95" x14ac:dyDescent="0.35">
       <c r="A73" t="s">
-        <v>162</v>
+        <v>171</v>
       </c>
     </row>
     <row r="74" spans="1:95" x14ac:dyDescent="0.35">
       <c r="A74" t="s">
-        <v>11</v>
+        <v>162</v>
       </c>
     </row>
     <row r="75" spans="1:95" x14ac:dyDescent="0.35">
       <c r="A75" t="s">
-        <v>54</v>
-      </c>
-      <c r="B75">
-        <v>2</v>
-      </c>
-      <c r="C75">
-        <v>1</v>
-      </c>
-      <c r="D75">
-        <v>1</v>
-      </c>
-      <c r="E75">
-        <v>1</v>
-      </c>
-      <c r="F75">
-        <v>3</v>
-      </c>
-      <c r="G75">
-        <v>2</v>
-      </c>
-      <c r="H75">
-        <v>3</v>
-      </c>
-      <c r="J75">
-        <v>1</v>
-      </c>
-      <c r="K75">
-        <v>1</v>
-      </c>
-      <c r="M75">
-        <v>3</v>
-      </c>
-      <c r="N75">
-        <v>4</v>
-      </c>
-      <c r="X75">
-        <v>6</v>
-      </c>
-      <c r="Y75">
-        <v>5</v>
-      </c>
-      <c r="Z75">
-        <v>1</v>
-      </c>
-      <c r="AD75">
-        <v>2</v>
-      </c>
-      <c r="AG75">
-        <v>3</v>
-      </c>
-      <c r="AJ75">
-        <v>2</v>
-      </c>
-      <c r="AM75">
-        <v>2</v>
-      </c>
-      <c r="AO75">
-        <v>3</v>
-      </c>
-      <c r="AQ75">
-        <v>2</v>
-      </c>
-      <c r="AT75">
-        <v>1</v>
-      </c>
-      <c r="AU75">
-        <v>4</v>
-      </c>
-      <c r="AV75">
-        <v>2</v>
-      </c>
-      <c r="AX75">
-        <v>1</v>
-      </c>
-      <c r="AY75">
-        <v>2</v>
-      </c>
-      <c r="AZ75">
-        <v>1</v>
-      </c>
-      <c r="BA75">
-        <v>4</v>
-      </c>
-      <c r="BB75">
-        <v>2</v>
-      </c>
-      <c r="BH75">
-        <v>1</v>
-      </c>
-      <c r="BR75">
-        <v>2</v>
+        <v>11</v>
       </c>
     </row>
     <row r="76" spans="1:95" x14ac:dyDescent="0.35">
       <c r="A76" t="s">
-        <v>20</v>
+        <v>54</v>
+      </c>
+      <c r="B76">
+        <v>2</v>
+      </c>
+      <c r="C76">
+        <v>1</v>
+      </c>
+      <c r="D76">
+        <v>1</v>
+      </c>
+      <c r="E76">
+        <v>1</v>
+      </c>
+      <c r="F76">
+        <v>3</v>
+      </c>
+      <c r="G76">
+        <v>2</v>
+      </c>
+      <c r="H76">
+        <v>3</v>
+      </c>
+      <c r="J76">
+        <v>1</v>
+      </c>
+      <c r="K76">
+        <v>1</v>
+      </c>
+      <c r="M76">
+        <v>3</v>
+      </c>
+      <c r="N76">
+        <v>4</v>
+      </c>
+      <c r="X76">
+        <v>6</v>
+      </c>
+      <c r="Y76">
+        <v>5</v>
+      </c>
+      <c r="Z76">
+        <v>1</v>
+      </c>
+      <c r="AD76">
+        <v>2</v>
+      </c>
+      <c r="AG76">
+        <v>3</v>
+      </c>
+      <c r="AJ76">
+        <v>2</v>
+      </c>
+      <c r="AM76">
+        <v>2</v>
+      </c>
+      <c r="AO76">
+        <v>3</v>
+      </c>
+      <c r="AQ76">
+        <v>2</v>
+      </c>
+      <c r="AT76">
+        <v>1</v>
+      </c>
+      <c r="AU76">
+        <v>4</v>
+      </c>
+      <c r="AV76">
+        <v>2</v>
+      </c>
+      <c r="AX76">
+        <v>1</v>
+      </c>
+      <c r="AY76">
+        <v>2</v>
+      </c>
+      <c r="AZ76">
+        <v>1</v>
+      </c>
+      <c r="BA76">
+        <v>4</v>
+      </c>
+      <c r="BB76">
+        <v>2</v>
+      </c>
+      <c r="BH76">
+        <v>1</v>
+      </c>
+      <c r="BR76">
+        <v>2</v>
       </c>
     </row>
     <row r="77" spans="1:95" x14ac:dyDescent="0.35">
       <c r="A77" t="s">
-        <v>80</v>
-      </c>
-      <c r="G77">
-        <v>3</v>
-      </c>
-      <c r="K77">
-        <v>1</v>
-      </c>
-      <c r="BG77">
-        <v>2</v>
-      </c>
-      <c r="BN77">
-        <v>4</v>
-      </c>
-      <c r="BP77">
-        <v>1</v>
-      </c>
-      <c r="BR77">
-        <v>2</v>
-      </c>
-      <c r="BS77">
-        <v>3</v>
-      </c>
-      <c r="BU77">
-        <v>3</v>
-      </c>
-      <c r="BV77">
-        <v>2</v>
-      </c>
-      <c r="BW77">
-        <v>2</v>
-      </c>
-      <c r="BX77">
-        <v>2</v>
-      </c>
-      <c r="BY77">
-        <v>2</v>
+        <v>20</v>
       </c>
     </row>
     <row r="78" spans="1:95" x14ac:dyDescent="0.35">
       <c r="A78" t="s">
-        <v>62</v>
-      </c>
-      <c r="B78">
-        <v>2</v>
-      </c>
-      <c r="D78">
-        <v>1</v>
-      </c>
-      <c r="AF78">
-        <v>2</v>
-      </c>
-      <c r="AQ78">
+        <v>80</v>
+      </c>
+      <c r="G78">
         <v>3</v>
       </c>
-      <c r="BF78">
-        <v>1</v>
-      </c>
-      <c r="BM78">
-        <v>1</v>
+      <c r="K78">
+        <v>1</v>
+      </c>
+      <c r="BG78">
+        <v>2</v>
+      </c>
+      <c r="BN78">
+        <v>4</v>
+      </c>
+      <c r="BP78">
+        <v>1</v>
+      </c>
+      <c r="BR78">
+        <v>2</v>
+      </c>
+      <c r="BS78">
+        <v>3</v>
+      </c>
+      <c r="BU78">
+        <v>3</v>
+      </c>
+      <c r="BV78">
+        <v>2</v>
       </c>
       <c r="BW78">
-        <v>1</v>
-      </c>
-      <c r="CB78">
-        <v>1</v>
-      </c>
-      <c r="CD78">
+        <v>2</v>
+      </c>
+      <c r="BX78">
+        <v>2</v>
+      </c>
+      <c r="BY78">
         <v>2</v>
       </c>
     </row>
     <row r="79" spans="1:95" x14ac:dyDescent="0.35">
       <c r="A79" t="s">
-        <v>82</v>
+        <v>62</v>
+      </c>
+      <c r="B79">
+        <v>2</v>
+      </c>
+      <c r="D79">
+        <v>1</v>
+      </c>
+      <c r="AF79">
+        <v>2</v>
+      </c>
+      <c r="AQ79">
+        <v>3</v>
+      </c>
+      <c r="BF79">
+        <v>1</v>
+      </c>
+      <c r="BM79">
+        <v>1</v>
+      </c>
+      <c r="BW79">
+        <v>1</v>
+      </c>
+      <c r="CB79">
+        <v>1</v>
+      </c>
+      <c r="CD79">
+        <v>2</v>
       </c>
     </row>
     <row r="80" spans="1:95" x14ac:dyDescent="0.35">
       <c r="A80" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="81" spans="1:96" x14ac:dyDescent="0.35">
+      <c r="A81" t="s">
         <v>153</v>
       </c>
     </row>
-    <row r="81" spans="1:95" x14ac:dyDescent="0.35">
-      <c r="A81" t="s">
+    <row r="82" spans="1:96" x14ac:dyDescent="0.35">
+      <c r="A82" t="s">
         <v>21</v>
       </c>
-      <c r="Y81">
-        <v>1</v>
-      </c>
-      <c r="AB81">
-        <v>2</v>
-      </c>
-      <c r="AD81">
+      <c r="Y82">
+        <v>1</v>
+      </c>
+      <c r="AB82">
+        <v>2</v>
+      </c>
+      <c r="AD82">
         <v>3</v>
       </c>
-      <c r="AI81">
-        <v>1</v>
-      </c>
-      <c r="AR81">
+      <c r="AI82">
+        <v>1</v>
+      </c>
+      <c r="AR82">
         <v>4</v>
       </c>
-      <c r="AV81">
+      <c r="AV82">
         <v>3</v>
       </c>
-      <c r="BA81">
-        <v>2</v>
-      </c>
-      <c r="BB81">
-        <v>5</v>
-      </c>
-      <c r="BE81">
+      <c r="BA82">
+        <v>2</v>
+      </c>
+      <c r="BB82">
+        <v>5</v>
+      </c>
+      <c r="BE82">
         <v>6</v>
       </c>
-      <c r="BS81">
-        <v>1</v>
-      </c>
-      <c r="BT81">
-        <v>1</v>
-      </c>
-      <c r="BU81">
-        <v>2</v>
-      </c>
-      <c r="BV81">
+      <c r="BS82">
+        <v>1</v>
+      </c>
+      <c r="BT82">
+        <v>1</v>
+      </c>
+      <c r="BU82">
+        <v>2</v>
+      </c>
+      <c r="BV82">
         <v>3</v>
       </c>
-      <c r="BX81">
-        <v>2</v>
-      </c>
-      <c r="CC81">
-        <v>2</v>
-      </c>
-      <c r="CG81">
-        <v>1</v>
-      </c>
-      <c r="CI81">
-        <v>1</v>
-      </c>
-      <c r="CM81">
+      <c r="BX82">
+        <v>2</v>
+      </c>
+      <c r="CC82">
+        <v>2</v>
+      </c>
+      <c r="CG82">
+        <v>1</v>
+      </c>
+      <c r="CI82">
+        <v>1</v>
+      </c>
+      <c r="CM82">
         <v>3</v>
       </c>
-      <c r="CP81">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="82" spans="1:95" x14ac:dyDescent="0.35">
-      <c r="A82" t="s">
+      <c r="CP82">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="83" spans="1:96" x14ac:dyDescent="0.35">
+      <c r="A83" t="s">
         <v>108</v>
       </c>
-      <c r="CP82">
-        <v>1</v>
-      </c>
-      <c r="CQ82">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="83" spans="1:95" x14ac:dyDescent="0.35">
-      <c r="A83" t="s">
+      <c r="CP83">
+        <v>1</v>
+      </c>
+      <c r="CQ83">
+        <v>1</v>
+      </c>
+      <c r="CR83">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="84" spans="1:96" x14ac:dyDescent="0.35">
+      <c r="A84" t="s">
         <v>127</v>
       </c>
-      <c r="AU83">
-        <v>1</v>
-      </c>
-      <c r="AV83">
-        <v>1</v>
-      </c>
-      <c r="AW83">
+      <c r="AU84">
+        <v>1</v>
+      </c>
+      <c r="AV84">
+        <v>1</v>
+      </c>
+      <c r="AW84">
         <v>3</v>
       </c>
-      <c r="AX83">
-        <v>1</v>
-      </c>
-      <c r="AZ83">
-        <v>1</v>
-      </c>
-      <c r="BC83">
-        <v>2</v>
-      </c>
-      <c r="BX83">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="84" spans="1:95" x14ac:dyDescent="0.35">
-      <c r="A84" t="s">
+      <c r="AX84">
+        <v>1</v>
+      </c>
+      <c r="AZ84">
+        <v>1</v>
+      </c>
+      <c r="BC84">
+        <v>2</v>
+      </c>
+      <c r="BX84">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="85" spans="1:96" x14ac:dyDescent="0.35">
+      <c r="A85" t="s">
         <v>43</v>
       </c>
-      <c r="N84">
+      <c r="N85">
         <v>3</v>
       </c>
-      <c r="S84">
-        <v>2</v>
-      </c>
-      <c r="AG84">
-        <v>2</v>
-      </c>
-      <c r="AI84">
-        <v>1</v>
-      </c>
-      <c r="AP84">
-        <v>2</v>
-      </c>
-      <c r="AQ84">
-        <v>1</v>
-      </c>
-      <c r="AR84">
+      <c r="S85">
+        <v>2</v>
+      </c>
+      <c r="AG85">
+        <v>2</v>
+      </c>
+      <c r="AI85">
+        <v>1</v>
+      </c>
+      <c r="AP85">
+        <v>2</v>
+      </c>
+      <c r="AQ85">
+        <v>1</v>
+      </c>
+      <c r="AR85">
         <v>3</v>
       </c>
-      <c r="AW84">
-        <v>1</v>
-      </c>
-      <c r="BA84">
-        <v>1</v>
-      </c>
-      <c r="BE84">
-        <v>1</v>
-      </c>
-      <c r="BI84">
-        <v>2</v>
-      </c>
-      <c r="BL84">
-        <v>2</v>
-      </c>
-      <c r="BN84">
-        <v>2</v>
-      </c>
-      <c r="BO84">
-        <v>1</v>
-      </c>
-      <c r="BP84">
-        <v>1</v>
-      </c>
-      <c r="BR84">
-        <v>1</v>
-      </c>
-      <c r="CH84">
-        <v>1</v>
-      </c>
-      <c r="CJ84">
-        <v>1</v>
-      </c>
-      <c r="CL84">
-        <v>1</v>
-      </c>
-      <c r="CM84">
-        <v>1</v>
-      </c>
-      <c r="CN84">
-        <v>1</v>
-      </c>
-      <c r="CO84">
-        <v>1</v>
-      </c>
-      <c r="CP84">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="85" spans="1:95" x14ac:dyDescent="0.35">
-      <c r="A85" t="s">
+      <c r="AW85">
+        <v>1</v>
+      </c>
+      <c r="BA85">
+        <v>1</v>
+      </c>
+      <c r="BE85">
+        <v>1</v>
+      </c>
+      <c r="BI85">
+        <v>2</v>
+      </c>
+      <c r="BL85">
+        <v>2</v>
+      </c>
+      <c r="BN85">
+        <v>2</v>
+      </c>
+      <c r="BO85">
+        <v>1</v>
+      </c>
+      <c r="BP85">
+        <v>1</v>
+      </c>
+      <c r="BR85">
+        <v>1</v>
+      </c>
+      <c r="CH85">
+        <v>1</v>
+      </c>
+      <c r="CJ85">
+        <v>1</v>
+      </c>
+      <c r="CL85">
+        <v>1</v>
+      </c>
+      <c r="CM85">
+        <v>1</v>
+      </c>
+      <c r="CN85">
+        <v>1</v>
+      </c>
+      <c r="CO85">
+        <v>1</v>
+      </c>
+      <c r="CP85">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="86" spans="1:96" x14ac:dyDescent="0.35">
+      <c r="A86" t="s">
         <v>130</v>
       </c>
-      <c r="BF85">
-        <v>1</v>
-      </c>
-      <c r="BG85">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="86" spans="1:95" x14ac:dyDescent="0.35">
-      <c r="A86" t="s">
+      <c r="BF86">
+        <v>1</v>
+      </c>
+      <c r="BG86">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="87" spans="1:96" x14ac:dyDescent="0.35">
+      <c r="A87" t="s">
         <v>8</v>
       </c>
-      <c r="B86">
-        <v>1</v>
-      </c>
-      <c r="H86">
-        <v>1</v>
-      </c>
-      <c r="J86">
-        <v>2</v>
-      </c>
-      <c r="Q86">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="87" spans="1:95" x14ac:dyDescent="0.35">
-      <c r="A87" t="s">
+      <c r="B87">
+        <v>1</v>
+      </c>
+      <c r="H87">
+        <v>1</v>
+      </c>
+      <c r="J87">
+        <v>2</v>
+      </c>
+      <c r="Q87">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="88" spans="1:96" x14ac:dyDescent="0.35">
+      <c r="A88" t="s">
         <v>81</v>
       </c>
-      <c r="B87">
-        <v>2</v>
-      </c>
-      <c r="C87">
-        <v>2</v>
-      </c>
-      <c r="D87">
-        <v>1</v>
-      </c>
-      <c r="E87">
-        <v>2</v>
-      </c>
-      <c r="F87">
-        <v>1</v>
-      </c>
-      <c r="G87">
-        <v>2</v>
-      </c>
-      <c r="H87">
-        <v>2</v>
-      </c>
-      <c r="I87">
+      <c r="B88">
+        <v>2</v>
+      </c>
+      <c r="C88">
+        <v>2</v>
+      </c>
+      <c r="D88">
+        <v>1</v>
+      </c>
+      <c r="E88">
+        <v>2</v>
+      </c>
+      <c r="F88">
+        <v>1</v>
+      </c>
+      <c r="G88">
+        <v>2</v>
+      </c>
+      <c r="H88">
+        <v>2</v>
+      </c>
+      <c r="I88">
         <v>3</v>
       </c>
-      <c r="J87">
+      <c r="J88">
         <v>4</v>
       </c>
-      <c r="L87">
+      <c r="L88">
         <v>4</v>
       </c>
-      <c r="M87">
-        <v>1</v>
-      </c>
-      <c r="N87">
-        <v>2</v>
-      </c>
-      <c r="O87">
-        <v>1</v>
-      </c>
-      <c r="P87">
-        <v>1</v>
-      </c>
-      <c r="Q87">
-        <v>1</v>
-      </c>
-      <c r="R87">
+      <c r="M88">
+        <v>1</v>
+      </c>
+      <c r="N88">
+        <v>2</v>
+      </c>
+      <c r="O88">
+        <v>1</v>
+      </c>
+      <c r="P88">
+        <v>1</v>
+      </c>
+      <c r="Q88">
+        <v>1</v>
+      </c>
+      <c r="R88">
         <v>3</v>
       </c>
-      <c r="S87">
+      <c r="S88">
         <v>3</v>
       </c>
-      <c r="U87">
+      <c r="U88">
         <v>3</v>
       </c>
-      <c r="V87">
-        <v>1</v>
-      </c>
-      <c r="W87">
+      <c r="V88">
+        <v>1</v>
+      </c>
+      <c r="W88">
         <v>3</v>
       </c>
-      <c r="AC87">
-        <v>1</v>
-      </c>
-      <c r="AF87">
-        <v>1</v>
-      </c>
-      <c r="AH87">
-        <v>2</v>
-      </c>
-      <c r="AI87">
+      <c r="AC88">
+        <v>1</v>
+      </c>
+      <c r="AF88">
+        <v>1</v>
+      </c>
+      <c r="AH88">
+        <v>2</v>
+      </c>
+      <c r="AI88">
         <v>3</v>
       </c>
-      <c r="AJ87">
-        <v>1</v>
-      </c>
-      <c r="AK87">
+      <c r="AJ88">
+        <v>1</v>
+      </c>
+      <c r="AK88">
         <v>4</v>
       </c>
-      <c r="AL87">
+      <c r="AL88">
         <v>3</v>
       </c>
-      <c r="AN87">
-        <v>1</v>
-      </c>
-      <c r="AP87">
-        <v>2</v>
-      </c>
-      <c r="AT87">
-        <v>2</v>
-      </c>
-      <c r="AU87">
+      <c r="AN88">
+        <v>1</v>
+      </c>
+      <c r="AP88">
+        <v>2</v>
+      </c>
+      <c r="AT88">
+        <v>2</v>
+      </c>
+      <c r="AU88">
         <v>3</v>
       </c>
-      <c r="AV87">
-        <v>1</v>
-      </c>
-      <c r="AW87">
-        <v>1</v>
-      </c>
-      <c r="AX87">
-        <v>1</v>
-      </c>
-      <c r="AY87">
-        <v>1</v>
-      </c>
-      <c r="AZ87">
-        <v>2</v>
-      </c>
-      <c r="BC87">
-        <v>2</v>
-      </c>
-      <c r="BD87">
-        <v>1</v>
-      </c>
-      <c r="BF87">
-        <v>2</v>
-      </c>
-      <c r="BH87">
+      <c r="AV88">
+        <v>1</v>
+      </c>
+      <c r="AW88">
+        <v>1</v>
+      </c>
+      <c r="AX88">
+        <v>1</v>
+      </c>
+      <c r="AY88">
+        <v>1</v>
+      </c>
+      <c r="AZ88">
+        <v>2</v>
+      </c>
+      <c r="BC88">
+        <v>2</v>
+      </c>
+      <c r="BD88">
+        <v>1</v>
+      </c>
+      <c r="BF88">
+        <v>2</v>
+      </c>
+      <c r="BH88">
         <v>3</v>
       </c>
-      <c r="BI87">
-        <v>1</v>
-      </c>
-      <c r="BJ87">
-        <v>2</v>
-      </c>
-      <c r="BK87">
+      <c r="BI88">
+        <v>1</v>
+      </c>
+      <c r="BJ88">
+        <v>2</v>
+      </c>
+      <c r="BK88">
         <v>3</v>
       </c>
-      <c r="BM87">
-        <v>2</v>
-      </c>
-      <c r="BN87">
+      <c r="BM88">
+        <v>2</v>
+      </c>
+      <c r="BN88">
         <v>3</v>
       </c>
-      <c r="BU87">
-        <v>1</v>
-      </c>
-      <c r="BV87">
+      <c r="BU88">
+        <v>1</v>
+      </c>
+      <c r="BV88">
         <v>3</v>
       </c>
-      <c r="BX87">
-        <v>2</v>
-      </c>
-      <c r="BY87">
-        <v>1</v>
-      </c>
-      <c r="BZ87">
-        <v>1</v>
-      </c>
-      <c r="CA87">
-        <v>1</v>
-      </c>
-      <c r="CB87">
-        <v>1</v>
-      </c>
-      <c r="CD87">
+      <c r="BX88">
+        <v>2</v>
+      </c>
+      <c r="BY88">
+        <v>1</v>
+      </c>
+      <c r="BZ88">
+        <v>1</v>
+      </c>
+      <c r="CA88">
+        <v>1</v>
+      </c>
+      <c r="CB88">
+        <v>1</v>
+      </c>
+      <c r="CD88">
         <v>3</v>
       </c>
-      <c r="CG87">
-        <v>1</v>
-      </c>
-      <c r="CH87">
-        <v>2</v>
-      </c>
-      <c r="CL87">
-        <v>2</v>
-      </c>
-      <c r="CP87">
-        <v>1</v>
-      </c>
-      <c r="CQ87">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="88" spans="1:95" x14ac:dyDescent="0.35">
-      <c r="A88" t="s">
+      <c r="CG88">
+        <v>1</v>
+      </c>
+      <c r="CH88">
+        <v>2</v>
+      </c>
+      <c r="CL88">
+        <v>2</v>
+      </c>
+      <c r="CP88">
+        <v>1</v>
+      </c>
+      <c r="CQ88">
+        <v>1</v>
+      </c>
+      <c r="CR88">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="89" spans="1:96" x14ac:dyDescent="0.35">
+      <c r="A89" t="s">
         <v>172</v>
       </c>
     </row>
-    <row r="89" spans="1:95" x14ac:dyDescent="0.35">
-      <c r="A89" t="s">
+    <row r="90" spans="1:96" x14ac:dyDescent="0.35">
+      <c r="A90" t="s">
         <v>48</v>
       </c>
-      <c r="G89">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="90" spans="1:95" x14ac:dyDescent="0.35">
-      <c r="A90" t="s">
+      <c r="G90">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="91" spans="1:96" x14ac:dyDescent="0.35">
+      <c r="A91" t="s">
         <v>155</v>
       </c>
     </row>
-    <row r="91" spans="1:95" x14ac:dyDescent="0.35">
-      <c r="A91" t="s">
+    <row r="92" spans="1:96" x14ac:dyDescent="0.35">
+      <c r="A92" t="s">
         <v>141</v>
       </c>
-      <c r="BZ91">
-        <v>5</v>
-      </c>
-      <c r="CA91">
-        <v>2</v>
-      </c>
-      <c r="CB91">
-        <v>1</v>
-      </c>
-      <c r="CJ91">
+      <c r="BZ92">
+        <v>5</v>
+      </c>
+      <c r="CA92">
+        <v>2</v>
+      </c>
+      <c r="CB92">
+        <v>1</v>
+      </c>
+      <c r="CJ92">
         <v>3</v>
       </c>
     </row>
-    <row r="92" spans="1:95" x14ac:dyDescent="0.35">
-      <c r="A92" t="s">
+    <row r="93" spans="1:96" x14ac:dyDescent="0.35">
+      <c r="A93" t="s">
         <v>84</v>
       </c>
-      <c r="K92">
+      <c r="K93">
         <v>4</v>
       </c>
-      <c r="L92">
-        <v>2</v>
-      </c>
-      <c r="M92">
-        <v>5</v>
-      </c>
-      <c r="CP92">
-        <v>2</v>
-      </c>
-      <c r="CQ92">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="93" spans="1:95" x14ac:dyDescent="0.35">
-      <c r="A93" t="s">
-        <v>5</v>
-      </c>
-      <c r="B93">
-        <v>1</v>
-      </c>
-      <c r="C93">
-        <v>2</v>
-      </c>
-      <c r="D93">
-        <v>2</v>
-      </c>
-      <c r="E93">
+      <c r="L93">
+        <v>2</v>
+      </c>
+      <c r="M93">
+        <v>5</v>
+      </c>
+      <c r="CP93">
+        <v>2</v>
+      </c>
+      <c r="CQ93">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="94" spans="1:96" x14ac:dyDescent="0.35">
+      <c r="A94" t="s">
+        <v>5</v>
+      </c>
+      <c r="B94">
+        <v>1</v>
+      </c>
+      <c r="C94">
+        <v>2</v>
+      </c>
+      <c r="D94">
+        <v>2</v>
+      </c>
+      <c r="E94">
         <v>3</v>
       </c>
-      <c r="F93">
-        <v>2</v>
-      </c>
-      <c r="G93">
+      <c r="F94">
+        <v>2</v>
+      </c>
+      <c r="G94">
         <v>3</v>
       </c>
-      <c r="H93">
-        <v>1</v>
-      </c>
-      <c r="M93">
+      <c r="H94">
+        <v>1</v>
+      </c>
+      <c r="M94">
         <v>4</v>
       </c>
-      <c r="N93">
+      <c r="N94">
         <v>6</v>
       </c>
-      <c r="P93">
-        <v>2</v>
-      </c>
-      <c r="Q93">
-        <v>1</v>
-      </c>
-      <c r="R93">
-        <v>2</v>
-      </c>
-      <c r="S93">
+      <c r="P94">
+        <v>2</v>
+      </c>
+      <c r="Q94">
+        <v>1</v>
+      </c>
+      <c r="R94">
+        <v>2</v>
+      </c>
+      <c r="S94">
         <v>3</v>
       </c>
-      <c r="V93">
-        <v>2</v>
-      </c>
-      <c r="W93">
-        <v>1</v>
-      </c>
-      <c r="X93">
-        <v>1</v>
-      </c>
-      <c r="Y93">
+      <c r="V94">
+        <v>2</v>
+      </c>
+      <c r="W94">
+        <v>1</v>
+      </c>
+      <c r="X94">
+        <v>1</v>
+      </c>
+      <c r="Y94">
         <v>4</v>
       </c>
-      <c r="Z93">
-        <v>5</v>
-      </c>
-      <c r="AA93">
-        <v>1</v>
-      </c>
-      <c r="AB93">
+      <c r="Z94">
+        <v>5</v>
+      </c>
+      <c r="AA94">
+        <v>1</v>
+      </c>
+      <c r="AB94">
         <v>3</v>
       </c>
-      <c r="AC93">
+      <c r="AC94">
         <v>4</v>
       </c>
-      <c r="AD93">
+      <c r="AD94">
         <v>3</v>
       </c>
-      <c r="AE93">
+      <c r="AE94">
         <v>3</v>
       </c>
-      <c r="AF93">
-        <v>2</v>
-      </c>
-      <c r="AG93">
-        <v>5</v>
-      </c>
-      <c r="AH93">
+      <c r="AF94">
+        <v>2</v>
+      </c>
+      <c r="AG94">
+        <v>5</v>
+      </c>
+      <c r="AH94">
         <v>7</v>
       </c>
-      <c r="AI93">
+      <c r="AI94">
         <v>3</v>
       </c>
-      <c r="AJ93">
-        <v>1</v>
-      </c>
-      <c r="AK93">
-        <v>1</v>
-      </c>
-      <c r="AL93">
+      <c r="AJ94">
+        <v>1</v>
+      </c>
+      <c r="AK94">
+        <v>1</v>
+      </c>
+      <c r="AL94">
         <v>6</v>
       </c>
-      <c r="AR93">
+      <c r="AR94">
         <v>3</v>
       </c>
-      <c r="AS93">
-        <v>2</v>
-      </c>
-      <c r="AV93">
-        <v>2</v>
-      </c>
-      <c r="AW93">
-        <v>1</v>
-      </c>
-      <c r="AX93">
+      <c r="AS94">
+        <v>2</v>
+      </c>
+      <c r="AV94">
+        <v>2</v>
+      </c>
+      <c r="AW94">
+        <v>1</v>
+      </c>
+      <c r="AX94">
         <v>4</v>
       </c>
-      <c r="AY93">
+      <c r="AY94">
         <v>3</v>
       </c>
-      <c r="AZ93">
+      <c r="AZ94">
         <v>4</v>
       </c>
-      <c r="BA93">
-        <v>5</v>
-      </c>
-      <c r="BB93">
+      <c r="BA94">
+        <v>5</v>
+      </c>
+      <c r="BB94">
         <v>6</v>
       </c>
-      <c r="BC93">
-        <v>2</v>
-      </c>
-      <c r="BD93">
-        <v>2</v>
-      </c>
-      <c r="BE93">
+      <c r="BC94">
+        <v>2</v>
+      </c>
+      <c r="BD94">
+        <v>2</v>
+      </c>
+      <c r="BE94">
         <v>7</v>
       </c>
-      <c r="BG93">
+      <c r="BG94">
         <v>4</v>
       </c>
-      <c r="BH93">
+      <c r="BH94">
         <v>3</v>
       </c>
-      <c r="BI93">
+      <c r="BI94">
         <v>4</v>
       </c>
-      <c r="BK93">
-        <v>1</v>
-      </c>
-      <c r="BL93">
+      <c r="BK94">
+        <v>1</v>
+      </c>
+      <c r="BL94">
         <v>8</v>
       </c>
-      <c r="BM93">
+      <c r="BM94">
         <v>4</v>
       </c>
-      <c r="BN93">
-        <v>5</v>
-      </c>
-      <c r="BO93">
+      <c r="BN94">
+        <v>5</v>
+      </c>
+      <c r="BO94">
         <v>3</v>
       </c>
-      <c r="BP93">
-        <v>1</v>
-      </c>
-      <c r="BQ93">
-        <v>1</v>
-      </c>
-      <c r="BR93">
+      <c r="BP94">
+        <v>1</v>
+      </c>
+      <c r="BQ94">
+        <v>1</v>
+      </c>
+      <c r="BR94">
         <v>3</v>
       </c>
-      <c r="BS93">
-        <v>1</v>
-      </c>
-      <c r="CF93">
+      <c r="BS94">
+        <v>1</v>
+      </c>
+      <c r="CF94">
         <v>4</v>
       </c>
-      <c r="CG93">
+      <c r="CG94">
         <v>4</v>
       </c>
-      <c r="CH93">
+      <c r="CH94">
         <v>6</v>
       </c>
-      <c r="CI93">
-        <v>2</v>
-      </c>
-      <c r="CJ93">
+      <c r="CI94">
+        <v>2</v>
+      </c>
+      <c r="CJ94">
         <v>7</v>
       </c>
-      <c r="CL93">
+      <c r="CL94">
         <v>3</v>
       </c>
-      <c r="CM93">
+      <c r="CM94">
         <v>6</v>
       </c>
-      <c r="CN93">
-        <v>2</v>
-      </c>
-      <c r="CO93">
-        <v>1</v>
-      </c>
-      <c r="CP93">
-        <v>1</v>
-      </c>
-      <c r="CQ93">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="94" spans="1:95" x14ac:dyDescent="0.35">
-      <c r="A94" t="s">
+      <c r="CN94">
+        <v>2</v>
+      </c>
+      <c r="CO94">
+        <v>1</v>
+      </c>
+      <c r="CP94">
+        <v>1</v>
+      </c>
+      <c r="CQ94">
+        <v>1</v>
+      </c>
+      <c r="CR94">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="95" spans="1:96" x14ac:dyDescent="0.35">
+      <c r="A95" t="s">
         <v>44</v>
       </c>
-      <c r="K94">
-        <v>1</v>
-      </c>
-      <c r="BJ94">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="95" spans="1:95" x14ac:dyDescent="0.35">
-      <c r="A95" t="s">
+      <c r="K95">
+        <v>1</v>
+      </c>
+      <c r="BJ95">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="96" spans="1:96" x14ac:dyDescent="0.35">
+      <c r="A96" t="s">
         <v>118</v>
       </c>
-      <c r="B95">
-        <v>1</v>
-      </c>
-      <c r="D95">
-        <v>1</v>
-      </c>
-      <c r="E95">
+      <c r="B96">
+        <v>1</v>
+      </c>
+      <c r="D96">
+        <v>1</v>
+      </c>
+      <c r="E96">
         <v>3</v>
       </c>
-      <c r="O95">
-        <v>2</v>
-      </c>
-      <c r="P95">
-        <v>2</v>
-      </c>
-      <c r="Q95">
-        <v>1</v>
-      </c>
-      <c r="R95">
-        <v>1</v>
-      </c>
-      <c r="AD95">
-        <v>1</v>
-      </c>
-      <c r="AE95">
-        <v>1</v>
-      </c>
-      <c r="AG95">
-        <v>1</v>
-      </c>
-      <c r="AH95">
-        <v>2</v>
-      </c>
-      <c r="AL95">
+      <c r="O96">
+        <v>2</v>
+      </c>
+      <c r="P96">
+        <v>2</v>
+      </c>
+      <c r="Q96">
+        <v>1</v>
+      </c>
+      <c r="R96">
+        <v>1</v>
+      </c>
+      <c r="AD96">
+        <v>1</v>
+      </c>
+      <c r="AE96">
+        <v>1</v>
+      </c>
+      <c r="AG96">
+        <v>1</v>
+      </c>
+      <c r="AH96">
+        <v>2</v>
+      </c>
+      <c r="AL96">
         <v>3</v>
       </c>
-      <c r="AM95">
-        <v>2</v>
-      </c>
-      <c r="AN95">
-        <v>1</v>
-      </c>
-      <c r="AO95">
-        <v>1</v>
-      </c>
-      <c r="AR95">
-        <v>1</v>
-      </c>
-      <c r="AS95">
-        <v>1</v>
-      </c>
-      <c r="AT95">
-        <v>1</v>
-      </c>
-      <c r="AV95">
-        <v>1</v>
-      </c>
-      <c r="AW95">
-        <v>2</v>
-      </c>
-      <c r="BD95">
-        <v>1</v>
-      </c>
-      <c r="BF95">
-        <v>1</v>
-      </c>
-      <c r="BI95">
-        <v>1</v>
-      </c>
-      <c r="BU95">
-        <v>2</v>
-      </c>
-      <c r="BW95">
-        <v>2</v>
-      </c>
-      <c r="CB95">
-        <v>1</v>
-      </c>
-      <c r="CL95">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="96" spans="1:95" x14ac:dyDescent="0.35">
-      <c r="A96" t="s">
-        <v>106</v>
-      </c>
-      <c r="Z96">
+      <c r="AM96">
+        <v>2</v>
+      </c>
+      <c r="AN96">
+        <v>1</v>
+      </c>
+      <c r="AO96">
+        <v>1</v>
+      </c>
+      <c r="AR96">
+        <v>1</v>
+      </c>
+      <c r="AS96">
+        <v>1</v>
+      </c>
+      <c r="AT96">
+        <v>1</v>
+      </c>
+      <c r="AV96">
+        <v>1</v>
+      </c>
+      <c r="AW96">
+        <v>2</v>
+      </c>
+      <c r="BD96">
+        <v>1</v>
+      </c>
+      <c r="BF96">
+        <v>1</v>
+      </c>
+      <c r="BI96">
+        <v>1</v>
+      </c>
+      <c r="BU96">
+        <v>2</v>
+      </c>
+      <c r="BW96">
+        <v>2</v>
+      </c>
+      <c r="CB96">
+        <v>1</v>
+      </c>
+      <c r="CL96">
         <v>1</v>
       </c>
     </row>
     <row r="97" spans="1:95" x14ac:dyDescent="0.35">
       <c r="A97" t="s">
-        <v>159</v>
+        <v>106</v>
+      </c>
+      <c r="Z97">
+        <v>1</v>
       </c>
     </row>
     <row r="98" spans="1:95" x14ac:dyDescent="0.35">
       <c r="A98" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="99" spans="1:95" x14ac:dyDescent="0.35">
+      <c r="A99" t="s">
         <v>117</v>
       </c>
     </row>
-    <row r="99" spans="1:95" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A99" t="s">
+    <row r="100" spans="1:95" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A100" t="s">
         <v>46</v>
-      </c>
-    </row>
-    <row r="100" spans="1:95" x14ac:dyDescent="0.35">
-      <c r="A100" t="s">
-        <v>16</v>
-      </c>
-      <c r="F100">
-        <v>2</v>
-      </c>
-      <c r="J100">
-        <v>1</v>
-      </c>
-      <c r="K100">
-        <v>1</v>
       </c>
     </row>
     <row r="101" spans="1:95" x14ac:dyDescent="0.35">
       <c r="A101" t="s">
-        <v>165</v>
+        <v>16</v>
+      </c>
+      <c r="F101">
+        <v>2</v>
+      </c>
+      <c r="J101">
+        <v>1</v>
+      </c>
+      <c r="K101">
+        <v>1</v>
       </c>
     </row>
     <row r="102" spans="1:95" x14ac:dyDescent="0.35">
       <c r="A102" t="s">
-        <v>85</v>
-      </c>
-      <c r="K102">
-        <v>5</v>
+        <v>165</v>
       </c>
     </row>
     <row r="103" spans="1:95" x14ac:dyDescent="0.35">
       <c r="A103" t="s">
+        <v>85</v>
+      </c>
+      <c r="K103">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="104" spans="1:95" x14ac:dyDescent="0.35">
+      <c r="A104" t="s">
         <v>15</v>
       </c>
-      <c r="C103">
+      <c r="C104">
         <v>4</v>
       </c>
-      <c r="D103">
+      <c r="D104">
         <v>3</v>
       </c>
-      <c r="F103">
-        <v>2</v>
-      </c>
-      <c r="G103">
-        <v>5</v>
-      </c>
-      <c r="H103">
+      <c r="F104">
+        <v>2</v>
+      </c>
+      <c r="G104">
+        <v>5</v>
+      </c>
+      <c r="H104">
         <v>3</v>
       </c>
-      <c r="I103">
-        <v>2</v>
-      </c>
-      <c r="J103">
-        <v>5</v>
-      </c>
-      <c r="K103">
+      <c r="I104">
+        <v>2</v>
+      </c>
+      <c r="J104">
+        <v>5</v>
+      </c>
+      <c r="K104">
         <v>3</v>
       </c>
-      <c r="L103">
-        <v>2</v>
-      </c>
-      <c r="M103">
+      <c r="L104">
+        <v>2</v>
+      </c>
+      <c r="M104">
         <v>3</v>
       </c>
-      <c r="O103">
-        <v>5</v>
-      </c>
-      <c r="P103">
-        <v>5</v>
-      </c>
-      <c r="Q103">
+      <c r="O104">
+        <v>5</v>
+      </c>
+      <c r="P104">
+        <v>5</v>
+      </c>
+      <c r="Q104">
         <v>3</v>
       </c>
-      <c r="R103">
-        <v>2</v>
-      </c>
-      <c r="S103">
+      <c r="R104">
+        <v>2</v>
+      </c>
+      <c r="S104">
         <v>3</v>
       </c>
-      <c r="T103">
-        <v>1</v>
-      </c>
-      <c r="U103">
-        <v>1</v>
-      </c>
-      <c r="V103">
+      <c r="T104">
+        <v>1</v>
+      </c>
+      <c r="U104">
+        <v>1</v>
+      </c>
+      <c r="V104">
         <v>3</v>
       </c>
-      <c r="W103">
+      <c r="W104">
         <v>3</v>
       </c>
-      <c r="X103">
-        <v>5</v>
-      </c>
-      <c r="Y103">
+      <c r="X104">
+        <v>5</v>
+      </c>
+      <c r="Y104">
         <v>4</v>
       </c>
-      <c r="Z103">
-        <v>1</v>
-      </c>
-      <c r="AA103">
+      <c r="Z104">
+        <v>1</v>
+      </c>
+      <c r="AA104">
         <v>3</v>
       </c>
-      <c r="AC103">
-        <v>1</v>
-      </c>
-      <c r="AE103">
+      <c r="AC104">
+        <v>1</v>
+      </c>
+      <c r="AE104">
         <v>4</v>
       </c>
-      <c r="AF103">
-        <v>2</v>
-      </c>
-      <c r="AG103">
+      <c r="AF104">
+        <v>2</v>
+      </c>
+      <c r="AG104">
         <v>3</v>
       </c>
-      <c r="AH103">
-        <v>2</v>
-      </c>
-      <c r="AI103">
-        <v>2</v>
-      </c>
-      <c r="AJ103">
+      <c r="AH104">
+        <v>2</v>
+      </c>
+      <c r="AI104">
+        <v>2</v>
+      </c>
+      <c r="AJ104">
         <v>7</v>
       </c>
-      <c r="AK103">
+      <c r="AK104">
         <v>3</v>
       </c>
-      <c r="AL103">
-        <v>5</v>
-      </c>
-      <c r="AM103">
-        <v>1</v>
-      </c>
-      <c r="AN103">
+      <c r="AL104">
+        <v>5</v>
+      </c>
+      <c r="AM104">
+        <v>1</v>
+      </c>
+      <c r="AN104">
         <v>4</v>
       </c>
-      <c r="AO103">
+      <c r="AO104">
         <v>3</v>
       </c>
-      <c r="AP103">
+      <c r="AP104">
         <v>6</v>
       </c>
-      <c r="AQ103">
+      <c r="AQ104">
         <v>4</v>
       </c>
-      <c r="AR103">
-        <v>5</v>
-      </c>
-      <c r="AS103">
+      <c r="AR104">
+        <v>5</v>
+      </c>
+      <c r="AS104">
         <v>3</v>
       </c>
-      <c r="AT103">
-        <v>2</v>
-      </c>
-      <c r="AU103">
-        <v>2</v>
-      </c>
-      <c r="AW103">
+      <c r="AT104">
+        <v>2</v>
+      </c>
+      <c r="AU104">
+        <v>2</v>
+      </c>
+      <c r="AW104">
         <v>3</v>
       </c>
-      <c r="AY103">
-        <v>1</v>
-      </c>
-      <c r="AZ103">
+      <c r="AY104">
+        <v>1</v>
+      </c>
+      <c r="AZ104">
         <v>3</v>
       </c>
-      <c r="BB103">
+      <c r="BB104">
         <v>4</v>
       </c>
-      <c r="BC103">
+      <c r="BC104">
         <v>4</v>
       </c>
-      <c r="BD103">
+      <c r="BD104">
         <v>3</v>
       </c>
-      <c r="BF103">
-        <v>2</v>
-      </c>
-      <c r="BG103">
+      <c r="BF104">
+        <v>2</v>
+      </c>
+      <c r="BG104">
         <v>4</v>
       </c>
-      <c r="BH103">
-        <v>5</v>
-      </c>
-      <c r="BJ103">
+      <c r="BH104">
+        <v>5</v>
+      </c>
+      <c r="BJ104">
         <v>4</v>
       </c>
-      <c r="BK103">
-        <v>2</v>
-      </c>
-      <c r="BL103">
+      <c r="BK104">
+        <v>2</v>
+      </c>
+      <c r="BL104">
         <v>4</v>
       </c>
-      <c r="BM103">
-        <v>1</v>
-      </c>
-      <c r="BN103">
-        <v>2</v>
-      </c>
-      <c r="BO103">
+      <c r="BM104">
+        <v>1</v>
+      </c>
+      <c r="BN104">
+        <v>2</v>
+      </c>
+      <c r="BO104">
         <v>3</v>
       </c>
-      <c r="BS103">
+      <c r="BS104">
         <v>3</v>
       </c>
-      <c r="BT103">
+      <c r="BT104">
         <v>4</v>
       </c>
-      <c r="BU103">
+      <c r="BU104">
         <v>4</v>
       </c>
-      <c r="BV103">
+      <c r="BV104">
         <v>3</v>
       </c>
-      <c r="BX103">
-        <v>5</v>
-      </c>
-      <c r="BY103">
-        <v>2</v>
-      </c>
-      <c r="BZ103">
+      <c r="BX104">
+        <v>5</v>
+      </c>
+      <c r="BY104">
+        <v>2</v>
+      </c>
+      <c r="BZ104">
         <v>3</v>
       </c>
-      <c r="CA103">
-        <v>1</v>
-      </c>
-      <c r="CG103">
+      <c r="CA104">
+        <v>1</v>
+      </c>
+      <c r="CG104">
         <v>3</v>
       </c>
-      <c r="CH103">
+      <c r="CH104">
         <v>6</v>
       </c>
-      <c r="CI103">
+      <c r="CI104">
         <v>3</v>
       </c>
-      <c r="CJ103">
+      <c r="CJ104">
         <v>3</v>
       </c>
-      <c r="CK103">
+      <c r="CK104">
         <v>4</v>
       </c>
-      <c r="CL103">
+      <c r="CL104">
         <v>8</v>
       </c>
-      <c r="CM103">
-        <v>1</v>
-      </c>
-      <c r="CQ103">
+      <c r="CM104">
+        <v>1</v>
+      </c>
+      <c r="CQ104">
         <v>4</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:CN103" xr:uid="{E6D73437-9035-4F38-AC23-65184BC2B5F6}">
-    <sortState ref="A2:CN103">
-      <sortCondition ref="A1:A103"/>
+  <autoFilter ref="A1:CN104" xr:uid="{E6D73437-9035-4F38-AC23-65184BC2B5F6}">
+    <sortState ref="A2:CN104">
+      <sortCondition ref="A1:A104"/>
     </sortState>
   </autoFilter>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/data/condominio.xlsx
+++ b/data/condominio.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\pedrohamacher\OneDrive\Documentos antigo\Projetos_jl\Streamlit\Dashboard Pelada\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="28" documentId="14_{AFBA81A4-2B23-449D-B209-30A32CB7CB1E}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{EED607B5-2F2C-4CDC-8922-B2AB6296AA49}"/>
+  <xr:revisionPtr revIDLastSave="2" documentId="14_{635D4D17-85D7-4E05-9D0F-EB38455AD74E}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{BAD098D3-527E-482F-BC95-546F40585C1D}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="19180" windowHeight="7870" firstSheet="1" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="19180" windowHeight="7870" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="notas" sheetId="1" r:id="rId1"/>
@@ -21,9 +21,9 @@
     <sheet name="artilharia total" sheetId="3" r:id="rId6"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">artilharia!$A$1:$CN$104</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">artilharia!$A$1:$CN$105</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'artilharia total'!$A$1:$AI$51</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">notas!$A$1:$DR$83</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">notas!$A$1:$DS$83</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
 </workbook>
@@ -54,7 +54,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9420" uniqueCount="174">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9456" uniqueCount="176">
   <si>
     <t>Jogador</t>
   </si>
@@ -557,9 +557,6 @@
     <t>último checkado</t>
   </si>
   <si>
-    <t>Miguel 2</t>
-  </si>
-  <si>
     <t>Vitor</t>
   </si>
   <si>
@@ -576,6 +573,15 @@
   </si>
   <si>
     <t>Felipe Menezes</t>
+  </si>
+  <si>
+    <t>Leo Lombardi</t>
+  </si>
+  <si>
+    <t>Miguel Gustavo</t>
+  </si>
+  <si>
+    <t>Mateus Vitório</t>
   </si>
 </sst>
 </file>
@@ -2649,7 +2655,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:DR104"/>
+  <dimension ref="A1:DS105"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="2" max="2" width="9.453125" hidden="1" customWidth="1"/>
@@ -2672,10 +2678,10 @@
     <col min="49" max="58" width="9.54296875" hidden="1" customWidth="1"/>
     <col min="59" max="65" width="10.453125" hidden="1" customWidth="1"/>
     <col min="66" max="80" width="11" hidden="1" customWidth="1"/>
-    <col min="81" max="116" width="11" customWidth="1"/>
+    <col min="81" max="117" width="11" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:122" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:123" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -3021,27 +3027,30 @@
       <c r="DK1" s="1">
         <v>46281</v>
       </c>
-      <c r="DL1" s="1"/>
-      <c r="DM1" t="s">
+      <c r="DL1" s="1">
+        <v>46288</v>
+      </c>
+      <c r="DM1" s="1"/>
+      <c r="DN1" t="s">
         <v>56</v>
       </c>
-      <c r="DN1" t="s">
+      <c r="DO1" t="s">
         <v>57</v>
       </c>
-      <c r="DO1" t="s">
+      <c r="DP1" t="s">
         <v>58</v>
       </c>
-      <c r="DP1" t="s">
+      <c r="DQ1" t="s">
         <v>61</v>
       </c>
-      <c r="DQ1" t="s">
+      <c r="DR1" t="s">
         <v>150</v>
       </c>
-      <c r="DR1" t="s">
+      <c r="DS1" t="s">
         <v>135</v>
       </c>
     </row>
-    <row r="2" spans="1:122" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:123" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>1</v>
       </c>
@@ -3381,31 +3390,34 @@
       <c r="DK2">
         <v>6</v>
       </c>
-      <c r="DM2">
-        <f>COUNT(B2:DK2)</f>
-        <v>107</v>
-      </c>
-      <c r="DN2" s="18">
-        <f>AVERAGE(B2:DK2)</f>
+      <c r="DL2">
         <v>6</v>
       </c>
-      <c r="DO2">
-        <f>IF(DM2&gt;1,_xlfn.STDEV.S(B2:DI2),"")</f>
+      <c r="DN2">
+        <f>COUNT(B2:DL2)</f>
+        <v>108</v>
+      </c>
+      <c r="DO2" s="18">
+        <f>AVERAGE(B2:DL2)</f>
+        <v>6</v>
+      </c>
+      <c r="DP2">
+        <f>IF(DN2&gt;1,_xlfn.STDEV.S(B2:DI2),"")</f>
         <v>1.1104729547135237</v>
       </c>
-      <c r="DP2">
-        <v>1</v>
-      </c>
       <c r="DQ2">
-        <f t="shared" ref="DQ2:DQ33" si="0">COUNT(DF2:DH2)</f>
+        <v>1</v>
+      </c>
+      <c r="DR2">
+        <f t="shared" ref="DR2:DR33" si="0">COUNT(DF2:DH2)</f>
         <v>3</v>
       </c>
-      <c r="DR2">
-        <f t="shared" ref="DR2:DR33" si="1">IF(DP2=0,DQ2,0)</f>
+      <c r="DS2">
+        <f t="shared" ref="DS2:DS33" si="1">IF(DQ2=0,DR2,0)</f>
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:122" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:123" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>10</v>
       </c>
@@ -3718,31 +3730,31 @@
       <c r="DE3">
         <v>5.5</v>
       </c>
-      <c r="DM3">
-        <f t="shared" ref="DM3:DM66" si="2">COUNT(B3:DI3)</f>
+      <c r="DN3">
+        <f t="shared" ref="DN3:DN66" si="2">COUNT(B3:DI3)</f>
         <v>94</v>
       </c>
-      <c r="DN3" s="18">
-        <f t="shared" ref="DN3:DN66" si="3">AVERAGE(B3:DI3)</f>
+      <c r="DO3" s="18">
+        <f t="shared" ref="DO3:DO66" si="3">AVERAGE(B3:DI3)</f>
         <v>5.6382978723404253</v>
       </c>
-      <c r="DO3">
-        <f t="shared" ref="DO3:DO66" si="4">IF(DM3&gt;1,_xlfn.STDEV.S(B3:DI3),"")</f>
+      <c r="DP3">
+        <f t="shared" ref="DP3:DP66" si="4">IF(DN3&gt;1,_xlfn.STDEV.S(B3:DI3),"")</f>
         <v>0.94869535577019815</v>
       </c>
-      <c r="DP3">
-        <v>1</v>
-      </c>
       <c r="DQ3">
+        <v>1</v>
+      </c>
+      <c r="DR3">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="DR3">
+      <c r="DS3">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:122" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:123" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>81</v>
       </c>
@@ -4052,31 +4064,34 @@
       <c r="DK4">
         <v>6</v>
       </c>
-      <c r="DM4">
+      <c r="DL4">
+        <v>6</v>
+      </c>
+      <c r="DN4">
         <f t="shared" si="2"/>
         <v>83</v>
       </c>
-      <c r="DN4" s="18">
+      <c r="DO4" s="18">
         <f t="shared" si="3"/>
         <v>6.524096385542169</v>
       </c>
-      <c r="DO4">
+      <c r="DP4">
         <f t="shared" si="4"/>
         <v>0.91699274692529897</v>
       </c>
-      <c r="DP4">
+      <c r="DQ4">
         <v>0</v>
       </c>
-      <c r="DQ4">
+      <c r="DR4">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="DR4">
+      <c r="DS4">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:122" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:123" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>9</v>
       </c>
@@ -4395,31 +4410,34 @@
       <c r="DK5">
         <v>6.5</v>
       </c>
-      <c r="DM5">
-        <f>COUNT(B5:DK5)</f>
-        <v>87</v>
-      </c>
-      <c r="DN5" s="18">
-        <f>AVERAGE(B5:DK5)</f>
-        <v>6.568965517241379</v>
-      </c>
-      <c r="DO5">
+      <c r="DL5">
+        <v>6</v>
+      </c>
+      <c r="DN5">
+        <f>COUNT(B5:DL5)</f>
+        <v>88</v>
+      </c>
+      <c r="DO5" s="18">
+        <f>AVERAGE(B5:DL5)</f>
+        <v>6.5625</v>
+      </c>
+      <c r="DP5">
         <f t="shared" si="4"/>
         <v>0.95277127855729371</v>
       </c>
-      <c r="DP5">
-        <v>1</v>
-      </c>
       <c r="DQ5">
+        <v>1</v>
+      </c>
+      <c r="DR5">
         <f t="shared" si="0"/>
         <v>2</v>
       </c>
-      <c r="DR5">
+      <c r="DS5">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:122" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:123" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>4</v>
       </c>
@@ -4684,31 +4702,31 @@
       <c r="DD6">
         <v>5.5</v>
       </c>
-      <c r="DM6">
+      <c r="DN6">
         <f t="shared" si="2"/>
         <v>73</v>
       </c>
-      <c r="DN6" s="18">
+      <c r="DO6" s="18">
         <f t="shared" si="3"/>
         <v>5.7054794520547949</v>
       </c>
-      <c r="DO6">
+      <c r="DP6">
         <f t="shared" si="4"/>
         <v>0.93851099723606146</v>
       </c>
-      <c r="DP6">
+      <c r="DQ6">
         <v>0</v>
       </c>
-      <c r="DQ6">
+      <c r="DR6">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="DR6">
+      <c r="DS6">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:122" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:123" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>5</v>
       </c>
@@ -5015,31 +5033,34 @@
       <c r="DK7">
         <v>6</v>
       </c>
-      <c r="DM7">
-        <f>COUNT(B7:DK7)</f>
-        <v>84</v>
-      </c>
-      <c r="DN7" s="18">
-        <f>AVERAGE(B7:DK7)</f>
-        <v>7.1964285714285712</v>
-      </c>
-      <c r="DO7">
+      <c r="DL7">
+        <v>6.5</v>
+      </c>
+      <c r="DN7">
+        <f>COUNT(B7:DL7)</f>
+        <v>85</v>
+      </c>
+      <c r="DO7" s="18">
+        <f>AVERAGE(B7:DL7)</f>
+        <v>7.1882352941176473</v>
+      </c>
+      <c r="DP7">
         <f t="shared" si="4"/>
         <v>1.105405404410513</v>
       </c>
-      <c r="DP7">
-        <v>1</v>
-      </c>
       <c r="DQ7">
+        <v>1</v>
+      </c>
+      <c r="DR7">
         <f t="shared" si="0"/>
         <v>3</v>
       </c>
-      <c r="DR7">
+      <c r="DS7">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:122" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:123" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>19</v>
       </c>
@@ -5307,31 +5328,31 @@
       <c r="DD8">
         <v>5.5</v>
       </c>
-      <c r="DM8">
+      <c r="DN8">
         <f t="shared" si="2"/>
         <v>72</v>
       </c>
-      <c r="DN8" s="18">
+      <c r="DO8" s="18">
         <f t="shared" si="3"/>
         <v>5.9375</v>
       </c>
-      <c r="DO8">
+      <c r="DP8">
         <f t="shared" si="4"/>
         <v>0.93423728023165931</v>
       </c>
-      <c r="DP8">
+      <c r="DQ8">
         <v>0</v>
       </c>
-      <c r="DQ8">
+      <c r="DR8">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="DR8">
+      <c r="DS8">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:122" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:123" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>11</v>
       </c>
@@ -5626,31 +5647,31 @@
       <c r="DF9">
         <v>5.5</v>
       </c>
-      <c r="DM9">
+      <c r="DN9">
         <f t="shared" si="2"/>
         <v>75</v>
       </c>
-      <c r="DN9" s="18">
+      <c r="DO9" s="18">
         <f t="shared" si="3"/>
         <v>5.753333333333333</v>
       </c>
-      <c r="DO9">
+      <c r="DP9">
         <f t="shared" si="4"/>
         <v>1.2664414214142996</v>
       </c>
-      <c r="DP9">
-        <v>1</v>
-      </c>
       <c r="DQ9">
+        <v>1</v>
+      </c>
+      <c r="DR9">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="DR9">
+      <c r="DS9">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:122" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:123" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
         <v>6</v>
       </c>
@@ -5900,31 +5921,31 @@
       <c r="CE10">
         <v>5</v>
       </c>
-      <c r="DM10">
+      <c r="DN10">
         <f t="shared" si="2"/>
         <v>68</v>
       </c>
-      <c r="DN10" s="18">
+      <c r="DO10" s="18">
         <f t="shared" si="3"/>
         <v>6.4191176470588234</v>
       </c>
-      <c r="DO10">
+      <c r="DP10">
         <f t="shared" si="4"/>
         <v>1.1769245721961776</v>
       </c>
-      <c r="DP10">
+      <c r="DQ10">
         <v>0</v>
       </c>
-      <c r="DQ10">
+      <c r="DR10">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="DR10">
+      <c r="DS10">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:122" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:123" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
         <v>15</v>
       </c>
@@ -6231,31 +6252,31 @@
       <c r="DJ11">
         <v>7</v>
       </c>
-      <c r="DM11">
+      <c r="DN11">
         <f t="shared" si="2"/>
         <v>74</v>
       </c>
-      <c r="DN11" s="18">
+      <c r="DO11" s="18">
         <f t="shared" si="3"/>
         <v>6.6351351351351351</v>
       </c>
-      <c r="DO11">
+      <c r="DP11">
         <f t="shared" si="4"/>
         <v>0.92268702784386913</v>
       </c>
-      <c r="DP11">
+      <c r="DQ11">
         <v>0</v>
       </c>
-      <c r="DQ11">
+      <c r="DR11">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="DR11">
+      <c r="DS11">
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
     </row>
-    <row r="12" spans="1:122" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:123" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
         <v>2</v>
       </c>
@@ -6562,31 +6583,31 @@
       <c r="DH12">
         <v>5.5</v>
       </c>
-      <c r="DM12">
+      <c r="DN12">
         <f t="shared" si="2"/>
         <v>70</v>
       </c>
-      <c r="DN12" s="18">
+      <c r="DO12" s="18">
         <f t="shared" si="3"/>
         <v>5.5357142857142856</v>
       </c>
-      <c r="DO12">
+      <c r="DP12">
         <f t="shared" si="4"/>
         <v>0.92986452407127196</v>
       </c>
-      <c r="DP12">
-        <v>1</v>
-      </c>
       <c r="DQ12">
+        <v>1</v>
+      </c>
+      <c r="DR12">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="DR12">
+      <c r="DS12">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:122" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:123" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
         <v>18</v>
       </c>
@@ -6911,31 +6932,34 @@
       <c r="DK13">
         <v>6</v>
       </c>
-      <c r="DM13">
+      <c r="DL13">
+        <v>6.5</v>
+      </c>
+      <c r="DN13">
         <f t="shared" si="2"/>
         <v>71</v>
       </c>
-      <c r="DN13" s="18">
+      <c r="DO13" s="18">
         <f t="shared" si="3"/>
         <v>6.225352112676056</v>
       </c>
-      <c r="DO13">
+      <c r="DP13">
         <f t="shared" si="4"/>
         <v>1.064990718921216</v>
       </c>
-      <c r="DP13">
-        <v>1</v>
-      </c>
       <c r="DQ13">
+        <v>1</v>
+      </c>
+      <c r="DR13">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="DR13">
+      <c r="DS13">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:122" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:123" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
         <v>118</v>
       </c>
@@ -7209,31 +7233,31 @@
       <c r="DF14">
         <v>6</v>
       </c>
-      <c r="DM14">
+      <c r="DN14">
         <f t="shared" si="2"/>
         <v>65</v>
       </c>
-      <c r="DN14" s="18">
+      <c r="DO14" s="18">
         <f t="shared" si="3"/>
         <v>6.2461538461538462</v>
       </c>
-      <c r="DO14">
+      <c r="DP14">
         <f t="shared" si="4"/>
         <v>1.0387909021846209</v>
       </c>
-      <c r="DP14">
+      <c r="DQ14">
         <v>0</v>
       </c>
-      <c r="DQ14">
+      <c r="DR14">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="DR14">
+      <c r="DS14">
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
     </row>
-    <row r="15" spans="1:122" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:123" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
         <v>55</v>
       </c>
@@ -7570,31 +7594,34 @@
       <c r="DK15">
         <v>6</v>
       </c>
-      <c r="DM15">
-        <f>COUNT(B15:DK15)</f>
-        <v>68</v>
-      </c>
-      <c r="DN15" s="18">
-        <f>AVERAGE(B15:DK15)</f>
-        <v>6.0441176470588234</v>
-      </c>
-      <c r="DO15">
+      <c r="DL15">
+        <v>6</v>
+      </c>
+      <c r="DN15">
+        <f>COUNT(B15:DL15)</f>
+        <v>69</v>
+      </c>
+      <c r="DO15" s="18">
+        <f>AVERAGE(B15:DL15)</f>
+        <v>6.0434782608695654</v>
+      </c>
+      <c r="DP15">
         <f t="shared" si="4"/>
         <v>0.80532175156462971</v>
       </c>
-      <c r="DP15">
-        <v>1</v>
-      </c>
       <c r="DQ15">
+        <v>1</v>
+      </c>
+      <c r="DR15">
         <f t="shared" si="0"/>
         <v>2</v>
       </c>
-      <c r="DR15">
+      <c r="DS15">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:122" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:123" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
         <v>13</v>
       </c>
@@ -7841,31 +7868,31 @@
       <c r="CW16">
         <v>6</v>
       </c>
-      <c r="DM16">
+      <c r="DN16">
         <f t="shared" si="2"/>
         <v>53</v>
       </c>
-      <c r="DN16" s="18">
+      <c r="DO16" s="18">
         <f t="shared" si="3"/>
         <v>5.6981132075471699</v>
       </c>
-      <c r="DO16">
+      <c r="DP16">
         <f t="shared" si="4"/>
         <v>0.83975513052632311</v>
       </c>
-      <c r="DP16">
+      <c r="DQ16">
         <v>0</v>
       </c>
-      <c r="DQ16">
+      <c r="DR16">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="DR16">
+      <c r="DS16">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:122" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:123" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
         <v>14</v>
       </c>
@@ -8160,31 +8187,31 @@
       <c r="DH17">
         <v>5.5</v>
       </c>
-      <c r="DM17">
+      <c r="DN17">
         <f t="shared" si="2"/>
         <v>52</v>
       </c>
-      <c r="DN17" s="18">
+      <c r="DO17" s="18">
         <f t="shared" si="3"/>
         <v>5.7115384615384617</v>
       </c>
-      <c r="DO17">
+      <c r="DP17">
         <f t="shared" si="4"/>
         <v>0.87080171448079058</v>
       </c>
-      <c r="DP17">
-        <v>1</v>
-      </c>
       <c r="DQ17">
+        <v>1</v>
+      </c>
+      <c r="DR17">
         <f t="shared" si="0"/>
         <v>2</v>
       </c>
-      <c r="DR17">
+      <c r="DS17">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:122" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:123" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
         <v>24</v>
       </c>
@@ -8434,31 +8461,31 @@
       <c r="CF18">
         <v>5.5</v>
       </c>
-      <c r="DM18">
+      <c r="DN18">
         <f t="shared" si="2"/>
         <v>47</v>
       </c>
-      <c r="DN18" s="18">
+      <c r="DO18" s="18">
         <f t="shared" si="3"/>
         <v>4.4255319148936172</v>
       </c>
-      <c r="DO18">
+      <c r="DP18">
         <f t="shared" si="4"/>
         <v>1.3391217246854428</v>
       </c>
-      <c r="DP18">
+      <c r="DQ18">
         <v>0</v>
       </c>
-      <c r="DQ18">
+      <c r="DR18">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="DR18">
+      <c r="DS18">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:122" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:123" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
         <v>83</v>
       </c>
@@ -8759,31 +8786,34 @@
       <c r="DK19">
         <v>5.5</v>
       </c>
-      <c r="DM19">
-        <f>COUNT(B19:DK19)</f>
-        <v>54</v>
-      </c>
-      <c r="DN19" s="18">
-        <f>AVERAGE(B19:DK19)</f>
-        <v>5.7685185185185182</v>
-      </c>
-      <c r="DO19">
+      <c r="DL19">
+        <v>5.5</v>
+      </c>
+      <c r="DN19">
+        <f>COUNT(B19:DL19)</f>
+        <v>55</v>
+      </c>
+      <c r="DO19" s="18">
+        <f>AVERAGE(B19:DL19)</f>
+        <v>5.7636363636363637</v>
+      </c>
+      <c r="DP19">
         <f t="shared" si="4"/>
         <v>0.80040525180633026</v>
       </c>
-      <c r="DP19">
-        <v>1</v>
-      </c>
       <c r="DQ19">
+        <v>1</v>
+      </c>
+      <c r="DR19">
         <f t="shared" si="0"/>
         <v>2</v>
       </c>
-      <c r="DR19">
+      <c r="DS19">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:122" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:123" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
         <v>43</v>
       </c>
@@ -9081,31 +9111,34 @@
       <c r="DK20">
         <v>5.5</v>
       </c>
-      <c r="DM20">
+      <c r="DL20">
+        <v>5.5</v>
+      </c>
+      <c r="DN20">
         <f t="shared" si="2"/>
         <v>53</v>
       </c>
-      <c r="DN20" s="18">
+      <c r="DO20" s="18">
         <f t="shared" si="3"/>
         <v>5.1132075471698117</v>
       </c>
-      <c r="DO20">
+      <c r="DP20">
         <f t="shared" si="4"/>
         <v>0.98372090629426312</v>
       </c>
-      <c r="DP20">
-        <v>1</v>
-      </c>
       <c r="DQ20">
+        <v>1</v>
+      </c>
+      <c r="DR20">
         <f t="shared" si="0"/>
         <v>2</v>
       </c>
-      <c r="DR20">
+      <c r="DS20">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:122" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:123" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
         <v>45</v>
       </c>
@@ -9391,31 +9424,31 @@
       <c r="CZ21">
         <v>5.5</v>
       </c>
-      <c r="DM21">
+      <c r="DN21">
         <f t="shared" si="2"/>
         <v>45</v>
       </c>
-      <c r="DN21" s="18">
+      <c r="DO21" s="18">
         <f t="shared" si="3"/>
         <v>5.2555555555555555</v>
       </c>
-      <c r="DO21">
+      <c r="DP21">
         <f t="shared" si="4"/>
         <v>1.1659088447830879</v>
       </c>
-      <c r="DP21">
+      <c r="DQ21">
         <v>0</v>
       </c>
-      <c r="DQ21">
+      <c r="DR21">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="DR21">
+      <c r="DS21">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:122" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:123" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
         <v>54</v>
       </c>
@@ -9659,31 +9692,31 @@
       <c r="CK22">
         <v>5.5</v>
       </c>
-      <c r="DM22">
+      <c r="DN22">
         <f t="shared" si="2"/>
         <v>39</v>
       </c>
-      <c r="DN22" s="18">
+      <c r="DO22" s="18">
         <f t="shared" si="3"/>
         <v>6.1410256410256414</v>
       </c>
-      <c r="DO22">
+      <c r="DP22">
         <f t="shared" si="4"/>
         <v>1.0879042984027267</v>
       </c>
-      <c r="DP22">
+      <c r="DQ22">
         <v>0</v>
       </c>
-      <c r="DQ22">
+      <c r="DR22">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="DR22">
+      <c r="DS22">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:122" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:123" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
         <v>47</v>
       </c>
@@ -9972,31 +10005,31 @@
       <c r="DH23">
         <v>6</v>
       </c>
-      <c r="DM23">
+      <c r="DN23">
         <f t="shared" si="2"/>
         <v>36</v>
       </c>
-      <c r="DN23" s="18">
+      <c r="DO23" s="18">
         <f t="shared" si="3"/>
         <v>6.2777777777777777</v>
       </c>
-      <c r="DO23">
+      <c r="DP23">
         <f t="shared" si="4"/>
         <v>0.9520237425343997</v>
       </c>
-      <c r="DP23">
+      <c r="DQ23">
         <v>0</v>
       </c>
-      <c r="DQ23">
+      <c r="DR23">
         <f t="shared" si="0"/>
         <v>2</v>
       </c>
-      <c r="DR23">
+      <c r="DS23">
         <f t="shared" si="1"/>
         <v>2</v>
       </c>
     </row>
-    <row r="24" spans="1:122" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:123" x14ac:dyDescent="0.35">
       <c r="A24" t="s">
         <v>65</v>
       </c>
@@ -10261,31 +10294,31 @@
       <c r="DD24">
         <v>6</v>
       </c>
-      <c r="DM24">
+      <c r="DN24">
         <f t="shared" si="2"/>
         <v>31</v>
       </c>
-      <c r="DN24" s="18">
+      <c r="DO24" s="18">
         <f t="shared" si="3"/>
         <v>5.4838709677419351</v>
       </c>
-      <c r="DO24">
+      <c r="DP24">
         <f t="shared" si="4"/>
         <v>0.67680463660426593</v>
       </c>
-      <c r="DP24">
+      <c r="DQ24">
         <v>0</v>
       </c>
-      <c r="DQ24">
+      <c r="DR24">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="DR24">
+      <c r="DS24">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:122" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:123" x14ac:dyDescent="0.35">
       <c r="A25" t="s">
         <v>21</v>
       </c>
@@ -10571,31 +10604,31 @@
       <c r="DJ25">
         <v>6</v>
       </c>
-      <c r="DM25">
+      <c r="DN25">
         <f>COUNT(B25:DJ25)</f>
         <v>31</v>
       </c>
-      <c r="DN25" s="18">
+      <c r="DO25" s="18">
         <f>AVERAGE(B25:DJ25)</f>
         <v>6.467741935483871</v>
       </c>
-      <c r="DO25">
+      <c r="DP25">
         <f t="shared" si="4"/>
         <v>0.63630578928001602</v>
       </c>
-      <c r="DP25">
-        <v>1</v>
-      </c>
       <c r="DQ25">
+        <v>1</v>
+      </c>
+      <c r="DR25">
         <f t="shared" si="0"/>
         <v>3</v>
       </c>
-      <c r="DR25">
+      <c r="DS25">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="1:122" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:123" x14ac:dyDescent="0.35">
       <c r="A26" t="s">
         <v>80</v>
       </c>
@@ -10896,31 +10929,31 @@
       <c r="DK26">
         <v>6</v>
       </c>
-      <c r="DM26">
+      <c r="DN26">
         <f>COUNT(B26:DK26)</f>
         <v>24</v>
       </c>
-      <c r="DN26" s="18">
+      <c r="DO26" s="18">
         <f>AVERAGE(B26:DK26)</f>
         <v>6.104166666666667</v>
       </c>
-      <c r="DO26">
+      <c r="DP26">
         <f t="shared" si="4"/>
         <v>0.65795169495977013</v>
       </c>
-      <c r="DP26">
+      <c r="DQ26">
         <v>0</v>
       </c>
-      <c r="DQ26">
+      <c r="DR26">
         <f t="shared" si="0"/>
         <v>2</v>
       </c>
-      <c r="DR26">
+      <c r="DS26">
         <f t="shared" si="1"/>
         <v>2</v>
       </c>
     </row>
-    <row r="27" spans="1:122" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:123" x14ac:dyDescent="0.35">
       <c r="A27" t="s">
         <v>3</v>
       </c>
@@ -11161,31 +11194,31 @@
       <c r="CB27" t="s">
         <v>25</v>
       </c>
-      <c r="DM27">
+      <c r="DN27">
         <f t="shared" si="2"/>
         <v>19</v>
       </c>
-      <c r="DN27" s="18">
+      <c r="DO27" s="18">
         <f t="shared" si="3"/>
         <v>5.7894736842105265</v>
       </c>
-      <c r="DO27">
+      <c r="DP27">
         <f t="shared" si="4"/>
         <v>1.3674366679797902</v>
       </c>
-      <c r="DP27">
+      <c r="DQ27">
         <v>0</v>
       </c>
-      <c r="DQ27">
+      <c r="DR27">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="DR27">
+      <c r="DS27">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="1:122" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:123" x14ac:dyDescent="0.35">
       <c r="A28" t="s">
         <v>62</v>
       </c>
@@ -11447,31 +11480,31 @@
       <c r="DG28">
         <v>5.5</v>
       </c>
-      <c r="DM28">
+      <c r="DN28">
         <f t="shared" si="2"/>
         <v>19</v>
       </c>
-      <c r="DN28" s="18">
+      <c r="DO28" s="18">
         <f t="shared" si="3"/>
         <v>5.0263157894736841</v>
       </c>
-      <c r="DO28">
+      <c r="DP28">
         <f t="shared" si="4"/>
         <v>0.84119102419206049</v>
       </c>
-      <c r="DP28">
+      <c r="DQ28">
         <v>0</v>
       </c>
-      <c r="DQ28">
+      <c r="DR28">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="DR28">
+      <c r="DS28">
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
     </row>
-    <row r="29" spans="1:122" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:123" x14ac:dyDescent="0.35">
       <c r="A29" t="s">
         <v>100</v>
       </c>
@@ -11712,31 +11745,31 @@
       <c r="CB29" t="s">
         <v>25</v>
       </c>
-      <c r="DM29">
+      <c r="DN29">
         <f t="shared" si="2"/>
         <v>18</v>
       </c>
-      <c r="DN29" s="18">
+      <c r="DO29" s="18">
         <f t="shared" si="3"/>
         <v>5.9444444444444446</v>
       </c>
-      <c r="DO29">
+      <c r="DP29">
         <f t="shared" si="4"/>
         <v>0.72535769855270305</v>
       </c>
-      <c r="DP29">
+      <c r="DQ29">
         <v>0</v>
       </c>
-      <c r="DQ29">
+      <c r="DR29">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="DR29">
+      <c r="DS29">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
-    <row r="30" spans="1:122" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:123" x14ac:dyDescent="0.35">
       <c r="A30" t="s">
         <v>8</v>
       </c>
@@ -11980,33 +12013,33 @@
       <c r="DD30">
         <v>5.5</v>
       </c>
-      <c r="DM30">
+      <c r="DN30">
         <f t="shared" si="2"/>
         <v>18</v>
       </c>
-      <c r="DN30" s="18">
+      <c r="DO30" s="18">
         <f t="shared" si="3"/>
         <v>5.333333333333333</v>
       </c>
-      <c r="DO30">
+      <c r="DP30">
         <f t="shared" si="4"/>
         <v>1.3060943124220303</v>
       </c>
-      <c r="DP30">
+      <c r="DQ30">
         <v>0</v>
       </c>
-      <c r="DQ30">
+      <c r="DR30">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="DR30">
+      <c r="DS30">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
-    <row r="31" spans="1:122" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:123" x14ac:dyDescent="0.35">
       <c r="A31" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="B31" t="s">
         <v>25</v>
@@ -12284,31 +12317,34 @@
       <c r="DK31">
         <v>6</v>
       </c>
-      <c r="DM31">
+      <c r="DL31">
+        <v>5.5</v>
+      </c>
+      <c r="DN31">
         <f t="shared" si="2"/>
         <v>20</v>
       </c>
-      <c r="DN31" s="18">
+      <c r="DO31" s="18">
         <f t="shared" si="3"/>
         <v>5.125</v>
       </c>
-      <c r="DO31">
+      <c r="DP31">
         <f t="shared" si="4"/>
         <v>1.3943023156290106</v>
       </c>
-      <c r="DP31">
-        <v>1</v>
-      </c>
       <c r="DQ31">
+        <v>1</v>
+      </c>
+      <c r="DR31">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="DR31">
+      <c r="DS31">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
-    <row r="32" spans="1:122" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:123" x14ac:dyDescent="0.35">
       <c r="A32" t="s">
         <v>67</v>
       </c>
@@ -12555,31 +12591,31 @@
       <c r="DA32">
         <v>5.5</v>
       </c>
-      <c r="DM32">
+      <c r="DN32">
         <f t="shared" si="2"/>
         <v>18</v>
       </c>
-      <c r="DN32" s="18">
+      <c r="DO32" s="18">
         <f t="shared" si="3"/>
         <v>4.583333333333333</v>
       </c>
-      <c r="DO32">
+      <c r="DP32">
         <f t="shared" si="4"/>
         <v>1.4677914581799016</v>
       </c>
-      <c r="DP32">
+      <c r="DQ32">
         <v>0</v>
       </c>
-      <c r="DQ32">
+      <c r="DR32">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="DR32">
+      <c r="DS32">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
-    <row r="33" spans="1:122" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:123" x14ac:dyDescent="0.35">
       <c r="A33" t="s">
         <v>7</v>
       </c>
@@ -12820,31 +12856,31 @@
       <c r="CB33">
         <v>5.5</v>
       </c>
-      <c r="DM33">
+      <c r="DN33">
         <f t="shared" si="2"/>
         <v>15</v>
       </c>
-      <c r="DN33" s="18">
+      <c r="DO33" s="18">
         <f t="shared" si="3"/>
         <v>3.8666666666666667</v>
       </c>
-      <c r="DO33">
+      <c r="DP33">
         <f t="shared" si="4"/>
         <v>2.3563490726929555</v>
       </c>
-      <c r="DP33">
+      <c r="DQ33">
         <v>0</v>
       </c>
-      <c r="DQ33">
+      <c r="DR33">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="DR33">
+      <c r="DS33">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
-    <row r="34" spans="1:122" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:123" x14ac:dyDescent="0.35">
       <c r="A34" t="s">
         <v>12</v>
       </c>
@@ -13094,31 +13130,34 @@
       <c r="DB34">
         <v>6.5</v>
       </c>
-      <c r="DM34">
+      <c r="DL34">
+        <v>6</v>
+      </c>
+      <c r="DN34">
         <f t="shared" si="2"/>
         <v>16</v>
       </c>
-      <c r="DN34" s="18">
+      <c r="DO34" s="18">
         <f t="shared" si="3"/>
         <v>7.125</v>
       </c>
-      <c r="DO34">
+      <c r="DP34">
         <f t="shared" si="4"/>
         <v>1.4433756729740645</v>
       </c>
-      <c r="DP34">
+      <c r="DQ34">
         <v>0</v>
       </c>
-      <c r="DQ34">
-        <f t="shared" ref="DQ34:DQ65" si="5">COUNT(DF34:DH34)</f>
+      <c r="DR34">
+        <f t="shared" ref="DR34:DR65" si="5">COUNT(DF34:DH34)</f>
         <v>0</v>
       </c>
-      <c r="DR34">
-        <f t="shared" ref="DR34:DR65" si="6">IF(DP34=0,DQ34,0)</f>
+      <c r="DS34">
+        <f t="shared" ref="DS34:DS65" si="6">IF(DQ34=0,DR34,0)</f>
         <v>0</v>
       </c>
     </row>
-    <row r="35" spans="1:122" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:123" x14ac:dyDescent="0.35">
       <c r="A35" t="s">
         <v>127</v>
       </c>
@@ -13401,31 +13440,31 @@
       <c r="DE35">
         <v>6.5</v>
       </c>
-      <c r="DM35">
+      <c r="DN35">
         <f t="shared" si="2"/>
         <v>21</v>
       </c>
-      <c r="DN35" s="18">
+      <c r="DO35" s="18">
         <f t="shared" si="3"/>
         <v>6.0952380952380949</v>
       </c>
-      <c r="DO35">
+      <c r="DP35">
         <f t="shared" si="4"/>
         <v>0.5616726720040689</v>
       </c>
-      <c r="DP35">
-        <v>1</v>
-      </c>
       <c r="DQ35">
+        <v>1</v>
+      </c>
+      <c r="DR35">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="DR35">
+      <c r="DS35">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
     </row>
-    <row r="36" spans="1:122" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:123" x14ac:dyDescent="0.35">
       <c r="A36" t="s">
         <v>129</v>
       </c>
@@ -13693,31 +13732,31 @@
       <c r="CQ36">
         <v>5.5</v>
       </c>
-      <c r="DM36">
+      <c r="DN36">
         <f t="shared" si="2"/>
         <v>12</v>
       </c>
-      <c r="DN36" s="18">
+      <c r="DO36" s="18">
         <f t="shared" si="3"/>
         <v>5.25</v>
       </c>
-      <c r="DO36">
+      <c r="DP36">
         <f t="shared" si="4"/>
         <v>0.3988620176087328</v>
       </c>
-      <c r="DP36">
+      <c r="DQ36">
         <v>0</v>
       </c>
-      <c r="DQ36">
+      <c r="DR36">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="DR36">
+      <c r="DS36">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
     </row>
-    <row r="37" spans="1:122" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:123" x14ac:dyDescent="0.35">
       <c r="A37" t="s">
         <v>16</v>
       </c>
@@ -13958,31 +13997,31 @@
       <c r="CB37" t="s">
         <v>25</v>
       </c>
-      <c r="DM37">
+      <c r="DN37">
         <f t="shared" si="2"/>
         <v>11</v>
       </c>
-      <c r="DN37" s="18">
+      <c r="DO37" s="18">
         <f t="shared" si="3"/>
         <v>4.6818181818181817</v>
       </c>
-      <c r="DO37">
+      <c r="DP37">
         <f t="shared" si="4"/>
         <v>0.81463879335344846</v>
       </c>
-      <c r="DP37">
+      <c r="DQ37">
         <v>0</v>
       </c>
-      <c r="DQ37">
+      <c r="DR37">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="DR37">
+      <c r="DS37">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
     </row>
-    <row r="38" spans="1:122" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:123" x14ac:dyDescent="0.35">
       <c r="A38" t="s">
         <v>44</v>
       </c>
@@ -14226,31 +14265,34 @@
       <c r="CC38">
         <v>6</v>
       </c>
-      <c r="DM38">
+      <c r="DL38">
+        <v>7</v>
+      </c>
+      <c r="DN38">
         <f t="shared" si="2"/>
         <v>10</v>
       </c>
-      <c r="DN38" s="18">
+      <c r="DO38" s="18">
         <f t="shared" si="3"/>
         <v>8.4499999999999993</v>
       </c>
-      <c r="DO38">
+      <c r="DP38">
         <f t="shared" si="4"/>
         <v>1.1890705987824657</v>
       </c>
-      <c r="DP38">
+      <c r="DQ38">
         <v>0</v>
       </c>
-      <c r="DQ38">
+      <c r="DR38">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="DR38">
+      <c r="DS38">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
     </row>
-    <row r="39" spans="1:122" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:123" x14ac:dyDescent="0.35">
       <c r="A39" t="s">
         <v>95</v>
       </c>
@@ -14494,31 +14536,31 @@
       <c r="CL39">
         <v>6</v>
       </c>
-      <c r="DM39">
+      <c r="DN39">
         <f t="shared" si="2"/>
         <v>8</v>
       </c>
-      <c r="DN39" s="18">
+      <c r="DO39" s="18">
         <f t="shared" si="3"/>
         <v>5.75</v>
       </c>
-      <c r="DO39">
+      <c r="DP39">
         <f t="shared" si="4"/>
         <v>0.53452248382484879</v>
       </c>
-      <c r="DP39">
+      <c r="DQ39">
         <v>0</v>
       </c>
-      <c r="DQ39">
+      <c r="DR39">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="DR39">
+      <c r="DS39">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
     </row>
-    <row r="40" spans="1:122" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:123" x14ac:dyDescent="0.35">
       <c r="A40" t="s">
         <v>151</v>
       </c>
@@ -14579,33 +14621,36 @@
       <c r="DK40">
         <v>6</v>
       </c>
-      <c r="DM40">
+      <c r="DL40">
+        <v>6.5</v>
+      </c>
+      <c r="DN40">
         <f t="shared" si="2"/>
         <v>18</v>
       </c>
-      <c r="DN40" s="18">
+      <c r="DO40" s="18">
         <f t="shared" si="3"/>
         <v>6.8611111111111107</v>
       </c>
-      <c r="DO40">
+      <c r="DP40">
         <f t="shared" si="4"/>
         <v>1.0262088360384556</v>
       </c>
-      <c r="DP40">
-        <v>1</v>
-      </c>
       <c r="DQ40">
+        <v>1</v>
+      </c>
+      <c r="DR40">
         <f t="shared" si="5"/>
         <v>3</v>
       </c>
-      <c r="DR40">
+      <c r="DS40">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
     </row>
-    <row r="41" spans="1:122" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:123" x14ac:dyDescent="0.35">
       <c r="A41" t="s">
-        <v>99</v>
+        <v>175</v>
       </c>
       <c r="B41" t="s">
         <v>25</v>
@@ -14862,31 +14907,31 @@
       <c r="CO41">
         <v>4.5</v>
       </c>
-      <c r="DM41">
+      <c r="DN41">
         <f t="shared" si="2"/>
         <v>7</v>
       </c>
-      <c r="DN41" s="18">
+      <c r="DO41" s="18">
         <f t="shared" si="3"/>
         <v>4.5</v>
       </c>
-      <c r="DO41">
+      <c r="DP41">
         <f t="shared" si="4"/>
         <v>1.2583057392117916</v>
       </c>
-      <c r="DP41">
+      <c r="DQ41">
         <v>0</v>
       </c>
-      <c r="DQ41">
+      <c r="DR41">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="DR41">
+      <c r="DS41">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
     </row>
-    <row r="42" spans="1:122" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:123" x14ac:dyDescent="0.35">
       <c r="A42" t="s">
         <v>143</v>
       </c>
@@ -14911,31 +14956,31 @@
       <c r="CY42">
         <v>4.5</v>
       </c>
-      <c r="DM42">
+      <c r="DN42">
         <f t="shared" si="2"/>
         <v>7</v>
       </c>
-      <c r="DN42" s="18">
+      <c r="DO42" s="18">
         <f t="shared" si="3"/>
         <v>5.6428571428571432</v>
       </c>
-      <c r="DO42">
+      <c r="DP42">
         <f t="shared" si="4"/>
         <v>1.248808956375558</v>
       </c>
-      <c r="DP42">
+      <c r="DQ42">
         <v>0</v>
       </c>
-      <c r="DQ42">
+      <c r="DR42">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="DR42">
+      <c r="DS42">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
     </row>
-    <row r="43" spans="1:122" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:123" x14ac:dyDescent="0.35">
       <c r="A43" t="s">
         <v>148</v>
       </c>
@@ -14975,31 +15020,31 @@
       <c r="DI43">
         <v>6</v>
       </c>
-      <c r="DM43">
+      <c r="DN43">
         <f t="shared" si="2"/>
         <v>12</v>
       </c>
-      <c r="DN43" s="18">
+      <c r="DO43" s="18">
         <f t="shared" si="3"/>
         <v>6.041666666666667</v>
       </c>
-      <c r="DO43">
+      <c r="DP43">
         <f t="shared" si="4"/>
         <v>0.39648073054937955</v>
       </c>
-      <c r="DP43">
+      <c r="DQ43">
         <v>0</v>
       </c>
-      <c r="DQ43">
+      <c r="DR43">
         <f t="shared" si="5"/>
         <v>1</v>
       </c>
-      <c r="DR43">
+      <c r="DS43">
         <f t="shared" si="6"/>
         <v>1</v>
       </c>
     </row>
-    <row r="44" spans="1:122" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:123" x14ac:dyDescent="0.35">
       <c r="A44" t="s">
         <v>97</v>
       </c>
@@ -15255,31 +15300,34 @@
       <c r="DK44">
         <v>6</v>
       </c>
-      <c r="DM44">
+      <c r="DL44">
+        <v>5.5</v>
+      </c>
+      <c r="DN44">
         <f t="shared" si="2"/>
         <v>5</v>
       </c>
-      <c r="DN44" s="18">
+      <c r="DO44" s="18">
         <f t="shared" si="3"/>
         <v>5.6</v>
       </c>
-      <c r="DO44">
+      <c r="DP44">
         <f t="shared" si="4"/>
         <v>1.0839741694339387</v>
       </c>
-      <c r="DP44">
+      <c r="DQ44">
         <v>0</v>
       </c>
-      <c r="DQ44">
+      <c r="DR44">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="DR44">
+      <c r="DS44">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
     </row>
-    <row r="45" spans="1:122" x14ac:dyDescent="0.35">
+    <row r="45" spans="1:123" x14ac:dyDescent="0.35">
       <c r="A45" t="s">
         <v>141</v>
       </c>
@@ -15535,31 +15583,31 @@
       <c r="CU45">
         <v>6</v>
       </c>
-      <c r="DM45">
+      <c r="DN45">
         <f t="shared" si="2"/>
         <v>5</v>
       </c>
-      <c r="DN45" s="18">
+      <c r="DO45" s="18">
         <f t="shared" si="3"/>
         <v>6.5</v>
       </c>
-      <c r="DO45">
+      <c r="DP45">
         <f t="shared" si="4"/>
         <v>0.5</v>
       </c>
-      <c r="DP45">
+      <c r="DQ45">
         <v>0</v>
       </c>
-      <c r="DQ45">
+      <c r="DR45">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="DR45">
+      <c r="DS45">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
     </row>
-    <row r="46" spans="1:122" x14ac:dyDescent="0.35">
+    <row r="46" spans="1:123" x14ac:dyDescent="0.35">
       <c r="A46" t="s">
         <v>23</v>
       </c>
@@ -15803,31 +15851,31 @@
       <c r="CH46">
         <v>6.5</v>
       </c>
-      <c r="DM46">
+      <c r="DN46">
         <f t="shared" si="2"/>
         <v>5</v>
       </c>
-      <c r="DN46" s="18">
+      <c r="DO46" s="18">
         <f t="shared" si="3"/>
         <v>7.8</v>
       </c>
-      <c r="DO46">
+      <c r="DP46">
         <f t="shared" si="4"/>
         <v>1.1510864433221351</v>
       </c>
-      <c r="DP46">
+      <c r="DQ46">
         <v>0</v>
       </c>
-      <c r="DQ46">
+      <c r="DR46">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="DR46">
+      <c r="DS46">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
     </row>
-    <row r="47" spans="1:122" x14ac:dyDescent="0.35">
+    <row r="47" spans="1:123" x14ac:dyDescent="0.35">
       <c r="A47" t="s">
         <v>59</v>
       </c>
@@ -16074,31 +16122,31 @@
       <c r="DJ47">
         <v>5.5</v>
       </c>
-      <c r="DM47">
+      <c r="DN47">
         <f t="shared" si="2"/>
         <v>5</v>
       </c>
-      <c r="DN47" s="18">
+      <c r="DO47" s="18">
         <f t="shared" si="3"/>
         <v>3.8</v>
       </c>
-      <c r="DO47">
+      <c r="DP47">
         <f t="shared" si="4"/>
         <v>1.0368220676663857</v>
       </c>
-      <c r="DP47">
+      <c r="DQ47">
         <v>0</v>
       </c>
-      <c r="DQ47">
+      <c r="DR47">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="DR47">
+      <c r="DS47">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
     </row>
-    <row r="48" spans="1:122" x14ac:dyDescent="0.35">
+    <row r="48" spans="1:123" x14ac:dyDescent="0.35">
       <c r="A48" t="s">
         <v>115</v>
       </c>
@@ -16348,31 +16396,31 @@
       <c r="CN48">
         <v>6</v>
       </c>
-      <c r="DM48">
+      <c r="DN48">
         <f t="shared" si="2"/>
         <v>5</v>
       </c>
-      <c r="DN48" s="18">
+      <c r="DO48" s="18">
         <f t="shared" si="3"/>
         <v>6.2</v>
       </c>
-      <c r="DO48">
+      <c r="DP48">
         <f t="shared" si="4"/>
         <v>0.44721359549995793</v>
       </c>
-      <c r="DP48">
+      <c r="DQ48">
         <v>0</v>
       </c>
-      <c r="DQ48">
+      <c r="DR48">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="DR48">
+      <c r="DS48">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
     </row>
-    <row r="49" spans="1:122" x14ac:dyDescent="0.35">
+    <row r="49" spans="1:123" x14ac:dyDescent="0.35">
       <c r="A49" t="s">
         <v>53</v>
       </c>
@@ -16619,31 +16667,31 @@
       <c r="DK49">
         <v>5.5</v>
       </c>
-      <c r="DM49">
+      <c r="DN49">
         <f t="shared" si="2"/>
         <v>5</v>
       </c>
-      <c r="DN49" s="18">
+      <c r="DO49" s="18">
         <f t="shared" si="3"/>
         <v>6.5</v>
       </c>
-      <c r="DO49">
+      <c r="DP49">
         <f t="shared" si="4"/>
         <v>1.0606601717798212</v>
       </c>
-      <c r="DP49">
+      <c r="DQ49">
         <v>0</v>
       </c>
-      <c r="DQ49">
+      <c r="DR49">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="DR49">
+      <c r="DS49">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
     </row>
-    <row r="50" spans="1:122" x14ac:dyDescent="0.35">
+    <row r="50" spans="1:123" x14ac:dyDescent="0.35">
       <c r="A50" t="s">
         <v>51</v>
       </c>
@@ -16890,31 +16938,31 @@
       <c r="CV50">
         <v>5.5</v>
       </c>
-      <c r="DM50">
+      <c r="DN50">
         <f t="shared" si="2"/>
         <v>4</v>
       </c>
-      <c r="DN50" s="18">
+      <c r="DO50" s="18">
         <f t="shared" si="3"/>
         <v>5.625</v>
       </c>
-      <c r="DO50">
+      <c r="DP50">
         <f t="shared" si="4"/>
         <v>0.25</v>
       </c>
-      <c r="DP50">
+      <c r="DQ50">
         <v>0</v>
       </c>
-      <c r="DQ50">
+      <c r="DR50">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="DR50">
+      <c r="DS50">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
     </row>
-    <row r="51" spans="1:122" x14ac:dyDescent="0.35">
+    <row r="51" spans="1:123" x14ac:dyDescent="0.35">
       <c r="A51" t="s">
         <v>60</v>
       </c>
@@ -17155,31 +17203,31 @@
       <c r="CB51" t="s">
         <v>25</v>
       </c>
-      <c r="DM51">
+      <c r="DN51">
         <f t="shared" si="2"/>
         <v>4</v>
       </c>
-      <c r="DN51" s="18">
+      <c r="DO51" s="18">
         <f t="shared" si="3"/>
         <v>5.625</v>
       </c>
-      <c r="DO51">
+      <c r="DP51">
         <f t="shared" si="4"/>
         <v>0.9464847243000456</v>
       </c>
-      <c r="DP51">
+      <c r="DQ51">
         <v>0</v>
       </c>
-      <c r="DQ51">
+      <c r="DR51">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="DR51">
+      <c r="DS51">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
     </row>
-    <row r="52" spans="1:122" x14ac:dyDescent="0.35">
+    <row r="52" spans="1:123" x14ac:dyDescent="0.35">
       <c r="A52" t="s">
         <v>20</v>
       </c>
@@ -17420,31 +17468,31 @@
       <c r="CB52" t="s">
         <v>25</v>
       </c>
-      <c r="DM52">
+      <c r="DN52">
         <f t="shared" si="2"/>
         <v>4</v>
       </c>
-      <c r="DN52" s="18">
+      <c r="DO52" s="18">
         <f t="shared" si="3"/>
         <v>1.375</v>
       </c>
-      <c r="DO52">
+      <c r="DP52">
         <f t="shared" si="4"/>
         <v>1.8874586088176875</v>
       </c>
-      <c r="DP52">
+      <c r="DQ52">
         <v>0</v>
       </c>
-      <c r="DQ52">
+      <c r="DR52">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="DR52">
+      <c r="DS52">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
     </row>
-    <row r="53" spans="1:122" x14ac:dyDescent="0.35">
+    <row r="53" spans="1:123" x14ac:dyDescent="0.35">
       <c r="A53" t="s">
         <v>98</v>
       </c>
@@ -17685,31 +17733,31 @@
       <c r="CB53" t="s">
         <v>25</v>
       </c>
-      <c r="DM53">
+      <c r="DN53">
         <f t="shared" si="2"/>
         <v>4</v>
       </c>
-      <c r="DN53" s="18">
+      <c r="DO53" s="18">
         <f t="shared" si="3"/>
         <v>4.625</v>
       </c>
-      <c r="DO53">
+      <c r="DP53">
         <f t="shared" si="4"/>
         <v>1.4361406616345072</v>
       </c>
-      <c r="DP53">
+      <c r="DQ53">
         <v>0</v>
       </c>
-      <c r="DQ53">
+      <c r="DR53">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="DR53">
+      <c r="DS53">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
     </row>
-    <row r="54" spans="1:122" x14ac:dyDescent="0.35">
+    <row r="54" spans="1:123" x14ac:dyDescent="0.35">
       <c r="A54" t="s">
         <v>112</v>
       </c>
@@ -17950,31 +17998,31 @@
       <c r="CB54" t="s">
         <v>25</v>
       </c>
-      <c r="DM54">
+      <c r="DN54">
         <f t="shared" si="2"/>
         <v>4</v>
       </c>
-      <c r="DN54" s="18">
+      <c r="DO54" s="18">
         <f t="shared" si="3"/>
         <v>6.25</v>
       </c>
-      <c r="DO54">
+      <c r="DP54">
         <f t="shared" si="4"/>
         <v>0.8660254037844386</v>
       </c>
-      <c r="DP54">
+      <c r="DQ54">
         <v>0</v>
       </c>
-      <c r="DQ54">
+      <c r="DR54">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="DR54">
+      <c r="DS54">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
     </row>
-    <row r="55" spans="1:122" x14ac:dyDescent="0.35">
+    <row r="55" spans="1:123" x14ac:dyDescent="0.35">
       <c r="A55" t="s">
         <v>42</v>
       </c>
@@ -18215,31 +18263,31 @@
       <c r="CB55" t="s">
         <v>25</v>
       </c>
-      <c r="DM55">
+      <c r="DN55">
         <f t="shared" si="2"/>
         <v>4</v>
       </c>
-      <c r="DN55" s="18">
+      <c r="DO55" s="18">
         <f t="shared" si="3"/>
         <v>2.875</v>
       </c>
-      <c r="DO55">
+      <c r="DP55">
         <f t="shared" si="4"/>
         <v>2.7801378862687129</v>
       </c>
-      <c r="DP55">
+      <c r="DQ55">
         <v>0</v>
       </c>
-      <c r="DQ55">
+      <c r="DR55">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="DR55">
+      <c r="DS55">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
     </row>
-    <row r="56" spans="1:122" x14ac:dyDescent="0.35">
+    <row r="56" spans="1:123" x14ac:dyDescent="0.35">
       <c r="A56" t="s">
         <v>17</v>
       </c>
@@ -18480,31 +18528,31 @@
       <c r="CB56" t="s">
         <v>25</v>
       </c>
-      <c r="DM56">
+      <c r="DN56">
         <f t="shared" si="2"/>
         <v>3</v>
       </c>
-      <c r="DN56" s="18">
+      <c r="DO56" s="18">
         <f t="shared" si="3"/>
         <v>4.666666666666667</v>
       </c>
-      <c r="DO56">
+      <c r="DP56">
         <f t="shared" si="4"/>
         <v>1.4433756729740652</v>
       </c>
-      <c r="DP56">
+      <c r="DQ56">
         <v>0</v>
       </c>
-      <c r="DQ56">
+      <c r="DR56">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="DR56">
+      <c r="DS56">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
     </row>
-    <row r="57" spans="1:122" x14ac:dyDescent="0.35">
+    <row r="57" spans="1:123" x14ac:dyDescent="0.35">
       <c r="A57" t="s">
         <v>84</v>
       </c>
@@ -18751,31 +18799,34 @@
       <c r="DJ57">
         <v>7</v>
       </c>
-      <c r="DM57">
+      <c r="DL57">
+        <v>6</v>
+      </c>
+      <c r="DN57">
         <f t="shared" si="2"/>
         <v>4</v>
       </c>
-      <c r="DN57" s="18">
+      <c r="DO57" s="18">
         <f t="shared" si="3"/>
         <v>7.875</v>
       </c>
-      <c r="DO57">
+      <c r="DP57">
         <f t="shared" si="4"/>
         <v>1.75</v>
       </c>
-      <c r="DP57">
+      <c r="DQ57">
         <v>0</v>
       </c>
-      <c r="DQ57">
+      <c r="DR57">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="DR57">
+      <c r="DS57">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
     </row>
-    <row r="58" spans="1:122" x14ac:dyDescent="0.35">
+    <row r="58" spans="1:123" x14ac:dyDescent="0.35">
       <c r="A58" t="s">
         <v>48</v>
       </c>
@@ -19016,31 +19067,31 @@
       <c r="CB58" t="s">
         <v>25</v>
       </c>
-      <c r="DM58">
+      <c r="DN58">
         <f t="shared" si="2"/>
         <v>3</v>
       </c>
-      <c r="DN58" s="18">
+      <c r="DO58" s="18">
         <f t="shared" si="3"/>
         <v>4</v>
       </c>
-      <c r="DO58">
+      <c r="DP58">
         <f t="shared" si="4"/>
         <v>1.7320508075688772</v>
       </c>
-      <c r="DP58">
+      <c r="DQ58">
         <v>0</v>
       </c>
-      <c r="DQ58">
+      <c r="DR58">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="DR58">
+      <c r="DS58">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
     </row>
-    <row r="59" spans="1:122" x14ac:dyDescent="0.35">
+    <row r="59" spans="1:123" x14ac:dyDescent="0.35">
       <c r="A59" t="s">
         <v>119</v>
       </c>
@@ -19284,31 +19335,31 @@
       <c r="CG59">
         <v>6</v>
       </c>
-      <c r="DM59">
+      <c r="DN59">
         <f t="shared" si="2"/>
         <v>3</v>
       </c>
-      <c r="DN59" s="18">
+      <c r="DO59" s="18">
         <f t="shared" si="3"/>
         <v>8.5</v>
       </c>
-      <c r="DO59">
+      <c r="DP59">
         <f t="shared" si="4"/>
         <v>2.179449471770337</v>
       </c>
-      <c r="DP59">
+      <c r="DQ59">
         <v>0</v>
       </c>
-      <c r="DQ59">
+      <c r="DR59">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="DR59">
+      <c r="DS59">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
     </row>
-    <row r="60" spans="1:122" x14ac:dyDescent="0.35">
+    <row r="60" spans="1:123" x14ac:dyDescent="0.35">
       <c r="A60" t="s">
         <v>52</v>
       </c>
@@ -19552,31 +19603,31 @@
       <c r="CS60">
         <v>5.5</v>
       </c>
-      <c r="DM60">
+      <c r="DN60">
         <f t="shared" si="2"/>
         <v>3</v>
       </c>
-      <c r="DN60" s="18">
+      <c r="DO60" s="18">
         <f t="shared" si="3"/>
         <v>5.333333333333333</v>
       </c>
-      <c r="DO60">
+      <c r="DP60">
         <f t="shared" si="4"/>
         <v>0.28867513459481287</v>
       </c>
-      <c r="DP60">
+      <c r="DQ60">
         <v>0</v>
       </c>
-      <c r="DQ60">
+      <c r="DR60">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="DR60">
+      <c r="DS60">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
     </row>
-    <row r="61" spans="1:122" x14ac:dyDescent="0.35">
+    <row r="61" spans="1:123" x14ac:dyDescent="0.35">
       <c r="A61" t="s">
         <v>138</v>
       </c>
@@ -19826,31 +19877,31 @@
       <c r="CJ61">
         <v>7</v>
       </c>
-      <c r="DM61">
+      <c r="DN61">
         <f t="shared" si="2"/>
         <v>3</v>
       </c>
-      <c r="DN61" s="18">
+      <c r="DO61" s="18">
         <f t="shared" si="3"/>
         <v>6.666666666666667</v>
       </c>
-      <c r="DO61">
+      <c r="DP61">
         <f t="shared" si="4"/>
         <v>0.57735026918962584</v>
       </c>
-      <c r="DP61">
+      <c r="DQ61">
         <v>0</v>
       </c>
-      <c r="DQ61">
+      <c r="DR61">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="DR61">
+      <c r="DS61">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
     </row>
-    <row r="62" spans="1:122" x14ac:dyDescent="0.35">
+    <row r="62" spans="1:123" x14ac:dyDescent="0.35">
       <c r="A62" t="s">
         <v>130</v>
       </c>
@@ -20094,31 +20145,31 @@
       <c r="DF62">
         <v>5</v>
       </c>
-      <c r="DM62">
+      <c r="DN62">
         <f t="shared" si="2"/>
         <v>3</v>
       </c>
-      <c r="DN62" s="18">
+      <c r="DO62" s="18">
         <f t="shared" si="3"/>
         <v>5.333333333333333</v>
       </c>
-      <c r="DO62">
+      <c r="DP62">
         <f t="shared" si="4"/>
         <v>0.28867513459481287</v>
       </c>
-      <c r="DP62">
+      <c r="DQ62">
         <v>0</v>
       </c>
-      <c r="DQ62">
+      <c r="DR62">
         <f t="shared" si="5"/>
         <v>1</v>
       </c>
-      <c r="DR62">
+      <c r="DS62">
         <f t="shared" si="6"/>
         <v>1</v>
       </c>
     </row>
-    <row r="63" spans="1:122" x14ac:dyDescent="0.35">
+    <row r="63" spans="1:123" x14ac:dyDescent="0.35">
       <c r="A63" t="s">
         <v>113</v>
       </c>
@@ -20362,31 +20413,31 @@
       <c r="CD63">
         <v>5.5</v>
       </c>
-      <c r="DM63">
+      <c r="DN63">
         <f t="shared" si="2"/>
         <v>2</v>
       </c>
-      <c r="DN63" s="18">
+      <c r="DO63" s="18">
         <f t="shared" si="3"/>
         <v>5.25</v>
       </c>
-      <c r="DO63">
+      <c r="DP63">
         <f t="shared" si="4"/>
         <v>0.35355339059327379</v>
       </c>
-      <c r="DP63">
+      <c r="DQ63">
         <v>0</v>
       </c>
-      <c r="DQ63">
+      <c r="DR63">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="DR63">
+      <c r="DS63">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
     </row>
-    <row r="64" spans="1:122" x14ac:dyDescent="0.35">
+    <row r="64" spans="1:123" x14ac:dyDescent="0.35">
       <c r="A64" t="s">
         <v>94</v>
       </c>
@@ -20627,31 +20678,31 @@
       <c r="CB64" t="s">
         <v>25</v>
       </c>
-      <c r="DM64">
+      <c r="DN64">
         <f t="shared" si="2"/>
         <v>2</v>
       </c>
-      <c r="DN64" s="18">
+      <c r="DO64" s="18">
         <f t="shared" si="3"/>
         <v>6.75</v>
       </c>
-      <c r="DO64">
+      <c r="DP64">
         <f t="shared" si="4"/>
         <v>2.4748737341529163</v>
       </c>
-      <c r="DP64">
+      <c r="DQ64">
         <v>0</v>
       </c>
-      <c r="DQ64">
+      <c r="DR64">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="DR64">
+      <c r="DS64">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
     </row>
-    <row r="65" spans="1:122" x14ac:dyDescent="0.35">
+    <row r="65" spans="1:123" x14ac:dyDescent="0.35">
       <c r="A65" t="s">
         <v>120</v>
       </c>
@@ -20892,31 +20943,31 @@
       <c r="CB65" t="s">
         <v>25</v>
       </c>
-      <c r="DM65">
+      <c r="DN65">
         <f t="shared" si="2"/>
         <v>2</v>
       </c>
-      <c r="DN65" s="18">
+      <c r="DO65" s="18">
         <f t="shared" si="3"/>
         <v>5.75</v>
       </c>
-      <c r="DO65">
+      <c r="DP65">
         <f t="shared" si="4"/>
         <v>1.0606601717798212</v>
       </c>
-      <c r="DP65">
+      <c r="DQ65">
         <v>0</v>
       </c>
-      <c r="DQ65">
+      <c r="DR65">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="DR65">
+      <c r="DS65">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
     </row>
-    <row r="66" spans="1:122" x14ac:dyDescent="0.35">
+    <row r="66" spans="1:123" x14ac:dyDescent="0.35">
       <c r="A66" t="s">
         <v>139</v>
       </c>
@@ -21160,31 +21211,31 @@
       <c r="CH66">
         <v>5</v>
       </c>
-      <c r="DM66">
+      <c r="DN66">
         <f t="shared" si="2"/>
         <v>2</v>
       </c>
-      <c r="DN66" s="18">
+      <c r="DO66" s="18">
         <f t="shared" si="3"/>
         <v>4.25</v>
       </c>
-      <c r="DO66">
+      <c r="DP66">
         <f t="shared" si="4"/>
         <v>1.0606601717798212</v>
       </c>
-      <c r="DP66">
+      <c r="DQ66">
         <v>0</v>
       </c>
-      <c r="DQ66">
-        <f t="shared" ref="DQ66:DQ89" si="7">COUNT(DF66:DH66)</f>
+      <c r="DR66">
+        <f t="shared" ref="DR66:DR89" si="7">COUNT(DF66:DH66)</f>
         <v>0</v>
       </c>
-      <c r="DR66">
-        <f t="shared" ref="DR66:DR89" si="8">IF(DP66=0,DQ66,0)</f>
+      <c r="DS66">
+        <f t="shared" ref="DS66:DS89" si="8">IF(DQ66=0,DR66,0)</f>
         <v>0</v>
       </c>
     </row>
-    <row r="67" spans="1:122" x14ac:dyDescent="0.35">
+    <row r="67" spans="1:123" x14ac:dyDescent="0.35">
       <c r="A67" t="s">
         <v>146</v>
       </c>
@@ -21194,62 +21245,62 @@
       <c r="DA67">
         <v>7</v>
       </c>
-      <c r="DM67">
-        <f t="shared" ref="DM67:DM102" si="9">COUNT(B67:DI67)</f>
-        <v>2</v>
-      </c>
-      <c r="DN67" s="18">
-        <f t="shared" ref="DN67:DN102" si="10">AVERAGE(B67:DI67)</f>
+      <c r="DN67">
+        <f t="shared" ref="DN67:DN102" si="9">COUNT(B67:DI67)</f>
+        <v>2</v>
+      </c>
+      <c r="DO67" s="18">
+        <f t="shared" ref="DO67:DO102" si="10">AVERAGE(B67:DI67)</f>
         <v>7.25</v>
       </c>
-      <c r="DO67">
-        <f t="shared" ref="DO67:DO102" si="11">IF(DM67&gt;1,_xlfn.STDEV.S(B67:DI67),"")</f>
+      <c r="DP67">
+        <f t="shared" ref="DP67:DP102" si="11">IF(DN67&gt;1,_xlfn.STDEV.S(B67:DI67),"")</f>
         <v>0.35355339059327379</v>
       </c>
-      <c r="DP67">
+      <c r="DQ67">
         <v>0</v>
       </c>
-      <c r="DQ67">
+      <c r="DR67">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="DR67">
+      <c r="DS67">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
     </row>
-    <row r="68" spans="1:122" x14ac:dyDescent="0.35">
+    <row r="68" spans="1:123" x14ac:dyDescent="0.35">
       <c r="A68" t="s">
         <v>147</v>
       </c>
       <c r="CV68">
         <v>6</v>
       </c>
-      <c r="DM68">
+      <c r="DN68">
         <f t="shared" si="9"/>
         <v>1</v>
       </c>
-      <c r="DN68" s="18">
+      <c r="DO68" s="18">
         <f t="shared" si="10"/>
         <v>6</v>
       </c>
-      <c r="DO68" t="str">
+      <c r="DP68" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
-      <c r="DP68">
+      <c r="DQ68">
         <v>0</v>
       </c>
-      <c r="DQ68">
+      <c r="DR68">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="DR68">
+      <c r="DS68">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
     </row>
-    <row r="69" spans="1:122" x14ac:dyDescent="0.35">
+    <row r="69" spans="1:123" x14ac:dyDescent="0.35">
       <c r="A69" t="s">
         <v>85</v>
       </c>
@@ -21490,31 +21541,31 @@
       <c r="CB69" t="s">
         <v>25</v>
       </c>
-      <c r="DM69">
+      <c r="DN69">
         <f t="shared" si="9"/>
         <v>1</v>
       </c>
-      <c r="DN69" s="18">
+      <c r="DO69" s="18">
         <f t="shared" si="10"/>
         <v>10</v>
       </c>
-      <c r="DO69" t="str">
+      <c r="DP69" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
-      <c r="DP69">
+      <c r="DQ69">
         <v>0</v>
       </c>
-      <c r="DQ69">
+      <c r="DR69">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="DR69">
+      <c r="DS69">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
     </row>
-    <row r="70" spans="1:122" x14ac:dyDescent="0.35">
+    <row r="70" spans="1:123" x14ac:dyDescent="0.35">
       <c r="A70" t="s">
         <v>76</v>
       </c>
@@ -21755,31 +21806,31 @@
       <c r="CB70" t="s">
         <v>25</v>
       </c>
-      <c r="DM70">
+      <c r="DN70">
         <f t="shared" si="9"/>
         <v>1</v>
       </c>
-      <c r="DN70" s="18">
+      <c r="DO70" s="18">
         <f t="shared" si="10"/>
         <v>7</v>
       </c>
-      <c r="DO70" t="str">
+      <c r="DP70" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
-      <c r="DP70">
+      <c r="DQ70">
         <v>0</v>
       </c>
-      <c r="DQ70">
+      <c r="DR70">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="DR70">
+      <c r="DS70">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
     </row>
-    <row r="71" spans="1:122" x14ac:dyDescent="0.35">
+    <row r="71" spans="1:123" x14ac:dyDescent="0.35">
       <c r="A71" t="s">
         <v>107</v>
       </c>
@@ -22020,31 +22071,31 @@
       <c r="CB71" t="s">
         <v>25</v>
       </c>
-      <c r="DM71">
+      <c r="DN71">
         <f t="shared" si="9"/>
         <v>1</v>
       </c>
-      <c r="DN71" s="18">
+      <c r="DO71" s="18">
         <f t="shared" si="10"/>
         <v>7</v>
       </c>
-      <c r="DO71" t="str">
+      <c r="DP71" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
-      <c r="DP71">
+      <c r="DQ71">
         <v>0</v>
       </c>
-      <c r="DQ71">
+      <c r="DR71">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="DR71">
+      <c r="DS71">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
     </row>
-    <row r="72" spans="1:122" x14ac:dyDescent="0.35">
+    <row r="72" spans="1:123" x14ac:dyDescent="0.35">
       <c r="A72" t="s">
         <v>79</v>
       </c>
@@ -22285,31 +22336,31 @@
       <c r="CB72" t="s">
         <v>25</v>
       </c>
-      <c r="DM72">
+      <c r="DN72">
         <f t="shared" si="9"/>
         <v>1</v>
       </c>
-      <c r="DN72" s="18">
+      <c r="DO72" s="18">
         <f t="shared" si="10"/>
         <v>7</v>
       </c>
-      <c r="DO72" t="str">
+      <c r="DP72" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
-      <c r="DP72">
+      <c r="DQ72">
         <v>0</v>
       </c>
-      <c r="DQ72">
+      <c r="DR72">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="DR72">
+      <c r="DS72">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
     </row>
-    <row r="73" spans="1:122" x14ac:dyDescent="0.35">
+    <row r="73" spans="1:123" x14ac:dyDescent="0.35">
       <c r="A73" t="s">
         <v>46</v>
       </c>
@@ -22550,31 +22601,31 @@
       <c r="CB73" t="s">
         <v>25</v>
       </c>
-      <c r="DM73">
+      <c r="DN73">
         <f t="shared" si="9"/>
         <v>1</v>
       </c>
-      <c r="DN73" s="18">
+      <c r="DO73" s="18">
         <f t="shared" si="10"/>
         <v>3.5</v>
       </c>
-      <c r="DO73" t="str">
+      <c r="DP73" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
-      <c r="DP73">
+      <c r="DQ73">
         <v>0</v>
       </c>
-      <c r="DQ73">
+      <c r="DR73">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="DR73">
+      <c r="DS73">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
     </row>
-    <row r="74" spans="1:122" x14ac:dyDescent="0.35">
+    <row r="74" spans="1:123" x14ac:dyDescent="0.35">
       <c r="A74" t="s">
         <v>82</v>
       </c>
@@ -22815,31 +22866,31 @@
       <c r="CB74" t="s">
         <v>25</v>
       </c>
-      <c r="DM74">
+      <c r="DN74">
         <f t="shared" si="9"/>
         <v>1</v>
       </c>
-      <c r="DN74" s="18">
+      <c r="DO74" s="18">
         <f t="shared" si="10"/>
         <v>3</v>
       </c>
-      <c r="DO74" t="str">
+      <c r="DP74" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
-      <c r="DP74">
+      <c r="DQ74">
         <v>0</v>
       </c>
-      <c r="DQ74">
+      <c r="DR74">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="DR74">
+      <c r="DS74">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
     </row>
-    <row r="75" spans="1:122" x14ac:dyDescent="0.35">
+    <row r="75" spans="1:123" x14ac:dyDescent="0.35">
       <c r="A75" t="s">
         <v>101</v>
       </c>
@@ -23080,31 +23131,31 @@
       <c r="CB75" t="s">
         <v>25</v>
       </c>
-      <c r="DM75">
+      <c r="DN75">
         <f t="shared" si="9"/>
         <v>1</v>
       </c>
-      <c r="DN75" s="18">
+      <c r="DO75" s="18">
         <f t="shared" si="10"/>
         <v>6.5</v>
       </c>
-      <c r="DO75" t="str">
+      <c r="DP75" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
-      <c r="DP75">
+      <c r="DQ75">
         <v>0</v>
       </c>
-      <c r="DQ75">
+      <c r="DR75">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="DR75">
+      <c r="DS75">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
     </row>
-    <row r="76" spans="1:122" x14ac:dyDescent="0.35">
+    <row r="76" spans="1:123" x14ac:dyDescent="0.35">
       <c r="A76" t="s">
         <v>104</v>
       </c>
@@ -23345,31 +23396,31 @@
       <c r="CB76" t="s">
         <v>25</v>
       </c>
-      <c r="DM76">
+      <c r="DN76">
         <f t="shared" si="9"/>
         <v>1</v>
       </c>
-      <c r="DN76" s="18">
+      <c r="DO76" s="18">
         <f t="shared" si="10"/>
         <v>4</v>
       </c>
-      <c r="DO76" t="str">
+      <c r="DP76" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
-      <c r="DP76">
+      <c r="DQ76">
         <v>0</v>
       </c>
-      <c r="DQ76">
+      <c r="DR76">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="DR76">
+      <c r="DS76">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
     </row>
-    <row r="77" spans="1:122" x14ac:dyDescent="0.35">
+    <row r="77" spans="1:123" x14ac:dyDescent="0.35">
       <c r="A77" t="s">
         <v>105</v>
       </c>
@@ -23610,31 +23661,31 @@
       <c r="CB77" t="s">
         <v>25</v>
       </c>
-      <c r="DM77">
+      <c r="DN77">
         <f t="shared" si="9"/>
         <v>1</v>
       </c>
-      <c r="DN77" s="18">
+      <c r="DO77" s="18">
         <f t="shared" si="10"/>
         <v>6.5</v>
       </c>
-      <c r="DO77" t="str">
+      <c r="DP77" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
-      <c r="DP77">
+      <c r="DQ77">
         <v>0</v>
       </c>
-      <c r="DQ77">
+      <c r="DR77">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="DR77">
+      <c r="DS77">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
     </row>
-    <row r="78" spans="1:122" x14ac:dyDescent="0.35">
+    <row r="78" spans="1:123" x14ac:dyDescent="0.35">
       <c r="A78" t="s">
         <v>106</v>
       </c>
@@ -23875,31 +23926,31 @@
       <c r="CB78" t="s">
         <v>25</v>
       </c>
-      <c r="DM78">
+      <c r="DN78">
         <f t="shared" si="9"/>
         <v>1</v>
       </c>
-      <c r="DN78" s="18">
+      <c r="DO78" s="18">
         <f t="shared" si="10"/>
         <v>5</v>
       </c>
-      <c r="DO78" t="str">
+      <c r="DP78" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
-      <c r="DP78">
+      <c r="DQ78">
         <v>0</v>
       </c>
-      <c r="DQ78">
+      <c r="DR78">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="DR78">
+      <c r="DS78">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
     </row>
-    <row r="79" spans="1:122" x14ac:dyDescent="0.35">
+    <row r="79" spans="1:123" x14ac:dyDescent="0.35">
       <c r="A79" t="s">
         <v>108</v>
       </c>
@@ -24149,31 +24200,34 @@
       <c r="DK79">
         <v>6.5</v>
       </c>
-      <c r="DM79">
+      <c r="DL79">
+        <v>6</v>
+      </c>
+      <c r="DN79">
         <f t="shared" si="9"/>
         <v>2</v>
       </c>
-      <c r="DN79" s="18">
+      <c r="DO79" s="18">
         <f t="shared" si="10"/>
         <v>5.75</v>
       </c>
-      <c r="DO79">
+      <c r="DP79">
         <f t="shared" si="11"/>
         <v>0.35355339059327379</v>
       </c>
-      <c r="DP79">
+      <c r="DQ79">
         <v>0</v>
       </c>
-      <c r="DQ79">
+      <c r="DR79">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="DR79">
+      <c r="DS79">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
     </row>
-    <row r="80" spans="1:122" x14ac:dyDescent="0.35">
+    <row r="80" spans="1:123" x14ac:dyDescent="0.35">
       <c r="A80" t="s">
         <v>116</v>
       </c>
@@ -24414,31 +24468,31 @@
       <c r="CB80" t="s">
         <v>25</v>
       </c>
-      <c r="DM80">
+      <c r="DN80">
         <f t="shared" si="9"/>
         <v>1</v>
       </c>
-      <c r="DN80" s="18">
+      <c r="DO80" s="18">
         <f t="shared" si="10"/>
         <v>2</v>
       </c>
-      <c r="DO80" t="str">
+      <c r="DP80" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
-      <c r="DP80">
+      <c r="DQ80">
         <v>0</v>
       </c>
-      <c r="DQ80">
+      <c r="DR80">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="DR80">
+      <c r="DS80">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
     </row>
-    <row r="81" spans="1:122" x14ac:dyDescent="0.35">
+    <row r="81" spans="1:123" x14ac:dyDescent="0.35">
       <c r="A81" t="s">
         <v>117</v>
       </c>
@@ -24679,31 +24733,31 @@
       <c r="CB81" t="s">
         <v>25</v>
       </c>
-      <c r="DM81">
+      <c r="DN81">
         <f t="shared" si="9"/>
         <v>1</v>
       </c>
-      <c r="DN81" s="18">
+      <c r="DO81" s="18">
         <f t="shared" si="10"/>
         <v>2.5</v>
       </c>
-      <c r="DO81" t="str">
+      <c r="DP81" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
-      <c r="DP81">
+      <c r="DQ81">
         <v>0</v>
       </c>
-      <c r="DQ81">
+      <c r="DR81">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="DR81">
+      <c r="DS81">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
     </row>
-    <row r="82" spans="1:122" x14ac:dyDescent="0.35">
+    <row r="82" spans="1:123" x14ac:dyDescent="0.35">
       <c r="A82" t="s">
         <v>125</v>
       </c>
@@ -24944,31 +24998,31 @@
       <c r="CB82" t="s">
         <v>25</v>
       </c>
-      <c r="DM82">
+      <c r="DN82">
         <f t="shared" si="9"/>
         <v>1</v>
       </c>
-      <c r="DN82" s="18">
+      <c r="DO82" s="18">
         <f t="shared" si="10"/>
         <v>7</v>
       </c>
-      <c r="DO82" t="str">
+      <c r="DP82" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
-      <c r="DP82">
+      <c r="DQ82">
         <v>0</v>
       </c>
-      <c r="DQ82">
+      <c r="DR82">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="DR82">
+      <c r="DS82">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
     </row>
-    <row r="83" spans="1:122" x14ac:dyDescent="0.35">
+    <row r="83" spans="1:123" x14ac:dyDescent="0.35">
       <c r="A83" t="s">
         <v>126</v>
       </c>
@@ -25209,31 +25263,31 @@
       <c r="CB83" t="s">
         <v>25</v>
       </c>
-      <c r="DM83">
+      <c r="DN83">
         <f t="shared" si="9"/>
         <v>1</v>
       </c>
-      <c r="DN83" s="18">
+      <c r="DO83" s="18">
         <f t="shared" si="10"/>
         <v>5.5</v>
       </c>
-      <c r="DO83" t="str">
+      <c r="DP83" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
-      <c r="DP83">
+      <c r="DQ83">
         <v>0</v>
       </c>
-      <c r="DQ83">
+      <c r="DR83">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="DR83">
+      <c r="DS83">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
     </row>
-    <row r="84" spans="1:122" x14ac:dyDescent="0.35">
+    <row r="84" spans="1:123" x14ac:dyDescent="0.35">
       <c r="A84" t="s">
         <v>128</v>
       </c>
@@ -25474,31 +25528,31 @@
       <c r="CB84" t="s">
         <v>25</v>
       </c>
-      <c r="DM84">
+      <c r="DN84">
         <f t="shared" si="9"/>
         <v>1</v>
       </c>
-      <c r="DN84" s="18">
+      <c r="DO84" s="18">
         <f t="shared" si="10"/>
         <v>5</v>
       </c>
-      <c r="DO84" t="str">
+      <c r="DP84" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
-      <c r="DP84">
+      <c r="DQ84">
         <v>0</v>
       </c>
-      <c r="DQ84">
+      <c r="DR84">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="DR84">
+      <c r="DS84">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
     </row>
-    <row r="85" spans="1:122" x14ac:dyDescent="0.35">
+    <row r="85" spans="1:123" x14ac:dyDescent="0.35">
       <c r="A85" t="s">
         <v>132</v>
       </c>
@@ -25739,31 +25793,31 @@
       <c r="CB85" t="s">
         <v>25</v>
       </c>
-      <c r="DM85">
+      <c r="DN85">
         <f t="shared" si="9"/>
         <v>1</v>
       </c>
-      <c r="DN85" s="18">
+      <c r="DO85" s="18">
         <f t="shared" si="10"/>
         <v>5.5</v>
       </c>
-      <c r="DO85" t="str">
+      <c r="DP85" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
-      <c r="DP85">
+      <c r="DQ85">
         <v>0</v>
       </c>
-      <c r="DQ85">
+      <c r="DR85">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="DR85">
+      <c r="DS85">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
     </row>
-    <row r="86" spans="1:122" x14ac:dyDescent="0.35">
+    <row r="86" spans="1:123" x14ac:dyDescent="0.35">
       <c r="A86" t="s">
         <v>133</v>
       </c>
@@ -26004,31 +26058,31 @@
       <c r="CB86" t="s">
         <v>25</v>
       </c>
-      <c r="DM86">
+      <c r="DN86">
         <f t="shared" si="9"/>
         <v>1</v>
       </c>
-      <c r="DN86" s="18">
+      <c r="DO86" s="18">
         <f t="shared" si="10"/>
         <v>5.5</v>
       </c>
-      <c r="DO86" t="str">
+      <c r="DP86" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
-      <c r="DP86">
+      <c r="DQ86">
         <v>0</v>
       </c>
-      <c r="DQ86">
+      <c r="DR86">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="DR86">
+      <c r="DS86">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
     </row>
-    <row r="87" spans="1:122" x14ac:dyDescent="0.35">
+    <row r="87" spans="1:123" x14ac:dyDescent="0.35">
       <c r="A87" t="s">
         <v>140</v>
       </c>
@@ -26272,31 +26326,31 @@
       <c r="CH87">
         <v>7.5</v>
       </c>
-      <c r="DM87">
+      <c r="DN87">
         <f t="shared" si="9"/>
         <v>1</v>
       </c>
-      <c r="DN87" s="18">
+      <c r="DO87" s="18">
         <f t="shared" si="10"/>
         <v>7.5</v>
       </c>
-      <c r="DO87" t="str">
+      <c r="DP87" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
-      <c r="DP87">
+      <c r="DQ87">
         <v>0</v>
       </c>
-      <c r="DQ87">
+      <c r="DR87">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="DR87">
+      <c r="DS87">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
     </row>
-    <row r="88" spans="1:122" x14ac:dyDescent="0.35">
+    <row r="88" spans="1:123" x14ac:dyDescent="0.35">
       <c r="A88" t="s">
         <v>142</v>
       </c>
@@ -26540,95 +26594,95 @@
       <c r="CI88">
         <v>7</v>
       </c>
-      <c r="DM88">
+      <c r="DN88">
         <f t="shared" si="9"/>
         <v>1</v>
       </c>
-      <c r="DN88" s="18">
+      <c r="DO88" s="18">
         <f t="shared" si="10"/>
         <v>7</v>
       </c>
-      <c r="DO88" t="str">
+      <c r="DP88" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
-      <c r="DP88">
+      <c r="DQ88">
         <v>0</v>
       </c>
-      <c r="DQ88">
+      <c r="DR88">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="DR88">
+      <c r="DS88">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
     </row>
-    <row r="89" spans="1:122" x14ac:dyDescent="0.35">
+    <row r="89" spans="1:123" x14ac:dyDescent="0.35">
       <c r="A89" t="s">
         <v>144</v>
       </c>
       <c r="CP89">
         <v>6.5</v>
       </c>
-      <c r="DM89">
+      <c r="DN89">
         <f t="shared" si="9"/>
         <v>1</v>
       </c>
-      <c r="DN89" s="18">
+      <c r="DO89" s="18">
         <f t="shared" si="10"/>
         <v>6.5</v>
       </c>
-      <c r="DO89" t="str">
+      <c r="DP89" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
-      <c r="DP89">
+      <c r="DQ89">
         <v>0</v>
       </c>
-      <c r="DQ89">
+      <c r="DR89">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="DR89">
+      <c r="DS89">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
     </row>
-    <row r="90" spans="1:122" x14ac:dyDescent="0.35">
+    <row r="90" spans="1:123" x14ac:dyDescent="0.35">
       <c r="A90" t="s">
         <v>145</v>
       </c>
       <c r="CQ90">
         <v>6.5</v>
       </c>
-      <c r="DM90">
+      <c r="DN90">
         <f t="shared" si="9"/>
         <v>1</v>
       </c>
-      <c r="DN90" s="18">
+      <c r="DO90" s="18">
         <f t="shared" si="10"/>
         <v>6.5</v>
       </c>
-      <c r="DO90" t="str">
+      <c r="DP90" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
-      <c r="DP90">
-        <v>1</v>
-      </c>
       <c r="DQ90">
-        <f t="shared" ref="DQ90:DQ102" si="12">COUNT(DF90:DH90)</f>
+        <v>1</v>
+      </c>
+      <c r="DR90">
+        <f t="shared" ref="DR90:DR102" si="12">COUNT(DF90:DH90)</f>
         <v>0</v>
       </c>
-      <c r="DR90">
-        <f t="shared" ref="DR90:DR102" si="13">IF(DP90=0,DQ90,0)</f>
+      <c r="DS90">
+        <f t="shared" ref="DS90:DS102" si="13">IF(DQ90=0,DR90,0)</f>
         <v>0</v>
       </c>
     </row>
-    <row r="91" spans="1:122" x14ac:dyDescent="0.35">
+    <row r="91" spans="1:123" x14ac:dyDescent="0.35">
       <c r="A91" t="s">
-        <v>152</v>
+        <v>174</v>
       </c>
       <c r="DB91">
         <v>6</v>
@@ -26639,31 +26693,34 @@
       <c r="DI91">
         <v>6</v>
       </c>
-      <c r="DM91">
+      <c r="DL91">
+        <v>5.5</v>
+      </c>
+      <c r="DN91">
         <f t="shared" si="9"/>
         <v>3</v>
       </c>
-      <c r="DN91" s="18">
+      <c r="DO91" s="18">
         <f t="shared" si="10"/>
         <v>6</v>
       </c>
-      <c r="DO91">
+      <c r="DP91">
         <f t="shared" si="11"/>
         <v>0</v>
       </c>
-      <c r="DP91">
-        <v>1</v>
-      </c>
       <c r="DQ91">
+        <v>1</v>
+      </c>
+      <c r="DR91">
         <f t="shared" si="12"/>
         <v>1</v>
       </c>
-      <c r="DR91">
+      <c r="DS91">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
     </row>
-    <row r="92" spans="1:122" x14ac:dyDescent="0.35">
+    <row r="92" spans="1:123" x14ac:dyDescent="0.35">
       <c r="A92" t="s">
         <v>165</v>
       </c>
@@ -26673,93 +26730,93 @@
       <c r="DH92">
         <v>6</v>
       </c>
-      <c r="DM92">
+      <c r="DN92">
         <f t="shared" si="9"/>
         <v>2</v>
       </c>
-      <c r="DN92" s="18">
+      <c r="DO92" s="18">
         <f t="shared" si="10"/>
         <v>6</v>
       </c>
-      <c r="DO92">
+      <c r="DP92">
         <f t="shared" si="11"/>
         <v>0</v>
       </c>
-      <c r="DP92">
-        <v>1</v>
-      </c>
       <c r="DQ92">
+        <v>1</v>
+      </c>
+      <c r="DR92">
         <f t="shared" si="12"/>
         <v>1</v>
       </c>
-      <c r="DR92">
+      <c r="DS92">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
     </row>
-    <row r="93" spans="1:122" x14ac:dyDescent="0.35">
+    <row r="93" spans="1:123" x14ac:dyDescent="0.35">
       <c r="A93" t="s">
         <v>159</v>
       </c>
       <c r="DF93">
         <v>5.5</v>
       </c>
-      <c r="DM93">
+      <c r="DN93">
         <f t="shared" si="9"/>
         <v>1</v>
       </c>
-      <c r="DN93" s="18">
+      <c r="DO93" s="18">
         <f t="shared" si="10"/>
         <v>5.5</v>
       </c>
-      <c r="DO93" t="str">
+      <c r="DP93" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
-      <c r="DP93">
-        <v>1</v>
-      </c>
       <c r="DQ93">
+        <v>1</v>
+      </c>
+      <c r="DR93">
         <f t="shared" si="12"/>
         <v>1</v>
       </c>
-      <c r="DR93">
+      <c r="DS93">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
     </row>
-    <row r="94" spans="1:122" x14ac:dyDescent="0.35">
+    <row r="94" spans="1:123" x14ac:dyDescent="0.35">
       <c r="A94" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="DF94">
         <v>6</v>
       </c>
-      <c r="DM94">
+      <c r="DN94">
         <f t="shared" si="9"/>
         <v>1</v>
       </c>
-      <c r="DN94" s="18">
+      <c r="DO94" s="18">
         <f t="shared" si="10"/>
         <v>6</v>
       </c>
-      <c r="DO94" t="str">
+      <c r="DP94" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
-      <c r="DP94">
-        <v>1</v>
-      </c>
       <c r="DQ94">
+        <v>1</v>
+      </c>
+      <c r="DR94">
         <f t="shared" si="12"/>
         <v>1</v>
       </c>
-      <c r="DR94">
+      <c r="DS94">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
     </row>
-    <row r="95" spans="1:122" x14ac:dyDescent="0.35">
+    <row r="95" spans="1:123" x14ac:dyDescent="0.35">
       <c r="A95" t="s">
         <v>160</v>
       </c>
@@ -26769,95 +26826,95 @@
       <c r="DK95">
         <v>6</v>
       </c>
-      <c r="DM95">
+      <c r="DN95">
         <f t="shared" si="9"/>
         <v>1</v>
       </c>
-      <c r="DN95" s="18">
+      <c r="DO95" s="18">
         <f t="shared" si="10"/>
         <v>6</v>
       </c>
-      <c r="DO95" t="str">
+      <c r="DP95" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
-      <c r="DP95">
-        <v>1</v>
-      </c>
       <c r="DQ95">
+        <v>1</v>
+      </c>
+      <c r="DR95">
         <f t="shared" si="12"/>
         <v>1</v>
       </c>
-      <c r="DR95">
+      <c r="DS95">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
     </row>
-    <row r="96" spans="1:122" x14ac:dyDescent="0.35">
+    <row r="96" spans="1:123" x14ac:dyDescent="0.35">
       <c r="A96" t="s">
         <v>161</v>
       </c>
       <c r="DG96">
         <v>5.5</v>
       </c>
-      <c r="DM96">
+      <c r="DN96">
         <f t="shared" si="9"/>
         <v>1</v>
       </c>
-      <c r="DN96" s="18">
+      <c r="DO96" s="18">
         <f t="shared" si="10"/>
         <v>5.5</v>
       </c>
-      <c r="DO96" t="str">
+      <c r="DP96" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
-      <c r="DP96">
-        <v>1</v>
-      </c>
       <c r="DQ96">
+        <v>1</v>
+      </c>
+      <c r="DR96">
         <f t="shared" si="12"/>
         <v>1</v>
       </c>
-      <c r="DR96">
+      <c r="DS96">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
     </row>
-    <row r="97" spans="1:122" x14ac:dyDescent="0.35">
+    <row r="97" spans="1:123" x14ac:dyDescent="0.35">
       <c r="A97" t="s">
         <v>162</v>
       </c>
       <c r="DG97">
         <v>6</v>
       </c>
-      <c r="DM97">
+      <c r="DN97">
         <f t="shared" si="9"/>
         <v>1</v>
       </c>
-      <c r="DN97" s="18">
+      <c r="DO97" s="18">
         <f t="shared" si="10"/>
         <v>6</v>
       </c>
-      <c r="DO97" t="str">
+      <c r="DP97" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
-      <c r="DP97">
-        <v>1</v>
-      </c>
       <c r="DQ97">
+        <v>1</v>
+      </c>
+      <c r="DR97">
         <f t="shared" si="12"/>
         <v>1</v>
       </c>
-      <c r="DR97">
+      <c r="DS97">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
     </row>
-    <row r="98" spans="1:122" x14ac:dyDescent="0.35">
+    <row r="98" spans="1:123" x14ac:dyDescent="0.35">
       <c r="A98" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="DG98">
         <v>5.5</v>
@@ -26865,93 +26922,93 @@
       <c r="DI98">
         <v>6</v>
       </c>
-      <c r="DM98">
+      <c r="DN98">
         <f t="shared" si="9"/>
         <v>2</v>
       </c>
-      <c r="DN98" s="18">
+      <c r="DO98" s="18">
         <f t="shared" si="10"/>
         <v>5.75</v>
       </c>
-      <c r="DO98">
+      <c r="DP98">
         <f t="shared" si="11"/>
         <v>0.35355339059327379</v>
       </c>
-      <c r="DP98">
-        <v>1</v>
-      </c>
       <c r="DQ98">
+        <v>1</v>
+      </c>
+      <c r="DR98">
         <f t="shared" si="12"/>
         <v>1</v>
       </c>
-      <c r="DR98">
+      <c r="DS98">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
     </row>
-    <row r="99" spans="1:122" x14ac:dyDescent="0.35">
+    <row r="99" spans="1:123" x14ac:dyDescent="0.35">
       <c r="A99" t="s">
         <v>153</v>
       </c>
       <c r="DB99">
         <v>5.5</v>
       </c>
-      <c r="DM99">
+      <c r="DN99">
         <f t="shared" si="9"/>
         <v>1</v>
       </c>
-      <c r="DN99" s="18">
+      <c r="DO99" s="18">
         <f t="shared" si="10"/>
         <v>5.5</v>
       </c>
-      <c r="DO99" t="str">
+      <c r="DP99" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
-      <c r="DP99">
-        <v>1</v>
-      </c>
       <c r="DQ99">
+        <v>1</v>
+      </c>
+      <c r="DR99">
         <f t="shared" si="12"/>
         <v>0</v>
       </c>
-      <c r="DR99">
+      <c r="DS99">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
     </row>
-    <row r="100" spans="1:122" x14ac:dyDescent="0.35">
+    <row r="100" spans="1:123" x14ac:dyDescent="0.35">
       <c r="A100" t="s">
         <v>154</v>
       </c>
       <c r="DB100">
         <v>5.5</v>
       </c>
-      <c r="DM100">
+      <c r="DN100">
         <f t="shared" si="9"/>
         <v>1</v>
       </c>
-      <c r="DN100" s="18">
+      <c r="DO100" s="18">
         <f t="shared" si="10"/>
         <v>5.5</v>
       </c>
-      <c r="DO100" t="str">
+      <c r="DP100" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
-      <c r="DP100">
-        <v>1</v>
-      </c>
       <c r="DQ100">
+        <v>1</v>
+      </c>
+      <c r="DR100">
         <f t="shared" si="12"/>
         <v>0</v>
       </c>
-      <c r="DR100">
+      <c r="DS100">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
     </row>
-    <row r="101" spans="1:122" x14ac:dyDescent="0.35">
+    <row r="101" spans="1:123" x14ac:dyDescent="0.35">
       <c r="A101" t="s">
         <v>149</v>
       </c>
@@ -26982,64 +27039,64 @@
       <c r="DK101">
         <v>6</v>
       </c>
-      <c r="DM101">
+      <c r="DN101">
         <f t="shared" si="9"/>
         <v>8</v>
       </c>
-      <c r="DN101" s="18">
+      <c r="DO101" s="18">
         <f t="shared" si="10"/>
         <v>6.4375</v>
       </c>
-      <c r="DO101">
+      <c r="DP101">
         <f t="shared" si="11"/>
         <v>0.77632375426014844</v>
       </c>
-      <c r="DP101">
-        <v>1</v>
-      </c>
       <c r="DQ101">
+        <v>1</v>
+      </c>
+      <c r="DR101">
         <f t="shared" si="12"/>
         <v>2</v>
       </c>
-      <c r="DR101">
+      <c r="DS101">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
     </row>
-    <row r="102" spans="1:122" x14ac:dyDescent="0.35">
+    <row r="102" spans="1:123" x14ac:dyDescent="0.35">
       <c r="A102" t="s">
         <v>155</v>
       </c>
       <c r="DC102">
         <v>6</v>
       </c>
-      <c r="DM102">
+      <c r="DN102">
         <f t="shared" si="9"/>
         <v>1</v>
       </c>
-      <c r="DN102" s="18">
+      <c r="DO102" s="18">
         <f t="shared" si="10"/>
         <v>6</v>
       </c>
-      <c r="DO102" t="str">
+      <c r="DP102" t="str">
         <f t="shared" si="11"/>
         <v/>
       </c>
-      <c r="DP102">
-        <v>1</v>
-      </c>
       <c r="DQ102">
+        <v>1</v>
+      </c>
+      <c r="DR102">
         <f t="shared" si="12"/>
         <v>0</v>
       </c>
-      <c r="DR102">
+      <c r="DS102">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
     </row>
-    <row r="103" spans="1:122" x14ac:dyDescent="0.35">
+    <row r="103" spans="1:123" x14ac:dyDescent="0.35">
       <c r="A103" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="DJ103">
         <v>6</v>
@@ -27047,68 +27104,76 @@
       <c r="DK103">
         <v>6</v>
       </c>
-      <c r="DM103">
-        <f t="shared" ref="DM103:DM104" si="14">COUNT(B103:DI103)</f>
+      <c r="DN103">
+        <f t="shared" ref="DN103:DN104" si="14">COUNT(B103:DI103)</f>
         <v>0</v>
       </c>
-      <c r="DN103" s="18" t="e">
-        <f t="shared" ref="DN103:DN104" si="15">AVERAGE(B103:DI103)</f>
+      <c r="DO103" s="18" t="e">
+        <f t="shared" ref="DO103:DO104" si="15">AVERAGE(B103:DI103)</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="DO103" t="str">
-        <f t="shared" ref="DO103:DO104" si="16">IF(DM103&gt;1,_xlfn.STDEV.S(B103:DI103),"")</f>
+      <c r="DP103" t="str">
+        <f t="shared" ref="DP103:DP104" si="16">IF(DN103&gt;1,_xlfn.STDEV.S(B103:DI103),"")</f>
         <v/>
       </c>
-      <c r="DP103">
-        <v>1</v>
-      </c>
       <c r="DQ103">
-        <f t="shared" ref="DQ103:DQ104" si="17">COUNT(DF103:DH103)</f>
+        <v>1</v>
+      </c>
+      <c r="DR103">
+        <f t="shared" ref="DR103:DR104" si="17">COUNT(DF103:DH103)</f>
         <v>0</v>
       </c>
-      <c r="DR103">
-        <f t="shared" ref="DR103:DR104" si="18">IF(DP103=0,DQ103,0)</f>
+      <c r="DS103">
+        <f t="shared" ref="DS103:DS104" si="18">IF(DQ103=0,DR103,0)</f>
         <v>0</v>
       </c>
     </row>
-    <row r="104" spans="1:122" x14ac:dyDescent="0.35">
+    <row r="104" spans="1:123" x14ac:dyDescent="0.35">
       <c r="A104" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="DK104">
         <v>6.5</v>
       </c>
-      <c r="DM104">
+      <c r="DN104">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
-      <c r="DN104" s="18" t="e">
+      <c r="DO104" s="18" t="e">
         <f t="shared" si="15"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="DO104" t="str">
+      <c r="DP104" t="str">
         <f t="shared" si="16"/>
         <v/>
       </c>
-      <c r="DP104">
-        <v>1</v>
-      </c>
       <c r="DQ104">
+        <v>1</v>
+      </c>
+      <c r="DR104">
         <f t="shared" si="17"/>
         <v>0</v>
       </c>
-      <c r="DR104">
+      <c r="DS104">
         <f t="shared" si="18"/>
         <v>0</v>
       </c>
     </row>
+    <row r="105" spans="1:123" x14ac:dyDescent="0.35">
+      <c r="A105" t="s">
+        <v>173</v>
+      </c>
+      <c r="DL105">
+        <v>6.5</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:DR83" xr:uid="{B9A4D56B-02EF-476F-9B0E-F093A198C591}">
-    <sortState ref="A2:DR102">
-      <sortCondition descending="1" ref="DM1:DM83"/>
+  <autoFilter ref="A1:DS83" xr:uid="{B9A4D56B-02EF-476F-9B0E-F093A198C591}">
+    <sortState ref="A2:DS102">
+      <sortCondition descending="1" ref="DN1:DN83"/>
     </sortState>
   </autoFilter>
-  <conditionalFormatting sqref="DM2:DM104">
+  <conditionalFormatting sqref="DN2:DN104">
     <cfRule type="colorScale" priority="98">
       <colorScale>
         <cfvo type="min"/>
@@ -27120,7 +27185,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="DO2:DO104">
+  <conditionalFormatting sqref="DP2:DP104">
     <cfRule type="colorScale" priority="96">
       <colorScale>
         <cfvo type="min"/>
@@ -27132,7 +27197,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="DM2:DM104">
+  <conditionalFormatting sqref="DN2:DN104">
     <cfRule type="colorScale" priority="91">
       <colorScale>
         <cfvo type="min"/>
@@ -27144,7 +27209,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="DN2:DN104">
+  <conditionalFormatting sqref="DO2:DO104">
     <cfRule type="colorScale" priority="90">
       <colorScale>
         <cfvo type="min"/>
@@ -27156,7 +27221,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="DN2:DN104">
+  <conditionalFormatting sqref="DO2:DO104">
     <cfRule type="colorScale" priority="88">
       <colorScale>
         <cfvo type="min"/>
@@ -27168,7 +27233,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="DM2:DM104">
+  <conditionalFormatting sqref="DN2:DN104">
     <cfRule type="colorScale" priority="55">
       <colorScale>
         <cfvo type="min"/>
@@ -27180,7 +27245,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="DN2:DN104">
+  <conditionalFormatting sqref="DO2:DO104">
     <cfRule type="colorScale" priority="54">
       <colorScale>
         <cfvo type="min"/>
@@ -27192,7 +27257,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="DL2:DL79">
+  <conditionalFormatting sqref="DM2:DM79">
     <cfRule type="colorScale" priority="16">
       <colorScale>
         <cfvo type="min"/>
@@ -27204,7 +27269,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="DL2:DL67">
+  <conditionalFormatting sqref="DM2:DM67">
     <cfRule type="colorScale" priority="139">
       <colorScale>
         <cfvo type="min"/>
@@ -27216,7 +27281,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="DL2:DL67">
+  <conditionalFormatting sqref="DM2:DM67">
     <cfRule type="colorScale" priority="141">
       <colorScale>
         <cfvo type="min"/>
@@ -27228,7 +27293,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="DL2:DL67">
+  <conditionalFormatting sqref="DM2:DM67">
     <cfRule type="colorScale" priority="143">
       <colorScale>
         <cfvo type="min"/>
@@ -27240,7 +27305,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B2:DK83">
+  <conditionalFormatting sqref="B2:DL83">
     <cfRule type="colorScale" priority="15">
       <colorScale>
         <cfvo type="min"/>
@@ -29499,10 +29564,10 @@
         <v>91.5</v>
       </c>
       <c r="AF2" s="1">
-        <v>46268</v>
+        <v>46289</v>
       </c>
       <c r="AG2" t="s">
-        <v>50</v>
+        <v>44</v>
       </c>
     </row>
     <row r="3" spans="1:33" x14ac:dyDescent="0.35">
@@ -29586,7 +29651,7 @@
       <c r="AA3" s="19">
         <v>85.84</v>
       </c>
-      <c r="AB3" s="21">
+      <c r="AB3" s="19">
         <v>91.5</v>
       </c>
     </row>
@@ -30312,7 +30377,7 @@
       <c r="AA13" s="19">
         <v>85.84</v>
       </c>
-      <c r="AB13" s="21">
+      <c r="AB13" s="19">
         <v>91.5</v>
       </c>
     </row>
@@ -31199,7 +31264,7 @@
       <c r="G29" s="19"/>
       <c r="H29" s="19"/>
       <c r="I29" s="19"/>
-      <c r="U29" s="21">
+      <c r="U29" s="19">
         <v>27</v>
       </c>
       <c r="AO29" s="33"/>
@@ -31374,7 +31439,7 @@
     </row>
     <row r="34" spans="1:29" x14ac:dyDescent="0.35">
       <c r="A34" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="C34" s="19">
         <v>25</v>
@@ -32539,7 +32604,7 @@
       <c r="AA84" s="19">
         <v>85.84</v>
       </c>
-      <c r="AB84" s="21">
+      <c r="AB84" s="19">
         <v>91.5</v>
       </c>
     </row>
@@ -32567,7 +32632,7 @@
       <c r="AA85" s="19">
         <v>85.84</v>
       </c>
-      <c r="AB85" s="21">
+      <c r="AB85" s="19">
         <v>27</v>
       </c>
     </row>
@@ -32809,7 +32874,7 @@
     </row>
     <row r="98" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A98" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="G98"/>
       <c r="H98"/>
@@ -33208,8 +33273,8 @@
         <v>1783.28</v>
       </c>
       <c r="U106" s="23">
-        <f>9*27+85.84*17</f>
-        <v>1702.28</v>
+        <f>10*27+85.84*17</f>
+        <v>1729.28</v>
       </c>
       <c r="V106" s="23">
         <f>19*27+85.84*17</f>
@@ -33236,8 +33301,8 @@
         <v>1837.28</v>
       </c>
       <c r="AB106" s="23">
-        <f>14*27+91.5*12</f>
-        <v>1476</v>
+        <f>15*27+91.5*15</f>
+        <v>1777.5</v>
       </c>
     </row>
     <row r="107" spans="1:28" x14ac:dyDescent="0.35">
@@ -33319,7 +33384,7 @@
       </c>
       <c r="U107" s="24">
         <f>U106/U105</f>
-        <v>0.91679143463415169</v>
+        <v>0.93133273731944566</v>
       </c>
       <c r="V107" s="24">
         <f t="shared" si="8"/>
@@ -33347,7 +33412,7 @@
       </c>
       <c r="AB107" s="24">
         <f t="shared" si="11"/>
-        <v>0.79418886198547212</v>
+        <v>0.95641646489104115</v>
       </c>
     </row>
   </sheetData>
@@ -33359,7 +33424,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:X333"/>
+  <dimension ref="A1:X336"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="10.54296875" bestFit="1" customWidth="1"/>
@@ -34529,7 +34594,7 @@
         <v>10</v>
       </c>
       <c r="E24" s="8" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="F24" s="8" t="s">
         <v>45</v>
@@ -34653,7 +34718,7 @@
         <v>10</v>
       </c>
       <c r="M26" s="8" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="N26" s="8" t="s">
         <v>45</v>
@@ -34985,7 +35050,7 @@
         <v>12</v>
       </c>
       <c r="G33" s="8" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="H33" s="8" t="s">
         <v>53</v>
@@ -35109,7 +35174,7 @@
         <v>12</v>
       </c>
       <c r="O35" s="8" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="P35" s="8" t="s">
         <v>53</v>
@@ -39023,7 +39088,7 @@
         <v>15</v>
       </c>
       <c r="G114" s="8" t="s">
-        <v>99</v>
+        <v>175</v>
       </c>
       <c r="H114" s="8" t="s">
         <v>49</v>
@@ -39050,7 +39115,7 @@
         <v>13</v>
       </c>
       <c r="P114" s="10" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
     </row>
     <row r="115" spans="1:16" x14ac:dyDescent="0.35">
@@ -39076,7 +39141,7 @@
         <v>13</v>
       </c>
       <c r="H115" s="10" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="I115" s="11">
         <v>5</v>
@@ -39147,7 +39212,7 @@
         <v>15</v>
       </c>
       <c r="O116" s="8" t="s">
-        <v>99</v>
+        <v>175</v>
       </c>
       <c r="P116" s="8" t="s">
         <v>49</v>
@@ -41871,7 +41936,7 @@
         <v>100</v>
       </c>
       <c r="H171" s="8" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="I171" s="9">
         <v>4</v>
@@ -41995,7 +42060,7 @@
         <v>100</v>
       </c>
       <c r="P173" s="8" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
     </row>
     <row r="174" spans="1:16" x14ac:dyDescent="0.35">
@@ -42015,7 +42080,7 @@
         <v>45</v>
       </c>
       <c r="F174" s="8" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="G174" s="8" t="s">
         <v>54</v>
@@ -42139,7 +42204,7 @@
         <v>45</v>
       </c>
       <c r="N176" s="8" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="O176" s="8" t="s">
         <v>54</v>
@@ -42233,7 +42298,7 @@
         <v>81</v>
       </c>
       <c r="N178" s="2" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="O178" s="2" t="s">
         <v>83</v>
@@ -42257,7 +42322,7 @@
         <v>81</v>
       </c>
       <c r="F179" s="2" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="G179" s="2" t="s">
         <v>83</v>
@@ -42762,7 +42827,7 @@
         <v>13</v>
       </c>
       <c r="M189" s="10" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="N189" s="10" t="s">
         <v>118</v>
@@ -42788,7 +42853,7 @@
         <v>13</v>
       </c>
       <c r="E190" s="10" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="F190" s="10" t="s">
         <v>118</v>
@@ -42971,7 +43036,7 @@
         <v>54</v>
       </c>
       <c r="P193" s="3" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
     </row>
     <row r="194" spans="1:16" x14ac:dyDescent="0.35">
@@ -42997,7 +43062,7 @@
         <v>54</v>
       </c>
       <c r="H194" s="3" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="I194" s="5">
         <v>6</v>
@@ -45826,7 +45891,7 @@
         <v>45</v>
       </c>
       <c r="P251" s="2" t="s">
-        <v>99</v>
+        <v>175</v>
       </c>
     </row>
     <row r="252" spans="1:16" x14ac:dyDescent="0.35">
@@ -45852,7 +45917,7 @@
         <v>45</v>
       </c>
       <c r="H252" s="2" t="s">
-        <v>99</v>
+        <v>175</v>
       </c>
       <c r="I252" s="5">
         <v>3</v>
@@ -45902,7 +45967,7 @@
         <v>83</v>
       </c>
       <c r="H253" s="8" t="s">
-        <v>99</v>
+        <v>175</v>
       </c>
       <c r="I253" s="9">
         <v>2</v>
@@ -46026,7 +46091,7 @@
         <v>83</v>
       </c>
       <c r="P255" s="8" t="s">
-        <v>99</v>
+        <v>175</v>
       </c>
     </row>
     <row r="256" spans="1:16" x14ac:dyDescent="0.35">
@@ -46049,10 +46114,10 @@
         <v>18</v>
       </c>
       <c r="G256" s="8" t="s">
-        <v>99</v>
+        <v>175</v>
       </c>
       <c r="H256" s="8" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="I256" s="9">
         <v>6</v>
@@ -46173,10 +46238,10 @@
         <v>18</v>
       </c>
       <c r="O258" s="8" t="s">
-        <v>99</v>
+        <v>175</v>
       </c>
       <c r="P258" s="8" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
     </row>
     <row r="259" spans="1:16" x14ac:dyDescent="0.35">
@@ -46217,7 +46282,7 @@
         <v>21</v>
       </c>
       <c r="M259" s="10" t="s">
-        <v>99</v>
+        <v>175</v>
       </c>
       <c r="N259" s="10" t="s">
         <v>43</v>
@@ -46243,7 +46308,7 @@
         <v>21</v>
       </c>
       <c r="E260" s="10" t="s">
-        <v>99</v>
+        <v>175</v>
       </c>
       <c r="F260" s="10" t="s">
         <v>43</v>
@@ -46273,7 +46338,7 @@
         <v>81</v>
       </c>
       <c r="O260" s="31" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="P260" s="2" t="s">
         <v>2</v>
@@ -46299,7 +46364,7 @@
         <v>81</v>
       </c>
       <c r="G261" s="31" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="H261" s="2" t="s">
         <v>2</v>
@@ -46352,7 +46417,7 @@
         <v>47</v>
       </c>
       <c r="H262" s="8" t="s">
-        <v>99</v>
+        <v>175</v>
       </c>
       <c r="I262" s="9">
         <v>1</v>
@@ -46364,7 +46429,7 @@
         <v>18</v>
       </c>
       <c r="L262" s="10" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="M262" s="10" t="s">
         <v>14</v>
@@ -46388,7 +46453,7 @@
         <v>18</v>
       </c>
       <c r="D263" s="10" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="E263" s="10" t="s">
         <v>14</v>
@@ -46468,7 +46533,7 @@
         <v>47</v>
       </c>
       <c r="P264" s="8" t="s">
-        <v>99</v>
+        <v>175</v>
       </c>
     </row>
     <row r="265" spans="1:16" x14ac:dyDescent="0.35">
@@ -46665,7 +46730,7 @@
         <v>15</v>
       </c>
       <c r="O268" s="10" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="P268" s="10" t="s">
         <v>127</v>
@@ -46691,7 +46756,7 @@
         <v>15</v>
       </c>
       <c r="G269" s="10" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="H269" s="10" t="s">
         <v>127</v>
@@ -46718,7 +46783,7 @@
         <v>97</v>
       </c>
       <c r="P269" s="2" t="s">
-        <v>99</v>
+        <v>175</v>
       </c>
     </row>
     <row r="270" spans="1:16" x14ac:dyDescent="0.35">
@@ -46744,7 +46809,7 @@
         <v>97</v>
       </c>
       <c r="H270" s="2" t="s">
-        <v>99</v>
+        <v>175</v>
       </c>
       <c r="I270" s="5">
         <v>6</v>
@@ -46929,7 +46994,7 @@
         <v>80</v>
       </c>
       <c r="G274" s="8" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="H274" s="8" t="s">
         <v>145</v>
@@ -47053,7 +47118,7 @@
         <v>80</v>
       </c>
       <c r="O276" s="8" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="P276" s="8" t="s">
         <v>145</v>
@@ -47082,7 +47147,7 @@
         <v>11</v>
       </c>
       <c r="H277" s="8" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="I277" s="9">
         <v>3</v>
@@ -47206,7 +47271,7 @@
         <v>11</v>
       </c>
       <c r="P279" s="8" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
     </row>
     <row r="280" spans="1:16" x14ac:dyDescent="0.35">
@@ -47591,7 +47656,7 @@
         <v>12</v>
       </c>
       <c r="O287" s="31" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="P287" s="2" t="s">
         <v>146</v>
@@ -47617,7 +47682,7 @@
         <v>12</v>
       </c>
       <c r="G288" s="31" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="H288" s="2" t="s">
         <v>146</v>
@@ -47866,7 +47931,7 @@
         <v>19</v>
       </c>
       <c r="N293" s="31" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="O293" s="31" t="s">
         <v>151</v>
@@ -47890,7 +47955,7 @@
         <v>19</v>
       </c>
       <c r="F294" s="31" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="G294" s="31" t="s">
         <v>151</v>
@@ -47963,7 +48028,7 @@
         <v>83</v>
       </c>
       <c r="O295" s="10" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="P295" s="10" t="s">
         <v>127</v>
@@ -48010,7 +48075,7 @@
         <v>81</v>
       </c>
       <c r="N296" s="10" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="O296" s="10" t="s">
         <v>53</v>
@@ -48036,7 +48101,7 @@
         <v>81</v>
       </c>
       <c r="F297" s="10" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="G297" s="10" t="s">
         <v>53</v>
@@ -48454,7 +48519,7 @@
         <v>153</v>
       </c>
       <c r="P305" s="10" t="s">
-        <v>152</v>
+        <v>174</v>
       </c>
     </row>
     <row r="306" spans="1:16" x14ac:dyDescent="0.35">
@@ -48480,7 +48545,7 @@
         <v>153</v>
       </c>
       <c r="H306" s="10" t="s">
-        <v>152</v>
+        <v>174</v>
       </c>
       <c r="I306" s="11">
         <v>4</v>
@@ -48577,7 +48642,7 @@
         <v>15</v>
       </c>
       <c r="G308" s="8" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="H308" s="8" t="s">
         <v>148</v>
@@ -48701,7 +48766,7 @@
         <v>15</v>
       </c>
       <c r="O310" s="8" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="P310" s="8" t="s">
         <v>148</v>
@@ -49080,7 +49145,7 @@
         <v>149</v>
       </c>
       <c r="P318" s="2" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
     </row>
     <row r="319" spans="1:16" x14ac:dyDescent="0.35">
@@ -49106,7 +49171,7 @@
         <v>149</v>
       </c>
       <c r="H319" s="2" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="I319" s="5">
         <v>5</v>
@@ -49177,7 +49242,7 @@
         <v>161</v>
       </c>
       <c r="O320" s="10" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="P320" s="10" t="s">
         <v>162</v>
@@ -49203,7 +49268,7 @@
         <v>161</v>
       </c>
       <c r="G321" s="10" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="H321" s="10" t="s">
         <v>162</v>
@@ -49250,10 +49315,10 @@
         <v>151</v>
       </c>
       <c r="F322" s="8" t="s">
+        <v>174</v>
+      </c>
+      <c r="G322" s="8" t="s">
         <v>167</v>
-      </c>
-      <c r="G322" s="8" t="s">
-        <v>168</v>
       </c>
       <c r="H322" s="8"/>
       <c r="I322" s="9">
@@ -49325,7 +49390,7 @@
         <v>55</v>
       </c>
       <c r="O323" s="31" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="P323" s="2"/>
     </row>
@@ -49349,7 +49414,7 @@
         <v>55</v>
       </c>
       <c r="G324" s="31" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="H324" s="2"/>
       <c r="I324" s="5">
@@ -49362,7 +49427,7 @@
         <v>43</v>
       </c>
       <c r="L324" s="8" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="M324" s="8" t="s">
         <v>80</v>
@@ -49371,10 +49436,10 @@
         <v>151</v>
       </c>
       <c r="O324" s="8" t="s">
+        <v>174</v>
+      </c>
+      <c r="P324" s="8" t="s">
         <v>167</v>
-      </c>
-      <c r="P324" s="8" t="s">
-        <v>168</v>
       </c>
     </row>
     <row r="325" spans="1:16" x14ac:dyDescent="0.35">
@@ -49397,7 +49462,7 @@
         <v>149</v>
       </c>
       <c r="G325" s="8" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="H325" s="8"/>
       <c r="I325" s="9">
@@ -49422,7 +49487,7 @@
         <v>148</v>
       </c>
       <c r="P325" s="10" t="s">
-        <v>152</v>
+        <v>174</v>
       </c>
     </row>
     <row r="326" spans="1:16" x14ac:dyDescent="0.35">
@@ -49448,7 +49513,7 @@
         <v>148</v>
       </c>
       <c r="H326" s="10" t="s">
-        <v>152</v>
+        <v>174</v>
       </c>
       <c r="I326" s="11">
         <v>4</v>
@@ -49466,7 +49531,7 @@
         <v>83</v>
       </c>
       <c r="N326" s="31" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="O326" s="31" t="s">
         <v>84</v>
@@ -49492,7 +49557,7 @@
         <v>83</v>
       </c>
       <c r="F327" s="31" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="G327" s="31" t="s">
         <v>84</v>
@@ -49519,7 +49584,7 @@
         <v>149</v>
       </c>
       <c r="O327" s="8" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="P327" s="8"/>
     </row>
@@ -49565,7 +49630,7 @@
         <v>97</v>
       </c>
       <c r="O328" s="10" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="P328" s="10"/>
     </row>
@@ -49589,7 +49654,7 @@
         <v>97</v>
       </c>
       <c r="G329" s="10" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="H329" s="10"/>
       <c r="I329" s="11">
@@ -49672,7 +49737,7 @@
         <v>81</v>
       </c>
       <c r="D331" s="8" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="E331" s="8" t="s">
         <v>97</v>
@@ -49684,7 +49749,7 @@
         <v>5</v>
       </c>
       <c r="H331" s="8" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="I331" s="9">
         <v>2</v>
@@ -49758,7 +49823,7 @@
         <v>160</v>
       </c>
       <c r="P332" s="2" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
     </row>
     <row r="333" spans="1:16" x14ac:dyDescent="0.35">
@@ -49784,7 +49849,7 @@
         <v>160</v>
       </c>
       <c r="H333" s="2" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="I333" s="5">
         <v>1</v>
@@ -49796,7 +49861,7 @@
         <v>81</v>
       </c>
       <c r="L333" s="8" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="M333" s="8" t="s">
         <v>97</v>
@@ -49808,6 +49873,152 @@
         <v>5</v>
       </c>
       <c r="P333" s="8" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="334" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="A334" s="1">
+        <v>46289</v>
+      </c>
+      <c r="B334" s="32">
+        <v>4</v>
+      </c>
+      <c r="C334" s="8" t="s">
+        <v>81</v>
+      </c>
+      <c r="D334" s="8" t="s">
+        <v>43</v>
+      </c>
+      <c r="E334" s="8" t="s">
+        <v>5</v>
+      </c>
+      <c r="F334" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="G334" s="8" t="s">
+        <v>174</v>
+      </c>
+      <c r="H334" s="8" t="s">
+        <v>173</v>
+      </c>
+      <c r="I334" s="9">
+        <v>7</v>
+      </c>
+      <c r="J334" s="10">
+        <v>3</v>
+      </c>
+      <c r="K334" s="10" t="s">
+        <v>1</v>
+      </c>
+      <c r="L334" s="10" t="s">
+        <v>44</v>
+      </c>
+      <c r="M334" s="10" t="s">
+        <v>55</v>
+      </c>
+      <c r="N334" s="10" t="s">
+        <v>151</v>
+      </c>
+      <c r="O334" s="10" t="s">
+        <v>169</v>
+      </c>
+      <c r="P334" s="10"/>
+    </row>
+    <row r="335" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="A335" s="1">
+        <v>46289</v>
+      </c>
+      <c r="B335" s="32">
+        <v>2</v>
+      </c>
+      <c r="C335" s="10" t="s">
+        <v>1</v>
+      </c>
+      <c r="D335" s="10" t="s">
+        <v>44</v>
+      </c>
+      <c r="E335" s="10" t="s">
+        <v>55</v>
+      </c>
+      <c r="F335" s="10" t="s">
+        <v>151</v>
+      </c>
+      <c r="G335" s="10" t="s">
+        <v>169</v>
+      </c>
+      <c r="H335" s="10"/>
+      <c r="I335" s="11">
+        <v>2</v>
+      </c>
+      <c r="J335" s="2">
+        <v>0</v>
+      </c>
+      <c r="K335" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="L335" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="M335" s="31" t="s">
+        <v>83</v>
+      </c>
+      <c r="N335" s="31" t="s">
+        <v>108</v>
+      </c>
+      <c r="O335" s="31" t="s">
+        <v>84</v>
+      </c>
+      <c r="P335" s="2" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="336" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="A336" s="1">
+        <v>46289</v>
+      </c>
+      <c r="B336" s="32">
+        <v>3</v>
+      </c>
+      <c r="C336" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D336" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E336" s="31" t="s">
+        <v>83</v>
+      </c>
+      <c r="F336" s="31" t="s">
+        <v>108</v>
+      </c>
+      <c r="G336" s="31" t="s">
+        <v>84</v>
+      </c>
+      <c r="H336" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="I336" s="5">
+        <v>3</v>
+      </c>
+      <c r="J336" s="8">
+        <v>3</v>
+      </c>
+      <c r="K336" s="8" t="s">
+        <v>81</v>
+      </c>
+      <c r="L336" s="8" t="s">
+        <v>43</v>
+      </c>
+      <c r="M336" s="8" t="s">
+        <v>5</v>
+      </c>
+      <c r="N336" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="O336" s="8" t="s">
+        <v>174</v>
+      </c>
+      <c r="P336" s="8" t="s">
         <v>173</v>
       </c>
     </row>
@@ -49818,7 +50029,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{77DDCCA6-42DC-4211-A42F-70F3625FA6AA}">
-  <dimension ref="A1:CR104"/>
+  <dimension ref="A1:CS105"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="16.81640625" bestFit="1" customWidth="1"/>
@@ -49830,10 +50041,10 @@
     <col min="13" max="13" width="9.54296875" bestFit="1" customWidth="1"/>
     <col min="14" max="92" width="10.453125" bestFit="1" customWidth="1"/>
     <col min="93" max="93" width="10.453125" customWidth="1"/>
-    <col min="94" max="96" width="10.453125" bestFit="1" customWidth="1"/>
+    <col min="94" max="97" width="10.453125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:96" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:97" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -50122,8 +50333,11 @@
       <c r="CR1" s="1">
         <v>46281</v>
       </c>
-    </row>
-    <row r="2" spans="1:96" x14ac:dyDescent="0.35">
+      <c r="CS1" s="1">
+        <v>46288</v>
+      </c>
+    </row>
+    <row r="2" spans="1:97" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>2</v>
       </c>
@@ -50200,7 +50414,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:96" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:97" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>23</v>
       </c>
@@ -50208,7 +50422,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="4" spans="1:96" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:97" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>100</v>
       </c>
@@ -50246,7 +50460,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="5" spans="1:96" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:97" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>149</v>
       </c>
@@ -50272,12 +50486,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:96" hidden="1" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:97" hidden="1" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>116</v>
       </c>
     </row>
-    <row r="7" spans="1:96" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:97" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>76</v>
       </c>
@@ -50285,7 +50499,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="8" spans="1:96" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:97" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>115</v>
       </c>
@@ -50302,7 +50516,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="9" spans="1:96" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:97" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>151</v>
       </c>
@@ -50348,8 +50562,11 @@
       <c r="CP9">
         <v>3</v>
       </c>
-    </row>
-    <row r="10" spans="1:96" x14ac:dyDescent="0.35">
+      <c r="CS9">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="10" spans="1:97" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
         <v>7</v>
       </c>
@@ -50357,7 +50574,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="11" spans="1:96" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:97" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
         <v>107</v>
       </c>
@@ -50365,17 +50582,17 @@
         <v>1</v>
       </c>
     </row>
-    <row r="12" spans="1:96" hidden="1" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:97" hidden="1" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
         <v>101</v>
       </c>
     </row>
-    <row r="13" spans="1:96" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:97" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
         <v>47</v>
       </c>
     </row>
-    <row r="14" spans="1:96" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:97" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
         <v>145</v>
       </c>
@@ -50383,7 +50600,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="15" spans="1:96" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:97" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
         <v>148</v>
       </c>
@@ -50406,12 +50623,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="16" spans="1:96" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:97" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
         <v>133</v>
       </c>
     </row>
-    <row r="17" spans="1:96" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:97" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
         <v>113</v>
       </c>
@@ -50419,12 +50636,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="18" spans="1:96" hidden="1" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:97" hidden="1" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="19" spans="1:96" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:97" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
         <v>24</v>
       </c>
@@ -50474,7 +50691,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="20" spans="1:96" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:97" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
         <v>13</v>
       </c>
@@ -50515,7 +50732,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="21" spans="1:96" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:97" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
         <v>129</v>
       </c>
@@ -50529,7 +50746,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="22" spans="1:96" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:97" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
         <v>53</v>
       </c>
@@ -50549,7 +50766,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="23" spans="1:96" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:97" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
         <v>65</v>
       </c>
@@ -50614,7 +50831,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="24" spans="1:96" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:97" x14ac:dyDescent="0.35">
       <c r="A24" t="s">
         <v>83</v>
       </c>
@@ -50739,7 +50956,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="25" spans="1:96" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:97" x14ac:dyDescent="0.35">
       <c r="A25" t="s">
         <v>142</v>
       </c>
@@ -50747,7 +50964,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="26" spans="1:96" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:97" x14ac:dyDescent="0.35">
       <c r="A26" t="s">
         <v>14</v>
       </c>
@@ -50824,12 +51041,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="27" spans="1:96" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:97" x14ac:dyDescent="0.35">
       <c r="A27" t="s">
         <v>161</v>
       </c>
     </row>
-    <row r="28" spans="1:96" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:97" x14ac:dyDescent="0.35">
       <c r="A28" t="s">
         <v>126</v>
       </c>
@@ -50837,7 +51054,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="29" spans="1:96" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:97" x14ac:dyDescent="0.35">
       <c r="A29" t="s">
         <v>6</v>
       </c>
@@ -50992,15 +51209,15 @@
         <v>2</v>
       </c>
     </row>
-    <row r="30" spans="1:96" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:97" x14ac:dyDescent="0.35">
       <c r="A30" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="CR30">
         <v>1</v>
       </c>
     </row>
-    <row r="31" spans="1:96" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:97" x14ac:dyDescent="0.35">
       <c r="A31" t="s">
         <v>97</v>
       </c>
@@ -51022,8 +51239,11 @@
       <c r="CR31">
         <v>1</v>
       </c>
-    </row>
-    <row r="32" spans="1:96" x14ac:dyDescent="0.35">
+      <c r="CS31">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="32" spans="1:97" x14ac:dyDescent="0.35">
       <c r="A32" t="s">
         <v>51</v>
       </c>
@@ -51031,12 +51251,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="33" spans="1:95" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:97" x14ac:dyDescent="0.35">
       <c r="A33" t="s">
         <v>154</v>
       </c>
     </row>
-    <row r="34" spans="1:95" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:97" x14ac:dyDescent="0.35">
       <c r="A34" t="s">
         <v>140</v>
       </c>
@@ -51044,12 +51264,12 @@
         <v>3</v>
       </c>
     </row>
-    <row r="35" spans="1:95" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:97" x14ac:dyDescent="0.35">
       <c r="A35" t="s">
         <v>139</v>
       </c>
     </row>
-    <row r="36" spans="1:95" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:97" x14ac:dyDescent="0.35">
       <c r="A36" t="s">
         <v>147</v>
       </c>
@@ -51057,7 +51277,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="37" spans="1:95" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:97" x14ac:dyDescent="0.35">
       <c r="A37" t="s">
         <v>12</v>
       </c>
@@ -51077,7 +51297,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="38" spans="1:95" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:97" x14ac:dyDescent="0.35">
       <c r="A38" t="s">
         <v>4</v>
       </c>
@@ -51181,7 +51401,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="39" spans="1:95" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:97" x14ac:dyDescent="0.35">
       <c r="A39" t="s">
         <v>112</v>
       </c>
@@ -51198,7 +51418,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="40" spans="1:95" hidden="1" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:97" hidden="1" x14ac:dyDescent="0.35">
       <c r="A40" t="s">
         <v>105</v>
       </c>
@@ -51206,7 +51426,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="41" spans="1:95" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:97" x14ac:dyDescent="0.35">
       <c r="A41" t="s">
         <v>1</v>
       </c>
@@ -51364,7 +51584,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="42" spans="1:95" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:97" x14ac:dyDescent="0.35">
       <c r="A42" t="s">
         <v>9</v>
       </c>
@@ -51530,8 +51750,11 @@
       <c r="CP42">
         <v>1</v>
       </c>
-    </row>
-    <row r="43" spans="1:95" x14ac:dyDescent="0.35">
+      <c r="CS42">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="43" spans="1:97" x14ac:dyDescent="0.35">
       <c r="A43" t="s">
         <v>143</v>
       </c>
@@ -51551,7 +51774,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="44" spans="1:95" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:97" x14ac:dyDescent="0.35">
       <c r="A44" t="s">
         <v>132</v>
       </c>
@@ -51559,7 +51782,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="45" spans="1:95" x14ac:dyDescent="0.35">
+    <row r="45" spans="1:97" x14ac:dyDescent="0.35">
       <c r="A45" t="s">
         <v>19</v>
       </c>
@@ -51681,276 +51904,267 @@
         <v>1</v>
       </c>
     </row>
-    <row r="46" spans="1:95" x14ac:dyDescent="0.35">
+    <row r="46" spans="1:97" x14ac:dyDescent="0.35">
       <c r="A46" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="47" spans="1:97" x14ac:dyDescent="0.35">
+      <c r="A47" t="s">
         <v>144</v>
       </c>
     </row>
-    <row r="47" spans="1:95" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A47" t="s">
+    <row r="48" spans="1:97" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A48" t="s">
         <v>60</v>
       </c>
-      <c r="D47">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="48" spans="1:95" x14ac:dyDescent="0.35">
-      <c r="A48" t="s">
+      <c r="D48">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="49" spans="1:97" x14ac:dyDescent="0.35">
+      <c r="A49" t="s">
         <v>79</v>
       </c>
-      <c r="F48">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="49" spans="1:95" x14ac:dyDescent="0.35">
-      <c r="A49" t="s">
+      <c r="F49">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="50" spans="1:97" x14ac:dyDescent="0.35">
+      <c r="A50" t="s">
         <v>160</v>
       </c>
     </row>
-    <row r="50" spans="1:95" x14ac:dyDescent="0.35">
-      <c r="A50" t="s">
+    <row r="51" spans="1:97" x14ac:dyDescent="0.35">
+      <c r="A51" t="s">
         <v>125</v>
       </c>
-      <c r="AW50">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="51" spans="1:95" x14ac:dyDescent="0.35">
-      <c r="A51" t="s">
+      <c r="AW51">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="52" spans="1:97" x14ac:dyDescent="0.35">
+      <c r="A52" t="s">
         <v>18</v>
       </c>
-      <c r="B51">
-        <v>2</v>
-      </c>
-      <c r="C51">
-        <v>1</v>
-      </c>
-      <c r="D51">
-        <v>1</v>
-      </c>
-      <c r="F51">
+      <c r="B52">
+        <v>2</v>
+      </c>
+      <c r="C52">
+        <v>1</v>
+      </c>
+      <c r="D52">
+        <v>1</v>
+      </c>
+      <c r="F52">
         <v>4</v>
       </c>
-      <c r="G51">
+      <c r="G52">
         <v>3</v>
       </c>
-      <c r="H51">
-        <v>1</v>
-      </c>
-      <c r="I51">
-        <v>1</v>
-      </c>
-      <c r="M51">
-        <v>2</v>
-      </c>
-      <c r="N51">
+      <c r="H52">
+        <v>1</v>
+      </c>
+      <c r="I52">
+        <v>1</v>
+      </c>
+      <c r="M52">
+        <v>2</v>
+      </c>
+      <c r="N52">
         <v>3</v>
       </c>
-      <c r="T51">
-        <v>1</v>
-      </c>
-      <c r="X51">
-        <v>1</v>
-      </c>
-      <c r="AA51">
-        <v>2</v>
-      </c>
-      <c r="AB51">
-        <v>2</v>
-      </c>
-      <c r="AC51">
-        <v>1</v>
-      </c>
-      <c r="AD51">
-        <v>2</v>
-      </c>
-      <c r="AE51">
-        <v>1</v>
-      </c>
-      <c r="AG51">
-        <v>1</v>
-      </c>
-      <c r="AH51">
-        <v>2</v>
-      </c>
-      <c r="AJ51">
-        <v>1</v>
-      </c>
-      <c r="AM51">
+      <c r="T52">
+        <v>1</v>
+      </c>
+      <c r="X52">
+        <v>1</v>
+      </c>
+      <c r="AA52">
+        <v>2</v>
+      </c>
+      <c r="AB52">
+        <v>2</v>
+      </c>
+      <c r="AC52">
+        <v>1</v>
+      </c>
+      <c r="AD52">
+        <v>2</v>
+      </c>
+      <c r="AE52">
+        <v>1</v>
+      </c>
+      <c r="AG52">
+        <v>1</v>
+      </c>
+      <c r="AH52">
+        <v>2</v>
+      </c>
+      <c r="AJ52">
+        <v>1</v>
+      </c>
+      <c r="AM52">
         <v>4</v>
       </c>
-      <c r="AN51">
-        <v>1</v>
-      </c>
-      <c r="AP51">
-        <v>1</v>
-      </c>
-      <c r="AR51">
-        <v>1</v>
-      </c>
-      <c r="AS51">
-        <v>1</v>
-      </c>
-      <c r="AT51">
-        <v>1</v>
-      </c>
-      <c r="AV51">
-        <v>1</v>
-      </c>
-      <c r="AZ51">
-        <v>2</v>
-      </c>
-      <c r="BA51">
-        <v>1</v>
-      </c>
-      <c r="BC51">
+      <c r="AN52">
+        <v>1</v>
+      </c>
+      <c r="AP52">
+        <v>1</v>
+      </c>
+      <c r="AR52">
+        <v>1</v>
+      </c>
+      <c r="AS52">
+        <v>1</v>
+      </c>
+      <c r="AT52">
+        <v>1</v>
+      </c>
+      <c r="AV52">
+        <v>1</v>
+      </c>
+      <c r="AZ52">
+        <v>2</v>
+      </c>
+      <c r="BA52">
+        <v>1</v>
+      </c>
+      <c r="BC52">
         <v>3</v>
       </c>
-      <c r="BD51">
-        <v>1</v>
-      </c>
-      <c r="BI51">
-        <v>1</v>
-      </c>
-      <c r="BJ51">
-        <v>1</v>
-      </c>
-      <c r="BK51">
+      <c r="BD52">
+        <v>1</v>
+      </c>
+      <c r="BI52">
+        <v>1</v>
+      </c>
+      <c r="BJ52">
+        <v>1</v>
+      </c>
+      <c r="BK52">
         <v>3</v>
       </c>
-      <c r="BL51">
-        <v>2</v>
-      </c>
-      <c r="BM51">
-        <v>5</v>
-      </c>
-      <c r="BO51">
-        <v>1</v>
-      </c>
-      <c r="BP51">
+      <c r="BL52">
+        <v>2</v>
+      </c>
+      <c r="BM52">
+        <v>5</v>
+      </c>
+      <c r="BO52">
+        <v>1</v>
+      </c>
+      <c r="BP52">
         <v>3</v>
       </c>
-      <c r="BQ51">
+      <c r="BQ52">
         <v>3</v>
       </c>
-      <c r="BS51">
-        <v>1</v>
-      </c>
-      <c r="BX51">
+      <c r="BS52">
+        <v>1</v>
+      </c>
+      <c r="BX52">
         <v>3</v>
       </c>
-      <c r="BY51">
-        <v>5</v>
-      </c>
-      <c r="BZ51">
-        <v>1</v>
-      </c>
-      <c r="CB51">
+      <c r="BY52">
+        <v>5</v>
+      </c>
+      <c r="BZ52">
+        <v>1</v>
+      </c>
+      <c r="CB52">
         <v>3</v>
       </c>
-      <c r="CC51">
-        <v>2</v>
-      </c>
-      <c r="CD51">
+      <c r="CC52">
+        <v>2</v>
+      </c>
+      <c r="CD52">
         <v>4</v>
       </c>
-      <c r="CF51">
-        <v>1</v>
-      </c>
-      <c r="CI51">
-        <v>2</v>
-      </c>
-      <c r="CJ51">
-        <v>2</v>
-      </c>
-      <c r="CK51">
-        <v>2</v>
-      </c>
-      <c r="CL51">
-        <v>1</v>
-      </c>
-      <c r="CM51">
+      <c r="CF52">
+        <v>1</v>
+      </c>
+      <c r="CI52">
+        <v>2</v>
+      </c>
+      <c r="CJ52">
+        <v>2</v>
+      </c>
+      <c r="CK52">
+        <v>2</v>
+      </c>
+      <c r="CL52">
+        <v>1</v>
+      </c>
+      <c r="CM52">
         <v>3</v>
       </c>
-      <c r="CQ51">
+      <c r="CQ52">
         <v>3</v>
       </c>
-    </row>
-    <row r="52" spans="1:95" x14ac:dyDescent="0.35">
-      <c r="A52" t="s">
+      <c r="CS52">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="53" spans="1:97" x14ac:dyDescent="0.35">
+      <c r="A53" t="s">
         <v>42</v>
       </c>
-      <c r="AQ52">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="53" spans="1:95" x14ac:dyDescent="0.35">
-      <c r="A53" t="s">
+      <c r="AQ53">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="54" spans="1:97" x14ac:dyDescent="0.35">
+      <c r="A54" t="s">
         <v>67</v>
       </c>
-      <c r="E53">
-        <v>1</v>
-      </c>
-      <c r="I53">
-        <v>1</v>
-      </c>
-      <c r="N53">
-        <v>1</v>
-      </c>
-      <c r="W53">
-        <v>2</v>
-      </c>
-      <c r="AQ53">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="54" spans="1:95" x14ac:dyDescent="0.35">
-      <c r="A54" t="s">
+      <c r="E54">
+        <v>1</v>
+      </c>
+      <c r="I54">
+        <v>1</v>
+      </c>
+      <c r="N54">
+        <v>1</v>
+      </c>
+      <c r="W54">
+        <v>2</v>
+      </c>
+      <c r="AQ54">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="55" spans="1:97" x14ac:dyDescent="0.35">
+      <c r="A55" t="s">
         <v>52</v>
       </c>
-      <c r="N54">
-        <v>1</v>
-      </c>
-      <c r="BZ54">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="55" spans="1:95" x14ac:dyDescent="0.35">
-      <c r="A55" t="s">
+      <c r="N55">
+        <v>1</v>
+      </c>
+      <c r="BZ55">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="56" spans="1:97" x14ac:dyDescent="0.35">
+      <c r="A56" t="s">
         <v>119</v>
       </c>
-      <c r="AM55">
-        <v>5</v>
-      </c>
-      <c r="BB55">
+      <c r="AM56">
+        <v>5</v>
+      </c>
+      <c r="BB56">
         <v>9</v>
       </c>
-      <c r="BN55">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="56" spans="1:95" x14ac:dyDescent="0.35">
-      <c r="A56" t="s">
-        <v>99</v>
-      </c>
-      <c r="U56">
-        <v>1</v>
-      </c>
-      <c r="BR56">
-        <v>1</v>
-      </c>
-      <c r="BS56">
-        <v>1</v>
-      </c>
-      <c r="BT56">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="57" spans="1:95" x14ac:dyDescent="0.35">
+      <c r="BN56">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="57" spans="1:97" x14ac:dyDescent="0.35">
       <c r="A57" t="s">
-        <v>170</v>
-      </c>
-      <c r="AN57">
+        <v>175</v>
+      </c>
+      <c r="U57">
         <v>1</v>
       </c>
       <c r="BR57">
@@ -51960,1763 +52174,1786 @@
         <v>1</v>
       </c>
       <c r="BT57">
-        <v>3</v>
-      </c>
-      <c r="CD57">
-        <v>1</v>
-      </c>
-      <c r="CJ57">
-        <v>1</v>
-      </c>
-      <c r="CN57">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="58" spans="1:95" x14ac:dyDescent="0.35">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="58" spans="1:97" x14ac:dyDescent="0.35">
       <c r="A58" t="s">
         <v>169</v>
       </c>
-    </row>
-    <row r="59" spans="1:95" x14ac:dyDescent="0.35">
+      <c r="AN58">
+        <v>1</v>
+      </c>
+      <c r="BR58">
+        <v>1</v>
+      </c>
+      <c r="BS58">
+        <v>1</v>
+      </c>
+      <c r="BT58">
+        <v>3</v>
+      </c>
+      <c r="CD58">
+        <v>1</v>
+      </c>
+      <c r="CJ58">
+        <v>1</v>
+      </c>
+      <c r="CN58">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="59" spans="1:97" x14ac:dyDescent="0.35">
       <c r="A59" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="60" spans="1:97" x14ac:dyDescent="0.35">
+      <c r="A60" t="s">
         <v>98</v>
       </c>
-      <c r="X59">
-        <v>1</v>
-      </c>
-      <c r="Y59">
-        <v>2</v>
-      </c>
-      <c r="AF59">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="60" spans="1:95" x14ac:dyDescent="0.35">
-      <c r="A60" t="s">
+      <c r="X60">
+        <v>1</v>
+      </c>
+      <c r="Y60">
+        <v>2</v>
+      </c>
+      <c r="AF60">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="61" spans="1:97" x14ac:dyDescent="0.35">
+      <c r="A61" t="s">
         <v>146</v>
       </c>
-      <c r="CB60">
-        <v>5</v>
-      </c>
-      <c r="CH60">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="61" spans="1:95" x14ac:dyDescent="0.35">
-      <c r="A61" t="s">
+      <c r="CB61">
+        <v>5</v>
+      </c>
+      <c r="CH61">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="62" spans="1:97" x14ac:dyDescent="0.35">
+      <c r="A62" t="s">
         <v>10</v>
       </c>
-      <c r="B61">
-        <v>2</v>
-      </c>
-      <c r="C61">
+      <c r="B62">
+        <v>2</v>
+      </c>
+      <c r="C62">
         <v>3</v>
       </c>
-      <c r="F61">
-        <v>2</v>
-      </c>
-      <c r="I61">
-        <v>2</v>
-      </c>
-      <c r="J61">
-        <v>2</v>
-      </c>
-      <c r="K61">
-        <v>1</v>
-      </c>
-      <c r="L61">
-        <v>1</v>
-      </c>
-      <c r="M61">
-        <v>1</v>
-      </c>
-      <c r="O61">
-        <v>2</v>
-      </c>
-      <c r="R61">
+      <c r="F62">
+        <v>2</v>
+      </c>
+      <c r="I62">
+        <v>2</v>
+      </c>
+      <c r="J62">
+        <v>2</v>
+      </c>
+      <c r="K62">
+        <v>1</v>
+      </c>
+      <c r="L62">
+        <v>1</v>
+      </c>
+      <c r="M62">
+        <v>1</v>
+      </c>
+      <c r="O62">
+        <v>2</v>
+      </c>
+      <c r="R62">
         <v>3</v>
       </c>
-      <c r="S61">
-        <v>1</v>
-      </c>
-      <c r="T61">
-        <v>1</v>
-      </c>
-      <c r="V61">
-        <v>1</v>
-      </c>
-      <c r="W61">
+      <c r="S62">
+        <v>1</v>
+      </c>
+      <c r="T62">
+        <v>1</v>
+      </c>
+      <c r="V62">
+        <v>1</v>
+      </c>
+      <c r="W62">
         <v>3</v>
       </c>
-      <c r="X61">
-        <v>1</v>
-      </c>
-      <c r="Y61">
-        <v>1</v>
-      </c>
-      <c r="Z61">
+      <c r="X62">
+        <v>1</v>
+      </c>
+      <c r="Y62">
+        <v>1</v>
+      </c>
+      <c r="Z62">
         <v>1.5</v>
       </c>
-      <c r="AC61">
-        <v>1</v>
-      </c>
-      <c r="AD61">
-        <v>2</v>
-      </c>
-      <c r="AE61">
-        <v>1</v>
-      </c>
-      <c r="AF61">
-        <v>2</v>
-      </c>
-      <c r="AH61">
-        <v>2</v>
-      </c>
-      <c r="AL61">
+      <c r="AC62">
+        <v>1</v>
+      </c>
+      <c r="AD62">
+        <v>2</v>
+      </c>
+      <c r="AE62">
+        <v>1</v>
+      </c>
+      <c r="AF62">
+        <v>2</v>
+      </c>
+      <c r="AH62">
+        <v>2</v>
+      </c>
+      <c r="AL62">
         <v>3</v>
       </c>
-      <c r="AP61">
-        <v>2</v>
-      </c>
-      <c r="AQ61">
+      <c r="AP62">
+        <v>2</v>
+      </c>
+      <c r="AQ62">
         <v>4</v>
       </c>
-      <c r="AR61">
+      <c r="AR62">
         <v>3</v>
       </c>
-      <c r="AS61">
+      <c r="AS62">
         <v>0.5</v>
       </c>
-      <c r="AU61">
-        <v>2</v>
-      </c>
-      <c r="AV61">
-        <v>1</v>
-      </c>
-      <c r="BC61">
-        <v>1</v>
-      </c>
-      <c r="BD61">
-        <v>1</v>
-      </c>
-      <c r="BE61">
+      <c r="AU62">
+        <v>2</v>
+      </c>
+      <c r="AV62">
+        <v>1</v>
+      </c>
+      <c r="BC62">
+        <v>1</v>
+      </c>
+      <c r="BD62">
+        <v>1</v>
+      </c>
+      <c r="BE62">
         <v>7</v>
       </c>
-      <c r="BH61">
-        <v>1</v>
-      </c>
-      <c r="BI61">
-        <v>1</v>
-      </c>
-      <c r="BJ61">
+      <c r="BH62">
+        <v>1</v>
+      </c>
+      <c r="BI62">
+        <v>1</v>
+      </c>
+      <c r="BJ62">
         <v>3</v>
       </c>
-      <c r="BK61">
+      <c r="BK62">
         <v>3</v>
       </c>
-      <c r="BL61">
-        <v>1</v>
-      </c>
-      <c r="BM61">
-        <v>1</v>
-      </c>
-      <c r="BN61">
+      <c r="BL62">
+        <v>1</v>
+      </c>
+      <c r="BM62">
+        <v>1</v>
+      </c>
+      <c r="BN62">
         <v>4</v>
       </c>
-      <c r="BP61">
-        <v>1</v>
-      </c>
-      <c r="BQ61">
+      <c r="BP62">
+        <v>1</v>
+      </c>
+      <c r="BQ62">
         <v>3</v>
       </c>
-      <c r="BR61">
-        <v>1</v>
-      </c>
-      <c r="BT61">
-        <v>1</v>
-      </c>
-      <c r="BV61">
-        <v>1</v>
-      </c>
-      <c r="BW61">
-        <v>2</v>
-      </c>
-      <c r="BX61">
-        <v>2</v>
-      </c>
-      <c r="BZ61">
-        <v>2</v>
-      </c>
-      <c r="CC61">
+      <c r="BR62">
+        <v>1</v>
+      </c>
+      <c r="BT62">
+        <v>1</v>
+      </c>
+      <c r="BV62">
+        <v>1</v>
+      </c>
+      <c r="BW62">
+        <v>2</v>
+      </c>
+      <c r="BX62">
+        <v>2</v>
+      </c>
+      <c r="BZ62">
+        <v>2</v>
+      </c>
+      <c r="CC62">
         <v>4</v>
       </c>
-      <c r="CD61">
-        <v>1</v>
-      </c>
-      <c r="CJ61">
-        <v>1</v>
-      </c>
-      <c r="CK61">
-        <v>1</v>
-      </c>
-      <c r="CL61">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="62" spans="1:95" x14ac:dyDescent="0.35">
-      <c r="A62" t="s">
+      <c r="CD62">
+        <v>1</v>
+      </c>
+      <c r="CJ62">
+        <v>1</v>
+      </c>
+      <c r="CK62">
+        <v>1</v>
+      </c>
+      <c r="CL62">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="63" spans="1:97" x14ac:dyDescent="0.35">
+      <c r="A63" t="s">
         <v>45</v>
       </c>
-      <c r="B62">
-        <v>1</v>
-      </c>
-      <c r="O62">
+      <c r="B63">
+        <v>1</v>
+      </c>
+      <c r="O63">
         <v>3</v>
       </c>
-      <c r="P62">
-        <v>1</v>
-      </c>
-      <c r="Q62">
-        <v>2</v>
-      </c>
-      <c r="AM62">
-        <v>1</v>
-      </c>
-      <c r="AN62">
-        <v>1</v>
-      </c>
-      <c r="AP62">
-        <v>1</v>
-      </c>
-      <c r="AS62">
-        <v>1</v>
-      </c>
-      <c r="AV62">
-        <v>1</v>
-      </c>
-      <c r="AX62">
-        <v>5</v>
-      </c>
-      <c r="AY62">
-        <v>1</v>
-      </c>
-      <c r="BA62">
-        <v>2</v>
-      </c>
-      <c r="BB62">
+      <c r="P63">
+        <v>1</v>
+      </c>
+      <c r="Q63">
+        <v>2</v>
+      </c>
+      <c r="AM63">
+        <v>1</v>
+      </c>
+      <c r="AN63">
+        <v>1</v>
+      </c>
+      <c r="AP63">
+        <v>1</v>
+      </c>
+      <c r="AS63">
+        <v>1</v>
+      </c>
+      <c r="AV63">
+        <v>1</v>
+      </c>
+      <c r="AX63">
+        <v>5</v>
+      </c>
+      <c r="AY63">
+        <v>1</v>
+      </c>
+      <c r="BA63">
+        <v>2</v>
+      </c>
+      <c r="BB63">
         <v>4</v>
       </c>
-      <c r="BE62">
+      <c r="BE63">
         <v>3</v>
       </c>
-      <c r="BF62">
-        <v>2</v>
-      </c>
-      <c r="BH62">
+      <c r="BF63">
+        <v>2</v>
+      </c>
+      <c r="BH63">
         <v>3</v>
       </c>
-      <c r="BK62">
-        <v>1</v>
-      </c>
-      <c r="BT62">
+      <c r="BK63">
+        <v>1</v>
+      </c>
+      <c r="BT63">
         <v>3</v>
       </c>
-      <c r="BZ62">
-        <v>1</v>
-      </c>
-      <c r="CB62">
-        <v>2</v>
-      </c>
-      <c r="CC62">
-        <v>1</v>
-      </c>
-      <c r="CD62">
-        <v>1</v>
-      </c>
-      <c r="CF62">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="63" spans="1:95" x14ac:dyDescent="0.35">
-      <c r="A63" t="s">
-        <v>152</v>
-      </c>
-      <c r="CN63">
-        <v>1</v>
-      </c>
-      <c r="CO63">
-        <v>1</v>
-      </c>
-      <c r="CP63">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="64" spans="1:95" hidden="1" x14ac:dyDescent="0.35">
+      <c r="BZ63">
+        <v>1</v>
+      </c>
+      <c r="CB63">
+        <v>2</v>
+      </c>
+      <c r="CC63">
+        <v>1</v>
+      </c>
+      <c r="CD63">
+        <v>1</v>
+      </c>
+      <c r="CF63">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="64" spans="1:97" x14ac:dyDescent="0.35">
       <c r="A64" t="s">
+        <v>174</v>
+      </c>
+      <c r="CN64">
+        <v>1</v>
+      </c>
+      <c r="CO64">
+        <v>1</v>
+      </c>
+      <c r="CP64">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="65" spans="1:95" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A65" t="s">
         <v>104</v>
-      </c>
-    </row>
-    <row r="65" spans="1:95" x14ac:dyDescent="0.35">
-      <c r="A65" t="s">
-        <v>128</v>
       </c>
     </row>
     <row r="66" spans="1:95" x14ac:dyDescent="0.35">
       <c r="A66" t="s">
-        <v>3</v>
-      </c>
-      <c r="F66">
-        <v>3</v>
-      </c>
-      <c r="L66">
-        <v>1</v>
-      </c>
-      <c r="S66">
-        <v>3</v>
-      </c>
-      <c r="AH66">
-        <v>1</v>
+        <v>128</v>
       </c>
     </row>
     <row r="67" spans="1:95" x14ac:dyDescent="0.35">
       <c r="A67" t="s">
-        <v>55</v>
-      </c>
-      <c r="C67">
         <v>3</v>
       </c>
-      <c r="E67">
-        <v>2</v>
-      </c>
       <c r="F67">
-        <v>1</v>
-      </c>
-      <c r="G67">
-        <v>2</v>
-      </c>
-      <c r="I67">
-        <v>1</v>
-      </c>
-      <c r="J67">
-        <v>1</v>
-      </c>
-      <c r="K67">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L67">
         <v>1</v>
       </c>
-      <c r="M67">
-        <v>1</v>
-      </c>
-      <c r="P67">
-        <v>1</v>
-      </c>
-      <c r="R67">
-        <v>1</v>
-      </c>
       <c r="S67">
-        <v>4</v>
-      </c>
-      <c r="T67">
-        <v>1</v>
-      </c>
-      <c r="V67">
-        <v>1</v>
-      </c>
-      <c r="W67">
-        <v>2</v>
-      </c>
-      <c r="Z67">
-        <v>2</v>
-      </c>
-      <c r="AA67">
-        <v>1</v>
-      </c>
-      <c r="AB67">
-        <v>4</v>
-      </c>
-      <c r="AC67">
-        <v>1</v>
-      </c>
-      <c r="AD67">
-        <v>1</v>
-      </c>
-      <c r="AX67">
-        <v>1</v>
-      </c>
-      <c r="AY67">
-        <v>1</v>
-      </c>
-      <c r="AZ67">
-        <v>2</v>
-      </c>
-      <c r="BD67">
-        <v>1</v>
-      </c>
-      <c r="BF67">
-        <v>1</v>
-      </c>
-      <c r="BH67">
-        <v>1</v>
-      </c>
-      <c r="BI67">
-        <v>1</v>
-      </c>
-      <c r="BJ67">
-        <v>2</v>
-      </c>
-      <c r="BK67">
-        <v>1</v>
-      </c>
-      <c r="BL67">
-        <v>2</v>
-      </c>
-      <c r="BM67">
-        <v>2</v>
-      </c>
-      <c r="BN67">
-        <v>2</v>
-      </c>
-      <c r="BO67">
-        <v>1</v>
-      </c>
-      <c r="BP67">
-        <v>1</v>
-      </c>
-      <c r="BR67">
-        <v>1</v>
-      </c>
-      <c r="BS67">
-        <v>2</v>
-      </c>
-      <c r="BU67">
-        <v>2</v>
-      </c>
-      <c r="BV67">
-        <v>1</v>
-      </c>
-      <c r="BX67">
-        <v>1</v>
-      </c>
-      <c r="BY67">
-        <v>2</v>
-      </c>
-      <c r="BZ67">
-        <v>2</v>
-      </c>
-      <c r="CA67">
-        <v>2</v>
-      </c>
-      <c r="CB67">
-        <v>2</v>
-      </c>
-      <c r="CC67">
-        <v>4</v>
-      </c>
-      <c r="CD67">
-        <v>5</v>
-      </c>
-      <c r="CG67">
-        <v>1</v>
-      </c>
-      <c r="CH67">
-        <v>1</v>
-      </c>
-      <c r="CI67">
-        <v>2</v>
-      </c>
-      <c r="CJ67">
-        <v>5</v>
-      </c>
-      <c r="CN67">
-        <v>1</v>
-      </c>
-      <c r="CO67">
-        <v>1</v>
-      </c>
-      <c r="CQ67">
+        <v>3</v>
+      </c>
+      <c r="AH67">
         <v>1</v>
       </c>
     </row>
     <row r="68" spans="1:95" x14ac:dyDescent="0.35">
       <c r="A68" t="s">
-        <v>120</v>
-      </c>
-      <c r="AN68">
+        <v>55</v>
+      </c>
+      <c r="C68">
         <v>3</v>
+      </c>
+      <c r="E68">
+        <v>2</v>
+      </c>
+      <c r="F68">
+        <v>1</v>
+      </c>
+      <c r="G68">
+        <v>2</v>
+      </c>
+      <c r="I68">
+        <v>1</v>
+      </c>
+      <c r="J68">
+        <v>1</v>
+      </c>
+      <c r="K68">
+        <v>1</v>
+      </c>
+      <c r="L68">
+        <v>1</v>
+      </c>
+      <c r="M68">
+        <v>1</v>
+      </c>
+      <c r="P68">
+        <v>1</v>
+      </c>
+      <c r="R68">
+        <v>1</v>
+      </c>
+      <c r="S68">
+        <v>4</v>
+      </c>
+      <c r="T68">
+        <v>1</v>
+      </c>
+      <c r="V68">
+        <v>1</v>
+      </c>
+      <c r="W68">
+        <v>2</v>
+      </c>
+      <c r="Z68">
+        <v>2</v>
+      </c>
+      <c r="AA68">
+        <v>1</v>
+      </c>
+      <c r="AB68">
+        <v>4</v>
+      </c>
+      <c r="AC68">
+        <v>1</v>
+      </c>
+      <c r="AD68">
+        <v>1</v>
+      </c>
+      <c r="AX68">
+        <v>1</v>
+      </c>
+      <c r="AY68">
+        <v>1</v>
+      </c>
+      <c r="AZ68">
+        <v>2</v>
+      </c>
+      <c r="BD68">
+        <v>1</v>
+      </c>
+      <c r="BF68">
+        <v>1</v>
+      </c>
+      <c r="BH68">
+        <v>1</v>
+      </c>
+      <c r="BI68">
+        <v>1</v>
+      </c>
+      <c r="BJ68">
+        <v>2</v>
+      </c>
+      <c r="BK68">
+        <v>1</v>
+      </c>
+      <c r="BL68">
+        <v>2</v>
+      </c>
+      <c r="BM68">
+        <v>2</v>
+      </c>
+      <c r="BN68">
+        <v>2</v>
+      </c>
+      <c r="BO68">
+        <v>1</v>
+      </c>
+      <c r="BP68">
+        <v>1</v>
+      </c>
+      <c r="BR68">
+        <v>1</v>
+      </c>
+      <c r="BS68">
+        <v>2</v>
+      </c>
+      <c r="BU68">
+        <v>2</v>
+      </c>
+      <c r="BV68">
+        <v>1</v>
+      </c>
+      <c r="BX68">
+        <v>1</v>
+      </c>
+      <c r="BY68">
+        <v>2</v>
+      </c>
+      <c r="BZ68">
+        <v>2</v>
+      </c>
+      <c r="CA68">
+        <v>2</v>
+      </c>
+      <c r="CB68">
+        <v>2</v>
+      </c>
+      <c r="CC68">
+        <v>4</v>
+      </c>
+      <c r="CD68">
+        <v>5</v>
+      </c>
+      <c r="CG68">
+        <v>1</v>
+      </c>
+      <c r="CH68">
+        <v>1</v>
+      </c>
+      <c r="CI68">
+        <v>2</v>
+      </c>
+      <c r="CJ68">
+        <v>5</v>
+      </c>
+      <c r="CN68">
+        <v>1</v>
+      </c>
+      <c r="CO68">
+        <v>1</v>
+      </c>
+      <c r="CQ68">
+        <v>1</v>
       </c>
     </row>
     <row r="69" spans="1:95" x14ac:dyDescent="0.35">
       <c r="A69" t="s">
-        <v>138</v>
-      </c>
-      <c r="BN69">
+        <v>120</v>
+      </c>
+      <c r="AN69">
         <v>3</v>
-      </c>
-      <c r="BO69">
-        <v>2</v>
-      </c>
-      <c r="BQ69">
-        <v>2</v>
       </c>
     </row>
     <row r="70" spans="1:95" x14ac:dyDescent="0.35">
       <c r="A70" t="s">
-        <v>59</v>
-      </c>
-      <c r="B70">
-        <v>2</v>
-      </c>
-      <c r="BF70">
-        <v>1</v>
-      </c>
-      <c r="BT70">
+        <v>138</v>
+      </c>
+      <c r="BN70">
+        <v>3</v>
+      </c>
+      <c r="BO70">
+        <v>2</v>
+      </c>
+      <c r="BQ70">
         <v>2</v>
       </c>
     </row>
     <row r="71" spans="1:95" x14ac:dyDescent="0.35">
       <c r="A71" t="s">
-        <v>95</v>
-      </c>
-      <c r="Q71">
-        <v>1</v>
-      </c>
-      <c r="U71">
-        <v>1</v>
-      </c>
-      <c r="W71">
-        <v>1</v>
-      </c>
-      <c r="X71">
-        <v>3</v>
-      </c>
-      <c r="Y71">
-        <v>1</v>
-      </c>
-      <c r="Z71">
-        <v>1</v>
+        <v>59</v>
+      </c>
+      <c r="B71">
+        <v>2</v>
+      </c>
+      <c r="BF71">
+        <v>1</v>
+      </c>
+      <c r="BT71">
+        <v>2</v>
       </c>
     </row>
     <row r="72" spans="1:95" x14ac:dyDescent="0.35">
       <c r="A72" t="s">
-        <v>94</v>
+        <v>95</v>
+      </c>
+      <c r="Q72">
+        <v>1</v>
+      </c>
+      <c r="U72">
+        <v>1</v>
+      </c>
+      <c r="W72">
+        <v>1</v>
+      </c>
+      <c r="X72">
+        <v>3</v>
+      </c>
+      <c r="Y72">
+        <v>1</v>
+      </c>
+      <c r="Z72">
+        <v>1</v>
       </c>
     </row>
     <row r="73" spans="1:95" x14ac:dyDescent="0.35">
       <c r="A73" t="s">
-        <v>171</v>
+        <v>94</v>
       </c>
     </row>
     <row r="74" spans="1:95" x14ac:dyDescent="0.35">
       <c r="A74" t="s">
-        <v>162</v>
+        <v>170</v>
       </c>
     </row>
     <row r="75" spans="1:95" x14ac:dyDescent="0.35">
       <c r="A75" t="s">
-        <v>11</v>
+        <v>162</v>
       </c>
     </row>
     <row r="76" spans="1:95" x14ac:dyDescent="0.35">
       <c r="A76" t="s">
-        <v>54</v>
-      </c>
-      <c r="B76">
-        <v>2</v>
-      </c>
-      <c r="C76">
-        <v>1</v>
-      </c>
-      <c r="D76">
-        <v>1</v>
-      </c>
-      <c r="E76">
-        <v>1</v>
-      </c>
-      <c r="F76">
-        <v>3</v>
-      </c>
-      <c r="G76">
-        <v>2</v>
-      </c>
-      <c r="H76">
-        <v>3</v>
-      </c>
-      <c r="J76">
-        <v>1</v>
-      </c>
-      <c r="K76">
-        <v>1</v>
-      </c>
-      <c r="M76">
-        <v>3</v>
-      </c>
-      <c r="N76">
-        <v>4</v>
-      </c>
-      <c r="X76">
-        <v>6</v>
-      </c>
-      <c r="Y76">
-        <v>5</v>
-      </c>
-      <c r="Z76">
-        <v>1</v>
-      </c>
-      <c r="AD76">
-        <v>2</v>
-      </c>
-      <c r="AG76">
-        <v>3</v>
-      </c>
-      <c r="AJ76">
-        <v>2</v>
-      </c>
-      <c r="AM76">
-        <v>2</v>
-      </c>
-      <c r="AO76">
-        <v>3</v>
-      </c>
-      <c r="AQ76">
-        <v>2</v>
-      </c>
-      <c r="AT76">
-        <v>1</v>
-      </c>
-      <c r="AU76">
-        <v>4</v>
-      </c>
-      <c r="AV76">
-        <v>2</v>
-      </c>
-      <c r="AX76">
-        <v>1</v>
-      </c>
-      <c r="AY76">
-        <v>2</v>
-      </c>
-      <c r="AZ76">
-        <v>1</v>
-      </c>
-      <c r="BA76">
-        <v>4</v>
-      </c>
-      <c r="BB76">
-        <v>2</v>
-      </c>
-      <c r="BH76">
-        <v>1</v>
-      </c>
-      <c r="BR76">
-        <v>2</v>
+        <v>11</v>
       </c>
     </row>
     <row r="77" spans="1:95" x14ac:dyDescent="0.35">
       <c r="A77" t="s">
-        <v>20</v>
+        <v>54</v>
+      </c>
+      <c r="B77">
+        <v>2</v>
+      </c>
+      <c r="C77">
+        <v>1</v>
+      </c>
+      <c r="D77">
+        <v>1</v>
+      </c>
+      <c r="E77">
+        <v>1</v>
+      </c>
+      <c r="F77">
+        <v>3</v>
+      </c>
+      <c r="G77">
+        <v>2</v>
+      </c>
+      <c r="H77">
+        <v>3</v>
+      </c>
+      <c r="J77">
+        <v>1</v>
+      </c>
+      <c r="K77">
+        <v>1</v>
+      </c>
+      <c r="M77">
+        <v>3</v>
+      </c>
+      <c r="N77">
+        <v>4</v>
+      </c>
+      <c r="X77">
+        <v>6</v>
+      </c>
+      <c r="Y77">
+        <v>5</v>
+      </c>
+      <c r="Z77">
+        <v>1</v>
+      </c>
+      <c r="AD77">
+        <v>2</v>
+      </c>
+      <c r="AG77">
+        <v>3</v>
+      </c>
+      <c r="AJ77">
+        <v>2</v>
+      </c>
+      <c r="AM77">
+        <v>2</v>
+      </c>
+      <c r="AO77">
+        <v>3</v>
+      </c>
+      <c r="AQ77">
+        <v>2</v>
+      </c>
+      <c r="AT77">
+        <v>1</v>
+      </c>
+      <c r="AU77">
+        <v>4</v>
+      </c>
+      <c r="AV77">
+        <v>2</v>
+      </c>
+      <c r="AX77">
+        <v>1</v>
+      </c>
+      <c r="AY77">
+        <v>2</v>
+      </c>
+      <c r="AZ77">
+        <v>1</v>
+      </c>
+      <c r="BA77">
+        <v>4</v>
+      </c>
+      <c r="BB77">
+        <v>2</v>
+      </c>
+      <c r="BH77">
+        <v>1</v>
+      </c>
+      <c r="BR77">
+        <v>2</v>
       </c>
     </row>
     <row r="78" spans="1:95" x14ac:dyDescent="0.35">
       <c r="A78" t="s">
-        <v>80</v>
-      </c>
-      <c r="G78">
-        <v>3</v>
-      </c>
-      <c r="K78">
-        <v>1</v>
-      </c>
-      <c r="BG78">
-        <v>2</v>
-      </c>
-      <c r="BN78">
-        <v>4</v>
-      </c>
-      <c r="BP78">
-        <v>1</v>
-      </c>
-      <c r="BR78">
-        <v>2</v>
-      </c>
-      <c r="BS78">
-        <v>3</v>
-      </c>
-      <c r="BU78">
-        <v>3</v>
-      </c>
-      <c r="BV78">
-        <v>2</v>
-      </c>
-      <c r="BW78">
-        <v>2</v>
-      </c>
-      <c r="BX78">
-        <v>2</v>
-      </c>
-      <c r="BY78">
-        <v>2</v>
+        <v>20</v>
       </c>
     </row>
     <row r="79" spans="1:95" x14ac:dyDescent="0.35">
       <c r="A79" t="s">
-        <v>62</v>
-      </c>
-      <c r="B79">
-        <v>2</v>
-      </c>
-      <c r="D79">
-        <v>1</v>
-      </c>
-      <c r="AF79">
-        <v>2</v>
-      </c>
-      <c r="AQ79">
+        <v>80</v>
+      </c>
+      <c r="G79">
         <v>3</v>
       </c>
-      <c r="BF79">
-        <v>1</v>
-      </c>
-      <c r="BM79">
-        <v>1</v>
+      <c r="K79">
+        <v>1</v>
+      </c>
+      <c r="BG79">
+        <v>2</v>
+      </c>
+      <c r="BN79">
+        <v>4</v>
+      </c>
+      <c r="BP79">
+        <v>1</v>
+      </c>
+      <c r="BR79">
+        <v>2</v>
+      </c>
+      <c r="BS79">
+        <v>3</v>
+      </c>
+      <c r="BU79">
+        <v>3</v>
+      </c>
+      <c r="BV79">
+        <v>2</v>
       </c>
       <c r="BW79">
-        <v>1</v>
-      </c>
-      <c r="CB79">
-        <v>1</v>
-      </c>
-      <c r="CD79">
+        <v>2</v>
+      </c>
+      <c r="BX79">
+        <v>2</v>
+      </c>
+      <c r="BY79">
         <v>2</v>
       </c>
     </row>
     <row r="80" spans="1:95" x14ac:dyDescent="0.35">
       <c r="A80" t="s">
+        <v>62</v>
+      </c>
+      <c r="B80">
+        <v>2</v>
+      </c>
+      <c r="D80">
+        <v>1</v>
+      </c>
+      <c r="AF80">
+        <v>2</v>
+      </c>
+      <c r="AQ80">
+        <v>3</v>
+      </c>
+      <c r="BF80">
+        <v>1</v>
+      </c>
+      <c r="BM80">
+        <v>1</v>
+      </c>
+      <c r="BW80">
+        <v>1</v>
+      </c>
+      <c r="CB80">
+        <v>1</v>
+      </c>
+      <c r="CD80">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="81" spans="1:97" x14ac:dyDescent="0.35">
+      <c r="A81" t="s">
         <v>82</v>
       </c>
     </row>
-    <row r="81" spans="1:96" x14ac:dyDescent="0.35">
-      <c r="A81" t="s">
+    <row r="82" spans="1:97" x14ac:dyDescent="0.35">
+      <c r="A82" t="s">
         <v>153</v>
       </c>
     </row>
-    <row r="82" spans="1:96" x14ac:dyDescent="0.35">
-      <c r="A82" t="s">
+    <row r="83" spans="1:97" x14ac:dyDescent="0.35">
+      <c r="A83" t="s">
         <v>21</v>
       </c>
-      <c r="Y82">
-        <v>1</v>
-      </c>
-      <c r="AB82">
-        <v>2</v>
-      </c>
-      <c r="AD82">
+      <c r="Y83">
+        <v>1</v>
+      </c>
+      <c r="AB83">
+        <v>2</v>
+      </c>
+      <c r="AD83">
         <v>3</v>
       </c>
-      <c r="AI82">
-        <v>1</v>
-      </c>
-      <c r="AR82">
+      <c r="AI83">
+        <v>1</v>
+      </c>
+      <c r="AR83">
         <v>4</v>
       </c>
-      <c r="AV82">
+      <c r="AV83">
         <v>3</v>
       </c>
-      <c r="BA82">
-        <v>2</v>
-      </c>
-      <c r="BB82">
-        <v>5</v>
-      </c>
-      <c r="BE82">
+      <c r="BA83">
+        <v>2</v>
+      </c>
+      <c r="BB83">
+        <v>5</v>
+      </c>
+      <c r="BE83">
         <v>6</v>
       </c>
-      <c r="BS82">
-        <v>1</v>
-      </c>
-      <c r="BT82">
-        <v>1</v>
-      </c>
-      <c r="BU82">
-        <v>2</v>
-      </c>
-      <c r="BV82">
+      <c r="BS83">
+        <v>1</v>
+      </c>
+      <c r="BT83">
+        <v>1</v>
+      </c>
+      <c r="BU83">
+        <v>2</v>
+      </c>
+      <c r="BV83">
         <v>3</v>
       </c>
-      <c r="BX82">
-        <v>2</v>
-      </c>
-      <c r="CC82">
-        <v>2</v>
-      </c>
-      <c r="CG82">
-        <v>1</v>
-      </c>
-      <c r="CI82">
-        <v>1</v>
-      </c>
-      <c r="CM82">
+      <c r="BX83">
+        <v>2</v>
+      </c>
+      <c r="CC83">
+        <v>2</v>
+      </c>
+      <c r="CG83">
+        <v>1</v>
+      </c>
+      <c r="CI83">
+        <v>1</v>
+      </c>
+      <c r="CM83">
         <v>3</v>
       </c>
-      <c r="CP82">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="83" spans="1:96" x14ac:dyDescent="0.35">
-      <c r="A83" t="s">
+      <c r="CP83">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="84" spans="1:97" x14ac:dyDescent="0.35">
+      <c r="A84" t="s">
         <v>108</v>
       </c>
-      <c r="CP83">
-        <v>1</v>
-      </c>
-      <c r="CQ83">
-        <v>1</v>
-      </c>
-      <c r="CR83">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="84" spans="1:96" x14ac:dyDescent="0.35">
-      <c r="A84" t="s">
+      <c r="CP84">
+        <v>1</v>
+      </c>
+      <c r="CQ84">
+        <v>1</v>
+      </c>
+      <c r="CR84">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="85" spans="1:97" x14ac:dyDescent="0.35">
+      <c r="A85" t="s">
         <v>127</v>
       </c>
-      <c r="AU84">
-        <v>1</v>
-      </c>
-      <c r="AV84">
-        <v>1</v>
-      </c>
-      <c r="AW84">
+      <c r="AU85">
+        <v>1</v>
+      </c>
+      <c r="AV85">
+        <v>1</v>
+      </c>
+      <c r="AW85">
         <v>3</v>
       </c>
-      <c r="AX84">
-        <v>1</v>
-      </c>
-      <c r="AZ84">
-        <v>1</v>
-      </c>
-      <c r="BC84">
-        <v>2</v>
-      </c>
-      <c r="BX84">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="85" spans="1:96" x14ac:dyDescent="0.35">
-      <c r="A85" t="s">
+      <c r="AX85">
+        <v>1</v>
+      </c>
+      <c r="AZ85">
+        <v>1</v>
+      </c>
+      <c r="BC85">
+        <v>2</v>
+      </c>
+      <c r="BX85">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="86" spans="1:97" x14ac:dyDescent="0.35">
+      <c r="A86" t="s">
         <v>43</v>
       </c>
-      <c r="N85">
+      <c r="N86">
         <v>3</v>
       </c>
-      <c r="S85">
-        <v>2</v>
-      </c>
-      <c r="AG85">
-        <v>2</v>
-      </c>
-      <c r="AI85">
-        <v>1</v>
-      </c>
-      <c r="AP85">
-        <v>2</v>
-      </c>
-      <c r="AQ85">
-        <v>1</v>
-      </c>
-      <c r="AR85">
+      <c r="S86">
+        <v>2</v>
+      </c>
+      <c r="AG86">
+        <v>2</v>
+      </c>
+      <c r="AI86">
+        <v>1</v>
+      </c>
+      <c r="AP86">
+        <v>2</v>
+      </c>
+      <c r="AQ86">
+        <v>1</v>
+      </c>
+      <c r="AR86">
         <v>3</v>
       </c>
-      <c r="AW85">
-        <v>1</v>
-      </c>
-      <c r="BA85">
-        <v>1</v>
-      </c>
-      <c r="BE85">
-        <v>1</v>
-      </c>
-      <c r="BI85">
-        <v>2</v>
-      </c>
-      <c r="BL85">
-        <v>2</v>
-      </c>
-      <c r="BN85">
-        <v>2</v>
-      </c>
-      <c r="BO85">
-        <v>1</v>
-      </c>
-      <c r="BP85">
-        <v>1</v>
-      </c>
-      <c r="BR85">
-        <v>1</v>
-      </c>
-      <c r="CH85">
-        <v>1</v>
-      </c>
-      <c r="CJ85">
-        <v>1</v>
-      </c>
-      <c r="CL85">
-        <v>1</v>
-      </c>
-      <c r="CM85">
-        <v>1</v>
-      </c>
-      <c r="CN85">
-        <v>1</v>
-      </c>
-      <c r="CO85">
-        <v>1</v>
-      </c>
-      <c r="CP85">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="86" spans="1:96" x14ac:dyDescent="0.35">
-      <c r="A86" t="s">
+      <c r="AW86">
+        <v>1</v>
+      </c>
+      <c r="BA86">
+        <v>1</v>
+      </c>
+      <c r="BE86">
+        <v>1</v>
+      </c>
+      <c r="BI86">
+        <v>2</v>
+      </c>
+      <c r="BL86">
+        <v>2</v>
+      </c>
+      <c r="BN86">
+        <v>2</v>
+      </c>
+      <c r="BO86">
+        <v>1</v>
+      </c>
+      <c r="BP86">
+        <v>1</v>
+      </c>
+      <c r="BR86">
+        <v>1</v>
+      </c>
+      <c r="CH86">
+        <v>1</v>
+      </c>
+      <c r="CJ86">
+        <v>1</v>
+      </c>
+      <c r="CL86">
+        <v>1</v>
+      </c>
+      <c r="CM86">
+        <v>1</v>
+      </c>
+      <c r="CN86">
+        <v>1</v>
+      </c>
+      <c r="CO86">
+        <v>1</v>
+      </c>
+      <c r="CP86">
+        <v>1</v>
+      </c>
+      <c r="CS86">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="87" spans="1:97" x14ac:dyDescent="0.35">
+      <c r="A87" t="s">
         <v>130</v>
       </c>
-      <c r="BF86">
-        <v>1</v>
-      </c>
-      <c r="BG86">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="87" spans="1:96" x14ac:dyDescent="0.35">
-      <c r="A87" t="s">
+      <c r="BF87">
+        <v>1</v>
+      </c>
+      <c r="BG87">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="88" spans="1:97" x14ac:dyDescent="0.35">
+      <c r="A88" t="s">
         <v>8</v>
       </c>
-      <c r="B87">
-        <v>1</v>
-      </c>
-      <c r="H87">
-        <v>1</v>
-      </c>
-      <c r="J87">
-        <v>2</v>
-      </c>
-      <c r="Q87">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="88" spans="1:96" x14ac:dyDescent="0.35">
-      <c r="A88" t="s">
+      <c r="B88">
+        <v>1</v>
+      </c>
+      <c r="H88">
+        <v>1</v>
+      </c>
+      <c r="J88">
+        <v>2</v>
+      </c>
+      <c r="Q88">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="89" spans="1:97" x14ac:dyDescent="0.35">
+      <c r="A89" t="s">
         <v>81</v>
       </c>
-      <c r="B88">
-        <v>2</v>
-      </c>
-      <c r="C88">
-        <v>2</v>
-      </c>
-      <c r="D88">
-        <v>1</v>
-      </c>
-      <c r="E88">
-        <v>2</v>
-      </c>
-      <c r="F88">
-        <v>1</v>
-      </c>
-      <c r="G88">
-        <v>2</v>
-      </c>
-      <c r="H88">
-        <v>2</v>
-      </c>
-      <c r="I88">
+      <c r="B89">
+        <v>2</v>
+      </c>
+      <c r="C89">
+        <v>2</v>
+      </c>
+      <c r="D89">
+        <v>1</v>
+      </c>
+      <c r="E89">
+        <v>2</v>
+      </c>
+      <c r="F89">
+        <v>1</v>
+      </c>
+      <c r="G89">
+        <v>2</v>
+      </c>
+      <c r="H89">
+        <v>2</v>
+      </c>
+      <c r="I89">
         <v>3</v>
       </c>
-      <c r="J88">
+      <c r="J89">
         <v>4</v>
       </c>
-      <c r="L88">
+      <c r="L89">
         <v>4</v>
       </c>
-      <c r="M88">
-        <v>1</v>
-      </c>
-      <c r="N88">
-        <v>2</v>
-      </c>
-      <c r="O88">
-        <v>1</v>
-      </c>
-      <c r="P88">
-        <v>1</v>
-      </c>
-      <c r="Q88">
-        <v>1</v>
-      </c>
-      <c r="R88">
+      <c r="M89">
+        <v>1</v>
+      </c>
+      <c r="N89">
+        <v>2</v>
+      </c>
+      <c r="O89">
+        <v>1</v>
+      </c>
+      <c r="P89">
+        <v>1</v>
+      </c>
+      <c r="Q89">
+        <v>1</v>
+      </c>
+      <c r="R89">
         <v>3</v>
       </c>
-      <c r="S88">
+      <c r="S89">
         <v>3</v>
       </c>
-      <c r="U88">
+      <c r="U89">
         <v>3</v>
       </c>
-      <c r="V88">
-        <v>1</v>
-      </c>
-      <c r="W88">
+      <c r="V89">
+        <v>1</v>
+      </c>
+      <c r="W89">
         <v>3</v>
       </c>
-      <c r="AC88">
-        <v>1</v>
-      </c>
-      <c r="AF88">
-        <v>1</v>
-      </c>
-      <c r="AH88">
-        <v>2</v>
-      </c>
-      <c r="AI88">
+      <c r="AC89">
+        <v>1</v>
+      </c>
+      <c r="AF89">
+        <v>1</v>
+      </c>
+      <c r="AH89">
+        <v>2</v>
+      </c>
+      <c r="AI89">
         <v>3</v>
       </c>
-      <c r="AJ88">
-        <v>1</v>
-      </c>
-      <c r="AK88">
+      <c r="AJ89">
+        <v>1</v>
+      </c>
+      <c r="AK89">
         <v>4</v>
       </c>
-      <c r="AL88">
+      <c r="AL89">
         <v>3</v>
       </c>
-      <c r="AN88">
-        <v>1</v>
-      </c>
-      <c r="AP88">
-        <v>2</v>
-      </c>
-      <c r="AT88">
-        <v>2</v>
-      </c>
-      <c r="AU88">
+      <c r="AN89">
+        <v>1</v>
+      </c>
+      <c r="AP89">
+        <v>2</v>
+      </c>
+      <c r="AT89">
+        <v>2</v>
+      </c>
+      <c r="AU89">
         <v>3</v>
       </c>
-      <c r="AV88">
-        <v>1</v>
-      </c>
-      <c r="AW88">
-        <v>1</v>
-      </c>
-      <c r="AX88">
-        <v>1</v>
-      </c>
-      <c r="AY88">
-        <v>1</v>
-      </c>
-      <c r="AZ88">
-        <v>2</v>
-      </c>
-      <c r="BC88">
-        <v>2</v>
-      </c>
-      <c r="BD88">
-        <v>1</v>
-      </c>
-      <c r="BF88">
-        <v>2</v>
-      </c>
-      <c r="BH88">
+      <c r="AV89">
+        <v>1</v>
+      </c>
+      <c r="AW89">
+        <v>1</v>
+      </c>
+      <c r="AX89">
+        <v>1</v>
+      </c>
+      <c r="AY89">
+        <v>1</v>
+      </c>
+      <c r="AZ89">
+        <v>2</v>
+      </c>
+      <c r="BC89">
+        <v>2</v>
+      </c>
+      <c r="BD89">
+        <v>1</v>
+      </c>
+      <c r="BF89">
+        <v>2</v>
+      </c>
+      <c r="BH89">
         <v>3</v>
       </c>
-      <c r="BI88">
-        <v>1</v>
-      </c>
-      <c r="BJ88">
-        <v>2</v>
-      </c>
-      <c r="BK88">
+      <c r="BI89">
+        <v>1</v>
+      </c>
+      <c r="BJ89">
+        <v>2</v>
+      </c>
+      <c r="BK89">
         <v>3</v>
       </c>
-      <c r="BM88">
-        <v>2</v>
-      </c>
-      <c r="BN88">
+      <c r="BM89">
+        <v>2</v>
+      </c>
+      <c r="BN89">
         <v>3</v>
       </c>
-      <c r="BU88">
-        <v>1</v>
-      </c>
-      <c r="BV88">
+      <c r="BU89">
+        <v>1</v>
+      </c>
+      <c r="BV89">
         <v>3</v>
       </c>
-      <c r="BX88">
-        <v>2</v>
-      </c>
-      <c r="BY88">
-        <v>1</v>
-      </c>
-      <c r="BZ88">
-        <v>1</v>
-      </c>
-      <c r="CA88">
-        <v>1</v>
-      </c>
-      <c r="CB88">
-        <v>1</v>
-      </c>
-      <c r="CD88">
+      <c r="BX89">
+        <v>2</v>
+      </c>
+      <c r="BY89">
+        <v>1</v>
+      </c>
+      <c r="BZ89">
+        <v>1</v>
+      </c>
+      <c r="CA89">
+        <v>1</v>
+      </c>
+      <c r="CB89">
+        <v>1</v>
+      </c>
+      <c r="CD89">
         <v>3</v>
       </c>
-      <c r="CG88">
-        <v>1</v>
-      </c>
-      <c r="CH88">
-        <v>2</v>
-      </c>
-      <c r="CL88">
-        <v>2</v>
-      </c>
-      <c r="CP88">
-        <v>1</v>
-      </c>
-      <c r="CQ88">
-        <v>1</v>
-      </c>
-      <c r="CR88">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="89" spans="1:96" x14ac:dyDescent="0.35">
-      <c r="A89" t="s">
-        <v>172</v>
-      </c>
-    </row>
-    <row r="90" spans="1:96" x14ac:dyDescent="0.35">
+      <c r="CG89">
+        <v>1</v>
+      </c>
+      <c r="CH89">
+        <v>2</v>
+      </c>
+      <c r="CL89">
+        <v>2</v>
+      </c>
+      <c r="CP89">
+        <v>1</v>
+      </c>
+      <c r="CQ89">
+        <v>1</v>
+      </c>
+      <c r="CR89">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="90" spans="1:97" x14ac:dyDescent="0.35">
       <c r="A90" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="91" spans="1:97" x14ac:dyDescent="0.35">
+      <c r="A91" t="s">
         <v>48</v>
       </c>
-      <c r="G90">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="91" spans="1:96" x14ac:dyDescent="0.35">
-      <c r="A91" t="s">
+      <c r="G91">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="92" spans="1:97" x14ac:dyDescent="0.35">
+      <c r="A92" t="s">
         <v>155</v>
       </c>
     </row>
-    <row r="92" spans="1:96" x14ac:dyDescent="0.35">
-      <c r="A92" t="s">
+    <row r="93" spans="1:97" x14ac:dyDescent="0.35">
+      <c r="A93" t="s">
         <v>141</v>
       </c>
-      <c r="BZ92">
-        <v>5</v>
-      </c>
-      <c r="CA92">
-        <v>2</v>
-      </c>
-      <c r="CB92">
-        <v>1</v>
-      </c>
-      <c r="CJ92">
+      <c r="BZ93">
+        <v>5</v>
+      </c>
+      <c r="CA93">
+        <v>2</v>
+      </c>
+      <c r="CB93">
+        <v>1</v>
+      </c>
+      <c r="CJ93">
         <v>3</v>
       </c>
     </row>
-    <row r="93" spans="1:96" x14ac:dyDescent="0.35">
-      <c r="A93" t="s">
+    <row r="94" spans="1:97" x14ac:dyDescent="0.35">
+      <c r="A94" t="s">
         <v>84</v>
       </c>
-      <c r="K93">
+      <c r="K94">
         <v>4</v>
       </c>
-      <c r="L93">
-        <v>2</v>
-      </c>
-      <c r="M93">
-        <v>5</v>
-      </c>
-      <c r="CP93">
-        <v>2</v>
-      </c>
-      <c r="CQ93">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="94" spans="1:96" x14ac:dyDescent="0.35">
-      <c r="A94" t="s">
-        <v>5</v>
-      </c>
-      <c r="B94">
-        <v>1</v>
-      </c>
-      <c r="C94">
-        <v>2</v>
-      </c>
-      <c r="D94">
-        <v>2</v>
-      </c>
-      <c r="E94">
+      <c r="L94">
+        <v>2</v>
+      </c>
+      <c r="M94">
+        <v>5</v>
+      </c>
+      <c r="CP94">
+        <v>2</v>
+      </c>
+      <c r="CQ94">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="95" spans="1:97" x14ac:dyDescent="0.35">
+      <c r="A95" t="s">
+        <v>5</v>
+      </c>
+      <c r="B95">
+        <v>1</v>
+      </c>
+      <c r="C95">
+        <v>2</v>
+      </c>
+      <c r="D95">
+        <v>2</v>
+      </c>
+      <c r="E95">
         <v>3</v>
       </c>
-      <c r="F94">
-        <v>2</v>
-      </c>
-      <c r="G94">
+      <c r="F95">
+        <v>2</v>
+      </c>
+      <c r="G95">
         <v>3</v>
       </c>
-      <c r="H94">
-        <v>1</v>
-      </c>
-      <c r="M94">
+      <c r="H95">
+        <v>1</v>
+      </c>
+      <c r="M95">
         <v>4</v>
       </c>
-      <c r="N94">
+      <c r="N95">
         <v>6</v>
       </c>
-      <c r="P94">
-        <v>2</v>
-      </c>
-      <c r="Q94">
-        <v>1</v>
-      </c>
-      <c r="R94">
-        <v>2</v>
-      </c>
-      <c r="S94">
+      <c r="P95">
+        <v>2</v>
+      </c>
+      <c r="Q95">
+        <v>1</v>
+      </c>
+      <c r="R95">
+        <v>2</v>
+      </c>
+      <c r="S95">
         <v>3</v>
       </c>
-      <c r="V94">
-        <v>2</v>
-      </c>
-      <c r="W94">
-        <v>1</v>
-      </c>
-      <c r="X94">
-        <v>1</v>
-      </c>
-      <c r="Y94">
+      <c r="V95">
+        <v>2</v>
+      </c>
+      <c r="W95">
+        <v>1</v>
+      </c>
+      <c r="X95">
+        <v>1</v>
+      </c>
+      <c r="Y95">
         <v>4</v>
       </c>
-      <c r="Z94">
-        <v>5</v>
-      </c>
-      <c r="AA94">
-        <v>1</v>
-      </c>
-      <c r="AB94">
+      <c r="Z95">
+        <v>5</v>
+      </c>
+      <c r="AA95">
+        <v>1</v>
+      </c>
+      <c r="AB95">
         <v>3</v>
       </c>
-      <c r="AC94">
+      <c r="AC95">
         <v>4</v>
       </c>
-      <c r="AD94">
+      <c r="AD95">
         <v>3</v>
       </c>
-      <c r="AE94">
+      <c r="AE95">
         <v>3</v>
       </c>
-      <c r="AF94">
-        <v>2</v>
-      </c>
-      <c r="AG94">
-        <v>5</v>
-      </c>
-      <c r="AH94">
+      <c r="AF95">
+        <v>2</v>
+      </c>
+      <c r="AG95">
+        <v>5</v>
+      </c>
+      <c r="AH95">
         <v>7</v>
       </c>
-      <c r="AI94">
+      <c r="AI95">
         <v>3</v>
       </c>
-      <c r="AJ94">
-        <v>1</v>
-      </c>
-      <c r="AK94">
-        <v>1</v>
-      </c>
-      <c r="AL94">
+      <c r="AJ95">
+        <v>1</v>
+      </c>
+      <c r="AK95">
+        <v>1</v>
+      </c>
+      <c r="AL95">
         <v>6</v>
       </c>
-      <c r="AR94">
+      <c r="AR95">
         <v>3</v>
       </c>
-      <c r="AS94">
-        <v>2</v>
-      </c>
-      <c r="AV94">
-        <v>2</v>
-      </c>
-      <c r="AW94">
-        <v>1</v>
-      </c>
-      <c r="AX94">
+      <c r="AS95">
+        <v>2</v>
+      </c>
+      <c r="AV95">
+        <v>2</v>
+      </c>
+      <c r="AW95">
+        <v>1</v>
+      </c>
+      <c r="AX95">
         <v>4</v>
       </c>
-      <c r="AY94">
+      <c r="AY95">
         <v>3</v>
       </c>
-      <c r="AZ94">
+      <c r="AZ95">
         <v>4</v>
       </c>
-      <c r="BA94">
-        <v>5</v>
-      </c>
-      <c r="BB94">
+      <c r="BA95">
+        <v>5</v>
+      </c>
+      <c r="BB95">
         <v>6</v>
       </c>
-      <c r="BC94">
-        <v>2</v>
-      </c>
-      <c r="BD94">
-        <v>2</v>
-      </c>
-      <c r="BE94">
+      <c r="BC95">
+        <v>2</v>
+      </c>
+      <c r="BD95">
+        <v>2</v>
+      </c>
+      <c r="BE95">
         <v>7</v>
       </c>
-      <c r="BG94">
+      <c r="BG95">
         <v>4</v>
       </c>
-      <c r="BH94">
+      <c r="BH95">
         <v>3</v>
       </c>
-      <c r="BI94">
+      <c r="BI95">
         <v>4</v>
       </c>
-      <c r="BK94">
-        <v>1</v>
-      </c>
-      <c r="BL94">
+      <c r="BK95">
+        <v>1</v>
+      </c>
+      <c r="BL95">
         <v>8</v>
       </c>
-      <c r="BM94">
+      <c r="BM95">
         <v>4</v>
       </c>
-      <c r="BN94">
-        <v>5</v>
-      </c>
-      <c r="BO94">
+      <c r="BN95">
+        <v>5</v>
+      </c>
+      <c r="BO95">
         <v>3</v>
       </c>
-      <c r="BP94">
-        <v>1</v>
-      </c>
-      <c r="BQ94">
-        <v>1</v>
-      </c>
-      <c r="BR94">
+      <c r="BP95">
+        <v>1</v>
+      </c>
+      <c r="BQ95">
+        <v>1</v>
+      </c>
+      <c r="BR95">
         <v>3</v>
       </c>
-      <c r="BS94">
-        <v>1</v>
-      </c>
-      <c r="CF94">
+      <c r="BS95">
+        <v>1</v>
+      </c>
+      <c r="CF95">
         <v>4</v>
       </c>
-      <c r="CG94">
+      <c r="CG95">
         <v>4</v>
       </c>
-      <c r="CH94">
+      <c r="CH95">
         <v>6</v>
       </c>
-      <c r="CI94">
-        <v>2</v>
-      </c>
-      <c r="CJ94">
+      <c r="CI95">
+        <v>2</v>
+      </c>
+      <c r="CJ95">
         <v>7</v>
       </c>
-      <c r="CL94">
+      <c r="CL95">
         <v>3</v>
       </c>
-      <c r="CM94">
+      <c r="CM95">
         <v>6</v>
       </c>
-      <c r="CN94">
-        <v>2</v>
-      </c>
-      <c r="CO94">
-        <v>1</v>
-      </c>
-      <c r="CP94">
-        <v>1</v>
-      </c>
-      <c r="CQ94">
-        <v>1</v>
-      </c>
-      <c r="CR94">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="95" spans="1:96" x14ac:dyDescent="0.35">
-      <c r="A95" t="s">
+      <c r="CN95">
+        <v>2</v>
+      </c>
+      <c r="CO95">
+        <v>1</v>
+      </c>
+      <c r="CP95">
+        <v>1</v>
+      </c>
+      <c r="CQ95">
+        <v>1</v>
+      </c>
+      <c r="CR95">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="96" spans="1:97" x14ac:dyDescent="0.35">
+      <c r="A96" t="s">
         <v>44</v>
       </c>
-      <c r="K95">
-        <v>1</v>
-      </c>
-      <c r="BJ95">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="96" spans="1:96" x14ac:dyDescent="0.35">
-      <c r="A96" t="s">
-        <v>118</v>
-      </c>
-      <c r="B96">
-        <v>1</v>
-      </c>
-      <c r="D96">
-        <v>1</v>
-      </c>
-      <c r="E96">
-        <v>3</v>
-      </c>
-      <c r="O96">
-        <v>2</v>
-      </c>
-      <c r="P96">
-        <v>2</v>
-      </c>
-      <c r="Q96">
-        <v>1</v>
-      </c>
-      <c r="R96">
-        <v>1</v>
-      </c>
-      <c r="AD96">
-        <v>1</v>
-      </c>
-      <c r="AE96">
-        <v>1</v>
-      </c>
-      <c r="AG96">
-        <v>1</v>
-      </c>
-      <c r="AH96">
-        <v>2</v>
-      </c>
-      <c r="AL96">
-        <v>3</v>
-      </c>
-      <c r="AM96">
-        <v>2</v>
-      </c>
-      <c r="AN96">
-        <v>1</v>
-      </c>
-      <c r="AO96">
-        <v>1</v>
-      </c>
-      <c r="AR96">
-        <v>1</v>
-      </c>
-      <c r="AS96">
-        <v>1</v>
-      </c>
-      <c r="AT96">
-        <v>1</v>
-      </c>
-      <c r="AV96">
-        <v>1</v>
-      </c>
-      <c r="AW96">
-        <v>2</v>
-      </c>
-      <c r="BD96">
-        <v>1</v>
-      </c>
-      <c r="BF96">
-        <v>1</v>
-      </c>
-      <c r="BI96">
-        <v>1</v>
-      </c>
-      <c r="BU96">
-        <v>2</v>
-      </c>
-      <c r="BW96">
-        <v>2</v>
-      </c>
-      <c r="CB96">
-        <v>1</v>
-      </c>
-      <c r="CL96">
+      <c r="K96">
+        <v>1</v>
+      </c>
+      <c r="BJ96">
+        <v>1</v>
+      </c>
+      <c r="CS96">
         <v>1</v>
       </c>
     </row>
     <row r="97" spans="1:95" x14ac:dyDescent="0.35">
       <c r="A97" t="s">
-        <v>106</v>
-      </c>
-      <c r="Z97">
+        <v>118</v>
+      </c>
+      <c r="B97">
+        <v>1</v>
+      </c>
+      <c r="D97">
+        <v>1</v>
+      </c>
+      <c r="E97">
+        <v>3</v>
+      </c>
+      <c r="O97">
+        <v>2</v>
+      </c>
+      <c r="P97">
+        <v>2</v>
+      </c>
+      <c r="Q97">
+        <v>1</v>
+      </c>
+      <c r="R97">
+        <v>1</v>
+      </c>
+      <c r="AD97">
+        <v>1</v>
+      </c>
+      <c r="AE97">
+        <v>1</v>
+      </c>
+      <c r="AG97">
+        <v>1</v>
+      </c>
+      <c r="AH97">
+        <v>2</v>
+      </c>
+      <c r="AL97">
+        <v>3</v>
+      </c>
+      <c r="AM97">
+        <v>2</v>
+      </c>
+      <c r="AN97">
+        <v>1</v>
+      </c>
+      <c r="AO97">
+        <v>1</v>
+      </c>
+      <c r="AR97">
+        <v>1</v>
+      </c>
+      <c r="AS97">
+        <v>1</v>
+      </c>
+      <c r="AT97">
+        <v>1</v>
+      </c>
+      <c r="AV97">
+        <v>1</v>
+      </c>
+      <c r="AW97">
+        <v>2</v>
+      </c>
+      <c r="BD97">
+        <v>1</v>
+      </c>
+      <c r="BF97">
+        <v>1</v>
+      </c>
+      <c r="BI97">
+        <v>1</v>
+      </c>
+      <c r="BU97">
+        <v>2</v>
+      </c>
+      <c r="BW97">
+        <v>2</v>
+      </c>
+      <c r="CB97">
+        <v>1</v>
+      </c>
+      <c r="CL97">
         <v>1</v>
       </c>
     </row>
     <row r="98" spans="1:95" x14ac:dyDescent="0.35">
       <c r="A98" t="s">
-        <v>159</v>
+        <v>106</v>
+      </c>
+      <c r="Z98">
+        <v>1</v>
       </c>
     </row>
     <row r="99" spans="1:95" x14ac:dyDescent="0.35">
       <c r="A99" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="100" spans="1:95" x14ac:dyDescent="0.35">
+      <c r="A100" t="s">
         <v>117</v>
       </c>
     </row>
-    <row r="100" spans="1:95" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A100" t="s">
+    <row r="101" spans="1:95" hidden="1" x14ac:dyDescent="0.35">
+      <c r="A101" t="s">
         <v>46</v>
-      </c>
-    </row>
-    <row r="101" spans="1:95" x14ac:dyDescent="0.35">
-      <c r="A101" t="s">
-        <v>16</v>
-      </c>
-      <c r="F101">
-        <v>2</v>
-      </c>
-      <c r="J101">
-        <v>1</v>
-      </c>
-      <c r="K101">
-        <v>1</v>
       </c>
     </row>
     <row r="102" spans="1:95" x14ac:dyDescent="0.35">
       <c r="A102" t="s">
-        <v>165</v>
+        <v>16</v>
+      </c>
+      <c r="F102">
+        <v>2</v>
+      </c>
+      <c r="J102">
+        <v>1</v>
+      </c>
+      <c r="K102">
+        <v>1</v>
       </c>
     </row>
     <row r="103" spans="1:95" x14ac:dyDescent="0.35">
       <c r="A103" t="s">
-        <v>85</v>
-      </c>
-      <c r="K103">
-        <v>5</v>
+        <v>165</v>
       </c>
     </row>
     <row r="104" spans="1:95" x14ac:dyDescent="0.35">
       <c r="A104" t="s">
+        <v>85</v>
+      </c>
+      <c r="K104">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="105" spans="1:95" x14ac:dyDescent="0.35">
+      <c r="A105" t="s">
         <v>15</v>
       </c>
-      <c r="C104">
+      <c r="C105">
         <v>4</v>
       </c>
-      <c r="D104">
+      <c r="D105">
         <v>3</v>
       </c>
-      <c r="F104">
-        <v>2</v>
-      </c>
-      <c r="G104">
-        <v>5</v>
-      </c>
-      <c r="H104">
+      <c r="F105">
+        <v>2</v>
+      </c>
+      <c r="G105">
+        <v>5</v>
+      </c>
+      <c r="H105">
         <v>3</v>
       </c>
-      <c r="I104">
-        <v>2</v>
-      </c>
-      <c r="J104">
-        <v>5</v>
-      </c>
-      <c r="K104">
+      <c r="I105">
+        <v>2</v>
+      </c>
+      <c r="J105">
+        <v>5</v>
+      </c>
+      <c r="K105">
         <v>3</v>
       </c>
-      <c r="L104">
-        <v>2</v>
-      </c>
-      <c r="M104">
+      <c r="L105">
+        <v>2</v>
+      </c>
+      <c r="M105">
         <v>3</v>
       </c>
-      <c r="O104">
-        <v>5</v>
-      </c>
-      <c r="P104">
-        <v>5</v>
-      </c>
-      <c r="Q104">
+      <c r="O105">
+        <v>5</v>
+      </c>
+      <c r="P105">
+        <v>5</v>
+      </c>
+      <c r="Q105">
         <v>3</v>
       </c>
-      <c r="R104">
-        <v>2</v>
-      </c>
-      <c r="S104">
+      <c r="R105">
+        <v>2</v>
+      </c>
+      <c r="S105">
         <v>3</v>
       </c>
-      <c r="T104">
-        <v>1</v>
-      </c>
-      <c r="U104">
-        <v>1</v>
-      </c>
-      <c r="V104">
+      <c r="T105">
+        <v>1</v>
+      </c>
+      <c r="U105">
+        <v>1</v>
+      </c>
+      <c r="V105">
         <v>3</v>
       </c>
-      <c r="W104">
+      <c r="W105">
         <v>3</v>
       </c>
-      <c r="X104">
-        <v>5</v>
-      </c>
-      <c r="Y104">
+      <c r="X105">
+        <v>5</v>
+      </c>
+      <c r="Y105">
         <v>4</v>
       </c>
-      <c r="Z104">
-        <v>1</v>
-      </c>
-      <c r="AA104">
+      <c r="Z105">
+        <v>1</v>
+      </c>
+      <c r="AA105">
         <v>3</v>
       </c>
-      <c r="AC104">
-        <v>1</v>
-      </c>
-      <c r="AE104">
+      <c r="AC105">
+        <v>1</v>
+      </c>
+      <c r="AE105">
         <v>4</v>
       </c>
-      <c r="AF104">
-        <v>2</v>
-      </c>
-      <c r="AG104">
+      <c r="AF105">
+        <v>2</v>
+      </c>
+      <c r="AG105">
         <v>3</v>
       </c>
-      <c r="AH104">
-        <v>2</v>
-      </c>
-      <c r="AI104">
-        <v>2</v>
-      </c>
-      <c r="AJ104">
+      <c r="AH105">
+        <v>2</v>
+      </c>
+      <c r="AI105">
+        <v>2</v>
+      </c>
+      <c r="AJ105">
         <v>7</v>
       </c>
-      <c r="AK104">
+      <c r="AK105">
         <v>3</v>
       </c>
-      <c r="AL104">
-        <v>5</v>
-      </c>
-      <c r="AM104">
-        <v>1</v>
-      </c>
-      <c r="AN104">
+      <c r="AL105">
+        <v>5</v>
+      </c>
+      <c r="AM105">
+        <v>1</v>
+      </c>
+      <c r="AN105">
         <v>4</v>
       </c>
-      <c r="AO104">
+      <c r="AO105">
         <v>3</v>
       </c>
-      <c r="AP104">
+      <c r="AP105">
         <v>6</v>
       </c>
-      <c r="AQ104">
+      <c r="AQ105">
         <v>4</v>
       </c>
-      <c r="AR104">
-        <v>5</v>
-      </c>
-      <c r="AS104">
+      <c r="AR105">
+        <v>5</v>
+      </c>
+      <c r="AS105">
         <v>3</v>
       </c>
-      <c r="AT104">
-        <v>2</v>
-      </c>
-      <c r="AU104">
-        <v>2</v>
-      </c>
-      <c r="AW104">
+      <c r="AT105">
+        <v>2</v>
+      </c>
+      <c r="AU105">
+        <v>2</v>
+      </c>
+      <c r="AW105">
         <v>3</v>
       </c>
-      <c r="AY104">
-        <v>1</v>
-      </c>
-      <c r="AZ104">
+      <c r="AY105">
+        <v>1</v>
+      </c>
+      <c r="AZ105">
         <v>3</v>
       </c>
-      <c r="BB104">
+      <c r="BB105">
         <v>4</v>
       </c>
-      <c r="BC104">
+      <c r="BC105">
         <v>4</v>
       </c>
-      <c r="BD104">
+      <c r="BD105">
         <v>3</v>
       </c>
-      <c r="BF104">
-        <v>2</v>
-      </c>
-      <c r="BG104">
+      <c r="BF105">
+        <v>2</v>
+      </c>
+      <c r="BG105">
         <v>4</v>
       </c>
-      <c r="BH104">
-        <v>5</v>
-      </c>
-      <c r="BJ104">
+      <c r="BH105">
+        <v>5</v>
+      </c>
+      <c r="BJ105">
         <v>4</v>
       </c>
-      <c r="BK104">
-        <v>2</v>
-      </c>
-      <c r="BL104">
+      <c r="BK105">
+        <v>2</v>
+      </c>
+      <c r="BL105">
         <v>4</v>
       </c>
-      <c r="BM104">
-        <v>1</v>
-      </c>
-      <c r="BN104">
-        <v>2</v>
-      </c>
-      <c r="BO104">
+      <c r="BM105">
+        <v>1</v>
+      </c>
+      <c r="BN105">
+        <v>2</v>
+      </c>
+      <c r="BO105">
         <v>3</v>
       </c>
-      <c r="BS104">
+      <c r="BS105">
         <v>3</v>
       </c>
-      <c r="BT104">
+      <c r="BT105">
         <v>4</v>
       </c>
-      <c r="BU104">
+      <c r="BU105">
         <v>4</v>
       </c>
-      <c r="BV104">
+      <c r="BV105">
         <v>3</v>
       </c>
-      <c r="BX104">
-        <v>5</v>
-      </c>
-      <c r="BY104">
-        <v>2</v>
-      </c>
-      <c r="BZ104">
+      <c r="BX105">
+        <v>5</v>
+      </c>
+      <c r="BY105">
+        <v>2</v>
+      </c>
+      <c r="BZ105">
         <v>3</v>
       </c>
-      <c r="CA104">
-        <v>1</v>
-      </c>
-      <c r="CG104">
+      <c r="CA105">
+        <v>1</v>
+      </c>
+      <c r="CG105">
         <v>3</v>
       </c>
-      <c r="CH104">
+      <c r="CH105">
         <v>6</v>
       </c>
-      <c r="CI104">
+      <c r="CI105">
         <v>3</v>
       </c>
-      <c r="CJ104">
+      <c r="CJ105">
         <v>3</v>
       </c>
-      <c r="CK104">
+      <c r="CK105">
         <v>4</v>
       </c>
-      <c r="CL104">
+      <c r="CL105">
         <v>8</v>
       </c>
-      <c r="CM104">
-        <v>1</v>
-      </c>
-      <c r="CQ104">
+      <c r="CM105">
+        <v>1</v>
+      </c>
+      <c r="CQ105">
         <v>4</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:CN104" xr:uid="{E6D73437-9035-4F38-AC23-65184BC2B5F6}">
-    <sortState ref="A2:CN104">
-      <sortCondition ref="A1:A104"/>
+  <autoFilter ref="A1:CN105" xr:uid="{E6D73437-9035-4F38-AC23-65184BC2B5F6}">
+    <sortState ref="A2:CN105">
+      <sortCondition ref="A1:A105"/>
     </sortState>
   </autoFilter>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
